--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="688">
   <si>
     <t>#</t>
   </si>
@@ -50,12 +50,24 @@
     <t>Manufacturer</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>Quantity (3 Boards)</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Unit Cost (3 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (3 Boards)</t>
+  </si>
+  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -80,6 +92,9 @@
     <t>100nF</t>
   </si>
   <si>
+    <t>Digikey</t>
+  </si>
+  <si>
     <t>C2, C165</t>
   </si>
   <si>
@@ -1277,6 +1292,9 @@
     <t>DNP</t>
   </si>
   <si>
+    <t>Do not place</t>
+  </si>
+  <si>
     <t>R14, R93</t>
   </si>
   <si>
@@ -1563,9 +1581,6 @@
   </si>
   <si>
     <t>R175, R231</t>
-  </si>
-  <si>
-    <t>Do not place</t>
   </si>
   <si>
     <t>R196</t>
@@ -2140,6 +2155,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -2164,18 +2187,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2713,19 +2729,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2734,7 +2750,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2858,7 +2874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2899,26 +2915,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3246,7 +3265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:O159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.57142857142857" style="2" customWidth="1"/>
@@ -3254,14 +3273,18 @@
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="33.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="21.4285714285714" customWidth="1"/>
-    <col min="9" max="9" width="17.8571428571429" customWidth="1"/>
-    <col min="10" max="10" width="16.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="29.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="60.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="14.7333333333333" customWidth="1"/>
+    <col min="9" max="9" width="8.56190476190476" customWidth="1"/>
+    <col min="10" max="10" width="7.20952380952381" customWidth="1"/>
+    <col min="11" max="11" width="9.17142857142857" customWidth="1"/>
+    <col min="12" max="12" width="16.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="22.8571428571429" customWidth="1"/>
+    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="15" max="15" width="29.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:11">
+    <row r="1" ht="15.75" spans="1:15">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3273,8 +3296,12 @@
       <c r="I1" s="15"/>
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3"/>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -3306,5027 +3333,6515 @@
       <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" ht="132.75" spans="1:11">
+      <c r="L2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="132.75" spans="1:15">
       <c r="A3" s="3"/>
       <c r="B3" s="8">
-        <f>ROW(B3)-ROW($B$2)</f>
+        <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
         <v>1</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" s="10">
         <v>97</v>
       </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" ht="15.75" spans="1:11">
+      <c r="K3" s="10">
+        <f>3*J3</f>
+        <v>291</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0.0107</v>
+      </c>
+      <c r="N3" s="10">
+        <f>M3*K3</f>
+        <v>3.1137</v>
+      </c>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:15">
       <c r="A4" s="3"/>
       <c r="B4" s="8">
-        <f>ROW(B4)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>13</v>
-      </c>
       <c r="G4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>15</v>
-      </c>
       <c r="I4" s="14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J4" s="13">
         <v>2</v>
       </c>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="5" ht="15.75" spans="1:11">
+      <c r="K4" s="10">
+        <f t="shared" ref="K4:K67" si="1">3*J4</f>
+        <v>6</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N4" s="10">
+        <f t="shared" ref="N4:N15" si="2">M4*K4</f>
+        <v>0.6</v>
+      </c>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" ht="15.75" spans="1:15">
       <c r="A5" s="3"/>
       <c r="B5" s="8">
-        <f>ROW(B5)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J5" s="10">
         <v>7</v>
       </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" ht="15.75" spans="1:11">
+      <c r="K5" s="10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.209</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="2"/>
+        <v>4.389</v>
+      </c>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" ht="15.75" spans="1:15">
       <c r="A6" s="3"/>
       <c r="B6" s="8">
-        <f>ROW(B6)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J6" s="13">
         <v>4</v>
       </c>
-      <c r="K6" s="13"/>
-    </row>
-    <row r="7" ht="15.75" spans="1:11">
+      <c r="K6" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0.145</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="2"/>
+        <v>1.74</v>
+      </c>
+      <c r="O6" s="13"/>
+    </row>
+    <row r="7" ht="15.75" spans="1:15">
       <c r="A7" s="3"/>
       <c r="B7" s="8">
-        <f>ROW(B7)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J7" s="10">
         <v>4</v>
       </c>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" ht="15.75" spans="1:11">
+      <c r="K7" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.456</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="2"/>
+        <v>5.472</v>
+      </c>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" ht="15.75" spans="1:15">
       <c r="A8" s="3"/>
       <c r="B8" s="8">
-        <f>ROW(B8)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J8" s="13">
         <v>3</v>
       </c>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0.28</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="2"/>
+        <v>2.52</v>
+      </c>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
-        <f>ROW(B9)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J9" s="10">
         <v>4</v>
       </c>
-      <c r="K9" s="10"/>
-    </row>
-    <row r="10" ht="24.75" spans="1:11">
+      <c r="K9" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" ht="24.75" spans="1:15">
       <c r="A10" s="3"/>
       <c r="B10" s="8">
-        <f>ROW(B10)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" s="13">
         <v>13</v>
       </c>
-      <c r="K10" s="13"/>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="10">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="13"/>
+    </row>
+    <row r="11" ht="15.75" spans="1:15">
       <c r="A11" s="3"/>
       <c r="B11" s="8">
-        <f>ROW(B11)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="J11" s="10">
         <v>4</v>
       </c>
-      <c r="K11" s="10"/>
-    </row>
-    <row r="12" ht="15.75" spans="1:11">
+      <c r="K11" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" ht="15.75" spans="1:15">
       <c r="A12" s="3"/>
       <c r="B12" s="8">
-        <f>ROW(B12)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J12" s="13">
         <v>4</v>
       </c>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" ht="15.75" spans="1:11">
+      <c r="K12" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="13"/>
+    </row>
+    <row r="13" ht="15.75" spans="1:15">
       <c r="A13" s="3"/>
       <c r="B13" s="8">
-        <f>ROW(B13)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J13" s="10">
         <v>2</v>
       </c>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" ht="15.75" spans="1:11">
+      <c r="K13" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" ht="15.75" spans="1:15">
       <c r="A14" s="3"/>
       <c r="B14" s="8">
-        <f>ROW(B14)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J14" s="13">
         <v>2</v>
       </c>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="15" ht="15.75" spans="1:11">
+      <c r="K14" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="13"/>
+    </row>
+    <row r="15" ht="15.75" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="8">
-        <f>ROW(B15)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J15" s="10">
         <v>2</v>
       </c>
-      <c r="K15" s="10"/>
-    </row>
-    <row r="16" ht="15.75" spans="1:11">
+      <c r="K15" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" ht="15.75" spans="1:15">
       <c r="A16" s="3"/>
       <c r="B16" s="8">
-        <f>ROW(B16)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J16" s="13">
         <v>2</v>
       </c>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" ht="15.75" spans="1:11">
+      <c r="K16" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+    </row>
+    <row r="17" ht="15.75" spans="1:15">
       <c r="A17" s="3"/>
       <c r="B17" s="8">
-        <f>ROW(B17)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
       </c>
-      <c r="K17" s="10"/>
-    </row>
-    <row r="18" ht="15.75" spans="1:11">
+      <c r="K17" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" ht="15.75" spans="1:15">
       <c r="A18" s="3"/>
       <c r="B18" s="8">
-        <f>ROW(B18)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" s="13">
         <v>1</v>
       </c>
-      <c r="K18" s="13"/>
-    </row>
-    <row r="19" ht="15.75" spans="1:11">
+      <c r="K18" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+    </row>
+    <row r="19" ht="15.75" spans="1:15">
       <c r="A19" s="3"/>
       <c r="B19" s="8">
-        <f>ROW(B19)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
       </c>
-      <c r="K19" s="10"/>
-    </row>
-    <row r="20" ht="15.75" spans="1:11">
+      <c r="K19" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" ht="15.75" spans="1:15">
       <c r="A20" s="3"/>
       <c r="B20" s="8">
-        <f>ROW(B20)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J20" s="13">
         <v>2</v>
       </c>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+    </row>
+    <row r="21" ht="15.75" spans="1:15">
       <c r="A21" s="3"/>
       <c r="B21" s="8">
-        <f>ROW(B21)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J21" s="10">
         <v>2</v>
       </c>
-      <c r="K21" s="10"/>
-    </row>
-    <row r="22" ht="15.75" spans="1:11">
+      <c r="K21" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+    </row>
+    <row r="22" ht="15.75" spans="1:15">
       <c r="A22" s="3"/>
       <c r="B22" s="8">
-        <f>ROW(B22)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J22" s="13">
         <v>1</v>
       </c>
-      <c r="K22" s="13"/>
-    </row>
-    <row r="23" ht="15.75" spans="1:11">
+      <c r="K22" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+    </row>
+    <row r="23" ht="15.75" spans="1:15">
       <c r="A23" s="3"/>
       <c r="B23" s="8">
-        <f>ROW(B23)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J23" s="10">
         <v>2</v>
       </c>
-      <c r="K23" s="10"/>
-    </row>
-    <row r="24" ht="24.75" spans="1:11">
+      <c r="K23" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" ht="24.75" spans="1:15">
       <c r="A24" s="3"/>
       <c r="B24" s="8">
-        <f>ROW(B24)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J24" s="13">
         <v>10</v>
       </c>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" ht="36.75" spans="1:11">
+      <c r="K24" s="10">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" ht="36.75" spans="1:15">
       <c r="A25" s="3"/>
       <c r="B25" s="8">
-        <f>ROW(B25)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J25" s="10">
         <v>1</v>
       </c>
-      <c r="K25" s="10"/>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="K25" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" ht="15.75" spans="1:15">
       <c r="A26" s="3"/>
       <c r="B26" s="8">
-        <f>ROW(B26)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J26" s="13">
         <v>7</v>
       </c>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="K26" s="10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+    </row>
+    <row r="27" ht="15.75" spans="1:15">
       <c r="A27" s="3"/>
       <c r="B27" s="8">
-        <f>ROW(B27)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J27" s="10">
         <v>4</v>
       </c>
-      <c r="K27" s="10"/>
-    </row>
-    <row r="28" ht="15.75" spans="1:11">
+      <c r="K27" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" ht="15.75" spans="1:15">
       <c r="A28" s="3"/>
       <c r="B28" s="8">
-        <f>ROW(B28)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" s="13">
         <v>7</v>
       </c>
-      <c r="K28" s="13"/>
-    </row>
-    <row r="29" ht="15.75" spans="1:11">
+      <c r="K28" s="10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+    </row>
+    <row r="29" ht="15.75" spans="1:15">
       <c r="A29" s="3"/>
       <c r="B29" s="8">
-        <f>ROW(B29)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J29" s="10">
         <v>2</v>
       </c>
-      <c r="K29" s="10"/>
-    </row>
-    <row r="30" ht="15.75" spans="1:11">
+      <c r="K29" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" ht="15.75" spans="1:15">
       <c r="A30" s="3"/>
       <c r="B30" s="8">
-        <f>ROW(B30)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J30" s="13">
         <v>2</v>
       </c>
-      <c r="K30" s="13"/>
-    </row>
-    <row r="31" ht="15.75" spans="1:11">
+      <c r="K30" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+    </row>
+    <row r="31" ht="15.75" spans="1:15">
       <c r="A31" s="3"/>
       <c r="B31" s="8">
-        <f>ROW(B31)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J31" s="10">
         <v>1</v>
       </c>
-      <c r="K31" s="10"/>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="K31" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" ht="15.75" spans="1:15">
       <c r="A32" s="3"/>
       <c r="B32" s="8">
-        <f>ROW(B32)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J32" s="13">
         <v>2</v>
       </c>
-      <c r="K32" s="13"/>
-    </row>
-    <row r="33" ht="15.75" spans="1:11">
+      <c r="K32" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+    </row>
+    <row r="33" ht="15.75" spans="1:15">
       <c r="A33" s="3"/>
       <c r="B33" s="8">
-        <f>ROW(B33)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J33" s="10">
         <v>1</v>
       </c>
-      <c r="K33" s="10"/>
-    </row>
-    <row r="34" ht="48.75" spans="1:11">
+      <c r="K33" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+    </row>
+    <row r="34" ht="48.75" spans="1:15">
       <c r="A34" s="3"/>
       <c r="B34" s="8">
-        <f>ROW(B34)-ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J34" s="13">
         <v>30</v>
       </c>
-      <c r="K34" s="13"/>
-    </row>
-    <row r="35" ht="24.75" spans="1:11">
+      <c r="K34" s="10">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+    </row>
+    <row r="35" ht="24.75" spans="1:15">
       <c r="A35" s="3"/>
       <c r="B35" s="8">
-        <f>ROW(B35)-ROW($B$2)</f>
+        <f t="shared" ref="B35:B57" si="3">ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J35" s="10">
         <v>2</v>
       </c>
-      <c r="K35" s="10"/>
-    </row>
-    <row r="36" ht="15.75" spans="1:11">
+      <c r="K35" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+    </row>
+    <row r="36" ht="15.75" spans="1:15">
       <c r="A36" s="3"/>
       <c r="B36" s="8">
-        <f>ROW(B36)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J36" s="13">
         <v>1</v>
       </c>
-      <c r="K36" s="13"/>
-    </row>
-    <row r="37" ht="15.75" spans="1:11">
+      <c r="K36" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+    </row>
+    <row r="37" ht="15.75" spans="1:15">
       <c r="A37" s="3"/>
       <c r="B37" s="8">
-        <f>ROW(B37)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J37" s="10">
         <v>6</v>
       </c>
-      <c r="K37" s="10"/>
-    </row>
-    <row r="38" ht="15.75" spans="1:11">
+      <c r="K37" s="10">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+    </row>
+    <row r="38" ht="15.75" spans="1:15">
       <c r="A38" s="3"/>
       <c r="B38" s="8">
-        <f>ROW(B38)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J38" s="13">
         <v>1</v>
       </c>
-      <c r="K38" s="13"/>
-    </row>
-    <row r="39" ht="36.75" spans="1:11">
+      <c r="K38" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+    </row>
+    <row r="39" ht="36.75" spans="1:15">
       <c r="A39" s="3"/>
       <c r="B39" s="8">
-        <f>ROW(B39)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J39" s="10">
         <v>21</v>
       </c>
-      <c r="K39" s="10"/>
-    </row>
-    <row r="40" ht="24.75" spans="1:11">
+      <c r="K39" s="10">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+    </row>
+    <row r="40" ht="24.75" spans="1:15">
       <c r="A40" s="3"/>
       <c r="B40" s="8">
-        <f>ROW(B40)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J40" s="13">
         <v>1</v>
       </c>
-      <c r="K40" s="13"/>
-    </row>
-    <row r="41" ht="36.75" spans="1:11">
+      <c r="K40" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+    </row>
+    <row r="41" ht="36.75" spans="1:15">
       <c r="A41" s="3"/>
       <c r="B41" s="8">
-        <f>ROW(B41)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J41" s="10">
         <v>2</v>
       </c>
-      <c r="K41" s="10"/>
-    </row>
-    <row r="42" ht="15.75" spans="1:11">
+      <c r="K41" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+    </row>
+    <row r="42" ht="15.75" spans="1:15">
       <c r="A42" s="3"/>
       <c r="B42" s="8">
-        <f>ROW(B42)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J42" s="13">
         <v>2</v>
       </c>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" ht="15.75" spans="1:11">
+      <c r="K42" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L42" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+    </row>
+    <row r="43" ht="15.75" spans="1:15">
       <c r="A43" s="3"/>
       <c r="B43" s="8">
-        <f>ROW(B43)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J43" s="10">
         <v>1</v>
       </c>
-      <c r="K43" s="10"/>
-    </row>
-    <row r="44" ht="24.75" spans="1:11">
+      <c r="K43" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+    </row>
+    <row r="44" ht="24.75" spans="1:15">
       <c r="A44" s="3"/>
       <c r="B44" s="8">
-        <f>ROW(B44)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J44" s="13">
         <v>1</v>
       </c>
-      <c r="K44" s="13"/>
-    </row>
-    <row r="45" ht="15.75" spans="1:11">
+      <c r="K44" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L44" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+    </row>
+    <row r="45" ht="15.75" spans="1:15">
       <c r="A45" s="3"/>
       <c r="B45" s="8">
-        <f>ROW(B45)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="10"/>
       <c r="I45" s="11" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J45" s="10">
         <v>1</v>
       </c>
-      <c r="K45" s="10"/>
-    </row>
-    <row r="46" ht="15.75" spans="1:11">
+      <c r="K45" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+    </row>
+    <row r="46" ht="15.75" spans="1:15">
       <c r="A46" s="3"/>
       <c r="B46" s="8">
-        <f>ROW(B46)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J46" s="13">
         <v>1</v>
       </c>
-      <c r="K46" s="13"/>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="K46" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+    </row>
+    <row r="47" ht="15.75" spans="1:15">
       <c r="A47" s="3"/>
       <c r="B47" s="8">
-        <f>ROW(B47)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="10">
         <v>2</v>
       </c>
-      <c r="K47" s="10"/>
-    </row>
-    <row r="48" ht="36.75" spans="1:11">
+      <c r="K47" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+    </row>
+    <row r="48" ht="36.75" spans="1:15">
       <c r="A48" s="3"/>
       <c r="B48" s="8">
-        <f>ROW(B48)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
       </c>
-      <c r="K48" s="10"/>
-    </row>
-    <row r="49" ht="24.75" spans="1:11">
+      <c r="K48" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+    </row>
+    <row r="49" ht="24.75" spans="1:15">
       <c r="A49" s="3"/>
       <c r="B49" s="8">
-        <f>ROW(B49)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J49" s="13">
         <v>1</v>
       </c>
-      <c r="K49" s="13"/>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="K49" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+    </row>
+    <row r="50" ht="15.75" spans="1:15">
       <c r="A50" s="3"/>
       <c r="B50" s="8">
-        <f>ROW(B50)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J50" s="10">
         <v>1</v>
       </c>
-      <c r="K50" s="10"/>
-    </row>
-    <row r="51" ht="36.75" spans="1:11">
+      <c r="K50" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+    </row>
+    <row r="51" ht="36.75" spans="1:15">
       <c r="A51" s="3"/>
       <c r="B51" s="8">
-        <f>ROW(B51)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J51" s="13">
         <v>1</v>
       </c>
-      <c r="K51" s="13"/>
-    </row>
-    <row r="52" ht="36.75" spans="1:11">
+      <c r="K51" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+    </row>
+    <row r="52" ht="36.75" spans="1:15">
       <c r="A52" s="3"/>
       <c r="B52" s="8">
-        <f>ROW(B52)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J52" s="10">
         <v>1</v>
       </c>
-      <c r="K52" s="10"/>
-    </row>
-    <row r="53" ht="36.75" spans="1:11">
+      <c r="K52" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+    </row>
+    <row r="53" ht="36.75" spans="1:15">
       <c r="A53" s="3"/>
       <c r="B53" s="8">
-        <f>ROW(B53)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J53" s="13">
         <v>1</v>
       </c>
-      <c r="K53" s="13"/>
-    </row>
-    <row r="54" ht="24.75" spans="1:11">
+      <c r="K53" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+    </row>
+    <row r="54" ht="24.75" spans="1:15">
       <c r="A54" s="3"/>
       <c r="B54" s="8">
-        <f>ROW(B54)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J54" s="10">
         <v>1</v>
       </c>
-      <c r="K54" s="10"/>
-    </row>
-    <row r="55" ht="36.75" spans="1:11">
+      <c r="K54" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+    </row>
+    <row r="55" ht="36.75" spans="1:15">
       <c r="A55" s="3"/>
       <c r="B55" s="8">
-        <f>ROW(B55)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J55" s="13">
         <v>1</v>
       </c>
-      <c r="K55" s="13"/>
-    </row>
-    <row r="56" ht="48.75" spans="1:11">
+      <c r="K55" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+    </row>
+    <row r="56" ht="48.75" spans="1:15">
       <c r="A56" s="3"/>
       <c r="B56" s="8">
-        <f>ROW(B56)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J56" s="10">
         <v>1</v>
       </c>
-      <c r="K56" s="10"/>
-    </row>
-    <row r="57" ht="48.75" spans="1:11">
+      <c r="K56" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+    </row>
+    <row r="57" ht="48.75" spans="1:15">
       <c r="A57" s="3"/>
       <c r="B57" s="8">
-        <f>ROW(B57)-ROW($B$2)</f>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J57" s="10">
         <v>2</v>
       </c>
-      <c r="K57" s="10"/>
-    </row>
-    <row r="58" ht="60.75" spans="1:11">
+      <c r="K57" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+    </row>
+    <row r="58" ht="60.75" spans="1:15">
       <c r="A58" s="3"/>
       <c r="B58" s="8">
-        <f t="shared" ref="B57:B159" si="0">ROW(B58)-ROW($B$2)</f>
+        <f t="shared" ref="B58:B158" si="4">ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J58" s="13">
         <v>5</v>
       </c>
-      <c r="K58" s="13"/>
-    </row>
-    <row r="59" ht="48.75" spans="1:11">
+      <c r="K58" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+    </row>
+    <row r="59" ht="48.75" spans="1:15">
       <c r="A59" s="3"/>
       <c r="B59" s="8">
-        <f>ROW(B59)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>57</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J59" s="10">
         <v>1</v>
       </c>
-      <c r="K59" s="10"/>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="K59" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+    </row>
+    <row r="60" ht="15.75" spans="1:15">
       <c r="A60" s="3"/>
       <c r="B60" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J60" s="13">
         <v>1</v>
       </c>
-      <c r="K60" s="13"/>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="K60" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+    </row>
+    <row r="61" ht="15.75" spans="1:15">
       <c r="A61" s="3"/>
       <c r="B61" s="8">
-        <f>ROW(B61)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>59</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J61" s="10">
         <v>1</v>
       </c>
-      <c r="K61" s="10"/>
-    </row>
-    <row r="62" ht="36.75" spans="1:11">
+      <c r="K61" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+    </row>
+    <row r="62" ht="36.75" spans="1:15">
       <c r="A62" s="3"/>
       <c r="B62" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J62" s="13">
         <v>1</v>
       </c>
-      <c r="K62" s="13"/>
-    </row>
-    <row r="63" ht="60.75" spans="1:11">
+      <c r="K62" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+    </row>
+    <row r="63" ht="60.75" spans="1:15">
       <c r="A63" s="3"/>
       <c r="B63" s="8">
-        <f>ROW(B63)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>61</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J63" s="10">
         <v>2</v>
       </c>
-      <c r="K63" s="10"/>
-    </row>
-    <row r="64" ht="48.75" spans="1:11">
+      <c r="K63" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+    </row>
+    <row r="64" ht="48.75" spans="1:15">
       <c r="A64" s="3"/>
       <c r="B64" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>62</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J64" s="13">
         <v>1</v>
       </c>
-      <c r="K64" s="13"/>
-    </row>
-    <row r="65" ht="36.75" spans="1:11">
+      <c r="K64" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+    </row>
+    <row r="65" ht="36.75" spans="1:15">
       <c r="A65" s="3"/>
       <c r="B65" s="8">
-        <f>ROW(B65)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J65" s="10">
         <v>1</v>
       </c>
-      <c r="K65" s="10"/>
-    </row>
-    <row r="66" ht="24.75" spans="1:11">
+      <c r="K65" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+    </row>
+    <row r="66" ht="24.75" spans="1:15">
       <c r="A66" s="3"/>
       <c r="B66" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J66" s="13">
         <v>1</v>
       </c>
-      <c r="K66" s="13"/>
-    </row>
-    <row r="67" spans="1:11">
+      <c r="K66" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+    </row>
+    <row r="67" ht="15.75" spans="1:15">
       <c r="A67" s="3"/>
       <c r="B67" s="8">
-        <f>ROW(B67)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J67" s="10">
         <v>1</v>
       </c>
-      <c r="K67" s="10"/>
-    </row>
-    <row r="68" ht="36.75" spans="1:11">
+      <c r="K67" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+    </row>
+    <row r="68" ht="36.75" spans="1:15">
       <c r="A68" s="3"/>
       <c r="B68" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>66</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J68" s="13">
         <v>2</v>
       </c>
-      <c r="K68" s="13"/>
-    </row>
-    <row r="69" ht="24.75" spans="1:11">
+      <c r="K68" s="10">
+        <f t="shared" ref="K68:K131" si="5">3*J68</f>
+        <v>6</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+    </row>
+    <row r="69" ht="24.75" spans="1:15">
       <c r="A69" s="3"/>
       <c r="B69" s="8">
-        <f>ROW(B69)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J69" s="10">
         <v>1</v>
       </c>
-      <c r="K69" s="10"/>
-    </row>
-    <row r="70" spans="1:11">
+      <c r="K69" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+    </row>
+    <row r="70" ht="15.75" spans="1:15">
       <c r="A70" s="3"/>
       <c r="B70" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J70" s="13">
         <v>5</v>
       </c>
-      <c r="K70" s="13"/>
-    </row>
-    <row r="71" ht="26.25" spans="1:11">
+      <c r="K70" s="10">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+    </row>
+    <row r="71" ht="26.25" spans="1:15">
       <c r="A71" s="3"/>
       <c r="B71" s="8">
-        <f>ROW(B71)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J71" s="10">
         <v>4</v>
       </c>
-      <c r="K71" s="10"/>
-    </row>
-    <row r="72" spans="1:11">
+      <c r="K71" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+    </row>
+    <row r="72" ht="15.75" spans="1:15">
       <c r="A72" s="3"/>
       <c r="B72" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="C72" s="12"/>
       <c r="D72" s="13" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J72" s="13">
         <v>1</v>
       </c>
-      <c r="K72" s="13"/>
-    </row>
-    <row r="73" spans="1:11">
+      <c r="K72" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13"/>
+      <c r="O72" s="13"/>
+    </row>
+    <row r="73" ht="15.75" spans="1:15">
       <c r="A73" s="3"/>
       <c r="B73" s="8">
-        <f>ROW(B73)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J73" s="10">
         <v>2</v>
       </c>
-      <c r="K73" s="10"/>
-    </row>
-    <row r="74" ht="24.75" spans="1:11">
+      <c r="K73" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+    </row>
+    <row r="74" ht="24.75" spans="1:15">
       <c r="A74" s="3"/>
       <c r="B74" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J74" s="13">
         <v>2</v>
       </c>
-      <c r="K74" s="13"/>
-    </row>
-    <row r="75" ht="24.75" spans="1:11">
+      <c r="K74" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13"/>
+      <c r="O74" s="13"/>
+    </row>
+    <row r="75" ht="24.75" spans="1:15">
       <c r="A75" s="3"/>
       <c r="B75" s="8">
-        <f>ROW(B75)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J75" s="10">
         <v>1</v>
       </c>
-      <c r="K75" s="10"/>
-    </row>
-    <row r="76" ht="24.75" spans="1:11">
+      <c r="K75" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+    </row>
+    <row r="76" ht="24.75" spans="1:15">
       <c r="A76" s="3"/>
       <c r="B76" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="E76" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F76" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="F76" s="13" t="s">
-        <v>326</v>
-      </c>
       <c r="G76" s="14" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J76" s="13">
         <v>2</v>
       </c>
-      <c r="K76" s="13"/>
-    </row>
-    <row r="77" ht="24.75" spans="1:11">
+      <c r="K76" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13"/>
+      <c r="O76" s="13"/>
+    </row>
+    <row r="77" ht="24.75" spans="1:15">
       <c r="A77" s="3"/>
       <c r="B77" s="8">
-        <f>ROW(B77)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J77" s="10">
         <v>1</v>
       </c>
-      <c r="K77" s="10"/>
-    </row>
-    <row r="78" ht="15.75" spans="1:11">
+      <c r="K77" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="10"/>
+    </row>
+    <row r="78" ht="15.75" spans="1:15">
       <c r="A78" s="3"/>
       <c r="B78" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="H78" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="I78" s="14" t="s">
         <v>342</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>337</v>
       </c>
       <c r="J78" s="13">
         <v>1</v>
       </c>
-      <c r="K78" s="13"/>
-    </row>
-    <row r="79" ht="15.75" spans="1:11">
+      <c r="K78" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L78" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+    </row>
+    <row r="79" ht="15.75" spans="1:15">
       <c r="A79" s="3"/>
       <c r="B79" s="8">
-        <f>ROW(B79)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I79" s="11" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J79" s="10">
         <v>1</v>
       </c>
-      <c r="K79" s="10"/>
-    </row>
-    <row r="80" ht="15.75" spans="1:11">
+      <c r="K79" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+    </row>
+    <row r="80" ht="15.75" spans="1:15">
       <c r="A80" s="3"/>
       <c r="B80" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D80" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="E80" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="H80" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="E80" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="F80" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="G80" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>342</v>
-      </c>
       <c r="I80" s="14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J80" s="13">
         <v>1</v>
       </c>
-      <c r="K80" s="13"/>
-    </row>
-    <row r="81" ht="24.75" spans="1:11">
+      <c r="K80" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L80" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13"/>
+    </row>
+    <row r="81" ht="24.75" spans="1:15">
       <c r="A81" s="3"/>
       <c r="B81" s="8">
-        <f>ROW(B81)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>79</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="I81" s="11" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J81" s="10">
         <v>6</v>
       </c>
-      <c r="K81" s="10"/>
-    </row>
-    <row r="82" ht="36.75" spans="1:11">
+      <c r="K81" s="10">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="10"/>
+    </row>
+    <row r="82" ht="36.75" spans="1:15">
       <c r="A82" s="3"/>
       <c r="B82" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J82" s="13">
         <v>1</v>
       </c>
-      <c r="K82" s="13"/>
-    </row>
-    <row r="83" ht="15.75" spans="1:11">
+      <c r="K82" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L82" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+    </row>
+    <row r="83" ht="15.75" spans="1:15">
       <c r="A83" s="3"/>
       <c r="B83" s="8">
-        <f>ROW(B83)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J83" s="10">
         <v>4</v>
       </c>
-      <c r="K83" s="10"/>
-    </row>
-    <row r="84" ht="24.75" spans="1:11">
+      <c r="K83" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="10"/>
+    </row>
+    <row r="84" ht="24.75" spans="1:15">
       <c r="A84" s="3"/>
       <c r="B84" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J84" s="13">
         <v>2</v>
       </c>
-      <c r="K84" s="13"/>
-    </row>
-    <row r="85" ht="24.75" spans="1:11">
+      <c r="K84" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L84" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13"/>
+    </row>
+    <row r="85" ht="24.75" spans="1:15">
       <c r="A85" s="3"/>
       <c r="B85" s="8">
-        <f>ROW(B85)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="J85" s="10">
         <v>5</v>
       </c>
-      <c r="K85" s="10"/>
-    </row>
-    <row r="86" ht="24.75" spans="1:11">
+      <c r="K85" s="10">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="10"/>
+    </row>
+    <row r="86" ht="24.75" spans="1:15">
       <c r="A86" s="3"/>
       <c r="B86" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D86" s="13" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J86" s="13">
         <v>1</v>
       </c>
-      <c r="K86" s="13"/>
-    </row>
-    <row r="87" ht="15.75" spans="1:11">
+      <c r="K86" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L86" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+    </row>
+    <row r="87" ht="15.75" spans="1:15">
       <c r="A87" s="3"/>
       <c r="B87" s="8">
-        <f>ROW(B87)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J87" s="10">
         <v>1</v>
       </c>
-      <c r="K87" s="10"/>
-    </row>
-    <row r="88" ht="48.75" spans="1:11">
+      <c r="K87" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="10"/>
+    </row>
+    <row r="88" ht="48.75" spans="1:15">
       <c r="A88" s="3"/>
       <c r="B88" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>86</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J88" s="13">
         <v>1</v>
       </c>
-      <c r="K88" s="13"/>
-    </row>
-    <row r="89" ht="60.75" spans="1:11">
+      <c r="K88" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L88" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="13"/>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13"/>
+    </row>
+    <row r="89" ht="60.75" spans="1:15">
       <c r="A89" s="3"/>
       <c r="B89" s="8">
-        <f>ROW(B89)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J89" s="10">
         <v>40</v>
       </c>
-      <c r="K89" s="10"/>
-    </row>
-    <row r="90" ht="15.75" spans="1:11">
+      <c r="K89" s="10">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="10"/>
+    </row>
+    <row r="90" ht="15.75" spans="1:15">
       <c r="A90" s="3"/>
       <c r="B90" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G90" s="14" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="J90" s="13">
         <v>6</v>
       </c>
-      <c r="K90" s="13"/>
-    </row>
-    <row r="91" ht="15.75" spans="1:11">
+      <c r="K90" s="10">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="L90" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="13"/>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13"/>
+    </row>
+    <row r="91" ht="15.75" spans="1:15">
       <c r="A91" s="3"/>
       <c r="B91" s="8">
-        <f>ROW(B91)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>89</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="J91" s="10">
         <v>7</v>
       </c>
-      <c r="K91" s="10"/>
-    </row>
-    <row r="92" ht="72.75" spans="1:11">
+      <c r="K91" s="10">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10"/>
+      <c r="O91" s="10"/>
+    </row>
+    <row r="92" ht="72.75" spans="1:15">
       <c r="A92" s="3"/>
       <c r="B92" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J92" s="13">
         <v>49</v>
       </c>
-      <c r="K92" s="13"/>
-    </row>
-    <row r="93" spans="1:11">
+      <c r="K92" s="10">
+        <f t="shared" si="5"/>
+        <v>147</v>
+      </c>
+      <c r="L92" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="13"/>
+      <c r="N92" s="13"/>
+      <c r="O92" s="13"/>
+    </row>
+    <row r="93" ht="15.75" spans="1:15">
       <c r="A93" s="3"/>
       <c r="B93" s="8">
-        <f>ROW(B93)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>91</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J93" s="10">
         <v>7</v>
       </c>
-      <c r="K93" s="10"/>
-    </row>
-    <row r="94" s="1" customFormat="1" ht="15.75" spans="1:11">
-      <c r="A94" s="16"/>
-      <c r="B94" s="17">
-        <f t="shared" si="0"/>
+      <c r="K93" s="10">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="10"/>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="15.75" spans="1:15">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18">
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="C94" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="D94" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="E94" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="F94" s="19" t="s">
-        <v>393</v>
-      </c>
-      <c r="G94" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="H94" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="J94" s="19">
+      <c r="C94" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="G94" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="H94" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="J94" s="20">
         <v>2</v>
       </c>
-      <c r="K94" s="19"/>
-    </row>
-    <row r="95" spans="1:11">
+      <c r="K94" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L94" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="20"/>
+      <c r="N94" s="20"/>
+      <c r="O94" s="23" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" spans="1:15">
       <c r="A95" s="3"/>
       <c r="B95" s="8">
-        <f>ROW(B95)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>93</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J95" s="10">
         <v>2</v>
       </c>
-      <c r="K95" s="10"/>
-    </row>
-    <row r="96" ht="48.75" spans="1:11">
+      <c r="K95" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="10"/>
+      <c r="N95" s="10"/>
+      <c r="O95" s="10"/>
+    </row>
+    <row r="96" ht="48.75" spans="1:15">
       <c r="A96" s="3"/>
       <c r="B96" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="J96" s="13">
         <v>26</v>
       </c>
-      <c r="K96" s="13"/>
-    </row>
-    <row r="97" ht="15.75" spans="1:11">
+      <c r="K96" s="10">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="L96" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="13"/>
+      <c r="N96" s="13"/>
+      <c r="O96" s="13"/>
+    </row>
+    <row r="97" ht="15.75" spans="1:15">
       <c r="A97" s="3"/>
       <c r="B97" s="8">
-        <f>ROW(B97)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>95</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D97" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E97" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="F97" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="E97" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>418</v>
-      </c>
       <c r="G97" s="11" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J97" s="10">
         <v>1</v>
       </c>
-      <c r="K97" s="10"/>
-    </row>
-    <row r="98" ht="36.75" spans="1:11">
+      <c r="K97" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="10"/>
+      <c r="N97" s="10"/>
+      <c r="O97" s="10"/>
+    </row>
+    <row r="98" ht="36.75" spans="1:15">
       <c r="A98" s="3"/>
       <c r="B98" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>96</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="J98" s="13">
         <v>27</v>
       </c>
-      <c r="K98" s="13"/>
-    </row>
-    <row r="99" spans="1:11">
+      <c r="K98" s="10">
+        <f t="shared" si="5"/>
+        <v>81</v>
+      </c>
+      <c r="L98" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="13"/>
+      <c r="N98" s="13"/>
+      <c r="O98" s="13"/>
+    </row>
+    <row r="99" ht="15.75" spans="1:15">
       <c r="A99" s="3"/>
       <c r="B99" s="8">
-        <f>ROW(B99)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>97</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J99" s="10">
         <v>4</v>
       </c>
-      <c r="K99" s="10"/>
-    </row>
-    <row r="100" ht="15.75" spans="1:11">
+      <c r="K99" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="10"/>
+    </row>
+    <row r="100" ht="15.75" spans="1:15">
       <c r="A100" s="3"/>
       <c r="B100" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>98</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="J100" s="13">
         <v>4</v>
       </c>
-      <c r="K100" s="13"/>
-    </row>
-    <row r="101" ht="15.75" spans="1:11">
+      <c r="K100" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L100" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="13"/>
+      <c r="N100" s="13"/>
+      <c r="O100" s="13"/>
+    </row>
+    <row r="101" ht="15.75" spans="1:15">
       <c r="A101" s="3"/>
       <c r="B101" s="8">
-        <f>ROW(B101)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>99</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="J101" s="10">
         <v>4</v>
       </c>
-      <c r="K101" s="10"/>
-    </row>
-    <row r="102" ht="15.75" spans="1:11">
+      <c r="K101" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10"/>
+      <c r="O101" s="10"/>
+    </row>
+    <row r="102" ht="15.75" spans="1:15">
       <c r="A102" s="3"/>
       <c r="B102" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J102" s="13">
         <v>1</v>
       </c>
-      <c r="K102" s="13"/>
-    </row>
-    <row r="103" ht="15.75" spans="1:11">
+      <c r="K102" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L102" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="13"/>
+      <c r="N102" s="13"/>
+      <c r="O102" s="13"/>
+    </row>
+    <row r="103" ht="15.75" spans="1:15">
       <c r="A103" s="3"/>
       <c r="B103" s="8">
-        <f>ROW(B103)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>101</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="J103" s="10">
         <v>5</v>
       </c>
-      <c r="K103" s="10"/>
-    </row>
-    <row r="104" ht="15.75" spans="1:11">
+      <c r="K103" s="10">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10"/>
+      <c r="O103" s="10"/>
+    </row>
+    <row r="104" ht="15.75" spans="1:15">
       <c r="A104" s="3"/>
       <c r="B104" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>102</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G104" s="14" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="J104" s="13">
         <v>1</v>
       </c>
-      <c r="K104" s="13"/>
-    </row>
-    <row r="105" ht="15.75" spans="1:11">
+      <c r="K104" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L104" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" s="13"/>
+      <c r="N104" s="13"/>
+      <c r="O104" s="13"/>
+    </row>
+    <row r="105" ht="15.75" spans="1:15">
       <c r="A105" s="3"/>
       <c r="B105" s="8">
-        <f>ROW(B105)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>103</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="J105" s="10">
         <v>1</v>
       </c>
-      <c r="K105" s="10"/>
-    </row>
-    <row r="106" ht="15.75" spans="1:11">
+      <c r="K105" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L105" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" s="10"/>
+      <c r="N105" s="10"/>
+      <c r="O105" s="10"/>
+    </row>
+    <row r="106" ht="15.75" spans="1:15">
       <c r="A106" s="3"/>
       <c r="B106" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>104</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G106" s="14" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="J106" s="13">
         <v>1</v>
       </c>
-      <c r="K106" s="13"/>
-    </row>
-    <row r="107" s="1" customFormat="1" ht="15.75" spans="1:11">
-      <c r="A107" s="16"/>
+      <c r="K106" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L106" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" s="13"/>
+      <c r="N106" s="13"/>
+      <c r="O106" s="13"/>
+    </row>
+    <row r="107" s="1" customFormat="1" ht="15.75" spans="1:15">
+      <c r="A107" s="17"/>
       <c r="B107" s="8">
-        <f>ROW(B107)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
-      <c r="C107" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="D107" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="E107" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="F107" s="22" t="s">
-        <v>393</v>
-      </c>
-      <c r="G107" s="23" t="s">
+      <c r="C107" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="D107" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="E107" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="F107" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="H107" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I107" s="23" t="s">
-        <v>415</v>
-      </c>
-      <c r="J107" s="22">
+      <c r="G107" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="H107" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="J107" s="23">
         <v>1</v>
       </c>
-      <c r="K107" s="22"/>
-    </row>
-    <row r="108" ht="15.75" spans="1:11">
+      <c r="K107" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M107" s="23"/>
+      <c r="N107" s="23"/>
+      <c r="O107" s="23" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" spans="1:15">
       <c r="A108" s="3"/>
       <c r="B108" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>106</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G108" s="14" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I108" s="14" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="J108" s="13">
         <v>2</v>
       </c>
-      <c r="K108" s="13"/>
-    </row>
-    <row r="109" ht="15.75" spans="1:11">
+      <c r="K108" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L108" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" s="13"/>
+      <c r="N108" s="13"/>
+      <c r="O108" s="13"/>
+    </row>
+    <row r="109" ht="15.75" spans="1:15">
       <c r="A109" s="3"/>
       <c r="B109" s="8">
-        <f>ROW(B109)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>107</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J109" s="10">
         <v>2</v>
       </c>
-      <c r="K109" s="10"/>
-    </row>
-    <row r="110" ht="15.75" spans="1:11">
+      <c r="K109" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L109" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M109" s="10"/>
+      <c r="N109" s="10"/>
+      <c r="O109" s="10"/>
+    </row>
+    <row r="110" ht="15.75" spans="1:15">
       <c r="A110" s="3"/>
       <c r="B110" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>108</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J110" s="13">
         <v>2</v>
       </c>
-      <c r="K110" s="13"/>
-    </row>
-    <row r="111" ht="15.75" spans="1:11">
+      <c r="K110" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L110" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" s="13"/>
+      <c r="N110" s="13"/>
+      <c r="O110" s="13"/>
+    </row>
+    <row r="111" ht="15.75" spans="1:15">
       <c r="A111" s="3"/>
       <c r="B111" s="8">
-        <f>ROW(B111)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>109</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="J111" s="10">
         <v>2</v>
       </c>
-      <c r="K111" s="10"/>
-    </row>
-    <row r="112" ht="15.75" spans="1:11">
+      <c r="K111" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L111" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M111" s="10"/>
+      <c r="N111" s="10"/>
+      <c r="O111" s="10"/>
+    </row>
+    <row r="112" ht="15.75" spans="1:15">
       <c r="A112" s="3"/>
       <c r="B112" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="J112" s="13">
         <v>2</v>
       </c>
-      <c r="K112" s="13"/>
-    </row>
-    <row r="113" ht="15.75" spans="1:11">
+      <c r="K112" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L112" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M112" s="13"/>
+      <c r="N112" s="13"/>
+      <c r="O112" s="13"/>
+    </row>
+    <row r="113" ht="15.75" spans="1:15">
       <c r="A113" s="3"/>
       <c r="B113" s="8">
-        <f>ROW(B113)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="J113" s="10">
         <v>4</v>
       </c>
-      <c r="K113" s="10"/>
-    </row>
-    <row r="114" ht="15.75" spans="1:11">
+      <c r="K113" s="10">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="L113" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M113" s="10"/>
+      <c r="N113" s="10"/>
+      <c r="O113" s="10"/>
+    </row>
+    <row r="114" ht="15.75" spans="1:15">
       <c r="A114" s="3"/>
       <c r="B114" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>112</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="I114" s="14" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="J114" s="13">
         <v>2</v>
       </c>
-      <c r="K114" s="13"/>
-    </row>
-    <row r="115" ht="15.75" spans="1:11">
+      <c r="K114" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L114" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" s="13"/>
+      <c r="N114" s="13"/>
+      <c r="O114" s="13"/>
+    </row>
+    <row r="115" ht="15.75" spans="1:15">
       <c r="A115" s="3"/>
       <c r="B115" s="8">
-        <f>ROW(B115)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="J115" s="10">
         <v>8</v>
       </c>
-      <c r="K115" s="10"/>
-    </row>
-    <row r="116" ht="15.75" spans="1:11">
+      <c r="K115" s="10">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="L115" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M115" s="10"/>
+      <c r="N115" s="10"/>
+      <c r="O115" s="10"/>
+    </row>
+    <row r="116" ht="15.75" spans="1:15">
       <c r="A116" s="3"/>
       <c r="B116" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>114</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="J116" s="13">
         <v>8</v>
       </c>
-      <c r="K116" s="13"/>
-    </row>
-    <row r="117" ht="15.75" spans="1:11">
+      <c r="K116" s="10">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="L116" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M116" s="13"/>
+      <c r="N116" s="13"/>
+      <c r="O116" s="13"/>
+    </row>
+    <row r="117" ht="15.75" spans="1:15">
       <c r="A117" s="3"/>
       <c r="B117" s="8">
-        <f>ROW(B117)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>115</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J117" s="10">
         <v>2</v>
       </c>
-      <c r="K117" s="10"/>
-    </row>
-    <row r="118" ht="15.75" spans="1:11">
+      <c r="K117" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L117" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M117" s="10"/>
+      <c r="N117" s="10"/>
+      <c r="O117" s="10"/>
+    </row>
+    <row r="118" ht="15.75" spans="1:15">
       <c r="A118" s="3"/>
       <c r="B118" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>116</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="F118" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I118" s="14" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="J118" s="13">
         <v>2</v>
       </c>
-      <c r="K118" s="13"/>
-    </row>
-    <row r="119" ht="15.75" spans="1:11">
+      <c r="K118" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L118" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M118" s="13"/>
+      <c r="N118" s="13"/>
+      <c r="O118" s="13"/>
+    </row>
+    <row r="119" ht="15.75" spans="1:15">
       <c r="A119" s="3"/>
       <c r="B119" s="8">
-        <f>ROW(B119)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>117</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J119" s="10">
         <v>2</v>
       </c>
-      <c r="K119" s="10"/>
-    </row>
-    <row r="120" ht="15.75" spans="1:11">
+      <c r="K119" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L119" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M119" s="10"/>
+      <c r="N119" s="10"/>
+      <c r="O119" s="10"/>
+    </row>
+    <row r="120" ht="15.75" spans="1:15">
       <c r="A120" s="3"/>
       <c r="B120" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>118</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D120" s="13" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="F120" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I120" s="14" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="J120" s="13">
         <v>2</v>
       </c>
-      <c r="K120" s="13"/>
-    </row>
-    <row r="121" s="1" customFormat="1" ht="15.75" spans="1:11">
-      <c r="A121" s="16"/>
+      <c r="K120" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L120" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M120" s="13"/>
+      <c r="N120" s="13"/>
+      <c r="O120" s="13"/>
+    </row>
+    <row r="121" s="1" customFormat="1" ht="15.75" spans="1:15">
+      <c r="A121" s="17"/>
       <c r="B121" s="8">
-        <f>ROW(B121)-ROW($B$2)</f>
+        <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="C121" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="D121" s="22" t="s">
-        <v>511</v>
-      </c>
-      <c r="E121" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F121" s="22" t="s">
-        <v>393</v>
-      </c>
-      <c r="G121" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="H121" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I121" s="23" t="s">
-        <v>415</v>
-      </c>
-      <c r="J121" s="22">
+      <c r="C121" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="D121" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="E121" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="F121" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="G121" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="H121" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="J121" s="23">
         <v>2</v>
       </c>
-      <c r="K121" s="22" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" spans="1:11">
+      <c r="K121" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L121" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M121" s="23"/>
+      <c r="N121" s="23"/>
+      <c r="O121" s="23" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" spans="1:15">
       <c r="A122" s="3"/>
       <c r="B122" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="F122" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I122" s="14" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="J122" s="13">
         <v>1</v>
       </c>
-      <c r="K122" s="13"/>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="K122" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L122" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M122" s="13"/>
+      <c r="N122" s="13"/>
+      <c r="O122" s="13"/>
+    </row>
+    <row r="123" ht="15.75" spans="1:15">
       <c r="A123" s="3"/>
       <c r="B123" s="8">
         <f>ROW(B123)-ROW($B$2)</f>
         <v>121</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="J123" s="10">
         <v>1</v>
       </c>
-      <c r="K123" s="10"/>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="K123" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L123" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M123" s="10"/>
+      <c r="N123" s="10"/>
+      <c r="O123" s="10"/>
+    </row>
+    <row r="124" ht="15.75" spans="1:15">
       <c r="A124" s="3"/>
       <c r="B124" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F124" s="13" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H124" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I124" s="14" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="J124" s="13">
         <v>2</v>
       </c>
-      <c r="K124" s="13"/>
-    </row>
-    <row r="125" ht="15.75" spans="1:11">
+      <c r="K124" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L124" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M124" s="13"/>
+      <c r="N124" s="13"/>
+      <c r="O124" s="13"/>
+    </row>
+    <row r="125" ht="15.75" spans="1:15">
       <c r="A125" s="3"/>
       <c r="B125" s="8">
         <f>ROW(B125)-ROW($B$2)</f>
         <v>123</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="J125" s="10">
         <v>1</v>
       </c>
-      <c r="K125" s="10"/>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="K125" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L125" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M125" s="10"/>
+      <c r="N125" s="10"/>
+      <c r="O125" s="10"/>
+    </row>
+    <row r="126" ht="15.75" spans="1:15">
       <c r="A126" s="3"/>
       <c r="B126" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>124</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="J126" s="13">
         <v>1</v>
       </c>
-      <c r="K126" s="13"/>
-    </row>
-    <row r="127" ht="15.75" spans="1:11">
+      <c r="K126" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L126" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M126" s="13"/>
+      <c r="N126" s="13"/>
+      <c r="O126" s="13"/>
+    </row>
+    <row r="127" ht="15.75" spans="1:15">
       <c r="A127" s="3"/>
       <c r="B127" s="8">
         <f>ROW(B127)-ROW($B$2)</f>
         <v>125</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="J127" s="10">
         <v>1</v>
       </c>
-      <c r="K127" s="10"/>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="K127" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L127" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M127" s="10"/>
+      <c r="N127" s="10"/>
+      <c r="O127" s="10"/>
+    </row>
+    <row r="128" ht="15.75" spans="1:15">
       <c r="A128" s="3"/>
       <c r="B128" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>126</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="F128" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="J128" s="13">
         <v>1</v>
       </c>
-      <c r="K128" s="13"/>
-    </row>
-    <row r="129" ht="15.75" spans="1:11">
+      <c r="K128" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L128" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M128" s="13"/>
+      <c r="N128" s="13"/>
+      <c r="O128" s="13"/>
+    </row>
+    <row r="129" ht="15.75" spans="1:15">
       <c r="A129" s="3"/>
       <c r="B129" s="8">
         <f>ROW(B129)-ROW($B$2)</f>
         <v>127</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J129" s="10">
         <v>2</v>
       </c>
-      <c r="K129" s="10"/>
-    </row>
-    <row r="130" ht="15.75" spans="1:11">
+      <c r="K129" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L129" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M129" s="10"/>
+      <c r="N129" s="10"/>
+      <c r="O129" s="10"/>
+    </row>
+    <row r="130" ht="15.75" spans="1:15">
       <c r="A130" s="3"/>
       <c r="B130" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>128</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J130" s="13">
         <v>1</v>
       </c>
-      <c r="K130" s="13"/>
-    </row>
-    <row r="131" ht="15.75" spans="1:11">
+      <c r="K130" s="10">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="L130" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M130" s="13"/>
+      <c r="N130" s="13"/>
+      <c r="O130" s="13"/>
+    </row>
+    <row r="131" ht="15.75" spans="1:15">
       <c r="A131" s="3"/>
       <c r="B131" s="8">
         <f>ROW(B131)-ROW($B$2)</f>
         <v>129</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="J131" s="10">
         <v>2</v>
       </c>
-      <c r="K131" s="10"/>
-    </row>
-    <row r="132" ht="36.75" spans="1:11">
+      <c r="K131" s="10">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="L131" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
+      <c r="O131" s="10"/>
+    </row>
+    <row r="132" ht="36.75" spans="1:15">
       <c r="A132" s="3"/>
       <c r="B132" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F132" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="J132" s="13">
         <v>6</v>
       </c>
-      <c r="K132" s="13"/>
-    </row>
-    <row r="133" ht="24.75" spans="1:11">
+      <c r="K132" s="10">
+        <f t="shared" ref="K132:K159" si="6">3*J132</f>
+        <v>18</v>
+      </c>
+      <c r="L132" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M132" s="13"/>
+      <c r="N132" s="13"/>
+      <c r="O132" s="13"/>
+    </row>
+    <row r="133" ht="24.75" spans="1:15">
       <c r="A133" s="3"/>
       <c r="B133" s="8">
         <f>ROW(B133)-ROW($B$2)</f>
         <v>131</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="G133" s="11" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="I133" s="11" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="J133" s="10">
         <v>1</v>
       </c>
-      <c r="K133" s="10"/>
-    </row>
-    <row r="134" ht="15.75" spans="1:11">
+      <c r="K133" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L133" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M133" s="10"/>
+      <c r="N133" s="10"/>
+      <c r="O133" s="10"/>
+    </row>
+    <row r="134" ht="15.75" spans="1:15">
       <c r="A134" s="3"/>
       <c r="B134" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="J134" s="13">
         <v>1</v>
       </c>
-      <c r="K134" s="13"/>
-    </row>
-    <row r="135" spans="1:11">
+      <c r="K134" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L134" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M134" s="13"/>
+      <c r="N134" s="13"/>
+      <c r="O134" s="13"/>
+    </row>
+    <row r="135" ht="15.75" spans="1:15">
       <c r="A135" s="3"/>
       <c r="B135" s="8">
         <f>ROW(B135)-ROW($B$2)</f>
         <v>133</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I135" s="11" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="J135" s="10">
         <v>2</v>
       </c>
-      <c r="K135" s="10"/>
-    </row>
-    <row r="136" spans="1:11">
+      <c r="K135" s="10">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L135" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M135" s="10"/>
+      <c r="N135" s="10"/>
+      <c r="O135" s="10"/>
+    </row>
+    <row r="136" ht="15.75" spans="1:15">
       <c r="A136" s="3"/>
       <c r="B136" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D136" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="E136" s="14" t="s">
+        <v>577</v>
+      </c>
+      <c r="F136" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="H136" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="E136" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="F136" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="G136" s="14" t="s">
-        <v>574</v>
-      </c>
-      <c r="H136" s="13" t="s">
-        <v>566</v>
-      </c>
       <c r="I136" s="14" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="J136" s="13">
         <v>1</v>
       </c>
-      <c r="K136" s="13"/>
-    </row>
-    <row r="137" ht="24.75" spans="1:11">
+      <c r="K136" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L136" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M136" s="13"/>
+      <c r="N136" s="13"/>
+      <c r="O136" s="13"/>
+    </row>
+    <row r="137" ht="24.75" spans="1:15">
       <c r="A137" s="3"/>
       <c r="B137" s="8">
         <f>ROW(B137)-ROW($B$2)</f>
         <v>135</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="I137" s="11" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="J137" s="10">
         <v>4</v>
       </c>
-      <c r="K137" s="10"/>
-    </row>
-    <row r="138" ht="15.75" spans="1:11">
+      <c r="K137" s="10">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="L137" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M137" s="10"/>
+      <c r="N137" s="10"/>
+      <c r="O137" s="10"/>
+    </row>
+    <row r="138" ht="15.75" spans="1:15">
       <c r="A138" s="3"/>
       <c r="B138" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F138" s="13" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J138" s="13">
         <v>1</v>
       </c>
-      <c r="K138" s="13"/>
-    </row>
-    <row r="139" ht="24.75" spans="1:11">
+      <c r="K138" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L138" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M138" s="13"/>
+      <c r="N138" s="13"/>
+      <c r="O138" s="13"/>
+    </row>
+    <row r="139" ht="24.75" spans="1:15">
       <c r="A139" s="3"/>
       <c r="B139" s="8">
         <f>ROW(B139)-ROW($B$2)</f>
         <v>137</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G139" s="11" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I139" s="11" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="J139" s="10">
         <v>1</v>
       </c>
-      <c r="K139" s="10"/>
-    </row>
-    <row r="140" ht="15.75" spans="1:11">
+      <c r="K139" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L139" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M139" s="10"/>
+      <c r="N139" s="10"/>
+      <c r="O139" s="10"/>
+    </row>
+    <row r="140" ht="15.75" spans="1:15">
       <c r="A140" s="3"/>
       <c r="B140" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>138</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="J140" s="13">
         <v>1</v>
       </c>
-      <c r="K140" s="13"/>
-    </row>
-    <row r="141" ht="15.75" spans="1:11">
+      <c r="K140" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L140" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M140" s="13"/>
+      <c r="N140" s="13"/>
+      <c r="O140" s="13"/>
+    </row>
+    <row r="141" ht="15.75" spans="1:15">
       <c r="A141" s="3"/>
       <c r="B141" s="8">
         <f>ROW(B141)-ROW($B$2)</f>
         <v>139</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="I141" s="11" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="J141" s="10">
         <v>1</v>
       </c>
-      <c r="K141" s="10"/>
-    </row>
-    <row r="142" ht="24.75" spans="1:11">
+      <c r="K141" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L141" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M141" s="10"/>
+      <c r="N141" s="10"/>
+      <c r="O141" s="10"/>
+    </row>
+    <row r="142" ht="24.75" spans="1:15">
       <c r="A142" s="3"/>
       <c r="B142" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="J142" s="13">
         <v>1</v>
       </c>
-      <c r="K142" s="13"/>
-    </row>
-    <row r="143" ht="15.75" spans="1:11">
+      <c r="K142" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L142" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M142" s="13"/>
+      <c r="N142" s="13"/>
+      <c r="O142" s="13"/>
+    </row>
+    <row r="143" ht="15.75" spans="1:15">
       <c r="A143" s="3"/>
       <c r="B143" s="8">
         <f>ROW(B143)-ROW($B$2)</f>
         <v>141</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I143" s="11" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="J143" s="10">
         <v>1</v>
       </c>
-      <c r="K143" s="10"/>
-    </row>
-    <row r="144" ht="24.75" spans="1:11">
+      <c r="K143" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L143" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M143" s="10"/>
+      <c r="N143" s="10"/>
+      <c r="O143" s="10"/>
+    </row>
+    <row r="144" ht="24.75" spans="1:15">
       <c r="A144" s="3"/>
       <c r="B144" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>142</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F144" s="13" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="J144" s="13">
         <v>2</v>
       </c>
-      <c r="K144" s="13"/>
-    </row>
-    <row r="145" ht="24.75" spans="1:11">
+      <c r="K144" s="10">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L144" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M144" s="13"/>
+      <c r="N144" s="13"/>
+      <c r="O144" s="13"/>
+    </row>
+    <row r="145" ht="24.75" spans="1:15">
       <c r="A145" s="3"/>
       <c r="B145" s="8">
         <f>ROW(B145)-ROW($B$2)</f>
         <v>143</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="F145" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="I145" s="11" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="J145" s="10">
         <v>1</v>
       </c>
-      <c r="K145" s="10"/>
-    </row>
-    <row r="146" ht="26.25" spans="1:11">
+      <c r="K145" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L145" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M145" s="10"/>
+      <c r="N145" s="10"/>
+      <c r="O145" s="10"/>
+    </row>
+    <row r="146" ht="26.25" spans="1:15">
       <c r="A146" s="3"/>
       <c r="B146" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="E146" s="14" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="F146" s="13" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="G146" s="14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="I146" s="14" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="J146" s="13">
         <v>1</v>
       </c>
-      <c r="K146" s="13"/>
-    </row>
-    <row r="147" ht="60.75" spans="1:11">
+      <c r="K146" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L146" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M146" s="13"/>
+      <c r="N146" s="13"/>
+      <c r="O146" s="13"/>
+    </row>
+    <row r="147" ht="60.75" spans="1:15">
       <c r="A147" s="3"/>
       <c r="B147" s="8">
         <f>ROW(B147)-ROW($B$2)</f>
         <v>145</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G147" s="11" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="I147" s="11" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="J147" s="10">
         <v>1</v>
       </c>
-      <c r="K147" s="10"/>
-    </row>
-    <row r="148" spans="1:11">
+      <c r="K147" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L147" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M147" s="10"/>
+      <c r="N147" s="10"/>
+      <c r="O147" s="10"/>
+    </row>
+    <row r="148" ht="15.75" spans="1:15">
       <c r="A148" s="3"/>
       <c r="B148" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="C148" s="12"/>
       <c r="D148" s="13" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="F148" s="13" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G148" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="J148" s="13">
         <v>1</v>
       </c>
-      <c r="K148" s="13"/>
-    </row>
-    <row r="149" ht="15.75" spans="1:11">
+      <c r="K148" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L148" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M148" s="13"/>
+      <c r="N148" s="13"/>
+      <c r="O148" s="13"/>
+    </row>
+    <row r="149" ht="15.75" spans="1:15">
       <c r="A149" s="3"/>
       <c r="B149" s="8">
         <f>ROW(B149)-ROW($B$2)</f>
         <v>147</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="G149" s="11" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I149" s="11" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="J149" s="10">
         <v>1</v>
       </c>
-      <c r="K149" s="10"/>
-    </row>
-    <row r="150" spans="1:11">
+      <c r="K149" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L149" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" s="10"/>
+      <c r="N149" s="10"/>
+      <c r="O149" s="10"/>
+    </row>
+    <row r="150" ht="15.75" spans="1:15">
       <c r="A150" s="3"/>
       <c r="B150" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="F150" s="13" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="G150" s="14" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="J150" s="13">
         <v>2</v>
       </c>
-      <c r="K150" s="13"/>
-    </row>
-    <row r="151" ht="24.75" spans="1:11">
+      <c r="K150" s="10">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L150" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M150" s="13"/>
+      <c r="N150" s="13"/>
+      <c r="O150" s="13"/>
+    </row>
+    <row r="151" ht="24.75" spans="1:15">
       <c r="A151" s="3"/>
       <c r="B151" s="8">
         <f>ROW(B151)-ROW($B$2)</f>
         <v>149</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G151" s="14" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="J151" s="13">
         <v>1</v>
       </c>
-      <c r="K151" s="13"/>
-    </row>
-    <row r="152" spans="1:11">
+      <c r="K151" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L151" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M151" s="13"/>
+      <c r="N151" s="13"/>
+      <c r="O151" s="13"/>
+    </row>
+    <row r="152" ht="15.75" spans="1:15">
       <c r="A152" s="3"/>
       <c r="B152" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="F152" s="13" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="G152" s="14" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="J152" s="13">
         <v>1</v>
       </c>
-      <c r="K152" s="13"/>
-    </row>
-    <row r="153" ht="15.75" spans="1:11">
+      <c r="K152" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L152" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M152" s="13"/>
+      <c r="N152" s="13"/>
+      <c r="O152" s="13"/>
+    </row>
+    <row r="153" ht="15.75" spans="1:15">
       <c r="A153" s="3"/>
       <c r="B153" s="8">
         <f>ROW(B153)-ROW($B$2)</f>
         <v>151</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="G153" s="11" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="I153" s="11" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="J153" s="10">
         <v>1</v>
       </c>
-      <c r="K153" s="10"/>
-    </row>
-    <row r="154" spans="1:11">
+      <c r="K153" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L153" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M153" s="10"/>
+      <c r="N153" s="10"/>
+      <c r="O153" s="10"/>
+    </row>
+    <row r="154" ht="15.75" spans="1:15">
       <c r="A154" s="3"/>
       <c r="B154" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>152</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="F154" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G154" s="14" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="J154" s="13">
         <v>1</v>
       </c>
-      <c r="K154" s="13"/>
-    </row>
-    <row r="155" ht="15.75" spans="1:11">
+      <c r="K154" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L154" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M154" s="13"/>
+      <c r="N154" s="13"/>
+      <c r="O154" s="13"/>
+    </row>
+    <row r="155" ht="15.75" spans="1:15">
       <c r="A155" s="3"/>
       <c r="B155" s="8">
         <f>ROW(B155)-ROW($B$2)</f>
         <v>153</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="I155" s="11" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J155" s="10">
         <v>1</v>
       </c>
-      <c r="K155" s="10"/>
-    </row>
-    <row r="156" ht="15.75" spans="1:11">
+      <c r="K155" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L155" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M155" s="10"/>
+      <c r="N155" s="10"/>
+      <c r="O155" s="10"/>
+    </row>
+    <row r="156" ht="15.75" spans="1:15">
       <c r="A156" s="3"/>
       <c r="B156" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>154</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="F156" s="13" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="G156" s="14" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="J156" s="13">
         <v>1</v>
       </c>
-      <c r="K156" s="13"/>
-    </row>
-    <row r="157" ht="24.75" spans="1:11">
+      <c r="K156" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L156" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M156" s="13"/>
+      <c r="N156" s="13"/>
+      <c r="O156" s="13"/>
+    </row>
+    <row r="157" ht="24.75" spans="1:15">
       <c r="A157" s="3"/>
       <c r="B157" s="8">
         <f>ROW(B157)-ROW($B$2)</f>
         <v>155</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="I157" s="11" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="J157" s="10">
         <v>1</v>
       </c>
-      <c r="K157" s="10"/>
-    </row>
-    <row r="158" ht="36.75" spans="1:11">
+      <c r="K157" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L157" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M157" s="10"/>
+      <c r="N157" s="10"/>
+      <c r="O157" s="10"/>
+    </row>
+    <row r="158" ht="36.75" spans="1:15">
       <c r="A158" s="3"/>
       <c r="B158" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="F158" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G158" s="14" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="J158" s="13">
         <v>1</v>
       </c>
-      <c r="K158" s="13"/>
-    </row>
-    <row r="159" ht="15.75" spans="1:11">
+      <c r="K158" s="10">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L158" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M158" s="13"/>
+      <c r="N158" s="13"/>
+      <c r="O158" s="13"/>
+    </row>
+    <row r="159" ht="15.75" spans="1:15">
       <c r="A159" s="3"/>
       <c r="B159" s="8">
         <f>ROW(B159)-ROW($B$2)</f>
         <v>157</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="F159" s="13" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="J159" s="10">
         <v>2</v>
       </c>
-      <c r="K159" s="10"/>
+      <c r="K159" s="10">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L159" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M159" s="10"/>
+      <c r="N159" s="10"/>
+      <c r="O159" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I1:O1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="L3" r:id="rId1" display="Digikey"/>
+    <hyperlink ref="L4" r:id="rId2" display="Digikey"/>
+    <hyperlink ref="L5" r:id="rId3" display="Digikey"/>
+    <hyperlink ref="L6" r:id="rId4" display="Digikey"/>
+    <hyperlink ref="L7" r:id="rId5" display="Digikey"/>
+    <hyperlink ref="L8" r:id="rId6" display="Digikey"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="683">
   <si>
     <t>#</t>
   </si>
@@ -476,6 +476,9 @@
     <t>TECH PUBLIC</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>D5, D6</t>
   </si>
   <si>
@@ -632,7 +635,7 @@
     <t>Ind-0805</t>
   </si>
   <si>
-    <t>100MHz</t>
+    <t>BLM21PG300SN1D</t>
   </si>
   <si>
     <t>FB2</t>
@@ -953,7 +956,7 @@
     <t>Omron</t>
   </si>
   <si>
-    <t>Common Mode Filter, [NoParam]</t>
+    <t>Common Mode Filter</t>
   </si>
   <si>
     <t>L1, L2, L3, L4</t>
@@ -965,6 +968,9 @@
     <t>MCZ1210DH900L2TA0G</t>
   </si>
   <si>
+    <t>Inductor</t>
+  </si>
+  <si>
     <t>L5</t>
   </si>
   <si>
@@ -980,9 +986,6 @@
     <t>4.7uH</t>
   </si>
   <si>
-    <t>Inductor</t>
-  </si>
-  <si>
     <t>L6, L9</t>
   </si>
   <si>
@@ -1031,9 +1034,6 @@
     <t>Foshan NationStar Optoelectronics</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>LED2, LED6</t>
   </si>
   <si>
@@ -1043,9 +1043,6 @@
     <t>NCD0603R3</t>
   </si>
   <si>
-    <t>RED</t>
-  </si>
-  <si>
     <t>LED3</t>
   </si>
   <si>
@@ -1055,9 +1052,6 @@
     <t>NCD0603Y2</t>
   </si>
   <si>
-    <t>Yellow</t>
-  </si>
-  <si>
     <t>LED4</t>
   </si>
   <si>
@@ -1082,9 +1076,6 @@
     <t>XZMDK68W-2</t>
   </si>
   <si>
-    <t>Red</t>
-  </si>
-  <si>
     <t>LED7</t>
   </si>
   <si>
@@ -1094,9 +1085,6 @@
     <t>XZCBD68W-2</t>
   </si>
   <si>
-    <t>Blue</t>
-  </si>
-  <si>
     <t>RGB  LED</t>
   </si>
   <si>
@@ -1155,9 +1143,6 @@
   </si>
   <si>
     <t>Comchip</t>
-  </si>
-  <si>
-    <t>S8050</t>
   </si>
   <si>
     <t>MOSFET</t>
@@ -2163,6 +2148,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -2182,14 +2175,6 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2744,7 +2729,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2874,7 +2859,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2918,26 +2903,32 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3273,7 +3264,7 @@
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="60.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="33.3809523809524" customWidth="1"/>
     <col min="8" max="8" width="14.7333333333333" customWidth="1"/>
     <col min="9" max="9" width="8.56190476190476" customWidth="1"/>
     <col min="10" max="10" width="7.20952380952381" customWidth="1"/>
@@ -3301,7 +3292,7 @@
       <c r="N1" s="15"/>
       <c r="O1" s="15"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" ht="15.75" spans="1:15">
       <c r="A2" s="3"/>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -3622,7 +3613,7 @@
       </c>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" ht="15.75" spans="1:15">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
         <f t="shared" si="0"/>
@@ -3656,13 +3647,15 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="10"/>
+      <c r="L9" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0.173</v>
+      </c>
       <c r="N9" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.076</v>
       </c>
       <c r="O9" s="10"/>
     </row>
@@ -3700,13 +3693,15 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="13"/>
+      <c r="L10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0.056</v>
+      </c>
       <c r="N10" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.184</v>
       </c>
       <c r="O10" s="13"/>
     </row>
@@ -3744,13 +3739,15 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="10"/>
+      <c r="L11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.224</v>
+      </c>
       <c r="N11" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="O11" s="10"/>
     </row>
@@ -3788,13 +3785,15 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="13"/>
+      <c r="L12" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0.753</v>
+      </c>
       <c r="N12" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9.036</v>
       </c>
       <c r="O12" s="13"/>
     </row>
@@ -3832,13 +3831,15 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="10"/>
+      <c r="L13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.22</v>
+      </c>
       <c r="N13" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O13" s="10"/>
     </row>
@@ -3876,13 +3877,15 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L14" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="13"/>
+      <c r="L14" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0.1</v>
+      </c>
       <c r="N14" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O14" s="13"/>
     </row>
@@ -3920,13 +3923,15 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="10"/>
+      <c r="L15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0.1</v>
+      </c>
       <c r="N15" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O15" s="10"/>
     </row>
@@ -3964,11 +3969,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L16" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
+      <c r="L16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" ref="N16:N29" si="3">M16*K16</f>
+        <v>0.6</v>
+      </c>
       <c r="O16" s="13"/>
     </row>
     <row r="17" ht="15.75" spans="1:15">
@@ -4005,11 +4015,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L17" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="L17" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="10">
+        <v>2.37</v>
+      </c>
+      <c r="N17" s="10">
+        <f t="shared" si="3"/>
+        <v>7.11</v>
+      </c>
       <c r="O17" s="10"/>
     </row>
     <row r="18" ht="15.75" spans="1:15">
@@ -4046,11 +4061,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L18" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
+      <c r="L18" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N18" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
       <c r="O18" s="13"/>
     </row>
     <row r="19" ht="15.75" spans="1:15">
@@ -4087,11 +4107,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L19" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="L19" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="N19" s="10">
+        <f t="shared" si="3"/>
+        <v>0.3</v>
+      </c>
       <c r="O19" s="10"/>
     </row>
     <row r="20" ht="15.75" spans="1:15">
@@ -4128,11 +4153,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
+      <c r="L20" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="13">
+        <v>0.69</v>
+      </c>
+      <c r="N20" s="10">
+        <f t="shared" si="3"/>
+        <v>4.14</v>
+      </c>
       <c r="O20" s="13"/>
     </row>
     <row r="21" ht="15.75" spans="1:15">
@@ -4169,11 +4199,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L21" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="L21" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
       <c r="O21" s="10"/>
     </row>
     <row r="22" ht="15.75" spans="1:15">
@@ -4210,11 +4245,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L22" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
+      <c r="L22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" si="3"/>
+        <v>0.78</v>
+      </c>
       <c r="O22" s="13"/>
     </row>
     <row r="23" ht="15.75" spans="1:15">
@@ -4251,11 +4291,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L23" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="L23" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="3"/>
+        <v>0.66</v>
+      </c>
       <c r="O23" s="10"/>
     </row>
     <row r="24" ht="24.75" spans="1:15">
@@ -4292,11 +4337,16 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L24" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
+      <c r="L24" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="13">
+        <v>0.27</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="3"/>
+        <v>8.1</v>
+      </c>
       <c r="O24" s="13"/>
     </row>
     <row r="25" ht="36.75" spans="1:15">
@@ -4337,7 +4387,10 @@
         <v>21</v>
       </c>
       <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
+      <c r="N25" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="O25" s="10"/>
     </row>
     <row r="26" ht="15.75" spans="1:15">
@@ -4374,11 +4427,16 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L26" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
+      <c r="L26" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="13">
+        <v>0.082</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="3"/>
+        <v>1.722</v>
+      </c>
       <c r="O26" s="13"/>
     </row>
     <row r="27" ht="15.75" spans="1:15">
@@ -4415,11 +4473,16 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L27" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
+      <c r="L27" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0.129</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" si="3"/>
+        <v>1.548</v>
+      </c>
       <c r="O27" s="10"/>
     </row>
     <row r="28" ht="15.75" spans="1:15">
@@ -4456,14 +4519,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L28" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
+      <c r="L28" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0.021</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="3"/>
+        <v>0.441</v>
+      </c>
       <c r="O28" s="13"/>
     </row>
-    <row r="29" ht="15.75" spans="1:15">
+    <row r="29" ht="24.75" spans="1:15">
       <c r="A29" s="3"/>
       <c r="B29" s="8">
         <f t="shared" si="0"/>
@@ -4497,11 +4565,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L29" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
+      <c r="L29" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
       <c r="O29" s="10"/>
     </row>
     <row r="30" ht="15.75" spans="1:15">
@@ -4538,11 +4611,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L30" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
+      <c r="L30" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" ref="N30:N39" si="4">M30*K30</f>
+        <v>0.6</v>
+      </c>
       <c r="O30" s="13"/>
     </row>
     <row r="31" ht="15.75" spans="1:15">
@@ -4579,11 +4657,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L31" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
+      <c r="L31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="N31" s="10">
+        <f t="shared" si="4"/>
+        <v>0.51</v>
+      </c>
       <c r="O31" s="10"/>
     </row>
     <row r="32" ht="15.75" spans="1:15">
@@ -4620,11 +4703,16 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
+      <c r="L32" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
       <c r="O32" s="13"/>
     </row>
     <row r="33" ht="15.75" spans="1:15">
@@ -4661,11 +4749,16 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L33" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
+      <c r="L33" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="N33" s="10">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
       <c r="O33" s="10"/>
     </row>
     <row r="34" ht="48.75" spans="1:15">
@@ -4693,7 +4786,7 @@
         <v>148</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J34" s="13">
         <v>30</v>
@@ -4706,35 +4799,38 @@
         <v>21</v>
       </c>
       <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
+      <c r="N34" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="O34" s="13"/>
     </row>
     <row r="35" ht="24.75" spans="1:15">
       <c r="A35" s="3"/>
       <c r="B35" s="8">
-        <f t="shared" ref="B35:B57" si="3">ROW(B35)-ROW($B$2)</f>
+        <f t="shared" ref="B35:B57" si="5">ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D35" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>152</v>
       </c>
       <c r="J35" s="10">
         <v>2</v>
@@ -4747,35 +4843,38 @@
         <v>21</v>
       </c>
       <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="N35" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="O35" s="10"/>
     </row>
     <row r="36" ht="15.75" spans="1:15">
       <c r="A36" s="3"/>
       <c r="B36" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>34</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>143</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="J36" s="13">
         <v>1</v>
@@ -4784,39 +4883,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L36" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
+      <c r="L36" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0.37</v>
+      </c>
+      <c r="N36" s="10">
+        <f t="shared" si="4"/>
+        <v>1.11</v>
+      </c>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" ht="15.75" spans="1:15">
+    <row r="37" ht="24.75" spans="1:15">
       <c r="A37" s="3"/>
       <c r="B37" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="J37" s="10">
         <v>6</v>
@@ -4825,39 +4929,44 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="L37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
+      <c r="L37" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="10">
+        <v>0.305</v>
+      </c>
+      <c r="N37" s="10">
+        <f t="shared" si="4"/>
+        <v>5.49</v>
+      </c>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" ht="15.75" spans="1:15">
+    <row r="38" ht="24.75" spans="1:15">
       <c r="A38" s="3"/>
       <c r="B38" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>143</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="J38" s="13">
         <v>1</v>
@@ -4866,39 +4975,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L38" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
+      <c r="L38" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0.21</v>
+      </c>
+      <c r="N38" s="10">
+        <f t="shared" si="4"/>
+        <v>0.63</v>
+      </c>
       <c r="O38" s="13"/>
     </row>
     <row r="39" ht="36.75" spans="1:15">
       <c r="A39" s="3"/>
       <c r="B39" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>37</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>148</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="J39" s="10">
         <v>21</v>
@@ -4911,35 +5025,38 @@
         <v>21</v>
       </c>
       <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
+      <c r="N39" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="O39" s="10"/>
     </row>
     <row r="40" ht="24.75" spans="1:15">
       <c r="A40" s="3"/>
       <c r="B40" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>143</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="J40" s="13">
         <v>1</v>
@@ -4952,35 +5069,38 @@
         <v>21</v>
       </c>
       <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
+      <c r="N40" s="10">
+        <f t="shared" ref="N40:N55" si="6">M40*K40</f>
+        <v>0</v>
+      </c>
       <c r="O40" s="13"/>
     </row>
     <row r="41" ht="36.75" spans="1:15">
       <c r="A41" s="3"/>
       <c r="B41" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>39</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>143</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="J41" s="10">
         <v>2</v>
@@ -4993,35 +5113,38 @@
         <v>21</v>
       </c>
       <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
+      <c r="N41" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O41" s="10"/>
     </row>
     <row r="42" ht="15.75" spans="1:15">
       <c r="A42" s="3"/>
       <c r="B42" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="J42" s="13">
         <v>2</v>
@@ -5030,39 +5153,44 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L42" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
+      <c r="L42" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="13">
+        <v>0.34</v>
+      </c>
+      <c r="N42" s="10">
+        <f t="shared" si="6"/>
+        <v>2.04</v>
+      </c>
       <c r="O42" s="13"/>
     </row>
     <row r="43" ht="15.75" spans="1:15">
       <c r="A43" s="3"/>
       <c r="B43" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>41</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="J43" s="10">
         <v>1</v>
@@ -5071,39 +5199,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L43" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
+      <c r="L43" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="N43" s="10">
+        <f t="shared" si="6"/>
+        <v>4.98</v>
+      </c>
       <c r="O43" s="10"/>
     </row>
     <row r="44" ht="24.75" spans="1:15">
       <c r="A44" s="3"/>
       <c r="B44" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="J44" s="13">
         <v>1</v>
@@ -5116,31 +5249,38 @@
         <v>21</v>
       </c>
       <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
+      <c r="N44" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O44" s="13"/>
     </row>
     <row r="45" ht="15.75" spans="1:15">
       <c r="A45" s="3"/>
       <c r="B45" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>43</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G45" s="11"/>
-      <c r="H45" s="10"/>
+        <v>201</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>44</v>
+      </c>
       <c r="I45" s="11" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="J45" s="10">
         <v>1</v>
@@ -5149,39 +5289,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L45" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
+      <c r="L45" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="6"/>
+        <v>0.36</v>
+      </c>
       <c r="O45" s="10"/>
     </row>
     <row r="46" ht="15.75" spans="1:15">
       <c r="A46" s="3"/>
       <c r="B46" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H46" s="13" t="s">
         <v>44</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="J46" s="13">
         <v>1</v>
@@ -5190,38 +5335,45 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L46" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
+      <c r="L46" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N46" s="10">
+        <f t="shared" si="6"/>
+        <v>0.3</v>
+      </c>
       <c r="O46" s="13"/>
     </row>
     <row r="47" ht="15.75" spans="1:15">
       <c r="A47" s="3"/>
       <c r="B47" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="I47" s="11"/>
+      <c r="I47" s="11" t="s">
+        <v>149</v>
+      </c>
       <c r="J47" s="10">
         <v>2</v>
       </c>
@@ -5229,39 +5381,44 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L47" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
+      <c r="L47" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="10">
+        <v>0.32</v>
+      </c>
+      <c r="N47" s="10">
+        <f t="shared" si="6"/>
+        <v>1.92</v>
+      </c>
       <c r="O47" s="10"/>
     </row>
     <row r="48" ht="36.75" spans="1:15">
       <c r="A48" s="3"/>
       <c r="B48" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>46</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
@@ -5274,35 +5431,38 @@
         <v>21</v>
       </c>
       <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
+      <c r="N48" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O48" s="10"/>
     </row>
     <row r="49" ht="24.75" spans="1:15">
       <c r="A49" s="3"/>
       <c r="B49" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>47</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>218</v>
+        <v>149</v>
       </c>
       <c r="J49" s="13">
         <v>1</v>
@@ -5315,35 +5475,38 @@
         <v>21</v>
       </c>
       <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
+      <c r="N49" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O49" s="13"/>
     </row>
-    <row r="50" ht="15.75" spans="1:15">
+    <row r="50" ht="24.75" spans="1:15">
       <c r="A50" s="3"/>
       <c r="B50" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>48</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="J50" s="10">
         <v>1</v>
@@ -5352,39 +5515,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L50" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
+      <c r="L50" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="10">
+        <v>1.26</v>
+      </c>
+      <c r="N50" s="10">
+        <f t="shared" si="6"/>
+        <v>3.78</v>
+      </c>
       <c r="O50" s="10"/>
     </row>
     <row r="51" ht="36.75" spans="1:15">
       <c r="A51" s="3"/>
       <c r="B51" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>228</v>
+        <v>149</v>
       </c>
       <c r="J51" s="13">
         <v>1</v>
@@ -5397,35 +5565,38 @@
         <v>21</v>
       </c>
       <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
+      <c r="N51" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O51" s="13"/>
     </row>
     <row r="52" ht="36.75" spans="1:15">
       <c r="A52" s="3"/>
       <c r="B52" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J52" s="10">
         <v>1</v>
@@ -5438,35 +5609,38 @@
         <v>21</v>
       </c>
       <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
+      <c r="N52" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O52" s="10"/>
     </row>
     <row r="53" ht="36.75" spans="1:15">
       <c r="A53" s="3"/>
       <c r="B53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="J53" s="13">
         <v>1</v>
@@ -5479,35 +5653,38 @@
         <v>21</v>
       </c>
       <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
+      <c r="N53" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O53" s="13"/>
     </row>
     <row r="54" ht="24.75" spans="1:15">
       <c r="A54" s="3"/>
       <c r="B54" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>52</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>240</v>
+        <v>220</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J54" s="10">
         <v>1</v>
@@ -5520,35 +5697,38 @@
         <v>21</v>
       </c>
       <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
+      <c r="N54" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O54" s="10"/>
     </row>
     <row r="55" ht="36.75" spans="1:15">
       <c r="A55" s="3"/>
       <c r="B55" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>53</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="J55" s="13">
         <v>1</v>
@@ -5561,35 +5741,38 @@
         <v>21</v>
       </c>
       <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
+      <c r="N55" s="10">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="O55" s="13"/>
     </row>
     <row r="56" ht="48.75" spans="1:15">
       <c r="A56" s="3"/>
       <c r="B56" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>54</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
+      </c>
+      <c r="I56" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J56" s="10">
         <v>1</v>
@@ -5602,35 +5785,38 @@
         <v>21</v>
       </c>
       <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
+      <c r="N56" s="10">
+        <f t="shared" ref="N56:N87" si="7">M56*K56</f>
+        <v>0</v>
+      </c>
       <c r="O56" s="10"/>
     </row>
     <row r="57" ht="48.75" spans="1:15">
       <c r="A57" s="3"/>
       <c r="B57" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J57" s="10">
         <v>2</v>
@@ -5643,35 +5829,38 @@
         <v>21</v>
       </c>
       <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
+      <c r="N57" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O57" s="10"/>
     </row>
     <row r="58" ht="60.75" spans="1:15">
       <c r="A58" s="3"/>
       <c r="B58" s="8">
-        <f t="shared" ref="B58:B158" si="4">ROW(B58)-ROW($B$2)</f>
+        <f t="shared" ref="B58:B158" si="8">ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>259</v>
+        <v>149</v>
       </c>
       <c r="J58" s="13">
         <v>5</v>
@@ -5684,35 +5873,38 @@
         <v>21</v>
       </c>
       <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
+      <c r="N58" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O58" s="13"/>
     </row>
     <row r="59" ht="48.75" spans="1:15">
       <c r="A59" s="3"/>
       <c r="B59" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>57</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>264</v>
+        <v>230</v>
+      </c>
+      <c r="I59" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J59" s="10">
         <v>1</v>
@@ -5725,35 +5917,38 @@
         <v>21</v>
       </c>
       <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
+      <c r="N59" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O59" s="10"/>
     </row>
     <row r="60" ht="15.75" spans="1:15">
       <c r="A60" s="3"/>
       <c r="B60" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>58</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>268</v>
+        <v>149</v>
       </c>
       <c r="J60" s="13">
         <v>1</v>
@@ -5762,39 +5957,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L60" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
+      <c r="L60" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="13">
+        <v>1.32</v>
+      </c>
+      <c r="N60" s="10">
+        <f t="shared" si="7"/>
+        <v>3.96</v>
+      </c>
       <c r="O60" s="13"/>
     </row>
     <row r="61" ht="15.75" spans="1:15">
       <c r="A61" s="3"/>
       <c r="B61" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>59</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
+      </c>
+      <c r="I61" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J61" s="10">
         <v>1</v>
@@ -5803,39 +6003,44 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L61" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
+      <c r="L61" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="10">
+        <v>0.46</v>
+      </c>
+      <c r="N61" s="10">
+        <f t="shared" si="7"/>
+        <v>1.38</v>
+      </c>
       <c r="O61" s="10"/>
     </row>
     <row r="62" ht="36.75" spans="1:15">
       <c r="A62" s="3"/>
       <c r="B62" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>277</v>
+        <v>149</v>
       </c>
       <c r="J62" s="13">
         <v>1</v>
@@ -5848,35 +6053,38 @@
         <v>21</v>
       </c>
       <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
+      <c r="N62" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O62" s="13"/>
     </row>
     <row r="63" ht="60.75" spans="1:15">
       <c r="A63" s="3"/>
       <c r="B63" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="I63" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
+      </c>
+      <c r="I63" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J63" s="10">
         <v>2</v>
@@ -5889,35 +6097,38 @@
         <v>21</v>
       </c>
       <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
+      <c r="N63" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O63" s="10"/>
     </row>
     <row r="64" ht="48.75" spans="1:15">
       <c r="A64" s="3"/>
       <c r="B64" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>286</v>
+        <v>149</v>
       </c>
       <c r="J64" s="13">
         <v>1</v>
@@ -5930,35 +6141,38 @@
         <v>21</v>
       </c>
       <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
+      <c r="N64" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O64" s="13"/>
     </row>
     <row r="65" ht="36.75" spans="1:15">
       <c r="A65" s="3"/>
       <c r="B65" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="I65" s="11" t="s">
-        <v>288</v>
+        <v>230</v>
+      </c>
+      <c r="I65" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J65" s="10">
         <v>1</v>
@@ -5971,35 +6185,38 @@
         <v>21</v>
       </c>
       <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
+      <c r="N65" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O65" s="10"/>
     </row>
     <row r="66" ht="24.75" spans="1:15">
       <c r="A66" s="3"/>
       <c r="B66" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>64</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="J66" s="13">
         <v>1</v>
@@ -6012,35 +6229,38 @@
         <v>21</v>
       </c>
       <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
+      <c r="N66" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O66" s="13"/>
     </row>
     <row r="67" ht="15.75" spans="1:15">
       <c r="A67" s="3"/>
       <c r="B67" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="I67" s="11" t="s">
-        <v>296</v>
+        <v>270</v>
+      </c>
+      <c r="I67" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J67" s="10">
         <v>1</v>
@@ -6049,347 +6269,384 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L67" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
+      <c r="L67" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="10">
+        <v>2.37</v>
+      </c>
+      <c r="N67" s="10">
+        <f t="shared" si="7"/>
+        <v>7.11</v>
+      </c>
       <c r="O67" s="10"/>
     </row>
     <row r="68" ht="36.75" spans="1:15">
       <c r="A68" s="3"/>
       <c r="B68" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>66</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>299</v>
+        <v>149</v>
       </c>
       <c r="J68" s="13">
         <v>2</v>
       </c>
       <c r="K68" s="10">
-        <f t="shared" ref="K68:K131" si="5">3*J68</f>
+        <f t="shared" ref="K68:K131" si="9">3*J68</f>
         <v>6</v>
       </c>
       <c r="L68" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
+      <c r="N68" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O68" s="13"/>
     </row>
     <row r="69" ht="24.75" spans="1:15">
       <c r="A69" s="3"/>
       <c r="B69" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>67</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="I69" s="11" t="s">
-        <v>302</v>
+        <v>246</v>
+      </c>
+      <c r="I69" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J69" s="10">
         <v>1</v>
       </c>
       <c r="K69" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L69" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
+      <c r="N69" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O69" s="10"/>
     </row>
     <row r="70" ht="15.75" spans="1:15">
       <c r="A70" s="3"/>
       <c r="B70" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>306</v>
+        <v>149</v>
       </c>
       <c r="J70" s="13">
         <v>5</v>
       </c>
       <c r="K70" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L70" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
+      <c r="L70" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="13">
+        <v>4.49</v>
+      </c>
+      <c r="N70" s="10">
+        <f t="shared" si="7"/>
+        <v>67.35</v>
+      </c>
       <c r="O70" s="13"/>
     </row>
-    <row r="71" ht="26.25" spans="1:15">
+    <row r="71" ht="15.75" spans="1:15">
       <c r="A71" s="3"/>
       <c r="B71" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I71" s="11" t="s">
-        <v>311</v>
+      <c r="I71" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J71" s="10">
         <v>4</v>
       </c>
       <c r="K71" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L71" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
+      <c r="N71" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O71" s="10"/>
     </row>
     <row r="72" ht="15.75" spans="1:15">
       <c r="A72" s="3"/>
       <c r="B72" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>70</v>
       </c>
-      <c r="C72" s="12"/>
+      <c r="C72" s="12" t="s">
+        <v>313</v>
+      </c>
       <c r="D72" s="13" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J72" s="13">
         <v>1</v>
       </c>
       <c r="K72" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L72" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
+      <c r="L72" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="13">
+        <v>0.39</v>
+      </c>
+      <c r="N72" s="10">
+        <f t="shared" si="7"/>
+        <v>1.17</v>
+      </c>
       <c r="O72" s="13"/>
     </row>
     <row r="73" ht="15.75" spans="1:15">
       <c r="A73" s="3"/>
       <c r="B73" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>71</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J73" s="10">
         <v>2</v>
       </c>
       <c r="K73" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L73" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
+      <c r="L73" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="N73" s="10">
+        <f t="shared" si="7"/>
+        <v>1.2</v>
+      </c>
       <c r="O73" s="10"/>
     </row>
     <row r="74" ht="24.75" spans="1:15">
       <c r="A74" s="3"/>
       <c r="B74" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>72</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F74" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J74" s="13">
         <v>2</v>
       </c>
       <c r="K74" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L74" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
+      <c r="N74" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O74" s="13"/>
     </row>
-    <row r="75" ht="24.75" spans="1:15">
+    <row r="75" ht="36.75" spans="1:15">
       <c r="A75" s="3"/>
       <c r="B75" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>73</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>334</v>
+        <v>149</v>
       </c>
       <c r="J75" s="10">
         <v>1</v>
       </c>
       <c r="K75" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L75" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M75" s="10"/>
-      <c r="N75" s="10"/>
+      <c r="N75" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O75" s="10"/>
     </row>
-    <row r="76" ht="24.75" spans="1:15">
+    <row r="76" ht="36.75" spans="1:15">
       <c r="A76" s="3"/>
       <c r="B76" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>335</v>
@@ -6398,514 +6655,562 @@
         <v>336</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G76" s="14" t="s">
         <v>337</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>338</v>
+        <v>149</v>
       </c>
       <c r="J76" s="13">
         <v>2</v>
       </c>
       <c r="K76" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L76" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M76" s="13"/>
-      <c r="N76" s="13"/>
+      <c r="N76" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O76" s="13"/>
     </row>
-    <row r="77" ht="24.75" spans="1:15">
+    <row r="77" ht="36.75" spans="1:15">
       <c r="A77" s="3"/>
       <c r="B77" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D77" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="E77" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="F77" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="G77" s="11" t="s">
-        <v>341</v>
-      </c>
       <c r="H77" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I77" s="11" t="s">
-        <v>342</v>
+        <v>149</v>
       </c>
       <c r="J77" s="10">
         <v>1</v>
       </c>
       <c r="K77" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L77" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M77" s="10"/>
-      <c r="N77" s="10"/>
+      <c r="N77" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O77" s="10"/>
     </row>
     <row r="78" ht="15.75" spans="1:15">
       <c r="A78" s="3"/>
       <c r="B78" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D78" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="F78" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="G78" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="H78" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G78" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="I78" s="14" t="s">
-        <v>342</v>
+      <c r="I78" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J78" s="13">
         <v>1</v>
       </c>
       <c r="K78" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L78" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="13"/>
-      <c r="N78" s="13"/>
+      <c r="L78" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="13">
+        <v>0.35</v>
+      </c>
+      <c r="N78" s="10">
+        <f t="shared" si="7"/>
+        <v>1.05</v>
+      </c>
       <c r="O78" s="13"/>
     </row>
     <row r="79" ht="15.75" spans="1:15">
       <c r="A79" s="3"/>
       <c r="B79" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D79" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="G79" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="E79" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="F79" s="10" t="s">
+      <c r="H79" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="G79" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>347</v>
-      </c>
       <c r="I79" s="11" t="s">
-        <v>351</v>
+        <v>149</v>
       </c>
       <c r="J79" s="10">
         <v>1</v>
       </c>
       <c r="K79" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L79" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
+      <c r="L79" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="N79" s="10">
+        <f t="shared" si="7"/>
+        <v>0.9</v>
+      </c>
       <c r="O79" s="10"/>
     </row>
     <row r="80" ht="15.75" spans="1:15">
       <c r="A80" s="3"/>
       <c r="B80" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>78</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F80" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="H80" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G80" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="I80" s="14" t="s">
-        <v>355</v>
+      <c r="I80" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J80" s="13">
         <v>1</v>
       </c>
       <c r="K80" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L80" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="13"/>
-      <c r="N80" s="13"/>
+      <c r="L80" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="13">
+        <v>0.51</v>
+      </c>
+      <c r="N80" s="10">
+        <f t="shared" si="7"/>
+        <v>1.53</v>
+      </c>
       <c r="O80" s="13"/>
     </row>
     <row r="81" ht="24.75" spans="1:15">
       <c r="A81" s="3"/>
       <c r="B81" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>79</v>
       </c>
       <c r="C81" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="G81" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="H81" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="E81" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>361</v>
-      </c>
       <c r="I81" s="11" t="s">
-        <v>360</v>
+        <v>149</v>
       </c>
       <c r="J81" s="10">
         <v>6</v>
       </c>
       <c r="K81" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="L81" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M81" s="10"/>
-      <c r="N81" s="10"/>
+      <c r="N81" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O81" s="10"/>
     </row>
     <row r="82" ht="36.75" spans="1:15">
       <c r="A82" s="3"/>
       <c r="B82" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="D82" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="E82" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="G82" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="H82" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="E82" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="G82" s="14" t="s">
-        <v>366</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="I82" s="14" t="s">
-        <v>366</v>
+      <c r="I82" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J82" s="13">
         <v>1</v>
       </c>
       <c r="K82" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L82" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="13"/>
-      <c r="N82" s="13"/>
+      <c r="L82" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="13">
+        <v>0.53</v>
+      </c>
+      <c r="N82" s="10">
+        <f t="shared" si="7"/>
+        <v>1.59</v>
+      </c>
       <c r="O82" s="13"/>
     </row>
-    <row r="83" ht="15.75" spans="1:15">
+    <row r="83" spans="1:15">
       <c r="A83" s="3"/>
       <c r="B83" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>148</v>
       </c>
       <c r="I83" s="11" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="J83" s="10">
         <v>4</v>
       </c>
       <c r="K83" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L83" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M83" s="10"/>
-      <c r="N83" s="10"/>
+      <c r="N83" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O83" s="10"/>
     </row>
     <row r="84" ht="24.75" spans="1:15">
       <c r="A84" s="3"/>
       <c r="B84" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="C84" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="H84" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="D84" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>373</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="G84" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="I84" s="14" t="s">
-        <v>376</v>
+      <c r="I84" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J84" s="13">
         <v>2</v>
       </c>
       <c r="K84" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L84" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="13"/>
-      <c r="N84" s="13"/>
+      <c r="L84" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="13">
+        <v>0.29</v>
+      </c>
+      <c r="N84" s="10">
+        <f t="shared" si="7"/>
+        <v>1.74</v>
+      </c>
       <c r="O84" s="13"/>
     </row>
     <row r="85" ht="24.75" spans="1:15">
       <c r="A85" s="3"/>
       <c r="B85" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I85" s="11" t="s">
-        <v>380</v>
+        <v>149</v>
       </c>
       <c r="J85" s="10">
         <v>5</v>
       </c>
       <c r="K85" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="L85" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M85" s="10"/>
-      <c r="N85" s="10"/>
+      <c r="N85" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O85" s="10"/>
     </row>
     <row r="86" ht="24.75" spans="1:15">
       <c r="A86" s="3"/>
       <c r="B86" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D86" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="D86" s="13" t="s">
-        <v>382</v>
-      </c>
       <c r="E86" s="14" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="I86" s="14" t="s">
-        <v>384</v>
+        <v>380</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J86" s="13">
         <v>1</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L86" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="13"/>
-      <c r="N86" s="13"/>
+      <c r="L86" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="13">
+        <v>0.44</v>
+      </c>
+      <c r="N86" s="10">
+        <f t="shared" si="7"/>
+        <v>1.32</v>
+      </c>
       <c r="O86" s="13"/>
     </row>
     <row r="87" ht="15.75" spans="1:15">
       <c r="A87" s="3"/>
       <c r="B87" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I87" s="11" t="s">
-        <v>389</v>
+        <v>149</v>
       </c>
       <c r="J87" s="10">
         <v>1</v>
       </c>
       <c r="K87" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L87" s="10" t="s">
         <v>21</v>
       </c>
       <c r="M87" s="10"/>
-      <c r="N87" s="10"/>
+      <c r="N87" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="O87" s="10"/>
     </row>
     <row r="88" ht="48.75" spans="1:15">
       <c r="A88" s="3"/>
       <c r="B88" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H88" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="I88" s="14" t="s">
-        <v>394</v>
+      <c r="I88" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="J88" s="13">
         <v>1</v>
       </c>
       <c r="K88" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L88" s="10" t="s">
@@ -6918,35 +7223,35 @@
     <row r="89" ht="60.75" spans="1:15">
       <c r="A89" s="3"/>
       <c r="B89" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I89" s="11" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J89" s="10">
         <v>40</v>
       </c>
       <c r="K89" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>120</v>
       </c>
       <c r="L89" s="10" t="s">
@@ -6959,35 +7264,35 @@
     <row r="90" ht="15.75" spans="1:15">
       <c r="A90" s="3"/>
       <c r="B90" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F90" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="G90" s="14" t="s">
         <v>398</v>
-      </c>
-      <c r="G90" s="14" t="s">
-        <v>403</v>
       </c>
       <c r="H90" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="J90" s="13">
         <v>6</v>
       </c>
       <c r="K90" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="L90" s="10" t="s">
@@ -7000,35 +7305,35 @@
     <row r="91" ht="15.75" spans="1:15">
       <c r="A91" s="3"/>
       <c r="B91" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I91" s="11" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J91" s="10">
         <v>7</v>
       </c>
       <c r="K91" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="L91" s="10" t="s">
@@ -7041,35 +7346,35 @@
     <row r="92" ht="72.75" spans="1:15">
       <c r="A92" s="3"/>
       <c r="B92" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H92" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="J92" s="13">
         <v>49</v>
       </c>
       <c r="K92" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>147</v>
       </c>
       <c r="L92" s="10" t="s">
@@ -7082,35 +7387,35 @@
     <row r="93" ht="15.75" spans="1:15">
       <c r="A93" s="3"/>
       <c r="B93" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H93" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I93" s="11" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J93" s="10">
         <v>7</v>
       </c>
       <c r="K93" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="L93" s="10" t="s">
@@ -7121,80 +7426,80 @@
       <c r="O93" s="10"/>
     </row>
     <row r="94" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A94" s="17"/>
-      <c r="B94" s="18">
-        <f t="shared" si="4"/>
+      <c r="A94" s="19"/>
+      <c r="B94" s="20">
+        <f t="shared" si="8"/>
         <v>92</v>
       </c>
-      <c r="C94" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="D94" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="F94" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="G94" s="21" t="s">
-        <v>419</v>
-      </c>
-      <c r="H94" s="20" t="s">
+      <c r="C94" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="D94" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="E94" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="F94" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="G94" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="H94" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I94" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="J94" s="20">
+      <c r="I94" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="J94" s="22">
         <v>2</v>
       </c>
       <c r="K94" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L94" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M94" s="20"/>
-      <c r="N94" s="20"/>
-      <c r="O94" s="23" t="s">
-        <v>421</v>
+      <c r="M94" s="22"/>
+      <c r="N94" s="22"/>
+      <c r="O94" s="25" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:15">
       <c r="A95" s="3"/>
       <c r="B95" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H95" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I95" s="11" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J95" s="10">
         <v>2</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L95" s="10" t="s">
@@ -7207,35 +7512,35 @@
     <row r="96" ht="48.75" spans="1:15">
       <c r="A96" s="3"/>
       <c r="B96" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H96" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J96" s="13">
         <v>26</v>
       </c>
       <c r="K96" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>78</v>
       </c>
       <c r="L96" s="10" t="s">
@@ -7248,35 +7553,35 @@
     <row r="97" ht="15.75" spans="1:15">
       <c r="A97" s="3"/>
       <c r="B97" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I97" s="11" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J97" s="10">
         <v>1</v>
       </c>
       <c r="K97" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L97" s="10" t="s">
@@ -7289,35 +7594,35 @@
     <row r="98" ht="36.75" spans="1:15">
       <c r="A98" s="3"/>
       <c r="B98" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F98" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H98" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J98" s="13">
         <v>27</v>
       </c>
       <c r="K98" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>81</v>
       </c>
       <c r="L98" s="10" t="s">
@@ -7330,35 +7635,35 @@
     <row r="99" ht="15.75" spans="1:15">
       <c r="A99" s="3"/>
       <c r="B99" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I99" s="11" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J99" s="10">
         <v>4</v>
       </c>
       <c r="K99" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L99" s="10" t="s">
@@ -7371,35 +7676,35 @@
     <row r="100" ht="15.75" spans="1:15">
       <c r="A100" s="3"/>
       <c r="B100" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H100" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="J100" s="13">
         <v>4</v>
       </c>
       <c r="K100" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L100" s="10" t="s">
@@ -7412,35 +7717,35 @@
     <row r="101" ht="15.75" spans="1:15">
       <c r="A101" s="3"/>
       <c r="B101" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I101" s="11" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="J101" s="10">
         <v>4</v>
       </c>
       <c r="K101" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L101" s="10" t="s">
@@ -7453,35 +7758,35 @@
     <row r="102" ht="15.75" spans="1:15">
       <c r="A102" s="3"/>
       <c r="B102" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="H102" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="J102" s="13">
         <v>1</v>
       </c>
       <c r="K102" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L102" s="10" t="s">
@@ -7494,35 +7799,35 @@
     <row r="103" ht="15.75" spans="1:15">
       <c r="A103" s="3"/>
       <c r="B103" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>101</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I103" s="11" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J103" s="10">
         <v>5</v>
       </c>
       <c r="K103" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="L103" s="10" t="s">
@@ -7535,35 +7840,35 @@
     <row r="104" ht="15.75" spans="1:15">
       <c r="A104" s="3"/>
       <c r="B104" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>102</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G104" s="14" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H104" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="J104" s="13">
         <v>1</v>
       </c>
       <c r="K104" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L104" s="10" t="s">
@@ -7576,35 +7881,35 @@
     <row r="105" ht="15.75" spans="1:15">
       <c r="A105" s="3"/>
       <c r="B105" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>103</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I105" s="11" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="J105" s="10">
         <v>1</v>
       </c>
       <c r="K105" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L105" s="10" t="s">
@@ -7617,35 +7922,35 @@
     <row r="106" ht="15.75" spans="1:15">
       <c r="A106" s="3"/>
       <c r="B106" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>104</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F106" s="13" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G106" s="14" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="H106" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="J106" s="13">
         <v>1</v>
       </c>
       <c r="K106" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L106" s="10" t="s">
@@ -7656,80 +7961,80 @@
       <c r="O106" s="13"/>
     </row>
     <row r="107" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A107" s="17"/>
+      <c r="A107" s="19"/>
       <c r="B107" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="C107" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="D107" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="E107" s="24" t="s">
-        <v>402</v>
-      </c>
-      <c r="F107" s="23" t="s">
+      <c r="C107" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="E107" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="F107" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="G107" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="G107" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="H107" s="23" t="s">
+      <c r="H107" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="I107" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="J107" s="23">
+      <c r="I107" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="J107" s="25">
         <v>1</v>
       </c>
       <c r="K107" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L107" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M107" s="23"/>
-      <c r="N107" s="23"/>
-      <c r="O107" s="23" t="s">
-        <v>421</v>
+      <c r="M107" s="25"/>
+      <c r="N107" s="25"/>
+      <c r="O107" s="25" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="108" ht="15.75" spans="1:15">
       <c r="A108" s="3"/>
       <c r="B108" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>106</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F108" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G108" s="14" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="H108" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I108" s="14" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J108" s="13">
         <v>2</v>
       </c>
       <c r="K108" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L108" s="10" t="s">
@@ -7742,35 +8047,35 @@
     <row r="109" ht="15.75" spans="1:15">
       <c r="A109" s="3"/>
       <c r="B109" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>107</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="11" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="J109" s="10">
         <v>2</v>
       </c>
       <c r="K109" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L109" s="10" t="s">
@@ -7783,35 +8088,35 @@
     <row r="110" ht="15.75" spans="1:15">
       <c r="A110" s="3"/>
       <c r="B110" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>108</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D110" s="13" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F110" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H110" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J110" s="13">
         <v>2</v>
       </c>
       <c r="K110" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L110" s="10" t="s">
@@ -7824,35 +8129,35 @@
     <row r="111" ht="15.75" spans="1:15">
       <c r="A111" s="3"/>
       <c r="B111" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>109</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G111" s="11" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="I111" s="11" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J111" s="10">
         <v>2</v>
       </c>
       <c r="K111" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L111" s="10" t="s">
@@ -7865,35 +8170,35 @@
     <row r="112" ht="15.75" spans="1:15">
       <c r="A112" s="3"/>
       <c r="B112" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H112" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J112" s="13">
         <v>2</v>
       </c>
       <c r="K112" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L112" s="10" t="s">
@@ -7906,35 +8211,35 @@
     <row r="113" ht="15.75" spans="1:15">
       <c r="A113" s="3"/>
       <c r="B113" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>111</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G113" s="11" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I113" s="11" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="J113" s="10">
         <v>4</v>
       </c>
       <c r="K113" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="L113" s="10" t="s">
@@ -7947,35 +8252,35 @@
     <row r="114" ht="15.75" spans="1:15">
       <c r="A114" s="3"/>
       <c r="B114" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G114" s="14" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="I114" s="14" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="J114" s="13">
         <v>2</v>
       </c>
       <c r="K114" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L114" s="10" t="s">
@@ -7988,35 +8293,35 @@
     <row r="115" ht="15.75" spans="1:15">
       <c r="A115" s="3"/>
       <c r="B115" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>113</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G115" s="11" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I115" s="11" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="J115" s="10">
         <v>8</v>
       </c>
       <c r="K115" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="L115" s="10" t="s">
@@ -8029,35 +8334,35 @@
     <row r="116" ht="15.75" spans="1:15">
       <c r="A116" s="3"/>
       <c r="B116" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>114</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H116" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J116" s="13">
         <v>8</v>
       </c>
       <c r="K116" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="L116" s="10" t="s">
@@ -8070,35 +8375,35 @@
     <row r="117" ht="15.75" spans="1:15">
       <c r="A117" s="3"/>
       <c r="B117" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>115</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G117" s="11" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I117" s="11" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="J117" s="10">
         <v>2</v>
       </c>
       <c r="K117" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L117" s="10" t="s">
@@ -8111,35 +8416,35 @@
     <row r="118" ht="15.75" spans="1:15">
       <c r="A118" s="3"/>
       <c r="B118" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>116</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F118" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G118" s="14" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="H118" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I118" s="14" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="J118" s="13">
         <v>2</v>
       </c>
       <c r="K118" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L118" s="10" t="s">
@@ -8152,35 +8457,35 @@
     <row r="119" ht="15.75" spans="1:15">
       <c r="A119" s="3"/>
       <c r="B119" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>117</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G119" s="11" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I119" s="11" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J119" s="10">
         <v>2</v>
       </c>
       <c r="K119" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L119" s="10" t="s">
@@ -8193,35 +8498,35 @@
     <row r="120" ht="15.75" spans="1:15">
       <c r="A120" s="3"/>
       <c r="B120" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>118</v>
       </c>
       <c r="C120" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="E120" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="D120" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="E120" s="14" t="s">
-        <v>514</v>
-      </c>
       <c r="F120" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G120" s="14" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="H120" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="14" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="J120" s="13">
         <v>2</v>
       </c>
       <c r="K120" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L120" s="10" t="s">
@@ -8232,80 +8537,80 @@
       <c r="O120" s="13"/>
     </row>
     <row r="121" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A121" s="17"/>
+      <c r="A121" s="19"/>
       <c r="B121" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>119</v>
       </c>
-      <c r="C121" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="D121" s="23" t="s">
-        <v>517</v>
-      </c>
-      <c r="E121" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="F121" s="23" t="s">
-        <v>398</v>
-      </c>
-      <c r="G121" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="H121" s="23" t="s">
+      <c r="C121" s="24" t="s">
+        <v>390</v>
+      </c>
+      <c r="D121" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="E121" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="F121" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="G121" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="H121" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="I121" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="J121" s="23">
+      <c r="I121" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="J121" s="25">
         <v>2</v>
       </c>
       <c r="K121" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L121" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M121" s="23"/>
-      <c r="N121" s="23"/>
-      <c r="O121" s="23" t="s">
-        <v>421</v>
+      <c r="M121" s="25"/>
+      <c r="N121" s="25"/>
+      <c r="O121" s="25" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="122" ht="15.75" spans="1:15">
       <c r="A122" s="3"/>
       <c r="B122" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D122" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F122" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G122" s="14" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="H122" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="J122" s="13">
         <v>1</v>
       </c>
       <c r="K122" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L122" s="10" t="s">
@@ -8322,31 +8627,31 @@
         <v>121</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="I123" s="11" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="J123" s="10">
         <v>1</v>
       </c>
       <c r="K123" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L123" s="10" t="s">
@@ -8359,35 +8664,35 @@
     <row r="124" ht="15.75" spans="1:15">
       <c r="A124" s="3"/>
       <c r="B124" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>122</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F124" s="13" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="G124" s="14" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="H124" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I124" s="14" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="J124" s="13">
         <v>2</v>
       </c>
       <c r="K124" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L124" s="10" t="s">
@@ -8404,31 +8709,31 @@
         <v>123</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I125" s="11" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="J125" s="10">
         <v>1</v>
       </c>
       <c r="K125" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L125" s="10" t="s">
@@ -8441,35 +8746,35 @@
     <row r="126" ht="15.75" spans="1:15">
       <c r="A126" s="3"/>
       <c r="B126" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>124</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G126" s="14" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="H126" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="J126" s="13">
         <v>1</v>
       </c>
       <c r="K126" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L126" s="10" t="s">
@@ -8486,31 +8791,31 @@
         <v>125</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G127" s="11" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I127" s="11" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="J127" s="10">
         <v>1</v>
       </c>
       <c r="K127" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L127" s="10" t="s">
@@ -8523,35 +8828,35 @@
     <row r="128" ht="15.75" spans="1:15">
       <c r="A128" s="3"/>
       <c r="B128" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>126</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F128" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G128" s="14" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="H128" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="J128" s="13">
         <v>1</v>
       </c>
       <c r="K128" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L128" s="10" t="s">
@@ -8568,31 +8873,31 @@
         <v>127</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G129" s="11" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I129" s="11" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="J129" s="10">
         <v>2</v>
       </c>
       <c r="K129" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L129" s="10" t="s">
@@ -8605,35 +8910,35 @@
     <row r="130" ht="15.75" spans="1:15">
       <c r="A130" s="3"/>
       <c r="B130" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>128</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G130" s="14" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="H130" s="13" t="s">
         <v>19</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="J130" s="13">
         <v>1</v>
       </c>
       <c r="K130" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="L130" s="10" t="s">
@@ -8650,31 +8955,31 @@
         <v>129</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G131" s="11" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I131" s="11" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="J131" s="10">
         <v>2</v>
       </c>
       <c r="K131" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="L131" s="10" t="s">
@@ -8687,35 +8992,35 @@
     <row r="132" ht="36.75" spans="1:15">
       <c r="A132" s="3"/>
       <c r="B132" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>130</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F132" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G132" s="14" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>559</v>
+        <v>149</v>
       </c>
       <c r="J132" s="13">
         <v>6</v>
       </c>
       <c r="K132" s="10">
-        <f t="shared" ref="K132:K159" si="6">3*J132</f>
+        <f t="shared" ref="K132:K159" si="10">3*J132</f>
         <v>18</v>
       </c>
       <c r="L132" s="10" t="s">
@@ -8732,31 +9037,31 @@
         <v>131</v>
       </c>
       <c r="C133" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="G133" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="D133" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="E133" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="G133" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="I133" s="11" t="s">
-        <v>565</v>
+      <c r="I133" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J133" s="10">
         <v>1</v>
       </c>
       <c r="K133" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L133" s="10" t="s">
@@ -8766,38 +9071,38 @@
       <c r="N133" s="10"/>
       <c r="O133" s="10"/>
     </row>
-    <row r="134" ht="15.75" spans="1:15">
+    <row r="134" ht="24.75" spans="1:15">
       <c r="A134" s="3"/>
       <c r="B134" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>132</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="E134" s="14" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F134" s="13" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G134" s="14" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>570</v>
+        <v>149</v>
       </c>
       <c r="J134" s="13">
         <v>1</v>
       </c>
       <c r="K134" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L134" s="10" t="s">
@@ -8814,31 +9119,31 @@
         <v>133</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D135" s="10" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="G135" s="11" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I135" s="11" t="s">
-        <v>575</v>
+        <v>159</v>
+      </c>
+      <c r="I135" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J135" s="10">
         <v>2</v>
       </c>
       <c r="K135" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="L135" s="10" t="s">
@@ -8848,38 +9153,38 @@
       <c r="N135" s="10"/>
       <c r="O135" s="10"/>
     </row>
-    <row r="136" ht="15.75" spans="1:15">
+    <row r="136" ht="24.75" spans="1:15">
       <c r="A136" s="3"/>
       <c r="B136" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>134</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E136" s="14" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F136" s="13" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G136" s="14" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>579</v>
+        <v>149</v>
       </c>
       <c r="J136" s="13">
         <v>1</v>
       </c>
       <c r="K136" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L136" s="10" t="s">
@@ -8896,31 +9201,31 @@
         <v>135</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="G137" s="11" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="I137" s="11" t="s">
-        <v>583</v>
+        <v>579</v>
+      </c>
+      <c r="I137" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J137" s="10">
         <v>4</v>
       </c>
       <c r="K137" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="L137" s="10" t="s">
@@ -8933,35 +9238,35 @@
     <row r="138" ht="15.75" spans="1:15">
       <c r="A138" s="3"/>
       <c r="B138" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>136</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="E138" s="14" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F138" s="13" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="G138" s="14" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>588</v>
+        <v>149</v>
       </c>
       <c r="J138" s="13">
         <v>1</v>
       </c>
       <c r="K138" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L138" s="10" t="s">
@@ -8978,31 +9283,31 @@
         <v>137</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D139" s="10" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G139" s="11" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="I139" s="11" t="s">
-        <v>593</v>
+        <v>566</v>
+      </c>
+      <c r="I139" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J139" s="10">
         <v>1</v>
       </c>
       <c r="K139" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L139" s="10" t="s">
@@ -9015,35 +9320,35 @@
     <row r="140" ht="15.75" spans="1:15">
       <c r="A140" s="3"/>
       <c r="B140" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>138</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D140" s="13" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E140" s="14" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G140" s="14" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>597</v>
+        <v>149</v>
       </c>
       <c r="J140" s="13">
         <v>1</v>
       </c>
       <c r="K140" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L140" s="10" t="s">
@@ -9060,31 +9365,31 @@
         <v>139</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D141" s="10" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="F141" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="G141" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="G141" s="11" t="s">
-        <v>601</v>
-      </c>
       <c r="H141" s="10" t="s">
-        <v>602</v>
-      </c>
-      <c r="I141" s="11" t="s">
-        <v>601</v>
+        <v>597</v>
+      </c>
+      <c r="I141" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J141" s="10">
         <v>1</v>
       </c>
       <c r="K141" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L141" s="10" t="s">
@@ -9097,35 +9402,35 @@
     <row r="142" ht="24.75" spans="1:15">
       <c r="A142" s="3"/>
       <c r="B142" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="E142" s="14" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="F142" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G142" s="14" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>606</v>
+        <v>149</v>
       </c>
       <c r="J142" s="13">
         <v>1</v>
       </c>
       <c r="K142" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L142" s="10" t="s">
@@ -9135,38 +9440,38 @@
       <c r="N142" s="13"/>
       <c r="O142" s="13"/>
     </row>
-    <row r="143" ht="15.75" spans="1:15">
+    <row r="143" ht="24.75" spans="1:15">
       <c r="A143" s="3"/>
       <c r="B143" s="8">
         <f>ROW(B143)-ROW($B$2)</f>
         <v>141</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D143" s="10" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="F143" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="I143" s="11" t="s">
-        <v>610</v>
+        <v>566</v>
+      </c>
+      <c r="I143" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J143" s="10">
         <v>1</v>
       </c>
       <c r="K143" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L143" s="10" t="s">
@@ -9179,35 +9484,35 @@
     <row r="144" ht="24.75" spans="1:15">
       <c r="A144" s="3"/>
       <c r="B144" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>142</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D144" s="13" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E144" s="14" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F144" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G144" s="14" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>614</v>
+        <v>149</v>
       </c>
       <c r="J144" s="13">
         <v>2</v>
       </c>
       <c r="K144" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="L144" s="10" t="s">
@@ -9224,31 +9529,31 @@
         <v>143</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="F145" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G145" s="11" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="I145" s="11" t="s">
-        <v>618</v>
+        <v>614</v>
+      </c>
+      <c r="I145" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J145" s="10">
         <v>1</v>
       </c>
       <c r="K145" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L145" s="10" t="s">
@@ -9261,35 +9566,35 @@
     <row r="146" ht="26.25" spans="1:15">
       <c r="A146" s="3"/>
       <c r="B146" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>144</v>
       </c>
       <c r="C146" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="D146" s="13" t="s">
+        <v>616</v>
+      </c>
+      <c r="E146" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="F146" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="G146" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="H146" s="13" t="s">
         <v>620</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>622</v>
-      </c>
-      <c r="F146" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="G146" s="14" t="s">
-        <v>624</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>625</v>
-      </c>
       <c r="I146" s="14" t="s">
-        <v>624</v>
+        <v>149</v>
       </c>
       <c r="J146" s="13">
         <v>1</v>
       </c>
       <c r="K146" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L146" s="10" t="s">
@@ -9306,31 +9611,31 @@
         <v>145</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D147" s="10" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G147" s="11" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="I147" s="11" t="s">
-        <v>629</v>
+        <v>625</v>
+      </c>
+      <c r="I147" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J147" s="10">
         <v>1</v>
       </c>
       <c r="K147" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L147" s="10" t="s">
@@ -9340,36 +9645,38 @@
       <c r="N147" s="10"/>
       <c r="O147" s="10"/>
     </row>
-    <row r="148" ht="15.75" spans="1:15">
+    <row r="148" spans="1:15">
       <c r="A148" s="3"/>
       <c r="B148" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>146</v>
       </c>
-      <c r="C148" s="12"/>
+      <c r="C148" s="12" t="s">
+        <v>556</v>
+      </c>
       <c r="D148" s="13" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E148" s="14" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="F148" s="13" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G148" s="14" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>634</v>
+        <v>149</v>
       </c>
       <c r="J148" s="13">
         <v>1</v>
       </c>
       <c r="K148" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L148" s="10" t="s">
@@ -9379,38 +9686,38 @@
       <c r="N148" s="13"/>
       <c r="O148" s="13"/>
     </row>
-    <row r="149" ht="15.75" spans="1:15">
+    <row r="149" ht="24.75" spans="1:15">
       <c r="A149" s="3"/>
       <c r="B149" s="8">
         <f>ROW(B149)-ROW($B$2)</f>
         <v>147</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G149" s="11" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="I149" s="11" t="s">
-        <v>639</v>
+        <v>566</v>
+      </c>
+      <c r="I149" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J149" s="10">
         <v>1</v>
       </c>
       <c r="K149" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L149" s="10" t="s">
@@ -9423,35 +9730,35 @@
     <row r="150" ht="15.75" spans="1:15">
       <c r="A150" s="3"/>
       <c r="B150" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>148</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D150" s="13" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="E150" s="14" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="F150" s="13" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="G150" s="14" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>643</v>
+        <v>149</v>
       </c>
       <c r="J150" s="13">
         <v>2</v>
       </c>
       <c r="K150" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="L150" s="10" t="s">
@@ -9468,31 +9775,31 @@
         <v>149</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D151" s="13" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="E151" s="14" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>111</v>
       </c>
       <c r="G151" s="14" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>647</v>
+        <v>149</v>
       </c>
       <c r="J151" s="13">
         <v>1</v>
       </c>
       <c r="K151" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L151" s="10" t="s">
@@ -9502,38 +9809,38 @@
       <c r="N151" s="13"/>
       <c r="O151" s="13"/>
     </row>
-    <row r="152" ht="15.75" spans="1:15">
+    <row r="152" ht="24.75" spans="1:15">
       <c r="A152" s="3"/>
       <c r="B152" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="F152" s="13" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G152" s="14" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>652</v>
+        <v>149</v>
       </c>
       <c r="J152" s="13">
         <v>1</v>
       </c>
       <c r="K152" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L152" s="10" t="s">
@@ -9543,38 +9850,38 @@
       <c r="N152" s="13"/>
       <c r="O152" s="13"/>
     </row>
-    <row r="153" ht="15.75" spans="1:15">
+    <row r="153" ht="24.75" spans="1:15">
       <c r="A153" s="3"/>
       <c r="B153" s="8">
         <f>ROW(B153)-ROW($B$2)</f>
         <v>151</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D153" s="10" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="G153" s="11" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="I153" s="11" t="s">
-        <v>657</v>
+        <v>566</v>
+      </c>
+      <c r="I153" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J153" s="10">
         <v>1</v>
       </c>
       <c r="K153" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L153" s="10" t="s">
@@ -9587,35 +9894,35 @@
     <row r="154" ht="15.75" spans="1:15">
       <c r="A154" s="3"/>
       <c r="B154" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>152</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F154" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G154" s="14" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>660</v>
+        <v>149</v>
       </c>
       <c r="J154" s="13">
         <v>1</v>
       </c>
       <c r="K154" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L154" s="10" t="s">
@@ -9632,31 +9939,31 @@
         <v>153</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D155" s="10" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>666</v>
-      </c>
-      <c r="I155" s="11" t="s">
-        <v>665</v>
+        <v>661</v>
+      </c>
+      <c r="I155" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J155" s="10">
         <v>1</v>
       </c>
       <c r="K155" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L155" s="10" t="s">
@@ -9666,38 +9973,38 @@
       <c r="N155" s="10"/>
       <c r="O155" s="10"/>
     </row>
-    <row r="156" ht="15.75" spans="1:15">
+    <row r="156" ht="24.75" spans="1:15">
       <c r="A156" s="3"/>
       <c r="B156" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>154</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="E156" s="14" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F156" s="13" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="G156" s="14" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>670</v>
+        <v>149</v>
       </c>
       <c r="J156" s="13">
         <v>1</v>
       </c>
       <c r="K156" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L156" s="10" t="s">
@@ -9707,38 +10014,38 @@
       <c r="N156" s="13"/>
       <c r="O156" s="13"/>
     </row>
-    <row r="157" ht="24.75" spans="1:15">
+    <row r="157" ht="36.75" spans="1:15">
       <c r="A157" s="3"/>
       <c r="B157" s="8">
         <f>ROW(B157)-ROW($B$2)</f>
         <v>155</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D157" s="10" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="G157" s="11" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>676</v>
-      </c>
-      <c r="I157" s="11" t="s">
-        <v>675</v>
+        <v>671</v>
+      </c>
+      <c r="I157" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="J157" s="10">
         <v>1</v>
       </c>
       <c r="K157" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L157" s="10" t="s">
@@ -9751,35 +10058,35 @@
     <row r="158" ht="36.75" spans="1:15">
       <c r="A158" s="3"/>
       <c r="B158" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>156</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="F158" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G158" s="14" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="J158" s="13">
         <v>1</v>
       </c>
       <c r="K158" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
       <c r="L158" s="10" t="s">
@@ -9796,31 +10103,31 @@
         <v>157</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="F159" s="13" t="s">
         <v>111</v>
       </c>
       <c r="G159" s="11" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="I159" s="11" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="J159" s="10">
         <v>2</v>
       </c>
       <c r="K159" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
       <c r="L159" s="10" t="s">
@@ -9841,6 +10148,51 @@
     <hyperlink ref="L6" r:id="rId4" display="Digikey"/>
     <hyperlink ref="L7" r:id="rId5" display="Digikey"/>
     <hyperlink ref="L8" r:id="rId6" display="Digikey"/>
+    <hyperlink ref="L9" r:id="rId7" display="Digikey"/>
+    <hyperlink ref="L10" r:id="rId8" display="Digikey"/>
+    <hyperlink ref="L11" r:id="rId9" display="Digikey"/>
+    <hyperlink ref="L12" r:id="rId10" display="Digikey"/>
+    <hyperlink ref="L13" r:id="rId11" display="Digikey"/>
+    <hyperlink ref="L14" r:id="rId12" display="Digikey"/>
+    <hyperlink ref="L15" r:id="rId13" display="Digikey"/>
+    <hyperlink ref="L16" r:id="rId14" display="Digikey"/>
+    <hyperlink ref="L17" r:id="rId15" display="Digikey"/>
+    <hyperlink ref="L18" r:id="rId16" display="Digikey"/>
+    <hyperlink ref="L19" r:id="rId17" display="Digikey"/>
+    <hyperlink ref="L20" r:id="rId18" display="Digikey"/>
+    <hyperlink ref="L21" r:id="rId19" display="Digikey"/>
+    <hyperlink ref="L22" r:id="rId20" display="Digikey"/>
+    <hyperlink ref="L23" r:id="rId21" display="Digikey"/>
+    <hyperlink ref="L24" r:id="rId22" display="Digikey"/>
+    <hyperlink ref="L26" r:id="rId23" display="Digikey"/>
+    <hyperlink ref="L27" r:id="rId24" display="Digikey"/>
+    <hyperlink ref="L28" r:id="rId12" display="Digikey"/>
+    <hyperlink ref="L29" r:id="rId25" display="Digikey"/>
+    <hyperlink ref="L30" r:id="rId26" display="Digikey"/>
+    <hyperlink ref="L31" r:id="rId27" display="Digikey"/>
+    <hyperlink ref="L32" r:id="rId28" display="Digikey"/>
+    <hyperlink ref="L33" r:id="rId29" display="Digikey"/>
+    <hyperlink ref="L36" r:id="rId30" display="Digikey"/>
+    <hyperlink ref="L37" r:id="rId31" display="Digikey"/>
+    <hyperlink ref="L38" r:id="rId32" display="Digikey"/>
+    <hyperlink ref="L42" r:id="rId33" display="Digikey"/>
+    <hyperlink ref="L43" r:id="rId34" display="Digikey"/>
+    <hyperlink ref="L45" r:id="rId35" display="Digikey"/>
+    <hyperlink ref="L46" r:id="rId36" display="Digikey"/>
+    <hyperlink ref="L47" r:id="rId37" display="Digikey"/>
+    <hyperlink ref="L50" r:id="rId38" display="Digikey"/>
+    <hyperlink ref="L60" r:id="rId39" display="Digikey"/>
+    <hyperlink ref="L61" r:id="rId40" display="Digikey"/>
+    <hyperlink ref="L67" r:id="rId41" display="Digikey"/>
+    <hyperlink ref="L70" r:id="rId42" display="Digikey"/>
+    <hyperlink ref="L72" r:id="rId43" display="Digikey"/>
+    <hyperlink ref="L73" r:id="rId44" display="Digikey"/>
+    <hyperlink ref="L78" r:id="rId45" display="Digikey"/>
+    <hyperlink ref="L79" r:id="rId46" display="Digikey"/>
+    <hyperlink ref="L80" r:id="rId47" display="Digikey"/>
+    <hyperlink ref="L82" r:id="rId48" display="Digikey"/>
+    <hyperlink ref="L84" r:id="rId49" display="Digikey"/>
+    <hyperlink ref="L86" r:id="rId50" display="Digikey"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="725">
   <si>
     <t>#</t>
   </si>
@@ -2076,19 +2081,143 @@
   </si>
   <si>
     <t>25MHz</t>
+  </si>
+  <si>
+    <t>U26</t>
+  </si>
+  <si>
+    <t>IC REG LDO ADJ 3A TO263-5</t>
+  </si>
+  <si>
+    <t>TO-263-5 (D2PAK)</t>
+  </si>
+  <si>
+    <t>MIC29302WU-TR</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsolete Part </t>
+  </si>
+  <si>
+    <t>1.18000</t>
+  </si>
+  <si>
+    <t>1.51000</t>
+  </si>
+  <si>
+    <t>1.79000</t>
+  </si>
+  <si>
+    <t>2.52540</t>
+  </si>
+  <si>
+    <t>5.57000</t>
+  </si>
+  <si>
+    <t>18.03000</t>
+  </si>
+  <si>
+    <t>1.06000</t>
+  </si>
+  <si>
+    <t>4.44000</t>
+  </si>
+  <si>
+    <t>0.78000</t>
+  </si>
+  <si>
+    <t>0.56000</t>
+  </si>
+  <si>
+    <t>2.89000</t>
+  </si>
+  <si>
+    <t>1.35000</t>
+  </si>
+  <si>
+    <t>2.13000</t>
+  </si>
+  <si>
+    <t>0.15685</t>
+  </si>
+  <si>
+    <t>0.36000</t>
+  </si>
+  <si>
+    <t>0.94000</t>
+  </si>
+  <si>
+    <t>0.28785</t>
+  </si>
+  <si>
+    <t>0.80600</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMA Antenna </t>
+  </si>
+  <si>
+    <t>UFL Antenna</t>
+  </si>
+  <si>
+    <t>Adaptor</t>
+  </si>
+  <si>
+    <t>Compute Module</t>
+  </si>
+  <si>
+    <t>TWN4 MultiTech 3 M</t>
+  </si>
+  <si>
+    <t>ELATEC</t>
+  </si>
+  <si>
+    <t>BA-T500IIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epson </t>
+  </si>
+  <si>
+    <t>Epson</t>
+  </si>
+  <si>
+    <t>AmaZon</t>
+  </si>
+  <si>
+    <t>Xenon 1900g</t>
+  </si>
+  <si>
+    <t>Honeywell</t>
+  </si>
+  <si>
+    <t>Honeywell 1900G-HD (High Density) 2D Barcode Scanner with USB Cable</t>
+  </si>
+  <si>
+    <t>Epson BA-T500IIS: M-T500II Series, 24V</t>
+  </si>
+  <si>
+    <t>Total Component Price</t>
+  </si>
+  <si>
+    <t>Single Component Price</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2101,21 +2230,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2123,20 +2252,20 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2144,7 +2273,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2152,7 +2281,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2160,7 +2289,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2168,7 +2297,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2176,100 +2305,7 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2277,46 +2313,37 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <strike/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2337,192 +2364,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2614,252 +2467,78 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="medium">
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="medium">
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2897,16 +2576,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2931,68 +2604,111 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3250,32 +2966,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O159"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.57142857142857" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.7142857142857" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="33.3809523809524" customWidth="1"/>
-    <col min="8" max="8" width="14.7333333333333" customWidth="1"/>
-    <col min="9" max="9" width="8.56190476190476" customWidth="1"/>
-    <col min="10" max="10" width="7.20952380952381" customWidth="1"/>
-    <col min="11" max="11" width="9.17142857142857" customWidth="1"/>
-    <col min="12" max="12" width="16.7142857142857" customWidth="1"/>
-    <col min="13" max="13" width="22.8571428571429" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="29.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:15">
+    <row r="1" spans="1:15">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3284,15 +3001,15 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-    </row>
-    <row r="2" ht="15.75" spans="1:15">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3"/>
       <c r="B2" s="6" t="s">
         <v>0</v>
@@ -3337,7 +3054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="132.75" spans="1:15">
+    <row r="3" spans="1:15" ht="132">
       <c r="A3" s="3"/>
       <c r="B3" s="8">
         <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
@@ -3371,19 +3088,19 @@
         <f>3*J3</f>
         <v>291</v>
       </c>
-      <c r="L3" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0.0107</v>
-      </c>
-      <c r="N3" s="10">
+      <c r="L3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="26">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="N3" s="26">
         <f>M3*K3</f>
-        <v>3.1137</v>
+        <v>3.1137000000000001</v>
       </c>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" ht="15.75" spans="1:15">
+    <row r="4" spans="1:15">
       <c r="A4" s="3"/>
       <c r="B4" s="8">
         <f t="shared" si="0"/>
@@ -3417,19 +3134,19 @@
         <f t="shared" ref="K4:K67" si="1">3*J4</f>
         <v>6</v>
       </c>
-      <c r="L4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="13">
+      <c r="L4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="26">
         <v>0.1</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="26">
         <f t="shared" ref="N4:N15" si="2">M4*K4</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" ht="15.75" spans="1:15">
+    <row r="5" spans="1:15">
       <c r="A5" s="3"/>
       <c r="B5" s="8">
         <f t="shared" si="0"/>
@@ -3463,19 +3180,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="10">
-        <v>0.209</v>
-      </c>
-      <c r="N5" s="10">
+      <c r="L5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="26">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="N5" s="26">
         <f t="shared" si="2"/>
-        <v>4.389</v>
+        <v>4.3890000000000002</v>
       </c>
       <c r="O5" s="10"/>
     </row>
-    <row r="6" ht="15.75" spans="1:15">
+    <row r="6" spans="1:15">
       <c r="A6" s="3"/>
       <c r="B6" s="8">
         <f t="shared" si="0"/>
@@ -3509,19 +3226,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0.145</v>
-      </c>
-      <c r="N6" s="10">
+      <c r="L6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="26">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="N6" s="26">
         <f t="shared" si="2"/>
-        <v>1.74</v>
+        <v>1.7399999999999998</v>
       </c>
       <c r="O6" s="13"/>
     </row>
-    <row r="7" ht="15.75" spans="1:15">
+    <row r="7" spans="1:15">
       <c r="A7" s="3"/>
       <c r="B7" s="8">
         <f t="shared" si="0"/>
@@ -3555,19 +3272,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L7" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0.456</v>
-      </c>
-      <c r="N7" s="10">
+      <c r="L7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="26">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="N7" s="26">
         <f t="shared" si="2"/>
-        <v>5.472</v>
+        <v>5.4720000000000004</v>
       </c>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" ht="15.75" spans="1:15">
+    <row r="8" spans="1:15">
       <c r="A8" s="3"/>
       <c r="B8" s="8">
         <f t="shared" si="0"/>
@@ -3601,19 +3318,19 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="13">
-        <v>0.28</v>
-      </c>
-      <c r="N8" s="10">
+      <c r="L8" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="26">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N8" s="26">
         <f t="shared" si="2"/>
-        <v>2.52</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="O8" s="13"/>
     </row>
-    <row r="9" ht="15.75" spans="1:15">
+    <row r="9" spans="1:15">
       <c r="A9" s="3"/>
       <c r="B9" s="8">
         <f t="shared" si="0"/>
@@ -3647,19 +3364,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="10">
-        <v>0.173</v>
-      </c>
-      <c r="N9" s="10">
+      <c r="L9" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="26">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="N9" s="26">
         <f t="shared" si="2"/>
-        <v>2.076</v>
+        <v>2.0759999999999996</v>
       </c>
       <c r="O9" s="10"/>
     </row>
-    <row r="10" ht="24.75" spans="1:15">
+    <row r="10" spans="1:15" ht="24">
       <c r="A10" s="3"/>
       <c r="B10" s="8">
         <f t="shared" si="0"/>
@@ -3693,19 +3410,19 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="L10" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0.056</v>
-      </c>
-      <c r="N10" s="10">
+      <c r="L10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="26">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="N10" s="26">
         <f t="shared" si="2"/>
-        <v>2.184</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="O10" s="13"/>
     </row>
-    <row r="11" ht="15.75" spans="1:15">
+    <row r="11" spans="1:15">
       <c r="A11" s="3"/>
       <c r="B11" s="8">
         <f t="shared" si="0"/>
@@ -3739,19 +3456,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="10">
+      <c r="L11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="26">
         <v>0.224</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="26">
         <f t="shared" si="2"/>
-        <v>2.688</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="O11" s="10"/>
     </row>
-    <row r="12" ht="15.75" spans="1:15">
+    <row r="12" spans="1:15">
       <c r="A12" s="3"/>
       <c r="B12" s="8">
         <f t="shared" si="0"/>
@@ -3785,19 +3502,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="13">
+      <c r="L12" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="26">
         <v>0.753</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="26">
         <f t="shared" si="2"/>
-        <v>9.036</v>
+        <v>9.0359999999999996</v>
       </c>
       <c r="O12" s="13"/>
     </row>
-    <row r="13" ht="15.75" spans="1:15">
+    <row r="13" spans="1:15">
       <c r="A13" s="3"/>
       <c r="B13" s="8">
         <f t="shared" si="0"/>
@@ -3831,19 +3548,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="10">
+      <c r="L13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="26">
         <v>0.22</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="26">
         <f t="shared" si="2"/>
         <v>1.32</v>
       </c>
       <c r="O13" s="10"/>
     </row>
-    <row r="14" ht="15.75" spans="1:15">
+    <row r="14" spans="1:15">
       <c r="A14" s="3"/>
       <c r="B14" s="8">
         <f t="shared" si="0"/>
@@ -3877,19 +3594,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="L14" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="26">
         <v>0.1</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="26">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" ht="15.75" spans="1:15">
+    <row r="15" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="8">
         <f t="shared" si="0"/>
@@ -3923,19 +3640,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="10">
+      <c r="L15" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="26">
         <v>0.1</v>
       </c>
-      <c r="N15" s="10">
+      <c r="N15" s="26">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O15" s="10"/>
     </row>
-    <row r="16" ht="15.75" spans="1:15">
+    <row r="16" spans="1:15">
       <c r="A16" s="3"/>
       <c r="B16" s="8">
         <f t="shared" si="0"/>
@@ -3969,19 +3686,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="13">
+      <c r="L16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="26">
         <v>0.1</v>
       </c>
-      <c r="N16" s="10">
+      <c r="N16" s="26">
         <f t="shared" ref="N16:N29" si="3">M16*K16</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O16" s="13"/>
     </row>
-    <row r="17" ht="15.75" spans="1:15">
+    <row r="17" spans="1:15">
       <c r="A17" s="3"/>
       <c r="B17" s="8">
         <f t="shared" si="0"/>
@@ -4015,19 +3732,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="10">
+      <c r="L17" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="26">
         <v>2.37</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="26">
         <f t="shared" si="3"/>
         <v>7.11</v>
       </c>
       <c r="O17" s="10"/>
     </row>
-    <row r="18" ht="15.75" spans="1:15">
+    <row r="18" spans="1:15">
       <c r="A18" s="3"/>
       <c r="B18" s="8">
         <f t="shared" si="0"/>
@@ -4061,19 +3778,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="13">
+      <c r="L18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="26">
         <v>0.1</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="26">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O18" s="13"/>
     </row>
-    <row r="19" ht="15.75" spans="1:15">
+    <row r="19" spans="1:15">
       <c r="A19" s="3"/>
       <c r="B19" s="8">
         <f t="shared" si="0"/>
@@ -4107,19 +3824,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L19" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="10">
+      <c r="L19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="26">
         <v>0.1</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N19" s="26">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O19" s="10"/>
     </row>
-    <row r="20" ht="15.75" spans="1:15">
+    <row r="20" spans="1:15">
       <c r="A20" s="3"/>
       <c r="B20" s="8">
         <f t="shared" si="0"/>
@@ -4153,19 +3870,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="13">
+      <c r="L20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="26">
         <v>0.69</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="26">
         <f t="shared" si="3"/>
-        <v>4.14</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="O20" s="13"/>
     </row>
-    <row r="21" ht="15.75" spans="1:15">
+    <row r="21" spans="1:15">
       <c r="A21" s="3"/>
       <c r="B21" s="8">
         <f t="shared" si="0"/>
@@ -4199,19 +3916,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L21" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="10">
+      <c r="L21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="26">
         <v>0.1</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="26">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O21" s="10"/>
     </row>
-    <row r="22" ht="15.75" spans="1:15">
+    <row r="22" spans="1:15">
       <c r="A22" s="3"/>
       <c r="B22" s="8">
         <f t="shared" si="0"/>
@@ -4245,19 +3962,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="13">
+      <c r="L22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="26">
         <v>0.26</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="26">
         <f t="shared" si="3"/>
         <v>0.78</v>
       </c>
       <c r="O22" s="13"/>
     </row>
-    <row r="23" ht="15.75" spans="1:15">
+    <row r="23" spans="1:15">
       <c r="A23" s="3"/>
       <c r="B23" s="8">
         <f t="shared" si="0"/>
@@ -4291,19 +4008,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L23" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="10">
+      <c r="L23" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="26">
         <v>0.11</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="26">
         <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
       <c r="O23" s="10"/>
     </row>
-    <row r="24" ht="24.75" spans="1:15">
+    <row r="24" spans="1:15" ht="24">
       <c r="A24" s="3"/>
       <c r="B24" s="8">
         <f t="shared" si="0"/>
@@ -4337,19 +4054,19 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L24" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="13">
+      <c r="L24" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="26">
         <v>0.27</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="26">
         <f t="shared" si="3"/>
-        <v>8.1</v>
+        <v>8.1000000000000014</v>
       </c>
       <c r="O24" s="13"/>
     </row>
-    <row r="25" ht="36.75" spans="1:15">
+    <row r="25" spans="1:15" ht="36">
       <c r="A25" s="3"/>
       <c r="B25" s="8">
         <f t="shared" si="0"/>
@@ -4383,17 +4100,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L25" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10">
+      <c r="L25" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M25" s="26">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="N25" s="26">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1704</v>
       </c>
       <c r="O25" s="10"/>
     </row>
-    <row r="26" ht="15.75" spans="1:15">
+    <row r="26" spans="1:15">
       <c r="A26" s="3"/>
       <c r="B26" s="8">
         <f t="shared" si="0"/>
@@ -4427,19 +4146,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L26" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0.082</v>
-      </c>
-      <c r="N26" s="10">
+      <c r="L26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="26">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="N26" s="26">
         <f t="shared" si="3"/>
         <v>1.722</v>
       </c>
       <c r="O26" s="13"/>
     </row>
-    <row r="27" ht="15.75" spans="1:15">
+    <row r="27" spans="1:15">
       <c r="A27" s="3"/>
       <c r="B27" s="8">
         <f t="shared" si="0"/>
@@ -4473,19 +4192,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L27" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="10">
+      <c r="L27" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="26">
         <v>0.129</v>
       </c>
-      <c r="N27" s="10">
+      <c r="N27" s="26">
         <f t="shared" si="3"/>
         <v>1.548</v>
       </c>
       <c r="O27" s="10"/>
     </row>
-    <row r="28" ht="15.75" spans="1:15">
+    <row r="28" spans="1:15">
       <c r="A28" s="3"/>
       <c r="B28" s="8">
         <f t="shared" si="0"/>
@@ -4519,19 +4238,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L28" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="13">
-        <v>0.021</v>
-      </c>
-      <c r="N28" s="10">
+      <c r="L28" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="26">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="N28" s="26">
         <f t="shared" si="3"/>
         <v>0.441</v>
       </c>
       <c r="O28" s="13"/>
     </row>
-    <row r="29" ht="24.75" spans="1:15">
+    <row r="29" spans="1:15" ht="24">
       <c r="A29" s="3"/>
       <c r="B29" s="8">
         <f t="shared" si="0"/>
@@ -4565,19 +4284,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L29" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="10">
+      <c r="L29" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="26">
         <v>0.1</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N29" s="26">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" ht="15.75" spans="1:15">
+    <row r="30" spans="1:15">
       <c r="A30" s="3"/>
       <c r="B30" s="8">
         <f t="shared" si="0"/>
@@ -4611,19 +4330,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L30" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="13">
+      <c r="L30" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="26">
         <v>0.1</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="26">
         <f t="shared" ref="N30:N39" si="4">M30*K30</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O30" s="13"/>
     </row>
-    <row r="31" ht="15.75" spans="1:15">
+    <row r="31" spans="1:15">
       <c r="A31" s="3"/>
       <c r="B31" s="8">
         <f t="shared" si="0"/>
@@ -4657,19 +4376,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L31" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="10">
+      <c r="L31" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="26">
         <v>0.17</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N31" s="26">
         <f t="shared" si="4"/>
         <v>0.51</v>
       </c>
       <c r="O31" s="10"/>
     </row>
-    <row r="32" ht="15.75" spans="1:15">
+    <row r="32" spans="1:15">
       <c r="A32" s="3"/>
       <c r="B32" s="8">
         <f t="shared" si="0"/>
@@ -4703,19 +4422,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L32" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="13">
+      <c r="L32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="26">
         <v>0.1</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="26">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O32" s="13"/>
     </row>
-    <row r="33" ht="15.75" spans="1:15">
+    <row r="33" spans="1:15">
       <c r="A33" s="3"/>
       <c r="B33" s="8">
         <f t="shared" si="0"/>
@@ -4749,19 +4468,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L33" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="10">
+      <c r="L33" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="26">
         <v>0.1</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="26">
         <f t="shared" si="4"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O33" s="10"/>
     </row>
-    <row r="34" ht="48.75" spans="1:15">
+    <row r="34" spans="1:15" ht="48">
       <c r="A34" s="3"/>
       <c r="B34" s="8">
         <f t="shared" si="0"/>
@@ -4795,17 +4514,19 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="L34" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="10">
+      <c r="L34" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M34" s="26">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="N34" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="O34" s="13"/>
     </row>
-    <row r="35" ht="24.75" spans="1:15">
+    <row r="35" spans="1:15" ht="24">
       <c r="A35" s="3"/>
       <c r="B35" s="8">
         <f t="shared" ref="B35:B57" si="5">ROW(B35)-ROW($B$2)</f>
@@ -4839,17 +4560,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L35" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10">
+      <c r="L35" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M35" s="26">
+        <v>6.2600000000000003E-2</v>
+      </c>
+      <c r="N35" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.37560000000000004</v>
       </c>
       <c r="O35" s="10"/>
     </row>
-    <row r="36" ht="15.75" spans="1:15">
+    <row r="36" spans="1:15">
       <c r="A36" s="3"/>
       <c r="B36" s="8">
         <f t="shared" si="5"/>
@@ -4883,19 +4606,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L36" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="13">
+      <c r="L36" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="26">
         <v>0.37</v>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="26">
         <f t="shared" si="4"/>
-        <v>1.11</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="O36" s="13"/>
     </row>
-    <row r="37" ht="24.75" spans="1:15">
+    <row r="37" spans="1:15" ht="24">
       <c r="A37" s="3"/>
       <c r="B37" s="8">
         <f t="shared" si="5"/>
@@ -4929,19 +4652,19 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="L37" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="10">
-        <v>0.305</v>
-      </c>
-      <c r="N37" s="10">
+      <c r="L37" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="26">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="N37" s="26">
         <f t="shared" si="4"/>
         <v>5.49</v>
       </c>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" ht="24.75" spans="1:15">
+    <row r="38" spans="1:15" ht="24">
       <c r="A38" s="3"/>
       <c r="B38" s="8">
         <f t="shared" si="5"/>
@@ -4975,19 +4698,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L38" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="18">
+      <c r="L38" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="26">
         <v>0.21</v>
       </c>
-      <c r="N38" s="10">
+      <c r="N38" s="26">
         <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="O38" s="13"/>
     </row>
-    <row r="39" ht="36.75" spans="1:15">
+    <row r="39" spans="1:15" ht="36">
       <c r="A39" s="3"/>
       <c r="B39" s="8">
         <f t="shared" si="5"/>
@@ -5021,17 +4744,19 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="L39" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10">
+      <c r="L39" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M39" s="26">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="N39" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.2033</v>
       </c>
       <c r="O39" s="10"/>
     </row>
-    <row r="40" ht="24.75" spans="1:15">
+    <row r="40" spans="1:15" ht="24">
       <c r="A40" s="3"/>
       <c r="B40" s="8">
         <f t="shared" si="5"/>
@@ -5065,17 +4790,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L40" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="13"/>
-      <c r="N40" s="10">
+      <c r="L40" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M40" s="26">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="N40" s="26">
         <f t="shared" ref="N40:N55" si="6">M40*K40</f>
-        <v>0</v>
+        <v>0.2382</v>
       </c>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" ht="36.75" spans="1:15">
+    <row r="41" spans="1:15" ht="36">
       <c r="A41" s="3"/>
       <c r="B41" s="8">
         <f t="shared" si="5"/>
@@ -5109,17 +4836,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L41" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10">
+      <c r="L41" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M41" s="26">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="N41" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.17460000000000001</v>
       </c>
       <c r="O41" s="10"/>
     </row>
-    <row r="42" ht="15.75" spans="1:15">
+    <row r="42" spans="1:15">
       <c r="A42" s="3"/>
       <c r="B42" s="8">
         <f t="shared" si="5"/>
@@ -5153,19 +4882,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L42" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="13">
+      <c r="L42" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="26">
         <v>0.34</v>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="26">
         <f t="shared" si="6"/>
         <v>2.04</v>
       </c>
       <c r="O42" s="13"/>
     </row>
-    <row r="43" ht="15.75" spans="1:15">
+    <row r="43" spans="1:15">
       <c r="A43" s="3"/>
       <c r="B43" s="8">
         <f t="shared" si="5"/>
@@ -5199,19 +4928,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L43" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="10">
+      <c r="L43" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="26">
         <v>1.66</v>
       </c>
-      <c r="N43" s="10">
+      <c r="N43" s="26">
         <f t="shared" si="6"/>
-        <v>4.98</v>
+        <v>4.9799999999999995</v>
       </c>
       <c r="O43" s="10"/>
     </row>
-    <row r="44" ht="24.75" spans="1:15">
+    <row r="44" spans="1:15" ht="24">
       <c r="A44" s="3"/>
       <c r="B44" s="8">
         <f t="shared" si="5"/>
@@ -5245,17 +4974,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L44" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="13"/>
-      <c r="N44" s="10">
+      <c r="L44" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M44" s="26">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N44" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1182</v>
       </c>
       <c r="O44" s="13"/>
     </row>
-    <row r="45" ht="15.75" spans="1:15">
+    <row r="45" spans="1:15">
       <c r="A45" s="3"/>
       <c r="B45" s="8">
         <f t="shared" si="5"/>
@@ -5289,19 +5020,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L45" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="10">
+      <c r="L45" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="26">
         <v>0.12</v>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="26">
         <f t="shared" si="6"/>
         <v>0.36</v>
       </c>
       <c r="O45" s="10"/>
     </row>
-    <row r="46" ht="15.75" spans="1:15">
+    <row r="46" spans="1:15">
       <c r="A46" s="3"/>
       <c r="B46" s="8">
         <f t="shared" si="5"/>
@@ -5335,19 +5066,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L46" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="13">
+      <c r="L46" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="26">
         <v>0.1</v>
       </c>
-      <c r="N46" s="10">
+      <c r="N46" s="26">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O46" s="13"/>
     </row>
-    <row r="47" ht="15.75" spans="1:15">
+    <row r="47" spans="1:15">
       <c r="A47" s="3"/>
       <c r="B47" s="8">
         <f t="shared" si="5"/>
@@ -5381,19 +5112,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L47" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="10">
+      <c r="L47" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="26">
         <v>0.32</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="26">
         <f t="shared" si="6"/>
         <v>1.92</v>
       </c>
       <c r="O47" s="10"/>
     </row>
-    <row r="48" ht="36.75" spans="1:15">
+    <row r="48" spans="1:15" ht="36">
       <c r="A48" s="3"/>
       <c r="B48" s="8">
         <f t="shared" si="5"/>
@@ -5427,17 +5158,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L48" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10">
+      <c r="L48" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M48" s="26">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="N48" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.2223</v>
       </c>
       <c r="O48" s="10"/>
     </row>
-    <row r="49" ht="24.75" spans="1:15">
+    <row r="49" spans="1:15" ht="24">
       <c r="A49" s="3"/>
       <c r="B49" s="8">
         <f t="shared" si="5"/>
@@ -5471,17 +5204,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L49" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" s="13"/>
-      <c r="N49" s="10">
+      <c r="L49" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M49" s="26">
+        <v>4.2946</v>
+      </c>
+      <c r="N49" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>12.883800000000001</v>
       </c>
       <c r="O49" s="13"/>
     </row>
-    <row r="50" ht="24.75" spans="1:15">
+    <row r="50" spans="1:15" ht="24">
       <c r="A50" s="3"/>
       <c r="B50" s="8">
         <f t="shared" si="5"/>
@@ -5515,19 +5250,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L50" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="10">
+      <c r="L50" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="26">
         <v>1.26</v>
       </c>
-      <c r="N50" s="10">
+      <c r="N50" s="26">
         <f t="shared" si="6"/>
-        <v>3.78</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="O50" s="10"/>
     </row>
-    <row r="51" ht="36.75" spans="1:15">
+    <row r="51" spans="1:15" ht="36">
       <c r="A51" s="3"/>
       <c r="B51" s="8">
         <f t="shared" si="5"/>
@@ -5561,17 +5296,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L51" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="10">
+      <c r="L51" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M51" s="26">
+        <v>1.52E-2</v>
+      </c>
+      <c r="N51" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="O51" s="13"/>
     </row>
-    <row r="52" ht="36.75" spans="1:15">
+    <row r="52" spans="1:15" ht="36">
       <c r="A52" s="3"/>
       <c r="B52" s="8">
         <f t="shared" si="5"/>
@@ -5605,17 +5342,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L52" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10">
+      <c r="L52" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M52" s="26">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="N52" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="O52" s="10"/>
     </row>
-    <row r="53" ht="36.75" spans="1:15">
+    <row r="53" spans="1:15" ht="48">
       <c r="A53" s="3"/>
       <c r="B53" s="8">
         <f t="shared" si="5"/>
@@ -5649,17 +5388,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L53" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="13"/>
-      <c r="N53" s="10">
+      <c r="L53" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M53" s="26">
+        <v>0.1726</v>
+      </c>
+      <c r="N53" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.51780000000000004</v>
       </c>
       <c r="O53" s="13"/>
     </row>
-    <row r="54" ht="24.75" spans="1:15">
+    <row r="54" spans="1:15" ht="24">
       <c r="A54" s="3"/>
       <c r="B54" s="8">
         <f t="shared" si="5"/>
@@ -5693,17 +5434,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L54" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10">
+      <c r="L54" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M54" s="26">
+        <v>0.70579999999999998</v>
+      </c>
+      <c r="N54" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2.1173999999999999</v>
       </c>
       <c r="O54" s="10"/>
     </row>
-    <row r="55" ht="36.75" spans="1:15">
+    <row r="55" spans="1:15" ht="48">
       <c r="A55" s="3"/>
       <c r="B55" s="8">
         <f t="shared" si="5"/>
@@ -5737,17 +5480,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L55" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="13"/>
-      <c r="N55" s="10">
+      <c r="L55" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M55" s="26">
+        <v>0.42970000000000003</v>
+      </c>
+      <c r="N55" s="26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1.2891000000000001</v>
       </c>
       <c r="O55" s="13"/>
     </row>
-    <row r="56" ht="48.75" spans="1:15">
+    <row r="56" spans="1:15" ht="48">
       <c r="A56" s="3"/>
       <c r="B56" s="8">
         <f t="shared" si="5"/>
@@ -5781,17 +5526,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L56" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10">
-        <f t="shared" ref="N56:N87" si="7">M56*K56</f>
-        <v>0</v>
+      <c r="L56" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M56" s="26">
+        <v>0.53859999999999997</v>
+      </c>
+      <c r="N56" s="26">
+        <f t="shared" ref="N56:N119" si="7">M56*K56</f>
+        <v>1.6157999999999999</v>
       </c>
       <c r="O56" s="10"/>
     </row>
-    <row r="57" ht="48.75" spans="1:15">
+    <row r="57" spans="1:15" ht="48">
       <c r="A57" s="3"/>
       <c r="B57" s="8">
         <f t="shared" si="5"/>
@@ -5825,20 +5572,22 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L57" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10">
+      <c r="L57" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M57" s="26">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N57" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O57" s="10"/>
     </row>
-    <row r="58" ht="60.75" spans="1:15">
+    <row r="58" spans="1:15" ht="60">
       <c r="A58" s="3"/>
       <c r="B58" s="8">
-        <f t="shared" ref="B58:B158" si="8">ROW(B58)-ROW($B$2)</f>
+        <f t="shared" ref="B58:B159" si="8">ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="12" t="s">
@@ -5869,17 +5618,19 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L58" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="13"/>
-      <c r="N58" s="10">
+      <c r="L58" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M58" s="26">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="N58" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.4804999999999999</v>
       </c>
       <c r="O58" s="13"/>
     </row>
-    <row r="59" ht="48.75" spans="1:15">
+    <row r="59" spans="1:15" ht="60">
       <c r="A59" s="3"/>
       <c r="B59" s="8">
         <f t="shared" si="8"/>
@@ -5913,17 +5664,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L59" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10">
+      <c r="L59" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M59" s="26">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="N59" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.56759999999999999</v>
       </c>
       <c r="O59" s="10"/>
     </row>
-    <row r="60" ht="15.75" spans="1:15">
+    <row r="60" spans="1:15">
       <c r="A60" s="3"/>
       <c r="B60" s="8">
         <f t="shared" si="8"/>
@@ -5957,19 +5710,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L60" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="13">
+      <c r="L60" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="26">
         <v>1.32</v>
       </c>
-      <c r="N60" s="10">
+      <c r="N60" s="26">
         <f t="shared" si="7"/>
         <v>3.96</v>
       </c>
       <c r="O60" s="13"/>
     </row>
-    <row r="61" ht="15.75" spans="1:15">
+    <row r="61" spans="1:15">
       <c r="A61" s="3"/>
       <c r="B61" s="8">
         <f t="shared" si="8"/>
@@ -6003,19 +5756,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L61" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="10">
+      <c r="L61" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="26">
         <v>0.46</v>
       </c>
-      <c r="N61" s="10">
+      <c r="N61" s="26">
         <f t="shared" si="7"/>
-        <v>1.38</v>
+        <v>1.3800000000000001</v>
       </c>
       <c r="O61" s="10"/>
     </row>
-    <row r="62" ht="36.75" spans="1:15">
+    <row r="62" spans="1:15" ht="36">
       <c r="A62" s="3"/>
       <c r="B62" s="8">
         <f t="shared" si="8"/>
@@ -6049,17 +5802,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L62" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="13"/>
-      <c r="N62" s="10">
+      <c r="L62" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M62" s="26">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N62" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3.9E-2</v>
       </c>
       <c r="O62" s="13"/>
     </row>
-    <row r="63" ht="60.75" spans="1:15">
+    <row r="63" spans="1:15" ht="60">
       <c r="A63" s="3"/>
       <c r="B63" s="8">
         <f t="shared" si="8"/>
@@ -6093,17 +5848,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L63" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10">
+      <c r="L63" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M63" s="26">
+        <v>2.5537999999999998</v>
+      </c>
+      <c r="N63" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>15.322799999999999</v>
       </c>
       <c r="O63" s="10"/>
     </row>
-    <row r="64" ht="48.75" spans="1:15">
+    <row r="64" spans="1:15" ht="48">
       <c r="A64" s="3"/>
       <c r="B64" s="8">
         <f t="shared" si="8"/>
@@ -6137,17 +5894,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L64" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="13"/>
-      <c r="N64" s="10">
+      <c r="L64" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M64" s="26">
+        <v>1.52E-2</v>
+      </c>
+      <c r="N64" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="O64" s="13"/>
     </row>
-    <row r="65" ht="36.75" spans="1:15">
+    <row r="65" spans="1:15" ht="36">
       <c r="A65" s="3"/>
       <c r="B65" s="8">
         <f t="shared" si="8"/>
@@ -6181,17 +5940,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L65" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10">
+      <c r="L65" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M65" s="26">
+        <v>1.67E-2</v>
+      </c>
+      <c r="N65" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="O65" s="10"/>
     </row>
-    <row r="66" ht="24.75" spans="1:15">
+    <row r="66" spans="1:15" ht="24">
       <c r="A66" s="3"/>
       <c r="B66" s="8">
         <f t="shared" si="8"/>
@@ -6225,17 +5986,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L66" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" s="13"/>
-      <c r="N66" s="10">
+      <c r="L66" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M66" s="26">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N66" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.0170000000000001</v>
       </c>
       <c r="O66" s="13"/>
     </row>
-    <row r="67" ht="15.75" spans="1:15">
+    <row r="67" spans="1:15">
       <c r="A67" s="3"/>
       <c r="B67" s="8">
         <f t="shared" si="8"/>
@@ -6269,19 +6032,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L67" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="10">
+      <c r="L67" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="26">
         <v>2.37</v>
       </c>
-      <c r="N67" s="10">
+      <c r="N67" s="26">
         <f t="shared" si="7"/>
         <v>7.11</v>
       </c>
       <c r="O67" s="10"/>
     </row>
-    <row r="68" ht="36.75" spans="1:15">
+    <row r="68" spans="1:15" ht="36">
       <c r="A68" s="3"/>
       <c r="B68" s="8">
         <f t="shared" si="8"/>
@@ -6315,17 +6078,19 @@
         <f t="shared" ref="K68:K131" si="9">3*J68</f>
         <v>6</v>
       </c>
-      <c r="L68" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="13"/>
-      <c r="N68" s="10">
+      <c r="L68" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M68" s="26">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="N68" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="O68" s="13"/>
     </row>
-    <row r="69" ht="24.75" spans="1:15">
+    <row r="69" spans="1:15" ht="24">
       <c r="A69" s="3"/>
       <c r="B69" s="8">
         <f t="shared" si="8"/>
@@ -6359,17 +6124,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L69" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10">
+      <c r="L69" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M69" s="26">
+        <v>0.49419999999999997</v>
+      </c>
+      <c r="N69" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.4825999999999999</v>
       </c>
       <c r="O69" s="10"/>
     </row>
-    <row r="70" ht="15.75" spans="1:15">
+    <row r="70" spans="1:15">
       <c r="A70" s="3"/>
       <c r="B70" s="8">
         <f t="shared" si="8"/>
@@ -6403,63 +6170,67 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L70" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="13">
+      <c r="L70" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="26">
         <v>4.49</v>
       </c>
-      <c r="N70" s="10">
+      <c r="N70" s="26">
         <f t="shared" si="7"/>
-        <v>67.35</v>
+        <v>67.350000000000009</v>
       </c>
       <c r="O70" s="13"/>
     </row>
-    <row r="71" ht="15.75" spans="1:15">
+    <row r="71" spans="1:15" ht="15.75">
       <c r="A71" s="3"/>
       <c r="B71" s="8">
         <f t="shared" si="8"/>
         <v>69</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="48" t="s">
         <v>309</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="49" t="s">
         <v>312</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I71" s="14" t="s">
+      <c r="I71" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="J71" s="10">
+      <c r="J71" s="44">
         <v>4</v>
       </c>
-      <c r="K71" s="10">
+      <c r="K71" s="44">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L71" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10">
+      <c r="L71" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="45">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N71" s="45">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O71" s="10"/>
-    </row>
-    <row r="72" ht="15.75" spans="1:15">
+        <v>6.9599999999999991</v>
+      </c>
+      <c r="O71" s="47" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="3"/>
       <c r="B72" s="8">
         <f t="shared" si="8"/>
@@ -6493,19 +6264,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L72" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="13">
+      <c r="L72" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="26">
         <v>0.39</v>
       </c>
-      <c r="N72" s="10">
+      <c r="N72" s="26">
         <f t="shared" si="7"/>
         <v>1.17</v>
       </c>
       <c r="O72" s="13"/>
     </row>
-    <row r="73" ht="15.75" spans="1:15">
+    <row r="73" spans="1:15">
       <c r="A73" s="3"/>
       <c r="B73" s="8">
         <f t="shared" si="8"/>
@@ -6539,19 +6310,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L73" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="10">
+      <c r="L73" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="26">
         <v>0.2</v>
       </c>
-      <c r="N73" s="10">
+      <c r="N73" s="26">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="O73" s="10"/>
     </row>
-    <row r="74" ht="24.75" spans="1:15">
+    <row r="74" spans="1:15" ht="24">
       <c r="A74" s="3"/>
       <c r="B74" s="8">
         <f t="shared" si="8"/>
@@ -6585,17 +6356,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L74" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="13"/>
-      <c r="N74" s="10">
+      <c r="L74" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M74" s="26">
+        <v>0.79559999999999997</v>
+      </c>
+      <c r="N74" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4.7736000000000001</v>
       </c>
       <c r="O74" s="13"/>
     </row>
-    <row r="75" ht="36.75" spans="1:15">
+    <row r="75" spans="1:15" ht="36">
       <c r="A75" s="3"/>
       <c r="B75" s="8">
         <f t="shared" si="8"/>
@@ -6629,17 +6402,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L75" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" s="10"/>
-      <c r="N75" s="10">
+      <c r="L75" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M75" s="26">
+        <v>2.18E-2</v>
+      </c>
+      <c r="N75" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.54E-2</v>
       </c>
       <c r="O75" s="10"/>
     </row>
-    <row r="76" ht="36.75" spans="1:15">
+    <row r="76" spans="1:15" ht="36">
       <c r="A76" s="3"/>
       <c r="B76" s="8">
         <f t="shared" si="8"/>
@@ -6673,17 +6448,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L76" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" s="13"/>
-      <c r="N76" s="10">
+      <c r="L76" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M76" s="26">
+        <v>2.18E-2</v>
+      </c>
+      <c r="N76" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1308</v>
       </c>
       <c r="O76" s="13"/>
     </row>
-    <row r="77" ht="36.75" spans="1:15">
+    <row r="77" spans="1:15" ht="36">
       <c r="A77" s="3"/>
       <c r="B77" s="8">
         <f t="shared" si="8"/>
@@ -6717,17 +6494,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L77" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="10"/>
-      <c r="N77" s="10">
+      <c r="L77" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M77" s="26">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="N77" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="O77" s="10"/>
     </row>
-    <row r="78" ht="15.75" spans="1:15">
+    <row r="78" spans="1:15">
       <c r="A78" s="3"/>
       <c r="B78" s="8">
         <f t="shared" si="8"/>
@@ -6761,19 +6540,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L78" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="13">
+      <c r="L78" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="26">
         <v>0.35</v>
       </c>
-      <c r="N78" s="10">
+      <c r="N78" s="26">
         <f t="shared" si="7"/>
-        <v>1.05</v>
+        <v>1.0499999999999998</v>
       </c>
       <c r="O78" s="13"/>
     </row>
-    <row r="79" ht="15.75" spans="1:15">
+    <row r="79" spans="1:15">
       <c r="A79" s="3"/>
       <c r="B79" s="8">
         <f t="shared" si="8"/>
@@ -6807,19 +6586,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L79" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="10">
+      <c r="L79" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="26">
         <v>0.3</v>
       </c>
-      <c r="N79" s="10">
+      <c r="N79" s="26">
         <f t="shared" si="7"/>
-        <v>0.9</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="O79" s="10"/>
     </row>
-    <row r="80" ht="15.75" spans="1:15">
+    <row r="80" spans="1:15">
       <c r="A80" s="3"/>
       <c r="B80" s="8">
         <f t="shared" si="8"/>
@@ -6853,19 +6632,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L80" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="13">
+      <c r="L80" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="26">
         <v>0.51</v>
       </c>
-      <c r="N80" s="10">
+      <c r="N80" s="26">
         <f t="shared" si="7"/>
         <v>1.53</v>
       </c>
       <c r="O80" s="13"/>
     </row>
-    <row r="81" ht="24.75" spans="1:15">
+    <row r="81" spans="1:15" ht="24">
       <c r="A81" s="3"/>
       <c r="B81" s="8">
         <f t="shared" si="8"/>
@@ -6899,17 +6678,19 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="L81" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="10"/>
-      <c r="N81" s="10">
+      <c r="L81" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M81" s="26">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="N81" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.5624</v>
       </c>
       <c r="O81" s="10"/>
     </row>
-    <row r="82" ht="36.75" spans="1:15">
+    <row r="82" spans="1:15" ht="36">
       <c r="A82" s="3"/>
       <c r="B82" s="8">
         <f t="shared" si="8"/>
@@ -6943,13 +6724,13 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L82" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="13">
+      <c r="L82" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="26">
         <v>0.53</v>
       </c>
-      <c r="N82" s="10">
+      <c r="N82" s="26">
         <f t="shared" si="7"/>
         <v>1.59</v>
       </c>
@@ -6989,17 +6770,19 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L83" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="10"/>
-      <c r="N83" s="10">
+      <c r="L83" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M83" s="26">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="N83" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.54480000000000006</v>
       </c>
       <c r="O83" s="10"/>
     </row>
-    <row r="84" ht="24.75" spans="1:15">
+    <row r="84" spans="1:15" ht="24">
       <c r="A84" s="3"/>
       <c r="B84" s="8">
         <f t="shared" si="8"/>
@@ -7033,19 +6816,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L84" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="13">
-        <v>0.29</v>
-      </c>
-      <c r="N84" s="10">
+      <c r="L84" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="26">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N84" s="26">
         <f t="shared" si="7"/>
-        <v>1.74</v>
+        <v>1.7399999999999998</v>
       </c>
       <c r="O84" s="13"/>
     </row>
-    <row r="85" ht="24.75" spans="1:15">
+    <row r="85" spans="1:15" ht="24">
       <c r="A85" s="3"/>
       <c r="B85" s="8">
         <f t="shared" si="8"/>
@@ -7079,17 +6862,19 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L85" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="10"/>
-      <c r="N85" s="10">
+      <c r="L85" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="26">
+        <v>0.41</v>
+      </c>
+      <c r="N85" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.1499999999999995</v>
       </c>
       <c r="O85" s="10"/>
     </row>
-    <row r="86" ht="24.75" spans="1:15">
+    <row r="86" spans="1:15" ht="24">
       <c r="A86" s="3"/>
       <c r="B86" s="8">
         <f t="shared" si="8"/>
@@ -7123,19 +6908,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L86" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="13">
+      <c r="L86" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="26">
         <v>0.44</v>
       </c>
-      <c r="N86" s="10">
+      <c r="N86" s="26">
         <f t="shared" si="7"/>
         <v>1.32</v>
       </c>
       <c r="O86" s="13"/>
     </row>
-    <row r="87" ht="15.75" spans="1:15">
+    <row r="87" spans="1:15">
       <c r="A87" s="3"/>
       <c r="B87" s="8">
         <f t="shared" si="8"/>
@@ -7169,17 +6954,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L87" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="10"/>
-      <c r="N87" s="10">
+      <c r="L87" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="26">
+        <v>0.25</v>
+      </c>
+      <c r="N87" s="26">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O87" s="10"/>
     </row>
-    <row r="88" ht="48.75" spans="1:15">
+    <row r="88" spans="1:15" ht="48">
       <c r="A88" s="3"/>
       <c r="B88" s="8">
         <f t="shared" si="8"/>
@@ -7213,14 +7000,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L88" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="13"/>
-      <c r="N88" s="13"/>
+      <c r="L88" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M88" s="26">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N88" s="26">
+        <f t="shared" si="7"/>
+        <v>8.4000000000000005E-2</v>
+      </c>
       <c r="O88" s="13"/>
     </row>
-    <row r="89" ht="60.75" spans="1:15">
+    <row r="89" spans="1:15" ht="60">
       <c r="A89" s="3"/>
       <c r="B89" s="8">
         <f t="shared" si="8"/>
@@ -7254,14 +7046,19 @@
         <f t="shared" si="9"/>
         <v>120</v>
       </c>
-      <c r="L89" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="10"/>
-      <c r="N89" s="10"/>
+      <c r="L89" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="26">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="N89" s="26">
+        <f t="shared" si="7"/>
+        <v>0.876</v>
+      </c>
       <c r="O89" s="10"/>
     </row>
-    <row r="90" ht="15.75" spans="1:15">
+    <row r="90" spans="1:15">
       <c r="A90" s="3"/>
       <c r="B90" s="8">
         <f t="shared" si="8"/>
@@ -7295,14 +7092,19 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="L90" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="13"/>
-      <c r="N90" s="13"/>
+      <c r="L90" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N90" s="26">
+        <f t="shared" si="7"/>
+        <v>0.27</v>
+      </c>
       <c r="O90" s="13"/>
     </row>
-    <row r="91" ht="15.75" spans="1:15">
+    <row r="91" spans="1:15">
       <c r="A91" s="3"/>
       <c r="B91" s="8">
         <f t="shared" si="8"/>
@@ -7336,14 +7138,19 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="L91" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M91" s="10"/>
-      <c r="N91" s="10"/>
+      <c r="L91" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" s="26">
+        <v>2.4E-2</v>
+      </c>
+      <c r="N91" s="26">
+        <f t="shared" si="7"/>
+        <v>0.504</v>
+      </c>
       <c r="O91" s="10"/>
     </row>
-    <row r="92" ht="72.75" spans="1:15">
+    <row r="92" spans="1:15" ht="84">
       <c r="A92" s="3"/>
       <c r="B92" s="8">
         <f t="shared" si="8"/>
@@ -7377,14 +7184,19 @@
         <f t="shared" si="9"/>
         <v>147</v>
       </c>
-      <c r="L92" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="13"/>
-      <c r="N92" s="13"/>
+      <c r="L92" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="26">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="N92" s="26">
+        <f t="shared" si="7"/>
+        <v>1.0730999999999999</v>
+      </c>
       <c r="O92" s="13"/>
     </row>
-    <row r="93" ht="15.75" spans="1:15">
+    <row r="93" spans="1:15">
       <c r="A93" s="3"/>
       <c r="B93" s="8">
         <f t="shared" si="8"/>
@@ -7418,57 +7230,66 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="L93" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="10"/>
-      <c r="N93" s="10"/>
+      <c r="L93" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N93" s="26">
+        <f t="shared" si="7"/>
+        <v>0.315</v>
+      </c>
       <c r="O93" s="10"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A94" s="19"/>
-      <c r="B94" s="20">
+    <row r="94" spans="1:15" s="1" customFormat="1">
+      <c r="A94" s="17"/>
+      <c r="B94" s="18">
         <f t="shared" si="8"/>
         <v>92</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="D94" s="22" t="s">
+      <c r="D94" s="20" t="s">
         <v>412</v>
       </c>
-      <c r="E94" s="23" t="s">
+      <c r="E94" s="21" t="s">
         <v>413</v>
       </c>
-      <c r="F94" s="22" t="s">
+      <c r="F94" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="G94" s="23" t="s">
+      <c r="G94" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="H94" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I94" s="23" t="s">
+      <c r="I94" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="J94" s="22">
+      <c r="J94" s="20">
         <v>2</v>
       </c>
-      <c r="K94" s="10">
+      <c r="K94" s="23">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L94" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="22"/>
-      <c r="N94" s="22"/>
-      <c r="O94" s="25" t="s">
+      <c r="L94" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N94" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="O94" s="27" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:15">
+    <row r="95" spans="1:15">
       <c r="A95" s="3"/>
       <c r="B95" s="8">
         <f t="shared" si="8"/>
@@ -7502,14 +7323,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L95" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="10"/>
-      <c r="N95" s="10"/>
+      <c r="L95" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N95" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O95" s="10"/>
     </row>
-    <row r="96" ht="48.75" spans="1:15">
+    <row r="96" spans="1:15" ht="48">
       <c r="A96" s="3"/>
       <c r="B96" s="8">
         <f t="shared" si="8"/>
@@ -7543,14 +7369,19 @@
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="L96" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="13"/>
-      <c r="N96" s="13"/>
+      <c r="L96" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="26">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="N96" s="26">
+        <f t="shared" si="7"/>
+        <v>0.68640000000000001</v>
+      </c>
       <c r="O96" s="13"/>
     </row>
-    <row r="97" ht="15.75" spans="1:15">
+    <row r="97" spans="1:15">
       <c r="A97" s="3"/>
       <c r="B97" s="8">
         <f t="shared" si="8"/>
@@ -7584,14 +7415,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L97" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="10"/>
-      <c r="N97" s="10"/>
+      <c r="L97" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="26">
+        <v>0.13463</v>
+      </c>
+      <c r="N97" s="26">
+        <f t="shared" si="7"/>
+        <v>0.40388999999999997</v>
+      </c>
       <c r="O97" s="10"/>
     </row>
-    <row r="98" ht="36.75" spans="1:15">
+    <row r="98" spans="1:15" ht="48">
       <c r="A98" s="3"/>
       <c r="B98" s="8">
         <f t="shared" si="8"/>
@@ -7625,14 +7461,19 @@
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
-      <c r="L98" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="13"/>
-      <c r="N98" s="13"/>
+      <c r="L98" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="26">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="N98" s="26">
+        <f t="shared" si="7"/>
+        <v>0.51839999999999997</v>
+      </c>
       <c r="O98" s="13"/>
     </row>
-    <row r="99" ht="15.75" spans="1:15">
+    <row r="99" spans="1:15">
       <c r="A99" s="3"/>
       <c r="B99" s="8">
         <f t="shared" si="8"/>
@@ -7666,14 +7507,19 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L99" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="10"/>
-      <c r="N99" s="10"/>
+      <c r="L99" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="26">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="N99" s="26">
+        <f t="shared" si="7"/>
+        <v>1.4040000000000001</v>
+      </c>
       <c r="O99" s="10"/>
     </row>
-    <row r="100" ht="15.75" spans="1:15">
+    <row r="100" spans="1:15">
       <c r="A100" s="3"/>
       <c r="B100" s="8">
         <f t="shared" si="8"/>
@@ -7707,14 +7553,19 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L100" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="13"/>
-      <c r="N100" s="13"/>
+      <c r="L100" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N100" s="26">
+        <f t="shared" si="7"/>
+        <v>0.18</v>
+      </c>
       <c r="O100" s="13"/>
     </row>
-    <row r="101" ht="15.75" spans="1:15">
+    <row r="101" spans="1:15">
       <c r="A101" s="3"/>
       <c r="B101" s="8">
         <f t="shared" si="8"/>
@@ -7748,14 +7599,19 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L101" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
+      <c r="L101" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="26">
+        <v>2.7E-2</v>
+      </c>
+      <c r="N101" s="26">
+        <f t="shared" si="7"/>
+        <v>0.32400000000000001</v>
+      </c>
       <c r="O101" s="10"/>
     </row>
-    <row r="102" ht="15.75" spans="1:15">
+    <row r="102" spans="1:15">
       <c r="A102" s="3"/>
       <c r="B102" s="8">
         <f t="shared" si="8"/>
@@ -7789,14 +7645,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L102" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="13"/>
-      <c r="N102" s="13"/>
+      <c r="L102" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="26">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N102" s="26">
+        <f t="shared" si="7"/>
+        <v>5.6999999999999995E-2</v>
+      </c>
       <c r="O102" s="13"/>
     </row>
-    <row r="103" ht="15.75" spans="1:15">
+    <row r="103" spans="1:15">
       <c r="A103" s="3"/>
       <c r="B103" s="8">
         <f t="shared" si="8"/>
@@ -7830,14 +7691,19 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L103" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="10"/>
-      <c r="N103" s="10"/>
+      <c r="L103" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N103" s="26">
+        <f t="shared" si="7"/>
+        <v>0.22499999999999998</v>
+      </c>
       <c r="O103" s="10"/>
     </row>
-    <row r="104" ht="15.75" spans="1:15">
+    <row r="104" spans="1:15">
       <c r="A104" s="3"/>
       <c r="B104" s="8">
         <f t="shared" si="8"/>
@@ -7871,14 +7737,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L104" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="13"/>
-      <c r="N104" s="13"/>
+      <c r="L104" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N104" s="26">
+        <f t="shared" si="7"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O104" s="13"/>
     </row>
-    <row r="105" ht="15.75" spans="1:15">
+    <row r="105" spans="1:15">
       <c r="A105" s="3"/>
       <c r="B105" s="8">
         <f t="shared" si="8"/>
@@ -7912,14 +7783,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L105" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="10"/>
-      <c r="N105" s="10"/>
+      <c r="L105" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N105" s="26">
+        <f t="shared" si="7"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O105" s="10"/>
     </row>
-    <row r="106" ht="15.75" spans="1:15">
+    <row r="106" spans="1:15">
       <c r="A106" s="3"/>
       <c r="B106" s="8">
         <f t="shared" si="8"/>
@@ -7953,57 +7829,66 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L106" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="13"/>
-      <c r="N106" s="13"/>
+      <c r="L106" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N106" s="26">
+        <f t="shared" si="7"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O106" s="13"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A107" s="19"/>
+    <row r="107" spans="1:15" s="1" customFormat="1">
+      <c r="A107" s="17"/>
       <c r="B107" s="8">
         <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="C107" s="24" t="s">
+      <c r="C107" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="D107" s="25" t="s">
+      <c r="D107" s="23" t="s">
         <v>465</v>
       </c>
-      <c r="E107" s="26" t="s">
+      <c r="E107" s="24" t="s">
         <v>397</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F107" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="G107" s="26" t="s">
+      <c r="G107" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="H107" s="25" t="s">
+      <c r="H107" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="I107" s="26" t="s">
+      <c r="I107" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="J107" s="25">
+      <c r="J107" s="23">
         <v>1</v>
       </c>
-      <c r="K107" s="10">
+      <c r="K107" s="23">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L107" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M107" s="25"/>
-      <c r="N107" s="25"/>
-      <c r="O107" s="25" t="s">
+      <c r="L107" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M107" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N107" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="O107" s="27" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="108" ht="15.75" spans="1:15">
+    <row r="108" spans="1:15">
       <c r="A108" s="3"/>
       <c r="B108" s="8">
         <f t="shared" si="8"/>
@@ -8037,14 +7922,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L108" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M108" s="13"/>
-      <c r="N108" s="13"/>
+      <c r="L108" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N108" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O108" s="13"/>
     </row>
-    <row r="109" ht="15.75" spans="1:15">
+    <row r="109" spans="1:15">
       <c r="A109" s="3"/>
       <c r="B109" s="8">
         <f t="shared" si="8"/>
@@ -8078,55 +7968,66 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L109" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" s="10"/>
-      <c r="N109" s="10"/>
+      <c r="L109" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M109" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N109" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O109" s="10"/>
     </row>
-    <row r="110" ht="15.75" spans="1:15">
+    <row r="110" spans="1:15">
       <c r="A110" s="3"/>
       <c r="B110" s="8">
         <f t="shared" si="8"/>
         <v>108</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="E110" s="14" t="s">
+      <c r="E110" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="F110" s="13" t="s">
+      <c r="F110" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="G110" s="14" t="s">
+      <c r="G110" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="H110" s="13" t="s">
+      <c r="H110" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I110" s="14" t="s">
+      <c r="I110" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="J110" s="13">
+      <c r="J110" s="20">
         <v>2</v>
       </c>
-      <c r="K110" s="10">
+      <c r="K110" s="23">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L110" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M110" s="13"/>
-      <c r="N110" s="13"/>
-      <c r="O110" s="13"/>
-    </row>
-    <row r="111" ht="15.75" spans="1:15">
+      <c r="L110" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N110" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="O110" s="27" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
       <c r="A111" s="3"/>
       <c r="B111" s="8">
         <f t="shared" si="8"/>
@@ -8160,14 +8061,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L111" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M111" s="10"/>
-      <c r="N111" s="10"/>
+      <c r="L111" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M111" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N111" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O111" s="10"/>
     </row>
-    <row r="112" ht="15.75" spans="1:15">
+    <row r="112" spans="1:15">
       <c r="A112" s="3"/>
       <c r="B112" s="8">
         <f t="shared" si="8"/>
@@ -8201,14 +8107,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L112" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M112" s="13"/>
-      <c r="N112" s="13"/>
+      <c r="L112" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M112" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N112" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O112" s="13"/>
     </row>
-    <row r="113" ht="15.75" spans="1:15">
+    <row r="113" spans="1:15">
       <c r="A113" s="3"/>
       <c r="B113" s="8">
         <f t="shared" si="8"/>
@@ -8242,14 +8153,19 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L113" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M113" s="10"/>
-      <c r="N113" s="10"/>
+      <c r="L113" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M113" s="26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N113" s="26">
+        <f t="shared" si="7"/>
+        <v>0.18</v>
+      </c>
       <c r="O113" s="10"/>
     </row>
-    <row r="114" ht="15.75" spans="1:15">
+    <row r="114" spans="1:15">
       <c r="A114" s="3"/>
       <c r="B114" s="8">
         <f t="shared" si="8"/>
@@ -8283,96 +8199,111 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L114" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M114" s="13"/>
-      <c r="N114" s="13"/>
+      <c r="L114" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" s="26">
+        <v>0.13</v>
+      </c>
+      <c r="N114" s="26">
+        <f t="shared" si="7"/>
+        <v>0.78</v>
+      </c>
       <c r="O114" s="13"/>
     </row>
-    <row r="115" ht="15.75" spans="1:15">
-      <c r="A115" s="3"/>
-      <c r="B115" s="8">
+    <row r="115" spans="1:15" s="37" customFormat="1">
+      <c r="A115" s="30"/>
+      <c r="B115" s="31">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="C115" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="33" t="s">
         <v>490</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="F115" s="10" t="s">
+      <c r="F115" s="33" t="s">
         <v>393</v>
       </c>
-      <c r="G115" s="11" t="s">
+      <c r="G115" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="H115" s="10" t="s">
+      <c r="H115" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I115" s="11" t="s">
+      <c r="I115" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="J115" s="10">
+      <c r="J115" s="33">
         <v>8</v>
       </c>
-      <c r="K115" s="10">
+      <c r="K115" s="33">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="L115" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M115" s="10"/>
-      <c r="N115" s="10"/>
-      <c r="O115" s="10"/>
-    </row>
-    <row r="116" ht="15.75" spans="1:15">
-      <c r="A116" s="3"/>
-      <c r="B116" s="8">
+      <c r="L115" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="M115" s="36">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N115" s="36">
+        <f t="shared" si="7"/>
+        <v>0.36</v>
+      </c>
+      <c r="O115" s="33"/>
+    </row>
+    <row r="116" spans="1:15" s="37" customFormat="1">
+      <c r="A116" s="30"/>
+      <c r="B116" s="31">
         <f t="shared" si="8"/>
         <v>114</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="32" t="s">
         <v>390</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="38" t="s">
         <v>494</v>
       </c>
-      <c r="E116" s="14" t="s">
+      <c r="E116" s="39" t="s">
         <v>413</v>
       </c>
-      <c r="F116" s="13" t="s">
+      <c r="F116" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="G116" s="14" t="s">
+      <c r="G116" s="39" t="s">
         <v>414</v>
       </c>
-      <c r="H116" s="13" t="s">
+      <c r="H116" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I116" s="14" t="s">
+      <c r="I116" s="39" t="s">
         <v>495</v>
       </c>
-      <c r="J116" s="13">
+      <c r="J116" s="38">
         <v>8</v>
       </c>
-      <c r="K116" s="10">
+      <c r="K116" s="33">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="L116" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M116" s="13"/>
-      <c r="N116" s="13"/>
-      <c r="O116" s="13"/>
-    </row>
-    <row r="117" ht="15.75" spans="1:15">
+      <c r="L116" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="M116" s="36">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N116" s="36">
+        <f t="shared" si="7"/>
+        <v>0.36</v>
+      </c>
+      <c r="O116" s="38"/>
+    </row>
+    <row r="117" spans="1:15">
       <c r="A117" s="3"/>
       <c r="B117" s="8">
         <f t="shared" si="8"/>
@@ -8406,14 +8337,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L117" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M117" s="10"/>
-      <c r="N117" s="10"/>
+      <c r="L117" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M117" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N117" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O117" s="10"/>
     </row>
-    <row r="118" ht="15.75" spans="1:15">
+    <row r="118" spans="1:15">
       <c r="A118" s="3"/>
       <c r="B118" s="8">
         <f t="shared" si="8"/>
@@ -8447,14 +8383,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L118" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M118" s="13"/>
-      <c r="N118" s="13"/>
+      <c r="L118" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M118" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N118" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O118" s="13"/>
     </row>
-    <row r="119" ht="15.75" spans="1:15">
+    <row r="119" spans="1:15">
       <c r="A119" s="3"/>
       <c r="B119" s="8">
         <f t="shared" si="8"/>
@@ -8488,14 +8429,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L119" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M119" s="10"/>
-      <c r="N119" s="10"/>
+      <c r="L119" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M119" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N119" s="26">
+        <f t="shared" si="7"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O119" s="10"/>
     </row>
-    <row r="120" ht="15.75" spans="1:15">
+    <row r="120" spans="1:15">
       <c r="A120" s="3"/>
       <c r="B120" s="8">
         <f t="shared" si="8"/>
@@ -8529,57 +8475,66 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L120" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M120" s="13"/>
-      <c r="N120" s="13"/>
+      <c r="L120" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M120" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N120" s="26">
+        <f t="shared" ref="N120:N160" si="10">M120*K120</f>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O120" s="13"/>
     </row>
-    <row r="121" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A121" s="19"/>
+    <row r="121" spans="1:15" s="1" customFormat="1">
+      <c r="A121" s="17"/>
       <c r="B121" s="8">
         <f t="shared" si="8"/>
         <v>119</v>
       </c>
-      <c r="C121" s="24" t="s">
+      <c r="C121" s="22" t="s">
         <v>390</v>
       </c>
-      <c r="D121" s="25" t="s">
+      <c r="D121" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="E121" s="26" t="s">
+      <c r="E121" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="F121" s="25" t="s">
+      <c r="F121" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="G121" s="26" t="s">
+      <c r="G121" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="H121" s="25" t="s">
+      <c r="H121" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="I121" s="26" t="s">
+      <c r="I121" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="J121" s="25">
+      <c r="J121" s="23">
         <v>2</v>
       </c>
-      <c r="K121" s="10">
+      <c r="K121" s="23">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L121" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M121" s="25"/>
-      <c r="N121" s="25"/>
-      <c r="O121" s="25" t="s">
+      <c r="L121" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M121" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="N121" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="O121" s="27" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="122" ht="15.75" spans="1:15">
+    <row r="122" spans="1:15">
       <c r="A122" s="3"/>
       <c r="B122" s="8">
         <f t="shared" si="8"/>
@@ -8613,14 +8568,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L122" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M122" s="13"/>
-      <c r="N122" s="13"/>
+      <c r="L122" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M122" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N122" s="26">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O122" s="13"/>
     </row>
-    <row r="123" ht="15.75" spans="1:15">
+    <row r="123" spans="1:15">
       <c r="A123" s="3"/>
       <c r="B123" s="8">
         <f>ROW(B123)-ROW($B$2)</f>
@@ -8654,14 +8614,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L123" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M123" s="10"/>
-      <c r="N123" s="10"/>
+      <c r="L123" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M123" s="26">
+        <v>0.11</v>
+      </c>
+      <c r="N123" s="26">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
       <c r="O123" s="10"/>
     </row>
-    <row r="124" ht="15.75" spans="1:15">
+    <row r="124" spans="1:15">
       <c r="A124" s="3"/>
       <c r="B124" s="8">
         <f t="shared" si="8"/>
@@ -8695,14 +8660,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L124" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M124" s="13"/>
-      <c r="N124" s="13"/>
+      <c r="L124" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M124" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N124" s="26">
+        <f t="shared" si="10"/>
+        <v>0.60000000000000009</v>
+      </c>
       <c r="O124" s="13"/>
     </row>
-    <row r="125" ht="15.75" spans="1:15">
+    <row r="125" spans="1:15">
       <c r="A125" s="3"/>
       <c r="B125" s="8">
         <f>ROW(B125)-ROW($B$2)</f>
@@ -8736,14 +8706,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L125" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M125" s="10"/>
-      <c r="N125" s="10"/>
+      <c r="L125" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M125" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N125" s="26">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O125" s="10"/>
     </row>
-    <row r="126" ht="15.75" spans="1:15">
+    <row r="126" spans="1:15">
       <c r="A126" s="3"/>
       <c r="B126" s="8">
         <f t="shared" si="8"/>
@@ -8777,14 +8752,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L126" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M126" s="13"/>
-      <c r="N126" s="13"/>
+      <c r="L126" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M126" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N126" s="26">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O126" s="13"/>
     </row>
-    <row r="127" ht="15.75" spans="1:15">
+    <row r="127" spans="1:15">
       <c r="A127" s="3"/>
       <c r="B127" s="8">
         <f>ROW(B127)-ROW($B$2)</f>
@@ -8818,14 +8798,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L127" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M127" s="10"/>
-      <c r="N127" s="10"/>
+      <c r="L127" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M127" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N127" s="26">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O127" s="10"/>
     </row>
-    <row r="128" ht="15.75" spans="1:15">
+    <row r="128" spans="1:15">
       <c r="A128" s="3"/>
       <c r="B128" s="8">
         <f t="shared" si="8"/>
@@ -8859,14 +8844,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L128" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M128" s="13"/>
-      <c r="N128" s="13"/>
+      <c r="L128" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M128" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N128" s="26">
+        <f t="shared" si="10"/>
+        <v>0.30000000000000004</v>
+      </c>
       <c r="O128" s="13"/>
     </row>
-    <row r="129" ht="15.75" spans="1:15">
+    <row r="129" spans="1:15">
       <c r="A129" s="3"/>
       <c r="B129" s="8">
         <f>ROW(B129)-ROW($B$2)</f>
@@ -8900,14 +8890,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L129" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M129" s="10"/>
-      <c r="N129" s="10"/>
+      <c r="L129" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M129" s="26">
+        <v>0.16</v>
+      </c>
+      <c r="N129" s="26">
+        <f t="shared" si="10"/>
+        <v>0.96</v>
+      </c>
       <c r="O129" s="10"/>
     </row>
-    <row r="130" ht="15.75" spans="1:15">
+    <row r="130" spans="1:15">
       <c r="A130" s="3"/>
       <c r="B130" s="8">
         <f t="shared" si="8"/>
@@ -8941,14 +8936,19 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L130" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M130" s="13"/>
-      <c r="N130" s="13"/>
+      <c r="L130" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M130" s="26">
+        <v>0.16</v>
+      </c>
+      <c r="N130" s="26">
+        <f t="shared" si="10"/>
+        <v>0.48</v>
+      </c>
       <c r="O130" s="13"/>
     </row>
-    <row r="131" ht="15.75" spans="1:15">
+    <row r="131" spans="1:15">
       <c r="A131" s="3"/>
       <c r="B131" s="8">
         <f>ROW(B131)-ROW($B$2)</f>
@@ -8982,14 +8982,19 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L131" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M131" s="10"/>
-      <c r="N131" s="10"/>
+      <c r="L131" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M131" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="N131" s="26">
+        <f t="shared" si="10"/>
+        <v>0.89999999999999991</v>
+      </c>
       <c r="O131" s="10"/>
     </row>
-    <row r="132" ht="36.75" spans="1:15">
+    <row r="132" spans="1:15" ht="36">
       <c r="A132" s="3"/>
       <c r="B132" s="8">
         <f t="shared" si="8"/>
@@ -9020,17 +9025,22 @@
         <v>6</v>
       </c>
       <c r="K132" s="10">
-        <f t="shared" ref="K132:K159" si="10">3*J132</f>
+        <f t="shared" ref="K132:K160" si="11">3*J132</f>
         <v>18</v>
       </c>
-      <c r="L132" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M132" s="13"/>
-      <c r="N132" s="13"/>
+      <c r="L132" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M132" s="26">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="N132" s="26">
+        <f t="shared" si="10"/>
+        <v>1.2492000000000001</v>
+      </c>
       <c r="O132" s="13"/>
     </row>
-    <row r="133" ht="24.75" spans="1:15">
+    <row r="133" spans="1:15" ht="24">
       <c r="A133" s="3"/>
       <c r="B133" s="8">
         <f>ROW(B133)-ROW($B$2)</f>
@@ -9061,58 +9071,70 @@
         <v>1</v>
       </c>
       <c r="K133" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L133" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M133" s="26">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="N133" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L133" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M133" s="10"/>
-      <c r="N133" s="10"/>
+        <v>0.76019999999999999</v>
+      </c>
       <c r="O133" s="10"/>
     </row>
-    <row r="134" ht="24.75" spans="1:15">
+    <row r="134" spans="1:15" ht="24">
       <c r="A134" s="3"/>
       <c r="B134" s="8">
         <f t="shared" si="8"/>
         <v>132</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="41" t="s">
         <v>556</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="D134" s="42" t="s">
         <v>562</v>
       </c>
-      <c r="E134" s="14" t="s">
+      <c r="E134" s="43" t="s">
         <v>563</v>
       </c>
-      <c r="F134" s="13" t="s">
+      <c r="F134" s="42" t="s">
         <v>564</v>
       </c>
-      <c r="G134" s="14" t="s">
+      <c r="G134" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="H134" s="13" t="s">
+      <c r="H134" s="42" t="s">
         <v>566</v>
       </c>
-      <c r="I134" s="14" t="s">
+      <c r="I134" s="43" t="s">
         <v>149</v>
       </c>
-      <c r="J134" s="13">
+      <c r="J134" s="42">
         <v>1</v>
       </c>
-      <c r="K134" s="10">
+      <c r="K134" s="44">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L134" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="M134" s="45">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="N134" s="45">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L134" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M134" s="13"/>
-      <c r="N134" s="13"/>
-      <c r="O134" s="13"/>
-    </row>
-    <row r="135" ht="15.75" spans="1:15">
+        <v>6.7799999999999994</v>
+      </c>
+      <c r="O134" s="40" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
       <c r="A135" s="3"/>
       <c r="B135" s="8">
         <f>ROW(B135)-ROW($B$2)</f>
@@ -9143,17 +9165,22 @@
         <v>2</v>
       </c>
       <c r="K135" s="10">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L135" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M135" s="26">
+        <v>0.46</v>
+      </c>
+      <c r="N135" s="26">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="L135" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M135" s="10"/>
-      <c r="N135" s="10"/>
+        <v>2.7600000000000002</v>
+      </c>
       <c r="O135" s="10"/>
     </row>
-    <row r="136" ht="24.75" spans="1:15">
+    <row r="136" spans="1:15" ht="24">
       <c r="A136" s="3"/>
       <c r="B136" s="8">
         <f t="shared" si="8"/>
@@ -9184,17 +9211,22 @@
         <v>1</v>
       </c>
       <c r="K136" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L136" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M136" s="26" t="s">
+        <v>690</v>
+      </c>
+      <c r="N136" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L136" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M136" s="13"/>
-      <c r="N136" s="13"/>
+        <v>3.54</v>
+      </c>
       <c r="O136" s="13"/>
     </row>
-    <row r="137" ht="24.75" spans="1:15">
+    <row r="137" spans="1:15" ht="24">
       <c r="A137" s="3"/>
       <c r="B137" s="8">
         <f>ROW(B137)-ROW($B$2)</f>
@@ -9225,17 +9257,22 @@
         <v>4</v>
       </c>
       <c r="K137" s="10">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="L137" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M137" s="26">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="N137" s="26">
         <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="L137" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M137" s="10"/>
-      <c r="N137" s="10"/>
+        <v>1.1255999999999999</v>
+      </c>
       <c r="O137" s="10"/>
     </row>
-    <row r="138" ht="15.75" spans="1:15">
+    <row r="138" spans="1:15">
       <c r="A138" s="3"/>
       <c r="B138" s="8">
         <f t="shared" si="8"/>
@@ -9266,17 +9303,22 @@
         <v>1</v>
       </c>
       <c r="K138" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L138" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M138" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="N138" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L138" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M138" s="13"/>
-      <c r="N138" s="13"/>
+        <v>4.53</v>
+      </c>
       <c r="O138" s="13"/>
     </row>
-    <row r="139" ht="24.75" spans="1:15">
+    <row r="139" spans="1:15" ht="24">
       <c r="A139" s="3"/>
       <c r="B139" s="8">
         <f>ROW(B139)-ROW($B$2)</f>
@@ -9307,17 +9349,22 @@
         <v>1</v>
       </c>
       <c r="K139" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L139" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M139" s="26" t="s">
+        <v>692</v>
+      </c>
+      <c r="N139" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L139" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M139" s="10"/>
-      <c r="N139" s="10"/>
+        <v>5.37</v>
+      </c>
       <c r="O139" s="10"/>
     </row>
-    <row r="140" ht="15.75" spans="1:15">
+    <row r="140" spans="1:15">
       <c r="A140" s="3"/>
       <c r="B140" s="8">
         <f t="shared" si="8"/>
@@ -9348,17 +9395,22 @@
         <v>1</v>
       </c>
       <c r="K140" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L140" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M140" s="26" t="s">
+        <v>693</v>
+      </c>
+      <c r="N140" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L140" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M140" s="13"/>
-      <c r="N140" s="13"/>
+        <v>7.5762</v>
+      </c>
       <c r="O140" s="13"/>
     </row>
-    <row r="141" ht="15.75" spans="1:15">
+    <row r="141" spans="1:15">
       <c r="A141" s="3"/>
       <c r="B141" s="8">
         <f>ROW(B141)-ROW($B$2)</f>
@@ -9389,17 +9441,22 @@
         <v>1</v>
       </c>
       <c r="K141" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L141" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M141" s="26" t="s">
+        <v>694</v>
+      </c>
+      <c r="N141" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L141" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M141" s="10"/>
-      <c r="N141" s="10"/>
+        <v>16.71</v>
+      </c>
       <c r="O141" s="10"/>
     </row>
-    <row r="142" ht="24.75" spans="1:15">
+    <row r="142" spans="1:15" ht="24">
       <c r="A142" s="3"/>
       <c r="B142" s="8">
         <f t="shared" si="8"/>
@@ -9430,17 +9487,22 @@
         <v>1</v>
       </c>
       <c r="K142" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L142" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M142" s="26" t="s">
+        <v>695</v>
+      </c>
+      <c r="N142" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L142" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M142" s="13"/>
-      <c r="N142" s="13"/>
+        <v>54.09</v>
+      </c>
       <c r="O142" s="13"/>
     </row>
-    <row r="143" ht="24.75" spans="1:15">
+    <row r="143" spans="1:15" ht="24">
       <c r="A143" s="3"/>
       <c r="B143" s="8">
         <f>ROW(B143)-ROW($B$2)</f>
@@ -9471,17 +9533,22 @@
         <v>1</v>
       </c>
       <c r="K143" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L143" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M143" s="26" t="s">
+        <v>696</v>
+      </c>
+      <c r="N143" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L143" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M143" s="10"/>
-      <c r="N143" s="10"/>
+        <v>3.18</v>
+      </c>
       <c r="O143" s="10"/>
     </row>
-    <row r="144" ht="24.75" spans="1:15">
+    <row r="144" spans="1:15" ht="24">
       <c r="A144" s="3"/>
       <c r="B144" s="8">
         <f t="shared" si="8"/>
@@ -9512,17 +9579,22 @@
         <v>2</v>
       </c>
       <c r="K144" s="10">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L144" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M144" s="26">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="N144" s="26">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="L144" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M144" s="13"/>
-      <c r="N144" s="13"/>
+        <v>0.13919999999999999</v>
+      </c>
       <c r="O144" s="13"/>
     </row>
-    <row r="145" ht="24.75" spans="1:15">
+    <row r="145" spans="1:15" ht="24">
       <c r="A145" s="3"/>
       <c r="B145" s="8">
         <f>ROW(B145)-ROW($B$2)</f>
@@ -9553,17 +9625,22 @@
         <v>1</v>
       </c>
       <c r="K145" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L145" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M145" s="26">
+        <v>8.3531999999999993</v>
+      </c>
+      <c r="N145" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L145" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M145" s="10"/>
-      <c r="N145" s="10"/>
+        <v>25.059599999999996</v>
+      </c>
       <c r="O145" s="10"/>
     </row>
-    <row r="146" ht="26.25" spans="1:15">
+    <row r="146" spans="1:15" ht="25.5">
       <c r="A146" s="3"/>
       <c r="B146" s="8">
         <f t="shared" si="8"/>
@@ -9594,17 +9671,22 @@
         <v>1</v>
       </c>
       <c r="K146" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L146" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M146" s="26">
+        <v>0.63719999999999999</v>
+      </c>
+      <c r="N146" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L146" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M146" s="13"/>
-      <c r="N146" s="13"/>
+        <v>1.9116</v>
+      </c>
       <c r="O146" s="13"/>
     </row>
-    <row r="147" ht="60.75" spans="1:15">
+    <row r="147" spans="1:15" ht="60">
       <c r="A147" s="3"/>
       <c r="B147" s="8">
         <f>ROW(B147)-ROW($B$2)</f>
@@ -9635,14 +9717,19 @@
         <v>1</v>
       </c>
       <c r="K147" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L147" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M147" s="26">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="N147" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L147" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M147" s="10"/>
-      <c r="N147" s="10"/>
+        <v>0.2364</v>
+      </c>
       <c r="O147" s="10"/>
     </row>
     <row r="148" spans="1:15">
@@ -9676,17 +9763,22 @@
         <v>1</v>
       </c>
       <c r="K148" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L148" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M148" s="26" t="s">
+        <v>697</v>
+      </c>
+      <c r="N148" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L148" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M148" s="13"/>
-      <c r="N148" s="13"/>
+        <v>13.32</v>
+      </c>
       <c r="O148" s="13"/>
     </row>
-    <row r="149" ht="24.75" spans="1:15">
+    <row r="149" spans="1:15" ht="24">
       <c r="A149" s="3"/>
       <c r="B149" s="8">
         <f>ROW(B149)-ROW($B$2)</f>
@@ -9717,17 +9809,22 @@
         <v>1</v>
       </c>
       <c r="K149" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L149" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" s="26" t="s">
+        <v>698</v>
+      </c>
+      <c r="N149" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L149" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M149" s="10"/>
-      <c r="N149" s="10"/>
+        <v>2.34</v>
+      </c>
       <c r="O149" s="10"/>
     </row>
-    <row r="150" ht="15.75" spans="1:15">
+    <row r="150" spans="1:15">
       <c r="A150" s="3"/>
       <c r="B150" s="8">
         <f t="shared" si="8"/>
@@ -9758,17 +9855,22 @@
         <v>2</v>
       </c>
       <c r="K150" s="10">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L150" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M150" s="26">
+        <v>0.99080000000000001</v>
+      </c>
+      <c r="N150" s="26">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="L150" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M150" s="13"/>
-      <c r="N150" s="13"/>
+        <v>5.9447999999999999</v>
+      </c>
       <c r="O150" s="13"/>
     </row>
-    <row r="151" ht="24.75" spans="1:15">
+    <row r="151" spans="1:15" ht="24">
       <c r="A151" s="3"/>
       <c r="B151" s="8">
         <f>ROW(B151)-ROW($B$2)</f>
@@ -9799,39 +9901,44 @@
         <v>1</v>
       </c>
       <c r="K151" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L151" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M151" s="26" t="s">
+        <v>699</v>
+      </c>
+      <c r="N151" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L151" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M151" s="13"/>
-      <c r="N151" s="13"/>
+        <v>1.6800000000000002</v>
+      </c>
       <c r="O151" s="13"/>
     </row>
-    <row r="152" ht="24.75" spans="1:15">
+    <row r="152" spans="1:15">
       <c r="A152" s="3"/>
       <c r="B152" s="8">
-        <f t="shared" si="8"/>
+        <f>ROW(B152)-ROW($B$2)</f>
         <v>150</v>
       </c>
-      <c r="C152" s="12" t="s">
+      <c r="C152" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="D152" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="E152" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>646</v>
-      </c>
-      <c r="G152" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="H152" s="13" t="s">
-        <v>648</v>
+      <c r="D152" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>687</v>
       </c>
       <c r="I152" s="14" t="s">
         <v>149</v>
@@ -9840,362 +9947,748 @@
         <v>1</v>
       </c>
       <c r="K152" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L152" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M152" s="26" t="s">
+        <v>700</v>
+      </c>
+      <c r="N152" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L152" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M152" s="13"/>
-      <c r="N152" s="13"/>
+        <v>8.67</v>
+      </c>
       <c r="O152" s="13"/>
     </row>
-    <row r="153" ht="24.75" spans="1:15">
+    <row r="153" spans="1:15" ht="24">
       <c r="A153" s="3"/>
       <c r="B153" s="8">
-        <f>ROW(B153)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>151</v>
       </c>
-      <c r="C153" s="9" t="s">
+      <c r="C153" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="D153" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="E153" s="11" t="s">
-        <v>650</v>
-      </c>
-      <c r="F153" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="G153" s="11" t="s">
-        <v>652</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>566</v>
+      <c r="D153" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="E153" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="F153" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="G153" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="H153" s="13" t="s">
+        <v>648</v>
       </c>
       <c r="I153" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J153" s="10">
+      <c r="J153" s="13">
         <v>1</v>
       </c>
       <c r="K153" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L153" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M153" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="N153" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L153" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M153" s="10"/>
-      <c r="N153" s="10"/>
-      <c r="O153" s="10"/>
-    </row>
-    <row r="154" ht="15.75" spans="1:15">
+        <v>4.0500000000000007</v>
+      </c>
+      <c r="O153" s="13"/>
+    </row>
+    <row r="154" spans="1:15" ht="24">
       <c r="A154" s="3"/>
       <c r="B154" s="8">
-        <f t="shared" si="8"/>
+        <f>ROW(B154)-ROW($B$2)</f>
         <v>152</v>
       </c>
-      <c r="C154" s="12" t="s">
+      <c r="C154" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>653</v>
-      </c>
-      <c r="E154" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G154" s="14" t="s">
-        <v>655</v>
-      </c>
-      <c r="H154" s="13" t="s">
-        <v>656</v>
+      <c r="D154" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="E154" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="G154" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>566</v>
       </c>
       <c r="I154" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J154" s="13">
+      <c r="J154" s="10">
         <v>1</v>
       </c>
       <c r="K154" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L154" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M154" s="26" t="s">
+        <v>702</v>
+      </c>
+      <c r="N154" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L154" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M154" s="13"/>
-      <c r="N154" s="13"/>
-      <c r="O154" s="13"/>
-    </row>
-    <row r="155" ht="15.75" spans="1:15">
+        <v>6.39</v>
+      </c>
+      <c r="O154" s="10"/>
+    </row>
+    <row r="155" spans="1:15">
       <c r="A155" s="3"/>
       <c r="B155" s="8">
-        <f>ROW(B155)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>153</v>
       </c>
-      <c r="C155" s="9" t="s">
+      <c r="C155" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>657</v>
-      </c>
-      <c r="E155" s="11" t="s">
-        <v>658</v>
-      </c>
-      <c r="F155" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="G155" s="11" t="s">
-        <v>660</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>661</v>
+      <c r="D155" s="13" t="s">
+        <v>653</v>
+      </c>
+      <c r="E155" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G155" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="H155" s="13" t="s">
+        <v>656</v>
       </c>
       <c r="I155" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J155" s="10">
+      <c r="J155" s="13">
         <v>1</v>
       </c>
       <c r="K155" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L155" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M155" s="26" t="s">
+        <v>703</v>
+      </c>
+      <c r="N155" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L155" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M155" s="10"/>
-      <c r="N155" s="10"/>
-      <c r="O155" s="10"/>
-    </row>
-    <row r="156" ht="24.75" spans="1:15">
+        <v>0.47054999999999997</v>
+      </c>
+      <c r="O155" s="13"/>
+    </row>
+    <row r="156" spans="1:15">
       <c r="A156" s="3"/>
       <c r="B156" s="8">
-        <f t="shared" si="8"/>
+        <f>ROW(B156)-ROW($B$2)</f>
         <v>154</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="D156" s="13" t="s">
-        <v>662</v>
-      </c>
-      <c r="E156" s="14" t="s">
-        <v>663</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>664</v>
-      </c>
-      <c r="G156" s="14" t="s">
-        <v>665</v>
-      </c>
-      <c r="H156" s="13" t="s">
-        <v>666</v>
+      <c r="D156" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="E156" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="G156" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>661</v>
       </c>
       <c r="I156" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J156" s="13">
+      <c r="J156" s="10">
         <v>1</v>
       </c>
       <c r="K156" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L156" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M156" s="26" t="s">
+        <v>704</v>
+      </c>
+      <c r="N156" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L156" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M156" s="13"/>
-      <c r="N156" s="13"/>
-      <c r="O156" s="13"/>
-    </row>
-    <row r="157" ht="36.75" spans="1:15">
+        <v>1.08</v>
+      </c>
+      <c r="O156" s="10"/>
+    </row>
+    <row r="157" spans="1:15" ht="24">
       <c r="A157" s="3"/>
       <c r="B157" s="8">
-        <f>ROW(B157)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>155</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>668</v>
-      </c>
-      <c r="F157" s="10" t="s">
-        <v>669</v>
-      </c>
-      <c r="G157" s="11" t="s">
-        <v>670</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>671</v>
+      <c r="D157" s="13" t="s">
+        <v>662</v>
+      </c>
+      <c r="E157" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="F157" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="G157" s="14" t="s">
+        <v>665</v>
+      </c>
+      <c r="H157" s="13" t="s">
+        <v>666</v>
       </c>
       <c r="I157" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J157" s="10">
+      <c r="J157" s="13">
         <v>1</v>
       </c>
       <c r="K157" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L157" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="M157" s="26">
+        <v>0.34460000000000002</v>
+      </c>
+      <c r="N157" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L157" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M157" s="10"/>
-      <c r="N157" s="10"/>
-      <c r="O157" s="10"/>
-    </row>
-    <row r="158" ht="36.75" spans="1:15">
+        <v>1.0338000000000001</v>
+      </c>
+      <c r="O157" s="13"/>
+    </row>
+    <row r="158" spans="1:15" ht="36">
       <c r="A158" s="3"/>
       <c r="B158" s="8">
-        <f t="shared" si="8"/>
+        <f>ROW(B158)-ROW($B$2)</f>
         <v>156</v>
       </c>
-      <c r="C158" s="12" t="s">
-        <v>672</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>673</v>
-      </c>
-      <c r="E158" s="14" t="s">
-        <v>674</v>
-      </c>
-      <c r="F158" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G158" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="H158" s="13" t="s">
-        <v>676</v>
+      <c r="C158" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D158" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="E158" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="F158" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="G158" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>671</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>677</v>
-      </c>
-      <c r="J158" s="13">
+        <v>149</v>
+      </c>
+      <c r="J158" s="10">
         <v>1</v>
       </c>
       <c r="K158" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L158" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M158" s="26" t="s">
+        <v>705</v>
+      </c>
+      <c r="N158" s="26">
         <f t="shared" si="10"/>
-        <v>3</v>
-      </c>
-      <c r="L158" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M158" s="13"/>
-      <c r="N158" s="13"/>
-      <c r="O158" s="13"/>
-    </row>
-    <row r="159" ht="15.75" spans="1:15">
+        <v>2.82</v>
+      </c>
+      <c r="O158" s="10"/>
+    </row>
+    <row r="159" spans="1:15" ht="36">
       <c r="A159" s="3"/>
       <c r="B159" s="8">
-        <f>ROW(B159)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>157</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C159" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>678</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>679</v>
+      <c r="D159" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="E159" s="14" t="s">
+        <v>674</v>
       </c>
       <c r="F159" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="G159" s="11" t="s">
+      <c r="G159" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="H159" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="I159" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="J159" s="13">
+        <v>1</v>
+      </c>
+      <c r="K159" s="10">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L159" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M159" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="N159" s="26">
+        <f t="shared" si="10"/>
+        <v>0.86355000000000004</v>
+      </c>
+      <c r="O159" s="13"/>
+    </row>
+    <row r="160" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A160" s="3"/>
+      <c r="B160" s="8">
+        <f>ROW(B160)-ROW($B$2)</f>
+        <v>158</v>
+      </c>
+      <c r="C160" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="D160" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="E160" s="11" t="s">
+        <v>679</v>
+      </c>
+      <c r="F160" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G160" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="H159" s="10" t="s">
+      <c r="H160" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="I159" s="11" t="s">
+      <c r="I160" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="J159" s="10">
+      <c r="J160" s="10">
         <v>2</v>
       </c>
-      <c r="K159" s="10">
+      <c r="K160" s="10">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="L160" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M160" s="26" t="s">
+        <v>707</v>
+      </c>
+      <c r="N160" s="26">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="L159" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M159" s="10"/>
-      <c r="N159" s="10"/>
-      <c r="O159" s="10"/>
+        <v>4.8360000000000003</v>
+      </c>
+      <c r="O160" s="10"/>
+    </row>
+    <row r="161" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B161" s="8">
+        <f t="shared" ref="B161:B167" si="12">ROW(B161)-ROW($B$2)</f>
+        <v>159</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="E161" s="11"/>
+      <c r="F161" s="13"/>
+      <c r="G161" s="11"/>
+      <c r="H161" s="10"/>
+      <c r="I161" s="11"/>
+      <c r="J161" s="10"/>
+      <c r="K161" s="10"/>
+      <c r="L161" s="16"/>
+      <c r="M161" s="26"/>
+      <c r="N161" s="26"/>
+      <c r="O161" s="10"/>
+    </row>
+    <row r="162" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B162" s="8">
+        <f t="shared" si="12"/>
+        <v>160</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D162" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="E162" s="11"/>
+      <c r="F162" s="13"/>
+      <c r="G162" s="11"/>
+      <c r="H162" s="10"/>
+      <c r="I162" s="11"/>
+      <c r="J162" s="10"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="16"/>
+      <c r="M162" s="26"/>
+      <c r="N162" s="26"/>
+      <c r="O162" s="10"/>
+    </row>
+    <row r="163" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B163" s="8">
+        <f t="shared" si="12"/>
+        <v>161</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E163" s="11"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="11"/>
+      <c r="H163" s="10"/>
+      <c r="I163" s="11"/>
+      <c r="J163" s="10"/>
+      <c r="K163" s="10"/>
+      <c r="L163" s="16"/>
+      <c r="M163" s="26"/>
+      <c r="N163" s="26"/>
+      <c r="O163" s="10"/>
+    </row>
+    <row r="164" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B164" s="8">
+        <f t="shared" si="12"/>
+        <v>162</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D164" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="E164" s="11"/>
+      <c r="F164" s="13"/>
+      <c r="G164" s="11"/>
+      <c r="H164" s="10"/>
+      <c r="I164" s="11"/>
+      <c r="J164" s="10"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="16"/>
+      <c r="M164" s="26"/>
+      <c r="N164" s="26"/>
+      <c r="O164" s="10"/>
+    </row>
+    <row r="165" spans="2:15" ht="15.75" thickBot="1">
+      <c r="B165" s="8">
+        <f t="shared" si="12"/>
+        <v>163</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D165" s="10"/>
+      <c r="E165" s="11"/>
+      <c r="F165" s="13"/>
+      <c r="G165" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="I165" s="11"/>
+      <c r="J165" s="10"/>
+      <c r="K165" s="10"/>
+      <c r="L165" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="M165" s="26"/>
+      <c r="N165" s="26"/>
+      <c r="O165" s="10"/>
+    </row>
+    <row r="166" spans="2:15" ht="24.75" thickBot="1">
+      <c r="B166" s="8">
+        <f t="shared" si="12"/>
+        <v>164</v>
+      </c>
+      <c r="C166" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D166" s="10"/>
+      <c r="E166" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="F166" s="13"/>
+      <c r="G166" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="I166" s="11"/>
+      <c r="J166" s="10"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="M166" s="26"/>
+      <c r="N166" s="26"/>
+      <c r="O166" s="10"/>
+    </row>
+    <row r="167" spans="2:15" s="29" customFormat="1" ht="24.75" thickBot="1">
+      <c r="B167" s="8">
+        <f t="shared" si="12"/>
+        <v>165</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>708</v>
+      </c>
+      <c r="D167" s="10"/>
+      <c r="E167" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="F167" s="13"/>
+      <c r="G167" s="11" t="s">
+        <v>719</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>720</v>
+      </c>
+      <c r="I167" s="11"/>
+      <c r="J167" s="10"/>
+      <c r="K167" s="10"/>
+      <c r="L167" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="M167" s="50"/>
+      <c r="N167" s="50"/>
+      <c r="O167" s="10"/>
+    </row>
+    <row r="168" spans="2:15">
+      <c r="M168" s="51" t="s">
+        <v>723</v>
+      </c>
+      <c r="N168" s="52">
+        <f>SUM(N3:N167)</f>
+        <v>450.46628999999996</v>
+      </c>
+    </row>
+    <row r="169" spans="2:15" ht="15.75" thickBot="1">
+      <c r="M169" s="53" t="s">
+        <v>724</v>
+      </c>
+      <c r="N169" s="54">
+        <f>N168/3</f>
+        <v>150.15543</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:O1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" display="Digikey"/>
-    <hyperlink ref="L4" r:id="rId2" display="Digikey"/>
-    <hyperlink ref="L5" r:id="rId3" display="Digikey"/>
-    <hyperlink ref="L6" r:id="rId4" display="Digikey"/>
-    <hyperlink ref="L7" r:id="rId5" display="Digikey"/>
-    <hyperlink ref="L8" r:id="rId6" display="Digikey"/>
-    <hyperlink ref="L9" r:id="rId7" display="Digikey"/>
-    <hyperlink ref="L10" r:id="rId8" display="Digikey"/>
-    <hyperlink ref="L11" r:id="rId9" display="Digikey"/>
-    <hyperlink ref="L12" r:id="rId10" display="Digikey"/>
-    <hyperlink ref="L13" r:id="rId11" display="Digikey"/>
-    <hyperlink ref="L14" r:id="rId12" display="Digikey"/>
-    <hyperlink ref="L15" r:id="rId13" display="Digikey"/>
-    <hyperlink ref="L16" r:id="rId14" display="Digikey"/>
-    <hyperlink ref="L17" r:id="rId15" display="Digikey"/>
-    <hyperlink ref="L18" r:id="rId16" display="Digikey"/>
-    <hyperlink ref="L19" r:id="rId17" display="Digikey"/>
-    <hyperlink ref="L20" r:id="rId18" display="Digikey"/>
-    <hyperlink ref="L21" r:id="rId19" display="Digikey"/>
-    <hyperlink ref="L22" r:id="rId20" display="Digikey"/>
-    <hyperlink ref="L23" r:id="rId21" display="Digikey"/>
-    <hyperlink ref="L24" r:id="rId22" display="Digikey"/>
-    <hyperlink ref="L26" r:id="rId23" display="Digikey"/>
-    <hyperlink ref="L27" r:id="rId24" display="Digikey"/>
-    <hyperlink ref="L28" r:id="rId12" display="Digikey"/>
-    <hyperlink ref="L29" r:id="rId25" display="Digikey"/>
-    <hyperlink ref="L30" r:id="rId26" display="Digikey"/>
-    <hyperlink ref="L31" r:id="rId27" display="Digikey"/>
-    <hyperlink ref="L32" r:id="rId28" display="Digikey"/>
-    <hyperlink ref="L33" r:id="rId29" display="Digikey"/>
-    <hyperlink ref="L36" r:id="rId30" display="Digikey"/>
-    <hyperlink ref="L37" r:id="rId31" display="Digikey"/>
-    <hyperlink ref="L38" r:id="rId32" display="Digikey"/>
-    <hyperlink ref="L42" r:id="rId33" display="Digikey"/>
-    <hyperlink ref="L43" r:id="rId34" display="Digikey"/>
-    <hyperlink ref="L45" r:id="rId35" display="Digikey"/>
-    <hyperlink ref="L46" r:id="rId36" display="Digikey"/>
-    <hyperlink ref="L47" r:id="rId37" display="Digikey"/>
-    <hyperlink ref="L50" r:id="rId38" display="Digikey"/>
-    <hyperlink ref="L60" r:id="rId39" display="Digikey"/>
-    <hyperlink ref="L61" r:id="rId40" display="Digikey"/>
-    <hyperlink ref="L67" r:id="rId41" display="Digikey"/>
-    <hyperlink ref="L70" r:id="rId42" display="Digikey"/>
-    <hyperlink ref="L72" r:id="rId43" display="Digikey"/>
-    <hyperlink ref="L73" r:id="rId44" display="Digikey"/>
-    <hyperlink ref="L78" r:id="rId45" display="Digikey"/>
-    <hyperlink ref="L79" r:id="rId46" display="Digikey"/>
-    <hyperlink ref="L80" r:id="rId47" display="Digikey"/>
-    <hyperlink ref="L82" r:id="rId48" display="Digikey"/>
-    <hyperlink ref="L84" r:id="rId49" display="Digikey"/>
-    <hyperlink ref="L86" r:id="rId50" display="Digikey"/>
+    <hyperlink ref="L3" r:id="rId1"/>
+    <hyperlink ref="L4" r:id="rId2"/>
+    <hyperlink ref="L5" r:id="rId3"/>
+    <hyperlink ref="L6" r:id="rId4"/>
+    <hyperlink ref="L7" r:id="rId5"/>
+    <hyperlink ref="L8" r:id="rId6"/>
+    <hyperlink ref="L9" r:id="rId7"/>
+    <hyperlink ref="L10" r:id="rId8"/>
+    <hyperlink ref="L11" r:id="rId9"/>
+    <hyperlink ref="L12" r:id="rId10"/>
+    <hyperlink ref="L13" r:id="rId11"/>
+    <hyperlink ref="L14" r:id="rId12"/>
+    <hyperlink ref="L15" r:id="rId13"/>
+    <hyperlink ref="L16" r:id="rId14"/>
+    <hyperlink ref="L17" r:id="rId15"/>
+    <hyperlink ref="L18" r:id="rId16"/>
+    <hyperlink ref="L19" r:id="rId17"/>
+    <hyperlink ref="L20" r:id="rId18"/>
+    <hyperlink ref="L21" r:id="rId19"/>
+    <hyperlink ref="L22" r:id="rId20"/>
+    <hyperlink ref="L23" r:id="rId21"/>
+    <hyperlink ref="L24" r:id="rId22"/>
+    <hyperlink ref="L26" r:id="rId23"/>
+    <hyperlink ref="L27" r:id="rId24"/>
+    <hyperlink ref="L28" r:id="rId25"/>
+    <hyperlink ref="L29" r:id="rId26"/>
+    <hyperlink ref="L30" r:id="rId27"/>
+    <hyperlink ref="L31" r:id="rId28"/>
+    <hyperlink ref="L32" r:id="rId29"/>
+    <hyperlink ref="L33" r:id="rId30"/>
+    <hyperlink ref="L36" r:id="rId31"/>
+    <hyperlink ref="L37" r:id="rId32"/>
+    <hyperlink ref="L38" r:id="rId33"/>
+    <hyperlink ref="L42" r:id="rId34"/>
+    <hyperlink ref="L43" r:id="rId35"/>
+    <hyperlink ref="L45" r:id="rId36"/>
+    <hyperlink ref="L46" r:id="rId37"/>
+    <hyperlink ref="L47" r:id="rId38"/>
+    <hyperlink ref="L50" r:id="rId39"/>
+    <hyperlink ref="L60" r:id="rId40"/>
+    <hyperlink ref="L61" r:id="rId41"/>
+    <hyperlink ref="L67" r:id="rId42"/>
+    <hyperlink ref="L70" r:id="rId43"/>
+    <hyperlink ref="L72" r:id="rId44"/>
+    <hyperlink ref="L73" r:id="rId45"/>
+    <hyperlink ref="L78" r:id="rId46"/>
+    <hyperlink ref="L79" r:id="rId47"/>
+    <hyperlink ref="L80" r:id="rId48"/>
+    <hyperlink ref="L82" r:id="rId49"/>
+    <hyperlink ref="L84" r:id="rId50"/>
+    <hyperlink ref="L86" r:id="rId51"/>
+    <hyperlink ref="L25" r:id="rId52"/>
+    <hyperlink ref="L34" r:id="rId53"/>
+    <hyperlink ref="L35" r:id="rId54"/>
+    <hyperlink ref="L39" r:id="rId55"/>
+    <hyperlink ref="L40" r:id="rId56"/>
+    <hyperlink ref="L41" r:id="rId57"/>
+    <hyperlink ref="L44" r:id="rId58"/>
+    <hyperlink ref="L48" r:id="rId59"/>
+    <hyperlink ref="L49" r:id="rId60"/>
+    <hyperlink ref="L51" r:id="rId61"/>
+    <hyperlink ref="L52" r:id="rId62"/>
+    <hyperlink ref="L53" r:id="rId63"/>
+    <hyperlink ref="L54" r:id="rId64"/>
+    <hyperlink ref="L55" r:id="rId65"/>
+    <hyperlink ref="L56" r:id="rId66"/>
+    <hyperlink ref="L57" r:id="rId67"/>
+    <hyperlink ref="L58" r:id="rId68"/>
+    <hyperlink ref="L59" r:id="rId69"/>
+    <hyperlink ref="L62" r:id="rId70"/>
+    <hyperlink ref="L63" r:id="rId71"/>
+    <hyperlink ref="L64" r:id="rId72"/>
+    <hyperlink ref="L65" r:id="rId73"/>
+    <hyperlink ref="L66" r:id="rId74"/>
+    <hyperlink ref="L68" r:id="rId75"/>
+    <hyperlink ref="L69" r:id="rId76"/>
+    <hyperlink ref="L74" r:id="rId77"/>
+    <hyperlink ref="L75" r:id="rId78"/>
+    <hyperlink ref="L76" r:id="rId79"/>
+    <hyperlink ref="L77" r:id="rId80"/>
+    <hyperlink ref="L81" r:id="rId81"/>
+    <hyperlink ref="L83" r:id="rId82"/>
+    <hyperlink ref="L85" r:id="rId83"/>
+    <hyperlink ref="L88" r:id="rId84"/>
+    <hyperlink ref="L87" r:id="rId85"/>
+    <hyperlink ref="L89" r:id="rId86"/>
+    <hyperlink ref="L90" r:id="rId87"/>
+    <hyperlink ref="L91" r:id="rId88"/>
+    <hyperlink ref="L92" r:id="rId89"/>
+    <hyperlink ref="L93" r:id="rId90"/>
+    <hyperlink ref="L95" r:id="rId91"/>
+    <hyperlink ref="L96" r:id="rId92"/>
+    <hyperlink ref="L97" r:id="rId93"/>
+    <hyperlink ref="L98" r:id="rId94"/>
+    <hyperlink ref="L99" r:id="rId95"/>
+    <hyperlink ref="L100" r:id="rId96"/>
+    <hyperlink ref="L101" r:id="rId97"/>
+    <hyperlink ref="L102" r:id="rId98"/>
+    <hyperlink ref="L103" r:id="rId99"/>
+    <hyperlink ref="L104" r:id="rId100"/>
+    <hyperlink ref="L105" r:id="rId101"/>
+    <hyperlink ref="L106" r:id="rId102"/>
+    <hyperlink ref="L108" r:id="rId103"/>
+    <hyperlink ref="L109" r:id="rId104"/>
+    <hyperlink ref="L111" r:id="rId105"/>
+    <hyperlink ref="L112" r:id="rId106"/>
+    <hyperlink ref="L113" r:id="rId107"/>
+    <hyperlink ref="L114" r:id="rId108"/>
+    <hyperlink ref="L115" r:id="rId109"/>
+    <hyperlink ref="L116" r:id="rId110"/>
+    <hyperlink ref="L117" r:id="rId111"/>
+    <hyperlink ref="L118" r:id="rId112"/>
+    <hyperlink ref="L119" r:id="rId113"/>
+    <hyperlink ref="L120" r:id="rId114"/>
+    <hyperlink ref="L122" r:id="rId115"/>
+    <hyperlink ref="L123" r:id="rId116"/>
+    <hyperlink ref="L124" r:id="rId117"/>
+    <hyperlink ref="L125" r:id="rId118"/>
+    <hyperlink ref="L126" r:id="rId119"/>
+    <hyperlink ref="L127" r:id="rId120"/>
+    <hyperlink ref="L128" r:id="rId121"/>
+    <hyperlink ref="L129" r:id="rId122"/>
+    <hyperlink ref="L130" r:id="rId123"/>
+    <hyperlink ref="L131" r:id="rId124"/>
+    <hyperlink ref="L132" r:id="rId125"/>
+    <hyperlink ref="L133" r:id="rId126"/>
+    <hyperlink ref="L134" r:id="rId127"/>
+    <hyperlink ref="L135" r:id="rId128"/>
+    <hyperlink ref="L136" r:id="rId129"/>
+    <hyperlink ref="L137" r:id="rId130"/>
+    <hyperlink ref="L138" r:id="rId131"/>
+    <hyperlink ref="L139" r:id="rId132"/>
+    <hyperlink ref="L140" r:id="rId133"/>
+    <hyperlink ref="L141" r:id="rId134"/>
+    <hyperlink ref="L142" r:id="rId135"/>
+    <hyperlink ref="L143" r:id="rId136"/>
+    <hyperlink ref="L144" r:id="rId137"/>
+    <hyperlink ref="L145" r:id="rId138"/>
+    <hyperlink ref="L146" r:id="rId139"/>
+    <hyperlink ref="L147" r:id="rId140"/>
+    <hyperlink ref="L148" r:id="rId141"/>
+    <hyperlink ref="L149" r:id="rId142"/>
+    <hyperlink ref="L150" r:id="rId143"/>
+    <hyperlink ref="L151" r:id="rId144"/>
+    <hyperlink ref="L152" r:id="rId145"/>
+    <hyperlink ref="L153" r:id="rId146"/>
+    <hyperlink ref="L154" r:id="rId147"/>
+    <hyperlink ref="L155" r:id="rId148"/>
+    <hyperlink ref="L156" r:id="rId149"/>
+    <hyperlink ref="L157" r:id="rId150"/>
+    <hyperlink ref="L158" r:id="rId151"/>
+    <hyperlink ref="L159" r:id="rId152"/>
+    <hyperlink ref="L160" r:id="rId153"/>
+    <hyperlink ref="L71" r:id="rId154"/>
+    <hyperlink ref="L166" r:id="rId155"/>
+    <hyperlink ref="L165" r:id="rId156"/>
+    <hyperlink ref="L167" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="716">
   <si>
     <t>#</t>
   </si>
@@ -773,18 +778,9 @@
     <t>Korean Hroparts Elec</t>
   </si>
   <si>
-    <t>Coaxial Connector</t>
-  </si>
-  <si>
     <t>J8</t>
   </si>
   <si>
-    <t>1 Inner bore MCX/MMCX Board Edge Bend 6.8mm 6GHz 50Ω 3.45mm Plugin RF Connectors / Coaxial Connectors ROHS</t>
-  </si>
-  <si>
-    <t>BWMMCX-KWE</t>
-  </si>
-  <si>
     <t>BAT WIRELESS</t>
   </si>
   <si>
@@ -959,21 +955,12 @@
     <t>Omron</t>
   </si>
   <si>
-    <t>Common Mode Filter</t>
-  </si>
-  <si>
     <t>L1, L2, L3, L4</t>
   </si>
   <si>
     <t>CMC 100MA 2LN 90 OHM SMD</t>
   </si>
   <si>
-    <t>MCZ1210DH900L2TA0G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obsolete Part </t>
-  </si>
-  <si>
     <t>Inductor</t>
   </si>
   <si>
@@ -1724,13 +1711,7 @@
     <t>U2</t>
   </si>
   <si>
-    <t>IC TRANSCEIVER FULL 2/2 16SOIC</t>
-  </si>
-  <si>
     <t>SOIC-16</t>
-  </si>
-  <si>
-    <t>MAX3232IDR</t>
   </si>
   <si>
     <t>Texas Instruments</t>
@@ -2176,21 +2157,41 @@
   </si>
   <si>
     <t>Single Component Price</t>
+  </si>
+  <si>
+    <t>HJ-SMA175</t>
+  </si>
+  <si>
+    <t>MCZ1210CH900CPTA0G</t>
+  </si>
+  <si>
+    <t>MAX3232EIDR</t>
+  </si>
+  <si>
+    <t>SMA Connector</t>
+  </si>
+  <si>
+    <t>1 Inner bore SMA Board Edge Bend 11mm 5.35mm Plugin RF Connectors / Coaxial Connectors ROHS</t>
+  </si>
+  <si>
+    <t>HJ Tech</t>
+  </si>
+  <si>
+    <t>Common Mode Choke</t>
+  </si>
+  <si>
+    <t>IC RS232 LINE DVR/RCVR 16-SOIC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2203,21 +2204,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2225,20 +2226,20 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2246,7 +2247,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2254,7 +2255,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2262,7 +2263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2270,7 +2271,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2278,7 +2279,7 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2286,7 +2287,7 @@
       <sz val="12"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2295,7 +2296,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2304,7 +2305,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2312,147 +2313,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2473,204 +2338,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -2826,253 +2499,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -3114,25 +2548,13 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3176,116 +2598,61 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3543,32 +2910,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:S169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.57142857142857" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7142857142857" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="4" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="33.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="14.7142857142857" customWidth="1"/>
-    <col min="9" max="9" width="8.57142857142857" customWidth="1"/>
-    <col min="10" max="10" width="8.71428571428571" customWidth="1"/>
-    <col min="11" max="11" width="18.2857142857143" customWidth="1"/>
-    <col min="12" max="12" width="8.71428571428571" customWidth="1"/>
-    <col min="13" max="13" width="22.5714285714286" customWidth="1"/>
-    <col min="14" max="14" width="19.2857142857143" customWidth="1"/>
-    <col min="15" max="15" width="29.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.42578125" customWidth="1"/>
+    <col min="17" max="17" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:15">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
       <c r="A1" s="5"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3577,15 +2946,15 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-    </row>
-    <row r="2" ht="15.75" spans="1:15">
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1">
       <c r="A2" s="5"/>
       <c r="B2" s="8" t="s">
         <v>0</v>
@@ -3630,7 +2999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="132.75" spans="1:15">
+    <row r="3" spans="1:15" ht="132.75" thickBot="1">
       <c r="A3" s="5"/>
       <c r="B3" s="10">
         <f t="shared" ref="B3:B34" si="0">ROW(B3)-ROW($B$2)</f>
@@ -3664,19 +3033,19 @@
         <f>3*J3</f>
         <v>291</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="19">
-        <v>0.0107</v>
-      </c>
-      <c r="N3" s="19">
+      <c r="L3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="18">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="N3" s="18">
         <f>M3*K3</f>
-        <v>3.1137</v>
+        <v>3.1137000000000001</v>
       </c>
       <c r="O3" s="12"/>
     </row>
-    <row r="4" ht="15.75" spans="1:15">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1">
       <c r="A4" s="5"/>
       <c r="B4" s="10">
         <f t="shared" si="0"/>
@@ -3710,19 +3079,19 @@
         <f t="shared" ref="K4:K67" si="1">3*J4</f>
         <v>6</v>
       </c>
-      <c r="L4" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="19">
+      <c r="L4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="18">
         <v>0.1</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="18">
         <f t="shared" ref="N4:N15" si="2">M4*K4</f>
         <v>0.6</v>
       </c>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" ht="15.75" spans="1:15">
+    <row r="5" spans="1:15" ht="15.75" thickBot="1">
       <c r="A5" s="5"/>
       <c r="B5" s="10">
         <f t="shared" si="0"/>
@@ -3756,19 +3125,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="19">
-        <v>0.209</v>
-      </c>
-      <c r="N5" s="19">
+      <c r="L5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="18">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="N5" s="18">
         <f t="shared" si="2"/>
-        <v>4.389</v>
+        <v>4.3890000000000002</v>
       </c>
       <c r="O5" s="12"/>
     </row>
-    <row r="6" ht="15.75" spans="1:15">
+    <row r="6" spans="1:15" ht="15.75" thickBot="1">
       <c r="A6" s="5"/>
       <c r="B6" s="10">
         <f t="shared" si="0"/>
@@ -3802,19 +3171,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L6" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0.145</v>
-      </c>
-      <c r="N6" s="19">
+      <c r="L6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="N6" s="18">
         <f t="shared" si="2"/>
         <v>1.74</v>
       </c>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" ht="15.75" spans="1:15">
+    <row r="7" spans="1:15" ht="15.75" thickBot="1">
       <c r="A7" s="5"/>
       <c r="B7" s="10">
         <f t="shared" si="0"/>
@@ -3848,19 +3217,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L7" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="19">
-        <v>0.456</v>
-      </c>
-      <c r="N7" s="19">
+      <c r="L7" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="N7" s="18">
         <f t="shared" si="2"/>
-        <v>5.472</v>
+        <v>5.4720000000000004</v>
       </c>
       <c r="O7" s="12"/>
     </row>
-    <row r="8" ht="15.75" spans="1:15">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1">
       <c r="A8" s="5"/>
       <c r="B8" s="10">
         <f t="shared" si="0"/>
@@ -3894,19 +3263,19 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L8" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="19">
-        <v>0.28</v>
-      </c>
-      <c r="N8" s="19">
+      <c r="L8" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N8" s="18">
         <f t="shared" si="2"/>
         <v>2.52</v>
       </c>
       <c r="O8" s="15"/>
     </row>
-    <row r="9" ht="15.75" spans="1:15">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1">
       <c r="A9" s="5"/>
       <c r="B9" s="10">
         <f t="shared" si="0"/>
@@ -3940,19 +3309,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="19">
-        <v>0.173</v>
-      </c>
-      <c r="N9" s="19">
+      <c r="L9" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="N9" s="18">
         <f t="shared" si="2"/>
-        <v>2.076</v>
+        <v>2.0760000000000001</v>
       </c>
       <c r="O9" s="12"/>
     </row>
-    <row r="10" ht="24.75" spans="1:15">
+    <row r="10" spans="1:15" ht="24.75" thickBot="1">
       <c r="A10" s="5"/>
       <c r="B10" s="10">
         <f t="shared" si="0"/>
@@ -3986,19 +3355,19 @@
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="L10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="19">
-        <v>0.056</v>
-      </c>
-      <c r="N10" s="19">
+      <c r="L10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="18">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="N10" s="18">
         <f t="shared" si="2"/>
-        <v>2.184</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="O10" s="15"/>
     </row>
-    <row r="11" ht="15.75" spans="1:15">
+    <row r="11" spans="1:15" ht="15.75" thickBot="1">
       <c r="A11" s="5"/>
       <c r="B11" s="10">
         <f t="shared" si="0"/>
@@ -4032,19 +3401,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="19">
+      <c r="L11" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="18">
         <v>0.224</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="18">
         <f t="shared" si="2"/>
-        <v>2.688</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="O11" s="12"/>
     </row>
-    <row r="12" ht="15.75" spans="1:15">
+    <row r="12" spans="1:15" ht="15.75" thickBot="1">
       <c r="A12" s="5"/>
       <c r="B12" s="10">
         <f t="shared" si="0"/>
@@ -4078,19 +3447,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L12" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="19">
+      <c r="L12" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="18">
         <v>0.753</v>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="18">
         <f t="shared" si="2"/>
-        <v>9.036</v>
+        <v>9.0359999999999996</v>
       </c>
       <c r="O12" s="15"/>
     </row>
-    <row r="13" ht="15.75" spans="1:15">
+    <row r="13" spans="1:15" ht="15.75" thickBot="1">
       <c r="A13" s="5"/>
       <c r="B13" s="10">
         <f t="shared" si="0"/>
@@ -4124,19 +3493,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L13" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="19">
+      <c r="L13" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="18">
         <v>0.22</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="18">
         <f t="shared" si="2"/>
         <v>1.32</v>
       </c>
       <c r="O13" s="12"/>
     </row>
-    <row r="14" ht="15.75" spans="1:15">
+    <row r="14" spans="1:15" ht="15.75" thickBot="1">
       <c r="A14" s="5"/>
       <c r="B14" s="10">
         <f t="shared" si="0"/>
@@ -4170,19 +3539,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L14" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="19">
+      <c r="L14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="18">
         <v>0.1</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="18">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="O14" s="15"/>
     </row>
-    <row r="15" ht="15.75" spans="1:15">
+    <row r="15" spans="1:15" ht="15.75" thickBot="1">
       <c r="A15" s="5"/>
       <c r="B15" s="10">
         <f t="shared" si="0"/>
@@ -4216,19 +3585,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L15" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="19">
+      <c r="L15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="18">
         <v>0.1</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="18">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="O15" s="12"/>
     </row>
-    <row r="16" ht="15.75" spans="1:15">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1">
       <c r="A16" s="5"/>
       <c r="B16" s="10">
         <f t="shared" si="0"/>
@@ -4262,19 +3631,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L16" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="19">
+      <c r="L16" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="18">
         <v>0.1</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="18">
         <f t="shared" ref="N16:N29" si="3">M16*K16</f>
         <v>0.6</v>
       </c>
       <c r="O16" s="15"/>
     </row>
-    <row r="17" ht="15.75" spans="1:15">
+    <row r="17" spans="1:15" ht="15.75" thickBot="1">
       <c r="A17" s="5"/>
       <c r="B17" s="10">
         <f t="shared" si="0"/>
@@ -4308,19 +3677,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L17" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="19">
+      <c r="L17" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="18">
         <v>2.37</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="18">
         <f t="shared" si="3"/>
         <v>7.11</v>
       </c>
       <c r="O17" s="12"/>
     </row>
-    <row r="18" ht="15.75" spans="1:15">
+    <row r="18" spans="1:15" ht="15.75" thickBot="1">
       <c r="A18" s="5"/>
       <c r="B18" s="10">
         <f t="shared" si="0"/>
@@ -4354,19 +3723,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L18" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="19">
+      <c r="L18" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="18">
         <v>0.1</v>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="18">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="O18" s="15"/>
     </row>
-    <row r="19" ht="15.75" spans="1:15">
+    <row r="19" spans="1:15" ht="15.75" thickBot="1">
       <c r="A19" s="5"/>
       <c r="B19" s="10">
         <f t="shared" si="0"/>
@@ -4400,19 +3769,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L19" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="19">
+      <c r="L19" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="18">
         <v>0.1</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="18">
         <f t="shared" si="3"/>
         <v>0.3</v>
       </c>
       <c r="O19" s="12"/>
     </row>
-    <row r="20" ht="15.75" spans="1:15">
+    <row r="20" spans="1:15" ht="15.75" thickBot="1">
       <c r="A20" s="5"/>
       <c r="B20" s="10">
         <f t="shared" si="0"/>
@@ -4446,19 +3815,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L20" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="19">
+      <c r="L20" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="18">
         <v>0.69</v>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="18">
         <f t="shared" si="3"/>
-        <v>4.14</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="O20" s="15"/>
     </row>
-    <row r="21" ht="15.75" spans="1:15">
+    <row r="21" spans="1:15" ht="15.75" thickBot="1">
       <c r="A21" s="5"/>
       <c r="B21" s="10">
         <f t="shared" si="0"/>
@@ -4492,19 +3861,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L21" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="19">
+      <c r="L21" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="18">
         <v>0.1</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="18">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O21" s="12"/>
     </row>
-    <row r="22" ht="15.75" spans="1:15">
+    <row r="22" spans="1:15" ht="15.75" thickBot="1">
       <c r="A22" s="5"/>
       <c r="B22" s="10">
         <f t="shared" si="0"/>
@@ -4538,19 +3907,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L22" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="19">
+      <c r="L22" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="18">
         <v>0.26</v>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="18">
         <f t="shared" si="3"/>
         <v>0.78</v>
       </c>
       <c r="O22" s="15"/>
     </row>
-    <row r="23" ht="15.75" spans="1:15">
+    <row r="23" spans="1:15" ht="15.75" thickBot="1">
       <c r="A23" s="5"/>
       <c r="B23" s="10">
         <f t="shared" si="0"/>
@@ -4584,19 +3953,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L23" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M23" s="19">
+      <c r="L23" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="18">
         <v>0.11</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="18">
         <f t="shared" si="3"/>
         <v>0.66</v>
       </c>
       <c r="O23" s="12"/>
     </row>
-    <row r="24" ht="24.75" spans="1:15">
+    <row r="24" spans="1:15" ht="24.75" thickBot="1">
       <c r="A24" s="5"/>
       <c r="B24" s="10">
         <f t="shared" si="0"/>
@@ -4630,19 +3999,19 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L24" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="19">
+      <c r="L24" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="18">
         <v>0.27</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="18">
         <f t="shared" si="3"/>
         <v>8.1</v>
       </c>
       <c r="O24" s="15"/>
     </row>
-    <row r="25" ht="36.75" spans="1:15">
+    <row r="25" spans="1:15" ht="36.75" thickBot="1">
       <c r="A25" s="5"/>
       <c r="B25" s="10">
         <f t="shared" si="0"/>
@@ -4676,19 +4045,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M25" s="19">
-        <v>0.0568</v>
-      </c>
-      <c r="N25" s="19">
+      <c r="M25" s="18">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="N25" s="18">
         <f t="shared" si="3"/>
         <v>0.1704</v>
       </c>
       <c r="O25" s="12"/>
     </row>
-    <row r="26" ht="15.75" spans="1:15">
+    <row r="26" spans="1:15" ht="15.75" thickBot="1">
       <c r="A26" s="5"/>
       <c r="B26" s="10">
         <f t="shared" si="0"/>
@@ -4722,19 +4091,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L26" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="19">
-        <v>0.082</v>
-      </c>
-      <c r="N26" s="19">
+      <c r="L26" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="18">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="N26" s="18">
         <f t="shared" si="3"/>
         <v>1.722</v>
       </c>
       <c r="O26" s="15"/>
     </row>
-    <row r="27" ht="15.75" spans="1:15">
+    <row r="27" spans="1:15" ht="15.75" thickBot="1">
       <c r="A27" s="5"/>
       <c r="B27" s="10">
         <f t="shared" si="0"/>
@@ -4768,19 +4137,19 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L27" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="19">
+      <c r="L27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="18">
         <v>0.129</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="18">
         <f t="shared" si="3"/>
         <v>1.548</v>
       </c>
       <c r="O27" s="12"/>
     </row>
-    <row r="28" ht="15.75" spans="1:15">
+    <row r="28" spans="1:15" ht="15.75" thickBot="1">
       <c r="A28" s="5"/>
       <c r="B28" s="10">
         <f t="shared" si="0"/>
@@ -4814,19 +4183,19 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="L28" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="19">
-        <v>0.021</v>
-      </c>
-      <c r="N28" s="19">
+      <c r="L28" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="18">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="N28" s="18">
         <f t="shared" si="3"/>
         <v>0.441</v>
       </c>
       <c r="O28" s="15"/>
     </row>
-    <row r="29" ht="24.75" spans="1:15">
+    <row r="29" spans="1:15" ht="24.75" thickBot="1">
       <c r="A29" s="5"/>
       <c r="B29" s="10">
         <f t="shared" si="0"/>
@@ -4860,19 +4229,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L29" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="19">
+      <c r="L29" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="18">
         <v>0.1</v>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="18">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="O29" s="12"/>
     </row>
-    <row r="30" ht="15.75" spans="1:15">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1">
       <c r="A30" s="5"/>
       <c r="B30" s="10">
         <f t="shared" si="0"/>
@@ -4906,19 +4275,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L30" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="19">
+      <c r="L30" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="18">
         <v>0.1</v>
       </c>
-      <c r="N30" s="19">
+      <c r="N30" s="18">
         <f t="shared" ref="N30:N39" si="4">M30*K30</f>
         <v>0.6</v>
       </c>
       <c r="O30" s="15"/>
     </row>
-    <row r="31" ht="15.75" spans="1:15">
+    <row r="31" spans="1:15" ht="15.75" thickBot="1">
       <c r="A31" s="5"/>
       <c r="B31" s="10">
         <f t="shared" si="0"/>
@@ -4952,19 +4321,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L31" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="19">
+      <c r="L31" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="18">
         <v>0.17</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="18">
         <f t="shared" si="4"/>
         <v>0.51</v>
       </c>
       <c r="O31" s="12"/>
     </row>
-    <row r="32" ht="15.75" spans="1:15">
+    <row r="32" spans="1:15" ht="15.75" thickBot="1">
       <c r="A32" s="5"/>
       <c r="B32" s="10">
         <f t="shared" si="0"/>
@@ -4998,19 +4367,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L32" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="19">
+      <c r="L32" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="18">
         <v>0.1</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="18">
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
       <c r="O32" s="15"/>
     </row>
-    <row r="33" ht="15.75" spans="1:15">
+    <row r="33" spans="1:15" ht="15.75" thickBot="1">
       <c r="A33" s="5"/>
       <c r="B33" s="10">
         <f t="shared" si="0"/>
@@ -5044,19 +4413,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L33" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="19">
+      <c r="L33" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="18">
         <v>0.1</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N33" s="18">
         <f t="shared" si="4"/>
         <v>0.3</v>
       </c>
       <c r="O33" s="12"/>
     </row>
-    <row r="34" ht="48.75" spans="1:15">
+    <row r="34" spans="1:15" ht="48.75" thickBot="1">
       <c r="A34" s="5"/>
       <c r="B34" s="10">
         <f t="shared" si="0"/>
@@ -5090,19 +4459,19 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="L34" s="20" t="s">
+      <c r="L34" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M34" s="19">
-        <v>0.0083</v>
-      </c>
-      <c r="N34" s="19">
+      <c r="M34" s="18">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="N34" s="18">
         <f t="shared" si="4"/>
         <v>0.747</v>
       </c>
       <c r="O34" s="15"/>
     </row>
-    <row r="35" ht="24.75" spans="1:15">
+    <row r="35" spans="1:15" ht="24.75" thickBot="1">
       <c r="A35" s="5"/>
       <c r="B35" s="10">
         <f t="shared" ref="B35:B57" si="5">ROW(B35)-ROW($B$2)</f>
@@ -5136,19 +4505,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L35" s="20" t="s">
+      <c r="L35" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M35" s="19">
-        <v>0.0626</v>
-      </c>
-      <c r="N35" s="19">
+      <c r="M35" s="18">
+        <v>6.2600000000000003E-2</v>
+      </c>
+      <c r="N35" s="18">
         <f t="shared" si="4"/>
-        <v>0.3756</v>
+        <v>0.37559999999999999</v>
       </c>
       <c r="O35" s="12"/>
     </row>
-    <row r="36" ht="15.75" spans="1:15">
+    <row r="36" spans="1:15" ht="15.75" thickBot="1">
       <c r="A36" s="5"/>
       <c r="B36" s="10">
         <f t="shared" si="5"/>
@@ -5182,19 +4551,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L36" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="19">
+      <c r="L36" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="18">
         <v>0.37</v>
       </c>
-      <c r="N36" s="19">
+      <c r="N36" s="18">
         <f t="shared" si="4"/>
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="O36" s="15"/>
     </row>
-    <row r="37" ht="24.75" spans="1:15">
+    <row r="37" spans="1:15" ht="24.75" thickBot="1">
       <c r="A37" s="5"/>
       <c r="B37" s="10">
         <f t="shared" si="5"/>
@@ -5228,19 +4597,19 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="L37" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0.305</v>
-      </c>
-      <c r="N37" s="19">
+      <c r="L37" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="N37" s="18">
         <f t="shared" si="4"/>
         <v>5.49</v>
       </c>
       <c r="O37" s="12"/>
     </row>
-    <row r="38" ht="24.75" spans="1:15">
+    <row r="38" spans="1:15" ht="24.75" thickBot="1">
       <c r="A38" s="5"/>
       <c r="B38" s="10">
         <f t="shared" si="5"/>
@@ -5274,19 +4643,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L38" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="19">
+      <c r="L38" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="18">
         <v>0.21</v>
       </c>
-      <c r="N38" s="19">
+      <c r="N38" s="18">
         <f t="shared" si="4"/>
         <v>0.63</v>
       </c>
       <c r="O38" s="15"/>
     </row>
-    <row r="39" ht="36.75" spans="1:15">
+    <row r="39" spans="1:15" ht="36.75" thickBot="1">
       <c r="A39" s="5"/>
       <c r="B39" s="10">
         <f t="shared" si="5"/>
@@ -5320,19 +4689,19 @@
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="L39" s="20" t="s">
+      <c r="L39" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M39" s="19">
-        <v>0.0191</v>
-      </c>
-      <c r="N39" s="19">
+      <c r="M39" s="18">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="N39" s="18">
         <f t="shared" si="4"/>
         <v>1.2033</v>
       </c>
       <c r="O39" s="12"/>
     </row>
-    <row r="40" ht="24.75" spans="1:15">
+    <row r="40" spans="1:15" ht="24.75" thickBot="1">
       <c r="A40" s="5"/>
       <c r="B40" s="10">
         <f t="shared" si="5"/>
@@ -5366,19 +4735,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L40" s="20" t="s">
+      <c r="L40" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M40" s="19">
-        <v>0.0794</v>
-      </c>
-      <c r="N40" s="19">
+      <c r="M40" s="18">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="N40" s="18">
         <f t="shared" ref="N40:N55" si="6">M40*K40</f>
         <v>0.2382</v>
       </c>
       <c r="O40" s="15"/>
     </row>
-    <row r="41" ht="36.75" spans="1:15">
+    <row r="41" spans="1:15" ht="36.75" thickBot="1">
       <c r="A41" s="5"/>
       <c r="B41" s="10">
         <f t="shared" si="5"/>
@@ -5412,19 +4781,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L41" s="20" t="s">
+      <c r="L41" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M41" s="19">
-        <v>0.0291</v>
-      </c>
-      <c r="N41" s="19">
+      <c r="M41" s="18">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="N41" s="18">
         <f t="shared" si="6"/>
-        <v>0.1746</v>
+        <v>0.17460000000000001</v>
       </c>
       <c r="O41" s="12"/>
     </row>
-    <row r="42" ht="15.75" spans="1:15">
+    <row r="42" spans="1:15" ht="15.75" thickBot="1">
       <c r="A42" s="5"/>
       <c r="B42" s="10">
         <f t="shared" si="5"/>
@@ -5458,19 +4827,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L42" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="19">
+      <c r="L42" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="18">
         <v>0.34</v>
       </c>
-      <c r="N42" s="19">
+      <c r="N42" s="18">
         <f t="shared" si="6"/>
         <v>2.04</v>
       </c>
       <c r="O42" s="15"/>
     </row>
-    <row r="43" ht="15.75" spans="1:15">
+    <row r="43" spans="1:15" ht="15.75" thickBot="1">
       <c r="A43" s="5"/>
       <c r="B43" s="10">
         <f t="shared" si="5"/>
@@ -5504,19 +4873,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L43" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="19">
+      <c r="L43" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="18">
         <v>1.66</v>
       </c>
-      <c r="N43" s="19">
+      <c r="N43" s="18">
         <f t="shared" si="6"/>
-        <v>4.98</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="O43" s="12"/>
     </row>
-    <row r="44" ht="24.75" spans="1:15">
+    <row r="44" spans="1:15" ht="24.75" thickBot="1">
       <c r="A44" s="5"/>
       <c r="B44" s="10">
         <f t="shared" si="5"/>
@@ -5550,19 +4919,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L44" s="20" t="s">
+      <c r="L44" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M44" s="19">
-        <v>0.0394</v>
-      </c>
-      <c r="N44" s="19">
+      <c r="M44" s="18">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N44" s="18">
         <f t="shared" si="6"/>
         <v>0.1182</v>
       </c>
       <c r="O44" s="15"/>
     </row>
-    <row r="45" ht="15.75" spans="1:15">
+    <row r="45" spans="1:15" ht="15.75" thickBot="1">
       <c r="A45" s="5"/>
       <c r="B45" s="10">
         <f t="shared" si="5"/>
@@ -5596,19 +4965,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L45" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="19">
+      <c r="L45" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="18">
         <v>0.12</v>
       </c>
-      <c r="N45" s="19">
+      <c r="N45" s="18">
         <f t="shared" si="6"/>
         <v>0.36</v>
       </c>
       <c r="O45" s="12"/>
     </row>
-    <row r="46" ht="15.75" spans="1:15">
+    <row r="46" spans="1:15" ht="15.75" thickBot="1">
       <c r="A46" s="5"/>
       <c r="B46" s="10">
         <f t="shared" si="5"/>
@@ -5642,19 +5011,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L46" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="19">
+      <c r="L46" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="18">
         <v>0.1</v>
       </c>
-      <c r="N46" s="19">
+      <c r="N46" s="18">
         <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="O46" s="15"/>
     </row>
-    <row r="47" ht="15.75" spans="1:15">
+    <row r="47" spans="1:15" ht="15.75" thickBot="1">
       <c r="A47" s="5"/>
       <c r="B47" s="10">
         <f t="shared" si="5"/>
@@ -5688,19 +5057,19 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L47" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="19">
+      <c r="L47" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="18">
         <v>0.32</v>
       </c>
-      <c r="N47" s="19">
+      <c r="N47" s="18">
         <f t="shared" si="6"/>
         <v>1.92</v>
       </c>
       <c r="O47" s="12"/>
     </row>
-    <row r="48" ht="36.75" spans="1:15">
+    <row r="48" spans="1:15" ht="36.75" thickBot="1">
       <c r="A48" s="5"/>
       <c r="B48" s="10">
         <f t="shared" si="5"/>
@@ -5734,19 +5103,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L48" s="20" t="s">
+      <c r="L48" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M48" s="19">
-        <v>0.0741</v>
-      </c>
-      <c r="N48" s="19">
+      <c r="M48" s="18">
+        <v>7.4099999999999999E-2</v>
+      </c>
+      <c r="N48" s="18">
         <f t="shared" si="6"/>
         <v>0.2223</v>
       </c>
       <c r="O48" s="12"/>
     </row>
-    <row r="49" ht="24.75" spans="1:15">
+    <row r="49" spans="1:15" ht="24.75" thickBot="1">
       <c r="A49" s="5"/>
       <c r="B49" s="10">
         <f t="shared" si="5"/>
@@ -5780,19 +5149,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L49" s="20" t="s">
+      <c r="L49" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="18">
         <v>4.2946</v>
       </c>
-      <c r="N49" s="19">
+      <c r="N49" s="18">
         <f t="shared" si="6"/>
-        <v>12.8838</v>
+        <v>12.883800000000001</v>
       </c>
       <c r="O49" s="15"/>
     </row>
-    <row r="50" ht="24.75" spans="1:15">
+    <row r="50" spans="1:15" ht="24.75" thickBot="1">
       <c r="A50" s="5"/>
       <c r="B50" s="10">
         <f t="shared" si="5"/>
@@ -5826,19 +5195,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L50" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="19">
+      <c r="L50" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="18">
         <v>1.26</v>
       </c>
-      <c r="N50" s="19">
+      <c r="N50" s="18">
         <f t="shared" si="6"/>
         <v>3.78</v>
       </c>
       <c r="O50" s="12"/>
     </row>
-    <row r="51" ht="36.75" spans="1:15">
+    <row r="51" spans="1:15" ht="36.75" thickBot="1">
       <c r="A51" s="5"/>
       <c r="B51" s="10">
         <f t="shared" si="5"/>
@@ -5872,19 +5241,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L51" s="20" t="s">
+      <c r="L51" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M51" s="19">
-        <v>0.0152</v>
-      </c>
-      <c r="N51" s="19">
+      <c r="M51" s="18">
+        <v>1.52E-2</v>
+      </c>
+      <c r="N51" s="18">
         <f t="shared" si="6"/>
-        <v>0.0456</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="O51" s="15"/>
     </row>
-    <row r="52" ht="36.75" spans="1:15">
+    <row r="52" spans="1:15" ht="36.75" thickBot="1">
       <c r="A52" s="5"/>
       <c r="B52" s="10">
         <f t="shared" si="5"/>
@@ -5918,19 +5287,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L52" s="20" t="s">
+      <c r="L52" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M52" s="19">
-        <v>0.0192</v>
-      </c>
-      <c r="N52" s="19">
+      <c r="M52" s="18">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="N52" s="18">
         <f t="shared" si="6"/>
-        <v>0.0576</v>
+        <v>5.7599999999999998E-2</v>
       </c>
       <c r="O52" s="12"/>
     </row>
-    <row r="53" ht="36.75" spans="1:15">
+    <row r="53" spans="1:15" ht="48.75" thickBot="1">
       <c r="A53" s="5"/>
       <c r="B53" s="10">
         <f t="shared" si="5"/>
@@ -5964,19 +5333,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L53" s="20" t="s">
+      <c r="L53" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="18">
         <v>0.1726</v>
       </c>
-      <c r="N53" s="19">
+      <c r="N53" s="18">
         <f t="shared" si="6"/>
-        <v>0.5178</v>
+        <v>0.51780000000000004</v>
       </c>
       <c r="O53" s="15"/>
     </row>
-    <row r="54" ht="24.75" spans="1:15">
+    <row r="54" spans="1:15" ht="24.75" thickBot="1">
       <c r="A54" s="5"/>
       <c r="B54" s="10">
         <f t="shared" si="5"/>
@@ -6010,19 +5379,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L54" s="20" t="s">
+      <c r="L54" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M54" s="19">
-        <v>0.7058</v>
-      </c>
-      <c r="N54" s="19">
+      <c r="M54" s="18">
+        <v>0.70579999999999998</v>
+      </c>
+      <c r="N54" s="18">
         <f t="shared" si="6"/>
-        <v>2.1174</v>
+        <v>2.1173999999999999</v>
       </c>
       <c r="O54" s="12"/>
     </row>
-    <row r="55" ht="36.75" spans="1:15">
+    <row r="55" spans="1:15" ht="48.75" thickBot="1">
       <c r="A55" s="5"/>
       <c r="B55" s="10">
         <f t="shared" si="5"/>
@@ -6056,41 +5425,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L55" s="20" t="s">
+      <c r="L55" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M55" s="19">
-        <v>0.4297</v>
-      </c>
-      <c r="N55" s="19">
+      <c r="M55" s="18">
+        <v>0.42970000000000003</v>
+      </c>
+      <c r="N55" s="18">
         <f t="shared" si="6"/>
-        <v>1.2891</v>
+        <v>1.2890999999999999</v>
       </c>
       <c r="O55" s="15"/>
     </row>
-    <row r="56" ht="48.75" spans="1:15">
+    <row r="56" spans="1:15" ht="36.75" thickBot="1">
       <c r="A56" s="5"/>
       <c r="B56" s="10">
         <f t="shared" si="5"/>
         <v>54</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="D56" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F56" s="12" t="s">
+      <c r="E56" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="F56" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G56" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>252</v>
+      <c r="G56" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>713</v>
       </c>
       <c r="I56" s="16" t="s">
         <v>150</v>
@@ -6102,41 +5471,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L56" s="20" t="s">
+      <c r="L56" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M56" s="19">
-        <v>0.5386</v>
-      </c>
-      <c r="N56" s="19">
+      <c r="M56" s="18">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="N56" s="18">
         <f t="shared" ref="N56:N119" si="7">M56*K56</f>
-        <v>1.6158</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="O56" s="12"/>
     </row>
-    <row r="57" ht="48.75" spans="1:15">
+    <row r="57" spans="1:15" ht="48.75" thickBot="1">
       <c r="A57" s="5"/>
       <c r="B57" s="10">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F57" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I57" s="16" t="s">
         <v>150</v>
@@ -6148,41 +5517,41 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L57" s="20" t="s">
+      <c r="L57" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M57" s="19">
-        <v>0.55</v>
-      </c>
-      <c r="N57" s="19">
+      <c r="M57" s="18">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N57" s="18">
         <f t="shared" si="7"/>
         <v>3.3</v>
       </c>
       <c r="O57" s="12"/>
     </row>
-    <row r="58" ht="60.75" spans="1:15">
+    <row r="58" spans="1:15" ht="60.75" thickBot="1">
       <c r="A58" s="5"/>
       <c r="B58" s="10">
         <f t="shared" ref="B58:B159" si="8">ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G58" s="16" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I58" s="16" t="s">
         <v>150</v>
@@ -6194,38 +5563,38 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L58" s="20" t="s">
+      <c r="L58" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M58" s="19">
-        <v>0.0987</v>
-      </c>
-      <c r="N58" s="19">
+      <c r="M58" s="18">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="N58" s="18">
         <f t="shared" si="7"/>
-        <v>1.4805</v>
+        <v>1.4804999999999999</v>
       </c>
       <c r="O58" s="15"/>
     </row>
-    <row r="59" ht="48.75" spans="1:15">
+    <row r="59" spans="1:15" ht="60.75" thickBot="1">
       <c r="A59" s="5"/>
       <c r="B59" s="10">
         <f t="shared" si="8"/>
         <v>57</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H59" s="12" t="s">
         <v>231</v>
@@ -6240,41 +5609,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L59" s="20" t="s">
+      <c r="L59" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M59" s="19">
-        <v>0.1892</v>
-      </c>
-      <c r="N59" s="19">
+      <c r="M59" s="18">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="N59" s="18">
         <f t="shared" si="7"/>
-        <v>0.5676</v>
+        <v>0.56759999999999999</v>
       </c>
       <c r="O59" s="12"/>
     </row>
-    <row r="60" ht="15.75" spans="1:15">
+    <row r="60" spans="1:15" ht="15.75" thickBot="1">
       <c r="A60" s="5"/>
       <c r="B60" s="10">
         <f t="shared" si="8"/>
         <v>58</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F60" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G60" s="16" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I60" s="16" t="s">
         <v>150</v>
@@ -6286,41 +5655,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L60" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="19">
+      <c r="L60" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="18">
         <v>1.32</v>
       </c>
-      <c r="N60" s="19">
+      <c r="N60" s="18">
         <f t="shared" si="7"/>
         <v>3.96</v>
       </c>
       <c r="O60" s="15"/>
     </row>
-    <row r="61" ht="15.75" spans="1:15">
+    <row r="61" spans="1:15" ht="15.75" thickBot="1">
       <c r="A61" s="5"/>
       <c r="B61" s="10">
         <f t="shared" si="8"/>
         <v>59</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F61" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I61" s="16" t="s">
         <v>150</v>
@@ -6332,19 +5701,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L61" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="19">
+      <c r="L61" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="18">
         <v>0.46</v>
       </c>
-      <c r="N61" s="19">
+      <c r="N61" s="18">
         <f t="shared" si="7"/>
         <v>1.38</v>
       </c>
       <c r="O61" s="12"/>
     </row>
-    <row r="62" ht="36.75" spans="1:15">
+    <row r="62" spans="1:15" ht="36.75" thickBot="1">
       <c r="A62" s="5"/>
       <c r="B62" s="10">
         <f t="shared" si="8"/>
@@ -6354,16 +5723,16 @@
         <v>227</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H62" s="15" t="s">
         <v>231</v>
@@ -6378,41 +5747,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L62" s="20" t="s">
+      <c r="L62" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M62" s="19">
-        <v>0.013</v>
-      </c>
-      <c r="N62" s="19">
+      <c r="M62" s="18">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N62" s="18">
         <f t="shared" si="7"/>
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="O62" s="15"/>
     </row>
-    <row r="63" ht="60.75" spans="1:15">
+    <row r="63" spans="1:15" ht="60.75" thickBot="1">
       <c r="A63" s="5"/>
       <c r="B63" s="10">
         <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>150</v>
@@ -6424,38 +5793,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L63" s="20" t="s">
+      <c r="L63" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M63" s="19">
-        <v>2.5538</v>
-      </c>
-      <c r="N63" s="19">
+      <c r="M63" s="18">
+        <v>2.5537999999999998</v>
+      </c>
+      <c r="N63" s="18">
         <f t="shared" si="7"/>
-        <v>15.3228</v>
+        <v>15.322800000000001</v>
       </c>
       <c r="O63" s="12"/>
     </row>
-    <row r="64" ht="48.75" spans="1:15">
+    <row r="64" spans="1:15" ht="48.75" thickBot="1">
       <c r="A64" s="5"/>
       <c r="B64" s="10">
         <f t="shared" si="8"/>
         <v>62</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F64" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H64" s="15" t="s">
         <v>231</v>
@@ -6470,19 +5839,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L64" s="20" t="s">
+      <c r="L64" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M64" s="19">
-        <v>0.0152</v>
-      </c>
-      <c r="N64" s="19">
+      <c r="M64" s="18">
+        <v>1.52E-2</v>
+      </c>
+      <c r="N64" s="18">
         <f t="shared" si="7"/>
-        <v>0.0456</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="O64" s="15"/>
     </row>
-    <row r="65" ht="36.75" spans="1:15">
+    <row r="65" spans="1:15" ht="36.75" thickBot="1">
       <c r="A65" s="5"/>
       <c r="B65" s="10">
         <f t="shared" si="8"/>
@@ -6492,16 +5861,16 @@
         <v>227</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>231</v>
@@ -6516,38 +5885,38 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L65" s="20" t="s">
+      <c r="L65" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M65" s="19">
-        <v>0.0167</v>
-      </c>
-      <c r="N65" s="19">
+      <c r="M65" s="18">
+        <v>1.67E-2</v>
+      </c>
+      <c r="N65" s="18">
         <f t="shared" si="7"/>
-        <v>0.0501</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="O65" s="12"/>
     </row>
-    <row r="66" ht="24.75" spans="1:15">
+    <row r="66" spans="1:15" ht="24.75" thickBot="1">
       <c r="A66" s="5"/>
       <c r="B66" s="10">
         <f t="shared" si="8"/>
         <v>64</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G66" s="16" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H66" s="15" t="s">
         <v>247</v>
@@ -6562,41 +5931,41 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L66" s="20" t="s">
+      <c r="L66" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M66" s="19">
-        <v>0.339</v>
-      </c>
-      <c r="N66" s="19">
+      <c r="M66" s="18">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N66" s="18">
         <f t="shared" si="7"/>
-        <v>1.017</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="O66" s="15"/>
     </row>
-    <row r="67" ht="15.75" spans="1:15">
+    <row r="67" spans="1:15" ht="15.75" thickBot="1">
       <c r="A67" s="5"/>
       <c r="B67" s="10">
         <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F67" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I67" s="16" t="s">
         <v>150</v>
@@ -6608,19 +5977,19 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="L67" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="19">
+      <c r="L67" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="18">
         <v>2.37</v>
       </c>
-      <c r="N67" s="19">
+      <c r="N67" s="18">
         <f t="shared" si="7"/>
         <v>7.11</v>
       </c>
       <c r="O67" s="12"/>
     </row>
-    <row r="68" ht="36.75" spans="1:15">
+    <row r="68" spans="1:15" ht="36.75" thickBot="1">
       <c r="A68" s="5"/>
       <c r="B68" s="10">
         <f t="shared" si="8"/>
@@ -6630,16 +5999,16 @@
         <v>227</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H68" s="15" t="s">
         <v>231</v>
@@ -6654,38 +6023,38 @@
         <f t="shared" ref="K68:K131" si="9">3*J68</f>
         <v>6</v>
       </c>
-      <c r="L68" s="20" t="s">
+      <c r="L68" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M68" s="19">
-        <v>0.0069</v>
-      </c>
-      <c r="N68" s="19">
+      <c r="M68" s="18">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="N68" s="18">
         <f t="shared" si="7"/>
-        <v>0.0414</v>
+        <v>4.1399999999999999E-2</v>
       </c>
       <c r="O68" s="15"/>
     </row>
-    <row r="69" ht="24.75" spans="1:15">
+    <row r="69" spans="1:15" ht="24.75" thickBot="1">
       <c r="A69" s="5"/>
       <c r="B69" s="10">
         <f t="shared" si="8"/>
         <v>67</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>247</v>
@@ -6700,41 +6069,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L69" s="20" t="s">
+      <c r="L69" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M69" s="19">
-        <v>0.4942</v>
-      </c>
-      <c r="N69" s="19">
+      <c r="M69" s="18">
+        <v>0.49419999999999997</v>
+      </c>
+      <c r="N69" s="18">
         <f t="shared" si="7"/>
-        <v>1.4826</v>
+        <v>1.4825999999999999</v>
       </c>
       <c r="O69" s="12"/>
     </row>
-    <row r="70" ht="15.75" spans="1:15">
+    <row r="70" spans="1:15" ht="15.75" thickBot="1">
       <c r="A70" s="5"/>
       <c r="B70" s="10">
         <f t="shared" si="8"/>
         <v>68</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F70" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I70" s="16" t="s">
         <v>150</v>
@@ -6746,92 +6115,90 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L70" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="19">
+      <c r="L70" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="18">
         <v>4.49</v>
       </c>
-      <c r="N70" s="19">
+      <c r="N70" s="18">
         <f t="shared" si="7"/>
-        <v>67.35</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="O70" s="15"/>
     </row>
-    <row r="71" ht="16.5" spans="1:15">
+    <row r="71" spans="1:15" ht="16.5" thickBot="1">
       <c r="A71" s="5"/>
       <c r="B71" s="10">
         <f t="shared" si="8"/>
         <v>69</v>
       </c>
-      <c r="C71" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F71" s="22" t="s">
+      <c r="C71" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="F71" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G71" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="H71" s="22" t="s">
+      <c r="G71" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="H71" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="I71" s="39" t="s">
+      <c r="I71" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J71" s="22">
+      <c r="J71" s="12">
         <v>4</v>
       </c>
-      <c r="K71" s="22">
+      <c r="K71" s="12">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L71" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" s="41">
-        <v>0.58</v>
-      </c>
-      <c r="N71" s="41">
+      <c r="L71" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="18">
+        <v>0.54</v>
+      </c>
+      <c r="N71" s="18">
         <f t="shared" si="7"/>
-        <v>6.96</v>
-      </c>
-      <c r="O71" s="42" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" spans="1:15">
+        <v>6.48</v>
+      </c>
+      <c r="O71" s="35"/>
+    </row>
+    <row r="72" spans="1:15" ht="15.75" thickBot="1">
       <c r="A72" s="5"/>
       <c r="B72" s="10">
         <f t="shared" si="8"/>
         <v>70</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G72" s="16" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I72" s="16" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J72" s="15">
         <v>1</v>
@@ -6840,44 +6207,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L72" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="19">
+      <c r="L72" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="18">
         <v>0.39</v>
       </c>
-      <c r="N72" s="19">
+      <c r="N72" s="18">
         <f t="shared" si="7"/>
         <v>1.17</v>
       </c>
       <c r="O72" s="15"/>
     </row>
-    <row r="73" ht="15.75" spans="1:15">
+    <row r="73" spans="1:15" ht="15.75" thickBot="1">
       <c r="A73" s="5"/>
       <c r="B73" s="10">
         <f t="shared" si="8"/>
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="D73" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>321</v>
-      </c>
       <c r="E73" s="13" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F73" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="J73" s="12">
         <v>2</v>
@@ -6886,44 +6253,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L73" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="19">
+      <c r="L73" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="18">
         <v>0.2</v>
       </c>
-      <c r="N73" s="19">
+      <c r="N73" s="18">
         <f t="shared" si="7"/>
         <v>1.2</v>
       </c>
       <c r="O73" s="12"/>
     </row>
-    <row r="74" ht="24.75" spans="1:15">
+    <row r="74" spans="1:15" ht="24.75" thickBot="1">
       <c r="A74" s="5"/>
       <c r="B74" s="10">
         <f t="shared" si="8"/>
         <v>72</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F74" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="H74" s="15" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I74" s="16" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="J74" s="15">
         <v>2</v>
@@ -6932,41 +6299,41 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L74" s="20" t="s">
+      <c r="L74" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M74" s="19">
-        <v>0.7956</v>
-      </c>
-      <c r="N74" s="19">
+      <c r="M74" s="18">
+        <v>0.79559999999999997</v>
+      </c>
+      <c r="N74" s="18">
         <f t="shared" si="7"/>
-        <v>4.7736</v>
+        <v>4.7736000000000001</v>
       </c>
       <c r="O74" s="15"/>
     </row>
-    <row r="75" ht="36.75" spans="1:15">
+    <row r="75" spans="1:15" ht="36.75" thickBot="1">
       <c r="A75" s="5"/>
       <c r="B75" s="10">
         <f t="shared" si="8"/>
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I75" s="13" t="s">
         <v>150</v>
@@ -6978,41 +6345,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L75" s="20" t="s">
+      <c r="L75" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M75" s="19">
-        <v>0.0218</v>
-      </c>
-      <c r="N75" s="19">
+      <c r="M75" s="18">
+        <v>2.18E-2</v>
+      </c>
+      <c r="N75" s="18">
         <f t="shared" si="7"/>
-        <v>0.0654</v>
+        <v>6.54E-2</v>
       </c>
       <c r="O75" s="12"/>
     </row>
-    <row r="76" ht="36.75" spans="1:15">
+    <row r="76" spans="1:15" ht="36.75" thickBot="1">
       <c r="A76" s="5"/>
       <c r="B76" s="10">
         <f t="shared" si="8"/>
         <v>74</v>
       </c>
       <c r="C76" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D76" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="D76" s="15" t="s">
-        <v>337</v>
-      </c>
       <c r="E76" s="16" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I76" s="16" t="s">
         <v>150</v>
@@ -7024,41 +6391,41 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L76" s="20" t="s">
+      <c r="L76" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M76" s="19">
-        <v>0.0218</v>
-      </c>
-      <c r="N76" s="19">
+      <c r="M76" s="18">
+        <v>2.18E-2</v>
+      </c>
+      <c r="N76" s="18">
         <f t="shared" si="7"/>
         <v>0.1308</v>
       </c>
       <c r="O76" s="15"/>
     </row>
-    <row r="77" ht="36.75" spans="1:15">
+    <row r="77" spans="1:15" ht="36.75" thickBot="1">
       <c r="A77" s="5"/>
       <c r="B77" s="10">
         <f t="shared" si="8"/>
         <v>75</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I77" s="13" t="s">
         <v>150</v>
@@ -7070,41 +6437,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L77" s="20" t="s">
+      <c r="L77" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M77" s="19">
-        <v>0.0196</v>
-      </c>
-      <c r="N77" s="19">
+      <c r="M77" s="18">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="N77" s="18">
         <f t="shared" si="7"/>
-        <v>0.0588</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="O77" s="12"/>
     </row>
-    <row r="78" ht="15.75" spans="1:15">
+    <row r="78" spans="1:15" ht="15.75" thickBot="1">
       <c r="A78" s="5"/>
       <c r="B78" s="10">
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="H78" s="15" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I78" s="13" t="s">
         <v>150</v>
@@ -7116,41 +6483,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L78" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="19">
+      <c r="L78" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="18">
         <v>0.35</v>
       </c>
-      <c r="N78" s="19">
+      <c r="N78" s="18">
         <f t="shared" si="7"/>
         <v>1.05</v>
       </c>
       <c r="O78" s="15"/>
     </row>
-    <row r="79" ht="15.75" spans="1:15">
+    <row r="79" spans="1:15" ht="15.75" thickBot="1">
       <c r="A79" s="5"/>
       <c r="B79" s="10">
         <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I79" s="13" t="s">
         <v>150</v>
@@ -7162,41 +6529,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L79" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="19">
+      <c r="L79" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="18">
         <v>0.3</v>
       </c>
-      <c r="N79" s="19">
+      <c r="N79" s="18">
         <f t="shared" si="7"/>
         <v>0.9</v>
       </c>
       <c r="O79" s="12"/>
     </row>
-    <row r="80" ht="15.75" spans="1:15">
+    <row r="80" spans="1:15" ht="15.75" thickBot="1">
       <c r="A80" s="5"/>
       <c r="B80" s="10">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I80" s="13" t="s">
         <v>150</v>
@@ -7208,41 +6575,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L80" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="19">
+      <c r="L80" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="18">
         <v>0.51</v>
       </c>
-      <c r="N80" s="19">
+      <c r="N80" s="18">
         <f t="shared" si="7"/>
         <v>1.53</v>
       </c>
       <c r="O80" s="15"/>
     </row>
-    <row r="81" ht="24.75" spans="1:15">
+    <row r="81" spans="1:19" ht="24.75" thickBot="1">
       <c r="A81" s="5"/>
       <c r="B81" s="10">
         <f t="shared" si="8"/>
         <v>79</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="I81" s="13" t="s">
         <v>150</v>
@@ -7254,41 +6621,41 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="L81" s="20" t="s">
+      <c r="L81" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M81" s="19">
-        <v>0.0868</v>
-      </c>
-      <c r="N81" s="19">
+      <c r="M81" s="18">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="N81" s="18">
         <f t="shared" si="7"/>
         <v>1.5624</v>
       </c>
       <c r="O81" s="12"/>
     </row>
-    <row r="82" ht="36.75" spans="1:15">
+    <row r="82" spans="1:19" ht="36.75" thickBot="1">
       <c r="A82" s="5"/>
       <c r="B82" s="10">
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G82" s="16" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="H82" s="15" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="I82" s="13" t="s">
         <v>150</v>
@@ -7300,38 +6667,38 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L82" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="19">
+      <c r="L82" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="18">
         <v>0.53</v>
       </c>
-      <c r="N82" s="19">
+      <c r="N82" s="18">
         <f t="shared" si="7"/>
         <v>1.59</v>
       </c>
       <c r="O82" s="15"/>
     </row>
-    <row r="83" ht="15.75" spans="1:15">
+    <row r="83" spans="1:19" ht="15.75" thickBot="1">
       <c r="A83" s="5"/>
       <c r="B83" s="10">
         <f t="shared" si="8"/>
         <v>81</v>
       </c>
       <c r="C83" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D83" s="12" t="s">
-        <v>366</v>
-      </c>
       <c r="E83" s="13" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F83" s="12" t="s">
         <v>186</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="H83" s="12" t="s">
         <v>149</v>
@@ -7346,41 +6713,41 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L83" s="20" t="s">
+      <c r="L83" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M83" s="19">
-        <v>0.0454</v>
-      </c>
-      <c r="N83" s="19">
+      <c r="M83" s="18">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="N83" s="18">
         <f t="shared" si="7"/>
-        <v>0.5448</v>
+        <v>0.54479999999999995</v>
       </c>
       <c r="O83" s="12"/>
     </row>
-    <row r="84" ht="24.75" spans="1:15">
+    <row r="84" spans="1:19" ht="24.75" thickBot="1">
       <c r="A84" s="5"/>
       <c r="B84" s="10">
         <f t="shared" si="8"/>
         <v>82</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="F84" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G84" s="16" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H84" s="15" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="I84" s="13" t="s">
         <v>150</v>
@@ -7392,41 +6759,41 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L84" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="19">
-        <v>0.29</v>
-      </c>
-      <c r="N84" s="19">
+      <c r="L84" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="18">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N84" s="18">
         <f t="shared" si="7"/>
         <v>1.74</v>
       </c>
       <c r="O84" s="15"/>
     </row>
-    <row r="85" ht="24.75" spans="1:15">
+    <row r="85" spans="1:19" ht="24.75" thickBot="1">
       <c r="A85" s="5"/>
       <c r="B85" s="10">
         <f t="shared" si="8"/>
         <v>83</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F85" s="12" t="s">
         <v>186</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="H85" s="12" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I85" s="13" t="s">
         <v>150</v>
@@ -7438,41 +6805,41 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L85" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="19">
+      <c r="L85" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="18">
         <v>0.41</v>
       </c>
-      <c r="N85" s="19">
+      <c r="N85" s="18">
         <f t="shared" si="7"/>
         <v>6.15</v>
       </c>
       <c r="O85" s="12"/>
     </row>
-    <row r="86" ht="24.75" spans="1:15">
+    <row r="86" spans="1:19" ht="24.75" thickBot="1">
       <c r="A86" s="5"/>
       <c r="B86" s="10">
         <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="C86" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="E86" s="16" t="s">
         <v>374</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>380</v>
       </c>
       <c r="F86" s="15" t="s">
         <v>186</v>
       </c>
       <c r="G86" s="16" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H86" s="15" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="I86" s="13" t="s">
         <v>150</v>
@@ -7484,41 +6851,41 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L86" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="19">
+      <c r="L86" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="18">
         <v>0.44</v>
       </c>
-      <c r="N86" s="19">
+      <c r="N86" s="18">
         <f t="shared" si="7"/>
         <v>1.32</v>
       </c>
       <c r="O86" s="15"/>
     </row>
-    <row r="87" ht="15.75" spans="1:15">
+    <row r="87" spans="1:19" ht="15.75" thickBot="1">
       <c r="A87" s="5"/>
       <c r="B87" s="10">
         <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="I87" s="13" t="s">
         <v>150</v>
@@ -7530,38 +6897,38 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L87" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="19">
+      <c r="L87" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="18">
         <v>0.25</v>
       </c>
-      <c r="N87" s="19">
+      <c r="N87" s="18">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="O87" s="12"/>
     </row>
-    <row r="88" ht="48.75" spans="1:15">
+    <row r="88" spans="1:19" ht="48.75" thickBot="1">
       <c r="A88" s="5"/>
       <c r="B88" s="10">
         <f t="shared" si="8"/>
         <v>86</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="H88" s="15" t="s">
         <v>149</v>
@@ -7576,44 +6943,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L88" s="20" t="s">
+      <c r="L88" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M88" s="19">
-        <v>0.028</v>
-      </c>
-      <c r="N88" s="19">
+      <c r="M88" s="18">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N88" s="18">
         <f t="shared" si="7"/>
-        <v>0.084</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="O88" s="15"/>
     </row>
-    <row r="89" ht="60.75" spans="1:15">
+    <row r="89" spans="1:19" ht="60.75" thickBot="1">
       <c r="A89" s="5"/>
       <c r="B89" s="10">
         <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J89" s="12">
         <v>40</v>
@@ -7622,44 +6989,44 @@
         <f t="shared" si="9"/>
         <v>120</v>
       </c>
-      <c r="L89" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="19">
-        <v>0.0073</v>
-      </c>
-      <c r="N89" s="19">
+      <c r="L89" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="18">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="N89" s="18">
         <f t="shared" si="7"/>
         <v>0.876</v>
       </c>
       <c r="O89" s="12"/>
     </row>
-    <row r="90" ht="15.75" spans="1:15">
+    <row r="90" spans="1:19" ht="15.75" thickBot="1">
       <c r="A90" s="5"/>
       <c r="B90" s="10">
         <f t="shared" si="8"/>
         <v>88</v>
       </c>
       <c r="C90" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="D90" s="15" t="s">
         <v>392</v>
       </c>
-      <c r="D90" s="15" t="s">
-        <v>398</v>
-      </c>
       <c r="E90" s="16" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="J90" s="15">
         <v>6</v>
@@ -7668,44 +7035,44 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="L90" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="19">
-        <v>0.015</v>
-      </c>
-      <c r="N90" s="19">
+      <c r="L90" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N90" s="18">
         <f t="shared" si="7"/>
         <v>0.27</v>
       </c>
       <c r="O90" s="15"/>
     </row>
-    <row r="91" ht="15.75" spans="1:15">
+    <row r="91" spans="1:19" ht="15.75" thickBot="1">
       <c r="A91" s="5"/>
       <c r="B91" s="10">
         <f t="shared" si="8"/>
         <v>89</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="H91" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="J91" s="12">
         <v>7</v>
@@ -7714,44 +7081,44 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="L91" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M91" s="19">
-        <v>0.024</v>
-      </c>
-      <c r="N91" s="19">
+      <c r="L91" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" s="18">
+        <v>2.4E-2</v>
+      </c>
+      <c r="N91" s="18">
         <f t="shared" si="7"/>
         <v>0.504</v>
       </c>
       <c r="O91" s="12"/>
     </row>
-    <row r="92" ht="72.75" spans="1:15">
+    <row r="92" spans="1:19" ht="84.75" thickBot="1">
       <c r="A92" s="5"/>
       <c r="B92" s="10">
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H92" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I92" s="16" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="J92" s="15">
         <v>49</v>
@@ -7760,44 +7127,44 @@
         <f t="shared" si="9"/>
         <v>147</v>
       </c>
-      <c r="L92" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="19">
-        <v>0.0073</v>
-      </c>
-      <c r="N92" s="19">
+      <c r="L92" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="18">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="N92" s="18">
         <f t="shared" si="7"/>
-        <v>1.0731</v>
+        <v>1.0730999999999999</v>
       </c>
       <c r="O92" s="15"/>
     </row>
-    <row r="93" ht="15.75" spans="1:15">
+    <row r="93" spans="1:19" ht="15.75" thickBot="1">
       <c r="A93" s="5"/>
       <c r="B93" s="10">
         <f t="shared" si="8"/>
         <v>91</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J93" s="12">
         <v>7</v>
@@ -7806,91 +7173,94 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="L93" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="19">
-        <v>0.015</v>
-      </c>
-      <c r="N93" s="19">
+      <c r="L93" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N93" s="18">
         <f t="shared" si="7"/>
         <v>0.315</v>
       </c>
       <c r="O93" s="12"/>
     </row>
-    <row r="94" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A94" s="24"/>
-      <c r="B94" s="25">
+    <row r="94" spans="1:19" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A94" s="20"/>
+      <c r="B94" s="21">
         <f t="shared" si="8"/>
         <v>92</v>
       </c>
-      <c r="C94" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="D94" s="27" t="s">
-        <v>414</v>
-      </c>
-      <c r="E94" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="F94" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="G94" s="28" t="s">
-        <v>416</v>
-      </c>
-      <c r="H94" s="27" t="s">
+      <c r="C94" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D94" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="G94" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="H94" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="I94" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="J94" s="27">
+      <c r="I94" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="J94" s="23">
         <v>2</v>
       </c>
-      <c r="K94" s="30">
+      <c r="K94" s="26">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L94" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="43" t="s">
+      <c r="L94" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="N94" s="43" t="s">
+      <c r="N94" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="O94" s="44" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" spans="1:15">
+      <c r="O94" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q94"/>
+      <c r="R94"/>
+      <c r="S94"/>
+    </row>
+    <row r="95" spans="1:19" ht="15.75" thickBot="1">
       <c r="A95" s="5"/>
       <c r="B95" s="10">
         <f t="shared" si="8"/>
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J95" s="12">
         <v>2</v>
@@ -7899,44 +7269,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L95" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="19">
+      <c r="L95" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="18">
         <v>0.1</v>
       </c>
-      <c r="N95" s="19">
+      <c r="N95" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O95" s="12"/>
     </row>
-    <row r="96" ht="48.75" spans="1:15">
+    <row r="96" spans="1:19" ht="48.75" thickBot="1">
       <c r="A96" s="5"/>
       <c r="B96" s="10">
         <f t="shared" si="8"/>
         <v>94</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H96" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I96" s="16" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="J96" s="15">
         <v>26</v>
@@ -7945,44 +7315,44 @@
         <f t="shared" si="9"/>
         <v>78</v>
       </c>
-      <c r="L96" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="19">
-        <v>0.0088</v>
-      </c>
-      <c r="N96" s="19">
+      <c r="L96" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="18">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="N96" s="18">
         <f t="shared" si="7"/>
-        <v>0.6864</v>
+        <v>0.68640000000000001</v>
       </c>
       <c r="O96" s="15"/>
     </row>
-    <row r="97" ht="15.75" spans="1:15">
+    <row r="97" spans="1:19" ht="15.75" thickBot="1">
       <c r="A97" s="5"/>
       <c r="B97" s="10">
         <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J97" s="12">
         <v>1</v>
@@ -7991,44 +7361,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L97" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="19">
+      <c r="L97" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="18">
         <v>0.13463</v>
       </c>
-      <c r="N97" s="19">
+      <c r="N97" s="18">
         <f t="shared" si="7"/>
-        <v>0.40389</v>
+        <v>0.40389000000000003</v>
       </c>
       <c r="O97" s="12"/>
     </row>
-    <row r="98" ht="36.75" spans="1:15">
+    <row r="98" spans="1:19" ht="48.75" thickBot="1">
       <c r="A98" s="5"/>
       <c r="B98" s="10">
         <f t="shared" si="8"/>
         <v>96</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="H98" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I98" s="16" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="J98" s="15">
         <v>27</v>
@@ -8037,44 +7407,44 @@
         <f t="shared" si="9"/>
         <v>81</v>
       </c>
-      <c r="L98" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="19">
-        <v>0.0064</v>
-      </c>
-      <c r="N98" s="19">
+      <c r="L98" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="18">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="N98" s="18">
         <f t="shared" si="7"/>
-        <v>0.5184</v>
+        <v>0.51839999999999997</v>
       </c>
       <c r="O98" s="15"/>
     </row>
-    <row r="99" ht="15.75" spans="1:15">
+    <row r="99" spans="1:19" ht="15.75" thickBot="1">
       <c r="A99" s="5"/>
       <c r="B99" s="10">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F99" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J99" s="12">
         <v>4</v>
@@ -8083,44 +7453,44 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L99" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="19">
-        <v>0.117</v>
-      </c>
-      <c r="N99" s="19">
+      <c r="L99" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="18">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="N99" s="18">
         <f t="shared" si="7"/>
-        <v>1.404</v>
+        <v>1.4039999999999999</v>
       </c>
       <c r="O99" s="12"/>
     </row>
-    <row r="100" ht="15.75" spans="1:15">
+    <row r="100" spans="1:19" ht="15.75" thickBot="1">
       <c r="A100" s="5"/>
       <c r="B100" s="10">
         <f t="shared" si="8"/>
         <v>98</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="H100" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I100" s="16" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J100" s="15">
         <v>4</v>
@@ -8129,44 +7499,44 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L100" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="19">
-        <v>0.015</v>
-      </c>
-      <c r="N100" s="19">
+      <c r="L100" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N100" s="18">
         <f t="shared" si="7"/>
         <v>0.18</v>
       </c>
       <c r="O100" s="15"/>
     </row>
-    <row r="101" ht="15.75" spans="1:15">
+    <row r="101" spans="1:19" ht="15.75" thickBot="1">
       <c r="A101" s="5"/>
       <c r="B101" s="10">
         <f t="shared" si="8"/>
         <v>99</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="J101" s="12">
         <v>4</v>
@@ -8175,44 +7545,44 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L101" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="19">
-        <v>0.027</v>
-      </c>
-      <c r="N101" s="19">
+      <c r="L101" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="18">
+        <v>2.7E-2</v>
+      </c>
+      <c r="N101" s="18">
         <f t="shared" si="7"/>
-        <v>0.324</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="O101" s="12"/>
     </row>
-    <row r="102" ht="15.75" spans="1:15">
+    <row r="102" spans="1:19" ht="15.75" thickBot="1">
       <c r="A102" s="5"/>
       <c r="B102" s="10">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I102" s="16" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="J102" s="15">
         <v>1</v>
@@ -8221,44 +7591,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L102" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="19">
-        <v>0.019</v>
-      </c>
-      <c r="N102" s="19">
+      <c r="L102" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="18">
+        <v>1.9E-2</v>
+      </c>
+      <c r="N102" s="18">
         <f t="shared" si="7"/>
-        <v>0.057</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O102" s="15"/>
     </row>
-    <row r="103" ht="15.75" spans="1:15">
+    <row r="103" spans="1:19" ht="15.75" thickBot="1">
       <c r="A103" s="5"/>
       <c r="B103" s="10">
         <f t="shared" si="8"/>
         <v>101</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="J103" s="12">
         <v>5</v>
@@ -8267,44 +7637,44 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="L103" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="19">
-        <v>0.015</v>
-      </c>
-      <c r="N103" s="19">
+      <c r="L103" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N103" s="18">
         <f t="shared" si="7"/>
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O103" s="12"/>
     </row>
-    <row r="104" ht="15.75" spans="1:15">
+    <row r="104" spans="1:19" ht="15.75" thickBot="1">
       <c r="A104" s="5"/>
       <c r="B104" s="10">
         <f t="shared" si="8"/>
         <v>102</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="H104" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I104" s="16" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="J104" s="15">
         <v>1</v>
@@ -8313,44 +7683,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L104" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="19">
+      <c r="L104" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" s="18">
         <v>0.1</v>
       </c>
-      <c r="N104" s="19">
+      <c r="N104" s="18">
         <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="O104" s="15"/>
     </row>
-    <row r="105" ht="15.75" spans="1:15">
+    <row r="105" spans="1:19" ht="15.75" thickBot="1">
       <c r="A105" s="5"/>
       <c r="B105" s="10">
         <f t="shared" si="8"/>
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -8359,44 +7729,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L105" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="19">
+      <c r="L105" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" s="18">
         <v>0.1</v>
       </c>
-      <c r="N105" s="19">
+      <c r="N105" s="18">
         <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="O105" s="12"/>
     </row>
-    <row r="106" ht="15.75" spans="1:15">
+    <row r="106" spans="1:19" ht="15.75" thickBot="1">
       <c r="A106" s="5"/>
       <c r="B106" s="10">
         <f t="shared" si="8"/>
         <v>104</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I106" s="16" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="J106" s="15">
         <v>1</v>
@@ -8405,91 +7775,94 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L106" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="19">
+      <c r="L106" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" s="18">
         <v>0.1</v>
       </c>
-      <c r="N106" s="19">
+      <c r="N106" s="18">
         <f t="shared" si="7"/>
         <v>0.3</v>
       </c>
       <c r="O106" s="15"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A107" s="24"/>
+    <row r="107" spans="1:19" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A107" s="20"/>
       <c r="B107" s="10">
         <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="C107" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="D107" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>399</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="G107" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="H107" s="30" t="s">
+      <c r="C107" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>461</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="G107" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="H107" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I107" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="J107" s="30">
+      <c r="I107" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="J107" s="26">
         <v>1</v>
       </c>
-      <c r="K107" s="30">
+      <c r="K107" s="26">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L107" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M107" s="43" t="s">
+      <c r="L107" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M107" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="N107" s="43" t="s">
+      <c r="N107" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="O107" s="44" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" spans="1:15">
+      <c r="O107" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q107"/>
+      <c r="R107"/>
+      <c r="S107"/>
+    </row>
+    <row r="108" spans="1:19" ht="15.75" thickBot="1">
       <c r="A108" s="5"/>
       <c r="B108" s="10">
         <f t="shared" si="8"/>
         <v>106</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I108" s="16" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="J108" s="15">
         <v>2</v>
@@ -8498,44 +7871,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L108" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M108" s="19">
+      <c r="L108" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" s="18">
         <v>0.1</v>
       </c>
-      <c r="N108" s="19">
+      <c r="N108" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O108" s="15"/>
     </row>
-    <row r="109" ht="15.75" spans="1:15">
+    <row r="109" spans="1:19" ht="15.75" thickBot="1">
       <c r="A109" s="5"/>
       <c r="B109" s="10">
         <f t="shared" si="8"/>
         <v>107</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="J109" s="12">
         <v>2</v>
@@ -8544,91 +7917,91 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L109" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" s="19">
+      <c r="L109" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M109" s="18">
         <v>0.1</v>
       </c>
-      <c r="N109" s="19">
+      <c r="N109" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O109" s="12"/>
     </row>
-    <row r="110" ht="15.75" spans="1:15">
+    <row r="110" spans="1:19" ht="15.75" thickBot="1">
       <c r="A110" s="5"/>
       <c r="B110" s="10">
         <f t="shared" si="8"/>
         <v>108</v>
       </c>
-      <c r="C110" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="D110" s="27" t="s">
-        <v>476</v>
-      </c>
-      <c r="E110" s="28" t="s">
-        <v>432</v>
-      </c>
-      <c r="F110" s="27" t="s">
-        <v>395</v>
-      </c>
-      <c r="G110" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="H110" s="27" t="s">
+      <c r="C110" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D110" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="E110" s="24" t="s">
+        <v>426</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="G110" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="H110" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="I110" s="28" t="s">
-        <v>417</v>
-      </c>
-      <c r="J110" s="27">
+      <c r="I110" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="J110" s="23">
         <v>2</v>
       </c>
-      <c r="K110" s="30">
+      <c r="K110" s="26">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L110" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M110" s="43" t="s">
+      <c r="L110" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="N110" s="43" t="s">
+      <c r="N110" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="O110" s="44" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" spans="1:15">
+      <c r="O110" s="37" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="15.75" thickBot="1">
       <c r="A111" s="5"/>
       <c r="B111" s="10">
         <f t="shared" si="8"/>
         <v>109</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G111" s="13" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J111" s="12">
         <v>2</v>
@@ -8637,44 +8010,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L111" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M111" s="19">
+      <c r="L111" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M111" s="18">
         <v>0.1</v>
       </c>
-      <c r="N111" s="19">
+      <c r="N111" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O111" s="12"/>
     </row>
-    <row r="112" ht="15.75" spans="1:15">
+    <row r="112" spans="1:19" ht="15.75" thickBot="1">
       <c r="A112" s="5"/>
       <c r="B112" s="10">
         <f t="shared" si="8"/>
         <v>110</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I112" s="16" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="J112" s="15">
         <v>2</v>
@@ -8683,44 +8056,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L112" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M112" s="19">
+      <c r="L112" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M112" s="18">
         <v>0.1</v>
       </c>
-      <c r="N112" s="19">
+      <c r="N112" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O112" s="15"/>
     </row>
-    <row r="113" ht="15.75" spans="1:15">
+    <row r="113" spans="1:19" ht="15.75" thickBot="1">
       <c r="A113" s="5"/>
       <c r="B113" s="10">
         <f t="shared" si="8"/>
         <v>111</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="J113" s="12">
         <v>4</v>
@@ -8729,44 +8102,44 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="L113" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M113" s="19">
-        <v>0.015</v>
-      </c>
-      <c r="N113" s="19">
+      <c r="L113" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M113" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N113" s="18">
         <f t="shared" si="7"/>
         <v>0.18</v>
       </c>
       <c r="O113" s="12"/>
     </row>
-    <row r="114" ht="15.75" spans="1:15">
+    <row r="114" spans="1:19" ht="15.75" thickBot="1">
       <c r="A114" s="5"/>
       <c r="B114" s="10">
         <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I114" s="16" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="J114" s="15">
         <v>2</v>
@@ -8775,136 +8148,142 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L114" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M114" s="19">
+      <c r="L114" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" s="18">
         <v>0.13</v>
       </c>
-      <c r="N114" s="19">
+      <c r="N114" s="18">
         <f t="shared" si="7"/>
         <v>0.78</v>
       </c>
       <c r="O114" s="15"/>
     </row>
-    <row r="115" s="2" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A115" s="32"/>
-      <c r="B115" s="33">
+    <row r="115" spans="1:19" s="2" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A115" s="28"/>
+      <c r="B115" s="29">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="C115" s="34" t="s">
-        <v>392</v>
-      </c>
-      <c r="D115" s="35" t="s">
-        <v>492</v>
-      </c>
-      <c r="E115" s="36" t="s">
-        <v>493</v>
-      </c>
-      <c r="F115" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="G115" s="36" t="s">
-        <v>494</v>
-      </c>
-      <c r="H115" s="35" t="s">
+      <c r="C115" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="D115" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="E115" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="F115" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="G115" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="H115" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="I115" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="J115" s="35">
+      <c r="I115" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="J115" s="31">
         <v>8</v>
       </c>
-      <c r="K115" s="35">
+      <c r="K115" s="31">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="L115" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="M115" s="46">
-        <v>0.015</v>
-      </c>
-      <c r="N115" s="46">
+      <c r="L115" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="M115" s="39">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N115" s="39">
         <f t="shared" si="7"/>
         <v>0.36</v>
       </c>
-      <c r="O115" s="35"/>
-    </row>
-    <row r="116" s="2" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A116" s="32"/>
-      <c r="B116" s="33">
+      <c r="O115" s="31"/>
+      <c r="Q115"/>
+      <c r="R115"/>
+      <c r="S115"/>
+    </row>
+    <row r="116" spans="1:19" s="2" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A116" s="28"/>
+      <c r="B116" s="29">
         <f t="shared" si="8"/>
         <v>114</v>
       </c>
-      <c r="C116" s="34" t="s">
-        <v>392</v>
-      </c>
-      <c r="D116" s="37" t="s">
-        <v>496</v>
-      </c>
-      <c r="E116" s="38" t="s">
-        <v>415</v>
-      </c>
-      <c r="F116" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="G116" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="H116" s="37" t="s">
+      <c r="C116" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="D116" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="E116" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="F116" s="33" t="s">
+        <v>389</v>
+      </c>
+      <c r="G116" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="H116" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I116" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="J116" s="37">
+      <c r="I116" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="J116" s="33">
         <v>8</v>
       </c>
-      <c r="K116" s="35">
+      <c r="K116" s="31">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="L116" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="M116" s="46">
-        <v>0.015</v>
-      </c>
-      <c r="N116" s="46">
+      <c r="L116" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="M116" s="39">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N116" s="39">
         <f t="shared" si="7"/>
         <v>0.36</v>
       </c>
-      <c r="O116" s="37"/>
-    </row>
-    <row r="117" ht="15.75" spans="1:15">
+      <c r="O116" s="33"/>
+      <c r="Q116"/>
+      <c r="R116"/>
+      <c r="S116"/>
+    </row>
+    <row r="117" spans="1:19" ht="15.75" thickBot="1">
       <c r="A117" s="5"/>
       <c r="B117" s="10">
         <f t="shared" si="8"/>
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="J117" s="12">
         <v>2</v>
@@ -8913,44 +8292,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L117" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M117" s="19">
+      <c r="L117" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M117" s="18">
         <v>0.1</v>
       </c>
-      <c r="N117" s="19">
+      <c r="N117" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O117" s="12"/>
     </row>
-    <row r="118" ht="15.75" spans="1:15">
+    <row r="118" spans="1:19" ht="15.75" thickBot="1">
       <c r="A118" s="5"/>
       <c r="B118" s="10">
         <f t="shared" si="8"/>
         <v>116</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I118" s="16" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="J118" s="15">
         <v>2</v>
@@ -8959,44 +8338,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L118" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M118" s="19">
+      <c r="L118" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M118" s="18">
         <v>0.1</v>
       </c>
-      <c r="N118" s="19">
+      <c r="N118" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O118" s="15"/>
     </row>
-    <row r="119" ht="15.75" spans="1:15">
+    <row r="119" spans="1:19" ht="15.75" thickBot="1">
       <c r="A119" s="5"/>
       <c r="B119" s="10">
         <f t="shared" si="8"/>
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="H119" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J119" s="12">
         <v>2</v>
@@ -9005,44 +8384,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L119" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M119" s="19">
+      <c r="L119" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M119" s="18">
         <v>0.1</v>
       </c>
-      <c r="N119" s="19">
+      <c r="N119" s="18">
         <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="O119" s="12"/>
     </row>
-    <row r="120" ht="15.75" spans="1:15">
+    <row r="120" spans="1:19" ht="15.75" thickBot="1">
       <c r="A120" s="5"/>
       <c r="B120" s="10">
         <f t="shared" si="8"/>
         <v>118</v>
       </c>
       <c r="C120" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="E120" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="G120" s="16" t="s">
         <v>506</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>511</v>
-      </c>
-      <c r="F120" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="G120" s="16" t="s">
-        <v>512</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="J120" s="15">
         <v>2</v>
@@ -9051,91 +8430,94 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L120" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M120" s="19">
+      <c r="L120" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M120" s="18">
         <v>0.1</v>
       </c>
-      <c r="N120" s="19">
+      <c r="N120" s="18">
         <f t="shared" ref="N120:N160" si="10">M120*K120</f>
         <v>0.6</v>
       </c>
       <c r="O120" s="15"/>
     </row>
-    <row r="121" s="1" customFormat="1" ht="15.75" spans="1:15">
-      <c r="A121" s="24"/>
+    <row r="121" spans="1:19" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A121" s="20"/>
       <c r="B121" s="10">
         <f t="shared" si="8"/>
         <v>119</v>
       </c>
-      <c r="C121" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="D121" s="30" t="s">
-        <v>514</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="G121" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="H121" s="30" t="s">
+      <c r="C121" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="D121" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="G121" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="H121" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="I121" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="J121" s="30">
+      <c r="I121" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="J121" s="26">
         <v>2</v>
       </c>
-      <c r="K121" s="30">
+      <c r="K121" s="26">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L121" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="M121" s="43" t="s">
+      <c r="L121" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M121" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="N121" s="43" t="s">
+      <c r="N121" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="O121" s="44" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" spans="1:15">
+      <c r="O121" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="Q121"/>
+      <c r="R121"/>
+      <c r="S121"/>
+    </row>
+    <row r="122" spans="1:19" ht="15.75" thickBot="1">
       <c r="A122" s="5"/>
       <c r="B122" s="10">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="16" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="J122" s="15">
         <v>1</v>
@@ -9144,44 +8526,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L122" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M122" s="19">
+      <c r="L122" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M122" s="18">
         <v>0.1</v>
       </c>
-      <c r="N122" s="19">
+      <c r="N122" s="18">
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="O122" s="15"/>
     </row>
-    <row r="123" ht="15.75" spans="1:15">
+    <row r="123" spans="1:19" ht="15.75" thickBot="1">
       <c r="A123" s="5"/>
       <c r="B123" s="10">
         <f>ROW(B123)-ROW($B$2)</f>
         <v>121</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="H123" s="12" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="J123" s="12">
         <v>1</v>
@@ -9190,44 +8572,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L123" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M123" s="19">
+      <c r="L123" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M123" s="18">
         <v>0.11</v>
       </c>
-      <c r="N123" s="19">
+      <c r="N123" s="18">
         <f t="shared" si="10"/>
         <v>0.33</v>
       </c>
       <c r="O123" s="12"/>
     </row>
-    <row r="124" ht="15.75" spans="1:15">
+    <row r="124" spans="1:19" ht="15.75" thickBot="1">
       <c r="A124" s="5"/>
       <c r="B124" s="10">
         <f t="shared" si="8"/>
         <v>122</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="H124" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I124" s="16" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="J124" s="15">
         <v>2</v>
@@ -9236,44 +8618,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L124" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M124" s="19">
+      <c r="L124" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M124" s="18">
         <v>0.1</v>
       </c>
-      <c r="N124" s="19">
+      <c r="N124" s="18">
         <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
       <c r="O124" s="15"/>
     </row>
-    <row r="125" ht="15.75" spans="1:15">
+    <row r="125" spans="1:19" ht="15.75" thickBot="1">
       <c r="A125" s="5"/>
       <c r="B125" s="10">
         <f>ROW(B125)-ROW($B$2)</f>
         <v>123</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G125" s="13" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="H125" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="J125" s="12">
         <v>1</v>
@@ -9282,44 +8664,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L125" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M125" s="19">
+      <c r="L125" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M125" s="18">
         <v>0.1</v>
       </c>
-      <c r="N125" s="19">
+      <c r="N125" s="18">
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="O125" s="12"/>
     </row>
-    <row r="126" ht="15.75" spans="1:15">
+    <row r="126" spans="1:19" ht="15.75" thickBot="1">
       <c r="A126" s="5"/>
       <c r="B126" s="10">
         <f t="shared" si="8"/>
         <v>124</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="H126" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I126" s="16" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="J126" s="15">
         <v>1</v>
@@ -9328,44 +8710,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L126" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M126" s="19">
+      <c r="L126" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M126" s="18">
         <v>0.1</v>
       </c>
-      <c r="N126" s="19">
+      <c r="N126" s="18">
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="O126" s="15"/>
     </row>
-    <row r="127" ht="15.75" spans="1:15">
+    <row r="127" spans="1:19" ht="15.75" thickBot="1">
       <c r="A127" s="5"/>
       <c r="B127" s="10">
         <f>ROW(B127)-ROW($B$2)</f>
         <v>125</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G127" s="13" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H127" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="J127" s="12">
         <v>1</v>
@@ -9374,44 +8756,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L127" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M127" s="19">
+      <c r="L127" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M127" s="18">
         <v>0.1</v>
       </c>
-      <c r="N127" s="19">
+      <c r="N127" s="18">
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="O127" s="12"/>
     </row>
-    <row r="128" ht="15.75" spans="1:15">
+    <row r="128" spans="1:19" ht="15.75" thickBot="1">
       <c r="A128" s="5"/>
       <c r="B128" s="10">
         <f t="shared" si="8"/>
         <v>126</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E128" s="16" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G128" s="16" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="H128" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I128" s="16" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="J128" s="15">
         <v>1</v>
@@ -9420,44 +8802,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L128" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M128" s="19">
+      <c r="L128" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M128" s="18">
         <v>0.1</v>
       </c>
-      <c r="N128" s="19">
+      <c r="N128" s="18">
         <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="O128" s="15"/>
     </row>
-    <row r="129" ht="15.75" spans="1:15">
+    <row r="129" spans="1:15" ht="15.75" thickBot="1">
       <c r="A129" s="5"/>
       <c r="B129" s="10">
         <f>ROW(B129)-ROW($B$2)</f>
         <v>127</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G129" s="13" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H129" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="J129" s="12">
         <v>2</v>
@@ -9466,44 +8848,44 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L129" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M129" s="19">
+      <c r="L129" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M129" s="18">
         <v>0.16</v>
       </c>
-      <c r="N129" s="19">
+      <c r="N129" s="18">
         <f t="shared" si="10"/>
         <v>0.96</v>
       </c>
       <c r="O129" s="12"/>
     </row>
-    <row r="130" ht="15.75" spans="1:15">
+    <row r="130" spans="1:15" ht="15.75" thickBot="1">
       <c r="A130" s="5"/>
       <c r="B130" s="10">
         <f t="shared" si="8"/>
         <v>128</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H130" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I130" s="16" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="J130" s="15">
         <v>1</v>
@@ -9512,44 +8894,44 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="L130" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M130" s="19">
+      <c r="L130" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M130" s="18">
         <v>0.16</v>
       </c>
-      <c r="N130" s="19">
+      <c r="N130" s="18">
         <f t="shared" si="10"/>
         <v>0.48</v>
       </c>
       <c r="O130" s="15"/>
     </row>
-    <row r="131" ht="15.75" spans="1:15">
+    <row r="131" spans="1:15" ht="15.75" thickBot="1">
       <c r="A131" s="5"/>
       <c r="B131" s="10">
         <f>ROW(B131)-ROW($B$2)</f>
         <v>129</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="G131" s="13" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="J131" s="12">
         <v>2</v>
@@ -9558,41 +8940,41 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="L131" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M131" s="19">
+      <c r="L131" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M131" s="18">
         <v>0.15</v>
       </c>
-      <c r="N131" s="19">
+      <c r="N131" s="18">
         <f t="shared" si="10"/>
         <v>0.9</v>
       </c>
       <c r="O131" s="12"/>
     </row>
-    <row r="132" ht="36.75" spans="1:15">
+    <row r="132" spans="1:15" ht="36.75" thickBot="1">
       <c r="A132" s="5"/>
       <c r="B132" s="10">
         <f t="shared" si="8"/>
         <v>130</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F132" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G132" s="16" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H132" s="15" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="I132" s="16" t="s">
         <v>150</v>
@@ -9604,41 +8986,41 @@
         <f t="shared" ref="K132:K160" si="11">3*J132</f>
         <v>18</v>
       </c>
-      <c r="L132" s="20" t="s">
+      <c r="L132" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M132" s="19">
-        <v>0.0694</v>
-      </c>
-      <c r="N132" s="19">
+      <c r="M132" s="18">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="N132" s="18">
         <f t="shared" si="10"/>
-        <v>1.2492</v>
+        <v>1.2492000000000001</v>
       </c>
       <c r="O132" s="15"/>
     </row>
-    <row r="133" ht="24.75" spans="1:15">
+    <row r="133" spans="1:15" ht="24.75" thickBot="1">
       <c r="A133" s="5"/>
       <c r="B133" s="10">
         <f>ROW(B133)-ROW($B$2)</f>
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="G133" s="13" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="I133" s="16" t="s">
         <v>150</v>
@@ -9650,86 +9032,84 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L133" s="20" t="s">
+      <c r="L133" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M133" s="19">
-        <v>0.2534</v>
-      </c>
-      <c r="N133" s="19">
+      <c r="M133" s="18">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="N133" s="18">
         <f t="shared" si="10"/>
-        <v>0.7602</v>
+        <v>0.76019999999999999</v>
       </c>
       <c r="O133" s="12"/>
     </row>
-    <row r="134" ht="24.75" spans="1:15">
+    <row r="134" spans="1:15" ht="24.75" thickBot="1">
       <c r="A134" s="5"/>
       <c r="B134" s="10">
         <f t="shared" si="8"/>
         <v>132</v>
       </c>
-      <c r="C134" s="47" t="s">
+      <c r="C134" s="11" t="s">
+        <v>552</v>
+      </c>
+      <c r="D134" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="D134" s="48" t="s">
-        <v>564</v>
-      </c>
-      <c r="E134" s="39" t="s">
-        <v>565</v>
-      </c>
-      <c r="F134" s="48" t="s">
-        <v>566</v>
-      </c>
-      <c r="G134" s="39" t="s">
-        <v>567</v>
-      </c>
-      <c r="H134" s="48" t="s">
-        <v>568</v>
-      </c>
-      <c r="I134" s="39" t="s">
+      <c r="E134" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="G134" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="I134" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J134" s="48">
+      <c r="J134" s="15">
         <v>1</v>
       </c>
-      <c r="K134" s="22">
+      <c r="K134" s="12">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L134" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="M134" s="41">
-        <v>2.26</v>
-      </c>
-      <c r="N134" s="41">
+      <c r="L134" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M134" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="N134" s="18">
         <f t="shared" si="10"/>
-        <v>6.78</v>
-      </c>
-      <c r="O134" s="49" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" spans="1:15">
+        <v>4.5</v>
+      </c>
+      <c r="O134" s="40"/>
+    </row>
+    <row r="135" spans="1:15" ht="15.75" thickBot="1">
       <c r="A135" s="5"/>
       <c r="B135" s="10">
         <f>ROW(B135)-ROW($B$2)</f>
         <v>133</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="H135" s="12" t="s">
         <v>160</v>
@@ -9744,41 +9124,41 @@
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="L135" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M135" s="19">
+      <c r="L135" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M135" s="18">
         <v>0.46</v>
       </c>
-      <c r="N135" s="19">
+      <c r="N135" s="18">
         <f t="shared" si="10"/>
         <v>2.76</v>
       </c>
       <c r="O135" s="12"/>
     </row>
-    <row r="136" ht="24.75" spans="1:15">
+    <row r="136" spans="1:15" ht="24.75" thickBot="1">
       <c r="A136" s="5"/>
       <c r="B136" s="10">
         <f t="shared" si="8"/>
         <v>134</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="H136" s="15" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I136" s="16" t="s">
         <v>150</v>
@@ -9790,41 +9170,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L136" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M136" s="19">
+      <c r="L136" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M136" s="18">
         <v>1.18</v>
       </c>
-      <c r="N136" s="19">
+      <c r="N136" s="18">
         <f t="shared" si="10"/>
         <v>3.54</v>
       </c>
       <c r="O136" s="15"/>
     </row>
-    <row r="137" ht="24.75" spans="1:15">
+    <row r="137" spans="1:15" ht="24.75" thickBot="1">
       <c r="A137" s="5"/>
       <c r="B137" s="10">
         <f>ROW(B137)-ROW($B$2)</f>
         <v>135</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="H137" s="12" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="I137" s="16" t="s">
         <v>150</v>
@@ -9836,41 +9216,41 @@
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="L137" s="20" t="s">
+      <c r="L137" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M137" s="19">
-        <v>0.0938</v>
-      </c>
-      <c r="N137" s="19">
+      <c r="M137" s="18">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="N137" s="18">
         <f t="shared" si="10"/>
-        <v>1.1256</v>
+        <v>1.1255999999999999</v>
       </c>
       <c r="O137" s="12"/>
     </row>
-    <row r="138" ht="15.75" spans="1:15">
+    <row r="138" spans="1:15" ht="15.75" thickBot="1">
       <c r="A138" s="5"/>
       <c r="B138" s="10">
         <f t="shared" si="8"/>
         <v>136</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="H138" s="15" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="I138" s="16" t="s">
         <v>150</v>
@@ -9882,41 +9262,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L138" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M138" s="19">
+      <c r="L138" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M138" s="18">
         <v>1.51</v>
       </c>
-      <c r="N138" s="19">
+      <c r="N138" s="18">
         <f t="shared" si="10"/>
         <v>4.53</v>
       </c>
       <c r="O138" s="15"/>
     </row>
-    <row r="139" ht="24.75" spans="1:15">
+    <row r="139" spans="1:15" ht="24.75" thickBot="1">
       <c r="A139" s="5"/>
       <c r="B139" s="10">
         <f>ROW(B139)-ROW($B$2)</f>
         <v>137</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="H139" s="12" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>150</v>
@@ -9928,41 +9308,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L139" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M139" s="19">
+      <c r="L139" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M139" s="18">
         <v>1.79</v>
       </c>
-      <c r="N139" s="19">
+      <c r="N139" s="18">
         <f t="shared" si="10"/>
         <v>5.37</v>
       </c>
       <c r="O139" s="12"/>
     </row>
-    <row r="140" ht="15.75" spans="1:15">
+    <row r="140" spans="1:15" ht="15.75" thickBot="1">
       <c r="A140" s="5"/>
       <c r="B140" s="10">
         <f t="shared" si="8"/>
         <v>138</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="H140" s="15" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="I140" s="16" t="s">
         <v>150</v>
@@ -9974,41 +9354,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L140" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M140" s="19">
-        <v>2.5254</v>
-      </c>
-      <c r="N140" s="19">
+      <c r="L140" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M140" s="18">
+        <v>2.5253999999999999</v>
+      </c>
+      <c r="N140" s="18">
         <f t="shared" si="10"/>
         <v>7.5762</v>
       </c>
       <c r="O140" s="15"/>
     </row>
-    <row r="141" ht="15.75" spans="1:15">
+    <row r="141" spans="1:15" ht="15.75" thickBot="1">
       <c r="A141" s="5"/>
       <c r="B141" s="10">
         <f>ROW(B141)-ROW($B$2)</f>
         <v>139</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="F141" s="12" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="H141" s="12" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>150</v>
@@ -10020,41 +9400,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L141" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M141" s="19">
+      <c r="L141" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M141" s="18">
         <v>5.57</v>
       </c>
-      <c r="N141" s="19">
+      <c r="N141" s="18">
         <f t="shared" si="10"/>
         <v>16.71</v>
       </c>
       <c r="O141" s="12"/>
     </row>
-    <row r="142" ht="24.75" spans="1:15">
+    <row r="142" spans="1:15" ht="24.75" thickBot="1">
       <c r="A142" s="5"/>
       <c r="B142" s="10">
         <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="E142" s="16" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="F142" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G142" s="16" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I142" s="16" t="s">
         <v>150</v>
@@ -10066,41 +9446,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L142" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M142" s="19">
+      <c r="L142" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M142" s="18">
         <v>18.03</v>
       </c>
-      <c r="N142" s="19">
+      <c r="N142" s="18">
         <f t="shared" si="10"/>
         <v>54.09</v>
       </c>
       <c r="O142" s="15"/>
     </row>
-    <row r="143" ht="24.75" spans="1:15">
+    <row r="143" spans="1:15" ht="24.75" thickBot="1">
       <c r="A143" s="5"/>
       <c r="B143" s="10">
         <f>ROW(B143)-ROW($B$2)</f>
         <v>141</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="F143" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I143" s="16" t="s">
         <v>150</v>
@@ -10112,41 +9492,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L143" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M143" s="19">
+      <c r="L143" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M143" s="18">
         <v>1.06</v>
       </c>
-      <c r="N143" s="19">
+      <c r="N143" s="18">
         <f t="shared" si="10"/>
         <v>3.18</v>
       </c>
       <c r="O143" s="12"/>
     </row>
-    <row r="144" ht="24.75" spans="1:15">
+    <row r="144" spans="1:15" ht="24.75" thickBot="1">
       <c r="A144" s="5"/>
       <c r="B144" s="10">
         <f t="shared" si="8"/>
         <v>142</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="E144" s="16" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="F144" s="15" t="s">
         <v>163</v>
       </c>
       <c r="G144" s="16" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="H144" s="15" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="I144" s="16" t="s">
         <v>150</v>
@@ -10158,41 +9538,41 @@
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="L144" s="20" t="s">
+      <c r="L144" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M144" s="19">
-        <v>0.0232</v>
-      </c>
-      <c r="N144" s="19">
+      <c r="M144" s="18">
+        <v>2.3199999999999998E-2</v>
+      </c>
+      <c r="N144" s="18">
         <f t="shared" si="10"/>
-        <v>0.1392</v>
+        <v>0.13919999999999999</v>
       </c>
       <c r="O144" s="15"/>
     </row>
-    <row r="145" ht="24.75" spans="1:15">
+    <row r="145" spans="1:15" ht="24.75" thickBot="1">
       <c r="A145" s="5"/>
       <c r="B145" s="10">
         <f>ROW(B145)-ROW($B$2)</f>
         <v>143</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="F145" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I145" s="16" t="s">
         <v>150</v>
@@ -10204,41 +9584,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L145" s="20" t="s">
+      <c r="L145" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M145" s="19">
-        <v>8.3532</v>
-      </c>
-      <c r="N145" s="19">
+      <c r="M145" s="18">
+        <v>8.3531999999999993</v>
+      </c>
+      <c r="N145" s="18">
         <f t="shared" si="10"/>
         <v>25.0596</v>
       </c>
       <c r="O145" s="12"/>
     </row>
-    <row r="146" ht="26.25" spans="1:15">
+    <row r="146" spans="1:15" ht="26.25" thickBot="1">
       <c r="A146" s="5"/>
       <c r="B146" s="10">
         <f t="shared" si="8"/>
         <v>144</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="E146" s="16" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="G146" s="16" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="H146" s="15" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I146" s="16" t="s">
         <v>150</v>
@@ -10250,41 +9630,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L146" s="20" t="s">
+      <c r="L146" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M146" s="19">
-        <v>0.6372</v>
-      </c>
-      <c r="N146" s="19">
+      <c r="M146" s="18">
+        <v>0.63719999999999999</v>
+      </c>
+      <c r="N146" s="18">
         <f t="shared" si="10"/>
         <v>1.9116</v>
       </c>
       <c r="O146" s="15"/>
     </row>
-    <row r="147" ht="60.75" spans="1:15">
+    <row r="147" spans="1:15" ht="60.75" thickBot="1">
       <c r="A147" s="5"/>
       <c r="B147" s="10">
         <f>ROW(B147)-ROW($B$2)</f>
         <v>145</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="H147" s="12" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="I147" s="16" t="s">
         <v>150</v>
@@ -10296,41 +9676,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L147" s="20" t="s">
+      <c r="L147" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M147" s="19">
-        <v>0.0788</v>
-      </c>
-      <c r="N147" s="19">
+      <c r="M147" s="18">
+        <v>7.8799999999999995E-2</v>
+      </c>
+      <c r="N147" s="18">
         <f t="shared" si="10"/>
         <v>0.2364</v>
       </c>
       <c r="O147" s="12"/>
     </row>
-    <row r="148" ht="15.75" spans="1:15">
+    <row r="148" spans="1:15" ht="15.75" thickBot="1">
       <c r="A148" s="5"/>
       <c r="B148" s="10">
         <f t="shared" si="8"/>
         <v>146</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="G148" s="16" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="H148" s="15" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I148" s="16" t="s">
         <v>150</v>
@@ -10342,41 +9722,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L148" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M148" s="19">
-        <v>4.44</v>
-      </c>
-      <c r="N148" s="19">
+      <c r="L148" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M148" s="18">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="N148" s="18">
         <f t="shared" si="10"/>
         <v>13.32</v>
       </c>
       <c r="O148" s="15"/>
     </row>
-    <row r="149" ht="24.75" spans="1:15">
+    <row r="149" spans="1:15" ht="24.75" thickBot="1">
       <c r="A149" s="5"/>
       <c r="B149" s="10">
         <f>ROW(B149)-ROW($B$2)</f>
         <v>147</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="H149" s="12" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I149" s="16" t="s">
         <v>150</v>
@@ -10388,41 +9768,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L149" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M149" s="19">
+      <c r="L149" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M149" s="18">
         <v>0.78</v>
       </c>
-      <c r="N149" s="19">
+      <c r="N149" s="18">
         <f t="shared" si="10"/>
         <v>2.34</v>
       </c>
       <c r="O149" s="12"/>
     </row>
-    <row r="150" ht="15.75" spans="1:15">
+    <row r="150" spans="1:15" ht="15.75" thickBot="1">
       <c r="A150" s="5"/>
       <c r="B150" s="10">
         <f t="shared" si="8"/>
         <v>148</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E150" s="16" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="G150" s="16" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="H150" s="15" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="I150" s="16" t="s">
         <v>150</v>
@@ -10434,41 +9814,41 @@
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="L150" s="20" t="s">
+      <c r="L150" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M150" s="19">
-        <v>0.9908</v>
-      </c>
-      <c r="N150" s="19">
+      <c r="M150" s="18">
+        <v>0.99080000000000001</v>
+      </c>
+      <c r="N150" s="18">
         <f t="shared" si="10"/>
-        <v>5.9448</v>
+        <v>5.9447999999999999</v>
       </c>
       <c r="O150" s="15"/>
     </row>
-    <row r="151" ht="24.75" spans="1:15">
+    <row r="151" spans="1:15" ht="24.75" thickBot="1">
       <c r="A151" s="5"/>
       <c r="B151" s="10">
         <f>ROW(B151)-ROW($B$2)</f>
         <v>149</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F151" s="12" t="s">
         <v>111</v>
       </c>
       <c r="G151" s="16" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="H151" s="15" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="I151" s="16" t="s">
         <v>150</v>
@@ -10480,41 +9860,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L151" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M151" s="19">
-        <v>0.56</v>
-      </c>
-      <c r="N151" s="19">
+      <c r="L151" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M151" s="18">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="N151" s="18">
         <f t="shared" si="10"/>
         <v>1.68</v>
       </c>
       <c r="O151" s="15"/>
     </row>
-    <row r="152" ht="15.75" spans="1:15">
+    <row r="152" spans="1:15" ht="15.75" thickBot="1">
       <c r="A152" s="5"/>
       <c r="B152" s="10">
         <f>ROW(B152)-ROW($B$2)</f>
         <v>150</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F152" s="12" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="G152" s="12" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="H152" s="12" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="I152" s="16" t="s">
         <v>150</v>
@@ -10526,41 +9906,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L152" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M152" s="19">
+      <c r="L152" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M152" s="18">
         <v>2.89</v>
       </c>
-      <c r="N152" s="19">
+      <c r="N152" s="18">
         <f t="shared" si="10"/>
         <v>8.67</v>
       </c>
       <c r="O152" s="15"/>
     </row>
-    <row r="153" ht="24.75" spans="1:15">
+    <row r="153" spans="1:15" ht="24.75" thickBot="1">
       <c r="A153" s="5"/>
       <c r="B153" s="10">
         <f t="shared" si="8"/>
         <v>151</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="E153" s="16" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="G153" s="16" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="H153" s="15" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I153" s="16" t="s">
         <v>150</v>
@@ -10572,41 +9952,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L153" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M153" s="19">
+      <c r="L153" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M153" s="18">
         <v>1.35</v>
       </c>
-      <c r="N153" s="19">
+      <c r="N153" s="18">
         <f t="shared" si="10"/>
         <v>4.05</v>
       </c>
       <c r="O153" s="15"/>
     </row>
-    <row r="154" ht="24.75" spans="1:15">
+    <row r="154" spans="1:15" ht="24.75" thickBot="1">
       <c r="A154" s="5"/>
       <c r="B154" s="10">
         <f>ROW(B154)-ROW($B$2)</f>
         <v>152</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="F154" s="12" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="H154" s="12" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I154" s="16" t="s">
         <v>150</v>
@@ -10618,41 +9998,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L154" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M154" s="19">
+      <c r="L154" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M154" s="18">
         <v>2.13</v>
       </c>
-      <c r="N154" s="19">
+      <c r="N154" s="18">
         <f t="shared" si="10"/>
         <v>6.39</v>
       </c>
       <c r="O154" s="12"/>
     </row>
-    <row r="155" ht="15.75" spans="1:15">
+    <row r="155" spans="1:15" ht="15.75" thickBot="1">
       <c r="A155" s="5"/>
       <c r="B155" s="10">
         <f t="shared" si="8"/>
         <v>153</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E155" s="16" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="F155" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G155" s="16" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="H155" s="15" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="I155" s="16" t="s">
         <v>150</v>
@@ -10664,41 +10044,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L155" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M155" s="19">
-        <v>0.15685</v>
-      </c>
-      <c r="N155" s="19">
+      <c r="L155" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M155" s="18">
+        <v>0.15684999999999999</v>
+      </c>
+      <c r="N155" s="18">
         <f t="shared" si="10"/>
-        <v>0.47055</v>
+        <v>0.47055000000000002</v>
       </c>
       <c r="O155" s="15"/>
     </row>
-    <row r="156" ht="15.75" spans="1:15">
+    <row r="156" spans="1:15" ht="15.75" thickBot="1">
       <c r="A156" s="5"/>
       <c r="B156" s="10">
         <f>ROW(B156)-ROW($B$2)</f>
         <v>154</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="F156" s="12" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="H156" s="12" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="I156" s="16" t="s">
         <v>150</v>
@@ -10710,41 +10090,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L156" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M156" s="19">
+      <c r="L156" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M156" s="18">
         <v>0.36</v>
       </c>
-      <c r="N156" s="19">
+      <c r="N156" s="18">
         <f t="shared" si="10"/>
         <v>1.08</v>
       </c>
       <c r="O156" s="12"/>
     </row>
-    <row r="157" ht="24.75" spans="1:15">
+    <row r="157" spans="1:15" ht="24.75" thickBot="1">
       <c r="A157" s="5"/>
       <c r="B157" s="10">
         <f t="shared" si="8"/>
         <v>155</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E157" s="16" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F157" s="15" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="G157" s="16" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="H157" s="15" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="I157" s="16" t="s">
         <v>150</v>
@@ -10756,41 +10136,41 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L157" s="20" t="s">
+      <c r="L157" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="M157" s="19">
-        <v>0.3446</v>
-      </c>
-      <c r="N157" s="19">
+      <c r="M157" s="18">
+        <v>0.34460000000000002</v>
+      </c>
+      <c r="N157" s="18">
         <f t="shared" si="10"/>
-        <v>1.0338</v>
+        <v>1.0338000000000001</v>
       </c>
       <c r="O157" s="15"/>
     </row>
-    <row r="158" ht="36.75" spans="1:15">
+    <row r="158" spans="1:15" ht="36.75" thickBot="1">
       <c r="A158" s="5"/>
       <c r="B158" s="10">
         <f>ROW(B158)-ROW($B$2)</f>
         <v>156</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F158" s="12" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="H158" s="12" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="I158" s="16" t="s">
         <v>150</v>
@@ -10802,44 +10182,44 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L158" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M158" s="19">
+      <c r="L158" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M158" s="18">
         <v>0.94</v>
       </c>
-      <c r="N158" s="19">
+      <c r="N158" s="18">
         <f t="shared" si="10"/>
         <v>2.82</v>
       </c>
       <c r="O158" s="12"/>
     </row>
-    <row r="159" ht="36.75" spans="1:15">
+    <row r="159" spans="1:15" ht="36.75" thickBot="1">
       <c r="A159" s="5"/>
       <c r="B159" s="10">
         <f t="shared" si="8"/>
         <v>157</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G159" s="16" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="H159" s="15" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="I159" s="16" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="J159" s="15">
         <v>1</v>
@@ -10848,44 +10228,44 @@
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L159" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M159" s="19">
-        <v>0.28785</v>
-      </c>
-      <c r="N159" s="19">
+      <c r="L159" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M159" s="18">
+        <v>0.28784999999999999</v>
+      </c>
+      <c r="N159" s="18">
         <f t="shared" si="10"/>
-        <v>0.86355</v>
+        <v>0.86355000000000004</v>
       </c>
       <c r="O159" s="15"/>
     </row>
-    <row r="160" ht="15.75" spans="1:15">
+    <row r="160" spans="1:15" ht="15.75" thickBot="1">
       <c r="A160" s="5"/>
       <c r="B160" s="10">
         <f>ROW(B160)-ROW($B$2)</f>
         <v>158</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="I160" s="13" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="J160" s="12">
         <v>2</v>
@@ -10894,28 +10274,28 @@
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="L160" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="M160" s="19">
-        <v>0.806</v>
-      </c>
-      <c r="N160" s="19">
+      <c r="L160" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="M160" s="18">
+        <v>0.80600000000000005</v>
+      </c>
+      <c r="N160" s="18">
         <f t="shared" si="10"/>
-        <v>4.836</v>
+        <v>4.8360000000000003</v>
       </c>
       <c r="O160" s="12"/>
     </row>
-    <row r="161" ht="15.75" spans="2:15">
+    <row r="161" spans="2:19" ht="15.75" thickBot="1">
       <c r="B161" s="10">
         <f t="shared" ref="B161:B167" si="12">ROW(B161)-ROW($B$2)</f>
         <v>159</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="E161" s="13"/>
       <c r="F161" s="15"/>
@@ -10924,36 +10304,36 @@
       <c r="I161" s="13"/>
       <c r="J161" s="12"/>
       <c r="K161" s="12"/>
-      <c r="L161" s="20"/>
-      <c r="M161" s="19"/>
-      <c r="N161" s="19">
+      <c r="L161" s="19"/>
+      <c r="M161" s="18"/>
+      <c r="N161" s="18">
         <f>M161*K161</f>
         <v>0</v>
       </c>
       <c r="O161" s="12"/>
     </row>
-    <row r="162" ht="36.75" spans="2:15">
+    <row r="162" spans="2:19" ht="36.75" thickBot="1">
       <c r="B162" s="10">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="F162" s="15" t="s">
         <v>150</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I162" s="13" t="s">
         <v>150</v>
@@ -10964,31 +10344,31 @@
       <c r="K162" s="12">
         <v>3</v>
       </c>
-      <c r="L162" s="18" t="s">
+      <c r="L162" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="M162" s="19">
+      <c r="M162" s="18">
         <v>0.43</v>
       </c>
-      <c r="N162" s="19">
+      <c r="N162" s="18">
         <f>M162*K162</f>
         <v>1.29</v>
       </c>
       <c r="O162" s="12"/>
     </row>
-    <row r="163" ht="30.75" spans="2:15">
+    <row r="163" spans="2:19" ht="30.75" thickBot="1">
       <c r="B163" s="10">
         <f t="shared" si="12"/>
         <v>161</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="F163" s="15" t="s">
         <v>150</v>
@@ -10997,7 +10377,7 @@
         <v>150</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>150</v>
@@ -11008,40 +10388,40 @@
       <c r="K163" s="12">
         <v>3</v>
       </c>
-      <c r="L163" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="M163" s="19">
+      <c r="L163" s="19" t="s">
+        <v>690</v>
+      </c>
+      <c r="M163" s="18">
         <v>7</v>
       </c>
-      <c r="N163" s="19">
+      <c r="N163" s="18">
         <f>M163*K163</f>
         <v>21</v>
       </c>
       <c r="O163" s="12"/>
     </row>
-    <row r="164" ht="15.75" spans="2:15">
+    <row r="164" spans="2:19" ht="15.75" thickBot="1">
       <c r="B164" s="10">
         <f t="shared" si="12"/>
         <v>162</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F164" s="15" t="s">
         <v>150</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="I164" s="13" t="s">
         <v>150</v>
@@ -11052,127 +10432,130 @@
       <c r="K164" s="12">
         <v>3</v>
       </c>
-      <c r="L164" s="20" t="s">
-        <v>703</v>
-      </c>
-      <c r="M164" s="19">
+      <c r="L164" s="19" t="s">
+        <v>695</v>
+      </c>
+      <c r="M164" s="18">
         <v>99</v>
       </c>
-      <c r="N164" s="19">
+      <c r="N164" s="18">
         <f>M164*K164</f>
         <v>297</v>
       </c>
       <c r="O164" s="12"/>
     </row>
-    <row r="165" ht="15.75" spans="2:15">
+    <row r="165" spans="2:19" ht="24.75" thickBot="1">
       <c r="B165" s="10">
         <f t="shared" si="12"/>
         <v>163</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="F165" s="15"/>
       <c r="G165" s="13" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="I165" s="13"/>
       <c r="J165" s="12"/>
       <c r="K165" s="12"/>
-      <c r="L165" s="18" t="s">
-        <v>706</v>
-      </c>
-      <c r="M165" s="19"/>
-      <c r="N165" s="19"/>
+      <c r="L165" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="M165" s="18"/>
+      <c r="N165" s="18"/>
       <c r="O165" s="12"/>
     </row>
-    <row r="166" ht="24.75" spans="2:15">
+    <row r="166" spans="2:19" ht="24.75" thickBot="1">
       <c r="B166" s="10">
         <f t="shared" si="12"/>
         <v>164</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="F166" s="15"/>
       <c r="G166" s="13" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="I166" s="13"/>
       <c r="J166" s="12"/>
       <c r="K166" s="12"/>
-      <c r="L166" s="18" t="s">
-        <v>709</v>
-      </c>
-      <c r="M166" s="19"/>
-      <c r="N166" s="19"/>
+      <c r="L166" s="17" t="s">
+        <v>701</v>
+      </c>
+      <c r="M166" s="18"/>
+      <c r="N166" s="18"/>
       <c r="O166" s="12"/>
     </row>
-    <row r="167" s="3" customFormat="1" ht="24.75" spans="2:15">
+    <row r="167" spans="2:19" s="3" customFormat="1" ht="24.75" thickBot="1">
       <c r="B167" s="10">
         <f t="shared" si="12"/>
         <v>165</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="D167" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="F167" s="15"/>
       <c r="G167" s="13" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="H167" s="12" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="I167" s="13"/>
       <c r="J167" s="12"/>
       <c r="K167" s="12"/>
-      <c r="L167" s="18" t="s">
-        <v>713</v>
-      </c>
-      <c r="M167" s="50"/>
-      <c r="N167" s="50"/>
+      <c r="L167" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="M167" s="41"/>
+      <c r="N167" s="41"/>
       <c r="O167" s="12"/>
-    </row>
-    <row r="168" spans="13:14">
-      <c r="M168" s="51" t="s">
-        <v>714</v>
-      </c>
-      <c r="N168" s="52">
+      <c r="Q167"/>
+      <c r="R167"/>
+      <c r="S167"/>
+    </row>
+    <row r="168" spans="2:19">
+      <c r="M168" s="42" t="s">
+        <v>706</v>
+      </c>
+      <c r="N168" s="43">
         <f>SUM(N3:N167)</f>
-        <v>769.75629</v>
-      </c>
-    </row>
-    <row r="169" ht="15.75" spans="13:14">
-      <c r="M169" s="53" t="s">
-        <v>715</v>
-      </c>
-      <c r="N169" s="54">
+        <v>767.79249000000004</v>
+      </c>
+    </row>
+    <row r="169" spans="2:19" ht="15.75" thickBot="1">
+      <c r="M169" s="44" t="s">
+        <v>707</v>
+      </c>
+      <c r="N169" s="45">
         <f>N168/3</f>
-        <v>256.58543</v>
+        <v>255.93083000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11180,168 +10563,167 @@
     <mergeCell ref="I1:O1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" display="Digikey"/>
-    <hyperlink ref="L4" r:id="rId2" display="Digikey"/>
-    <hyperlink ref="L5" r:id="rId3" display="Digikey"/>
-    <hyperlink ref="L6" r:id="rId4" display="Digikey"/>
-    <hyperlink ref="L7" r:id="rId5" display="Digikey"/>
-    <hyperlink ref="L8" r:id="rId6" display="Digikey"/>
-    <hyperlink ref="L9" r:id="rId7" display="Digikey"/>
-    <hyperlink ref="L10" r:id="rId8" display="Digikey"/>
-    <hyperlink ref="L11" r:id="rId9" display="Digikey"/>
-    <hyperlink ref="L12" r:id="rId10" display="Digikey"/>
-    <hyperlink ref="L13" r:id="rId11" display="Digikey"/>
-    <hyperlink ref="L14" r:id="rId12" display="Digikey"/>
-    <hyperlink ref="L15" r:id="rId13" display="Digikey"/>
-    <hyperlink ref="L16" r:id="rId14" display="Digikey"/>
-    <hyperlink ref="L17" r:id="rId15" display="Digikey"/>
-    <hyperlink ref="L18" r:id="rId16" display="Digikey"/>
-    <hyperlink ref="L19" r:id="rId17" display="Digikey"/>
-    <hyperlink ref="L20" r:id="rId18" display="Digikey"/>
-    <hyperlink ref="L21" r:id="rId19" display="Digikey"/>
-    <hyperlink ref="L22" r:id="rId20" display="Digikey"/>
-    <hyperlink ref="L23" r:id="rId21" display="Digikey"/>
-    <hyperlink ref="L24" r:id="rId22" display="Digikey"/>
-    <hyperlink ref="L26" r:id="rId23" display="Digikey"/>
-    <hyperlink ref="L27" r:id="rId24" display="Digikey"/>
-    <hyperlink ref="L28" r:id="rId12" display="Digikey"/>
-    <hyperlink ref="L29" r:id="rId25" display="Digikey"/>
-    <hyperlink ref="L30" r:id="rId26" display="Digikey"/>
-    <hyperlink ref="L31" r:id="rId27" display="Digikey"/>
-    <hyperlink ref="L32" r:id="rId28" display="Digikey"/>
-    <hyperlink ref="L33" r:id="rId29" display="Digikey"/>
-    <hyperlink ref="L36" r:id="rId30" display="Digikey"/>
-    <hyperlink ref="L37" r:id="rId31" display="Digikey"/>
-    <hyperlink ref="L38" r:id="rId32" display="Digikey"/>
-    <hyperlink ref="L42" r:id="rId33" display="Digikey"/>
-    <hyperlink ref="L43" r:id="rId34" display="Digikey"/>
-    <hyperlink ref="L45" r:id="rId35" display="Digikey"/>
-    <hyperlink ref="L46" r:id="rId36" display="Digikey"/>
-    <hyperlink ref="L47" r:id="rId37" display="Digikey"/>
-    <hyperlink ref="L50" r:id="rId38" display="Digikey"/>
-    <hyperlink ref="L60" r:id="rId39" display="Digikey"/>
-    <hyperlink ref="L61" r:id="rId40" display="Digikey"/>
-    <hyperlink ref="L67" r:id="rId41" display="Digikey"/>
-    <hyperlink ref="L70" r:id="rId42" display="Digikey"/>
-    <hyperlink ref="L72" r:id="rId43" display="Digikey"/>
-    <hyperlink ref="L73" r:id="rId44" display="Digikey"/>
-    <hyperlink ref="L78" r:id="rId45" display="Digikey"/>
-    <hyperlink ref="L79" r:id="rId46" display="Digikey"/>
-    <hyperlink ref="L80" r:id="rId47" display="Digikey"/>
-    <hyperlink ref="L82" r:id="rId48" display="Digikey"/>
-    <hyperlink ref="L84" r:id="rId49" display="Digikey"/>
-    <hyperlink ref="L86" r:id="rId50" display="Digikey"/>
-    <hyperlink ref="L25" r:id="rId51" display="LCSC"/>
-    <hyperlink ref="L34" r:id="rId52" display="LCSC"/>
-    <hyperlink ref="L35" r:id="rId53" display="LCSC"/>
-    <hyperlink ref="L39" r:id="rId54" display="LCSC"/>
-    <hyperlink ref="L40" r:id="rId55" display="LCSC"/>
-    <hyperlink ref="L41" r:id="rId56" display="LCSC"/>
-    <hyperlink ref="L44" r:id="rId57" display="LCSC"/>
-    <hyperlink ref="L48" r:id="rId58" display="LCSC"/>
-    <hyperlink ref="L49" r:id="rId59" display="LCSC"/>
-    <hyperlink ref="L51" r:id="rId60" display="LCSC"/>
-    <hyperlink ref="L52" r:id="rId61" display="LCSC"/>
-    <hyperlink ref="L53" r:id="rId62" display="LCSC"/>
-    <hyperlink ref="L54" r:id="rId63" display="LCSC"/>
-    <hyperlink ref="L55" r:id="rId64" display="LCSC"/>
-    <hyperlink ref="L56" r:id="rId65" display="LCSC"/>
-    <hyperlink ref="L57" r:id="rId66" display="LCSC"/>
-    <hyperlink ref="L58" r:id="rId67" display="LCSC"/>
-    <hyperlink ref="L59" r:id="rId68" display="LCSC"/>
-    <hyperlink ref="L62" r:id="rId69" display="LCSC"/>
-    <hyperlink ref="L63" r:id="rId70" display="LCSC"/>
-    <hyperlink ref="L64" r:id="rId71" display="LCSC"/>
-    <hyperlink ref="L65" r:id="rId72" display="LCSC"/>
-    <hyperlink ref="L66" r:id="rId73" display="LCSC"/>
-    <hyperlink ref="L68" r:id="rId74" display="LCSC"/>
-    <hyperlink ref="L69" r:id="rId75" display="LCSC"/>
-    <hyperlink ref="L74" r:id="rId76" display="LCSC"/>
-    <hyperlink ref="L75" r:id="rId77" display="LCSC"/>
-    <hyperlink ref="L76" r:id="rId78" display="LCSC"/>
-    <hyperlink ref="L77" r:id="rId79" display="LCSC"/>
-    <hyperlink ref="L81" r:id="rId80" display="LCSC"/>
-    <hyperlink ref="L83" r:id="rId81" display="LCSC"/>
-    <hyperlink ref="L85" r:id="rId82" display="Digikey"/>
-    <hyperlink ref="L88" r:id="rId83" display="LCSC"/>
-    <hyperlink ref="L87" r:id="rId84" display="Digikey"/>
-    <hyperlink ref="L89" r:id="rId85" display="Digikey"/>
-    <hyperlink ref="L90" r:id="rId86" display="Digikey"/>
-    <hyperlink ref="L91" r:id="rId87" display="Digikey"/>
-    <hyperlink ref="L92" r:id="rId88" display="Digikey"/>
-    <hyperlink ref="L93" r:id="rId89" display="Digikey"/>
-    <hyperlink ref="L95" r:id="rId90" display="Digikey"/>
-    <hyperlink ref="L96" r:id="rId91" display="Digikey"/>
-    <hyperlink ref="L97" r:id="rId92" display="Digikey"/>
-    <hyperlink ref="L98" r:id="rId93" display="Digikey"/>
-    <hyperlink ref="L99" r:id="rId94" display="Digikey"/>
-    <hyperlink ref="L100" r:id="rId95" display="Digikey"/>
-    <hyperlink ref="L101" r:id="rId96" display="Digikey"/>
-    <hyperlink ref="L102" r:id="rId97" display="Digikey"/>
-    <hyperlink ref="L103" r:id="rId98" display="Digikey"/>
-    <hyperlink ref="L104" r:id="rId99" display="Digikey"/>
-    <hyperlink ref="L105" r:id="rId100" display="Digikey"/>
-    <hyperlink ref="L106" r:id="rId101" display="Digikey"/>
-    <hyperlink ref="L108" r:id="rId102" display="Digikey"/>
-    <hyperlink ref="L109" r:id="rId103" display="Digikey"/>
-    <hyperlink ref="L111" r:id="rId104" display="Digikey"/>
-    <hyperlink ref="L112" r:id="rId105" display="Digikey"/>
-    <hyperlink ref="L113" r:id="rId106" display="Digikey"/>
-    <hyperlink ref="L114" r:id="rId107" display="Digikey"/>
-    <hyperlink ref="L115" r:id="rId108" display="Digikey"/>
-    <hyperlink ref="L116" r:id="rId109" display="Digikey"/>
-    <hyperlink ref="L117" r:id="rId110" display="Digikey"/>
-    <hyperlink ref="L118" r:id="rId111" display="Digikey"/>
-    <hyperlink ref="L119" r:id="rId112" display="Digikey"/>
-    <hyperlink ref="L120" r:id="rId113" display="Digikey"/>
-    <hyperlink ref="L122" r:id="rId114" display="Digikey"/>
-    <hyperlink ref="L123" r:id="rId115" display="Digikey"/>
-    <hyperlink ref="L124" r:id="rId116" display="Digikey"/>
-    <hyperlink ref="L125" r:id="rId117" display="Digikey"/>
-    <hyperlink ref="L126" r:id="rId118" display="Digikey"/>
-    <hyperlink ref="L127" r:id="rId119" display="Digikey"/>
-    <hyperlink ref="L128" r:id="rId120" display="Digikey"/>
-    <hyperlink ref="L129" r:id="rId121" display="Digikey"/>
-    <hyperlink ref="L130" r:id="rId122" display="Digikey"/>
-    <hyperlink ref="L131" r:id="rId123" display="Digikey"/>
-    <hyperlink ref="L132" r:id="rId124" display="LCSC"/>
-    <hyperlink ref="L133" r:id="rId125" display="LCSC"/>
-    <hyperlink ref="L134" r:id="rId126" display="Digikey"/>
-    <hyperlink ref="L135" r:id="rId127" display="Digikey"/>
-    <hyperlink ref="L136" r:id="rId128" display="Digikey"/>
-    <hyperlink ref="L137" r:id="rId129" display="LCSC"/>
-    <hyperlink ref="L138" r:id="rId130" display="Digikey"/>
-    <hyperlink ref="L139" r:id="rId131" display="Digikey"/>
-    <hyperlink ref="L140" r:id="rId132" display="Digikey"/>
-    <hyperlink ref="L141" r:id="rId133" display="Digikey"/>
-    <hyperlink ref="L142" r:id="rId134" display="Digikey"/>
-    <hyperlink ref="L143" r:id="rId135" display="Digikey"/>
-    <hyperlink ref="L144" r:id="rId136" display="LCSC"/>
-    <hyperlink ref="L145" r:id="rId137" display="LCSC"/>
-    <hyperlink ref="L146" r:id="rId138" display="LCSC"/>
-    <hyperlink ref="L147" r:id="rId139" display="LCSC"/>
-    <hyperlink ref="L148" r:id="rId140" display="Digikey"/>
-    <hyperlink ref="L149" r:id="rId141" display="Digikey"/>
-    <hyperlink ref="L150" r:id="rId142" display="LCSC"/>
-    <hyperlink ref="L151" r:id="rId143" display="Digikey"/>
-    <hyperlink ref="L152" r:id="rId144" display="Digikey"/>
-    <hyperlink ref="L153" r:id="rId145" display="Digikey"/>
-    <hyperlink ref="L154" r:id="rId146" display="Digikey"/>
-    <hyperlink ref="L155" r:id="rId147" display="Digikey"/>
-    <hyperlink ref="L156" r:id="rId148" display="Digikey"/>
-    <hyperlink ref="L157" r:id="rId149" display="LCSC"/>
-    <hyperlink ref="L158" r:id="rId150" display="Digikey"/>
-    <hyperlink ref="L159" r:id="rId151" display="Digikey"/>
-    <hyperlink ref="L160" r:id="rId152" display="Digikey"/>
-    <hyperlink ref="L71" r:id="rId153" display="Digikey"/>
-    <hyperlink ref="L166" r:id="rId154" display="Epson"/>
-    <hyperlink ref="L165" r:id="rId155" display="ELATEC"/>
-    <hyperlink ref="L167" r:id="rId156" display="AmaZon"/>
-    <hyperlink ref="L163" r:id="rId157" display="Aliexpress"/>
-    <hyperlink ref="L162" r:id="rId158" display="LCSC"/>
+    <hyperlink ref="L3" r:id="rId1"/>
+    <hyperlink ref="L4" r:id="rId2"/>
+    <hyperlink ref="L5" r:id="rId3"/>
+    <hyperlink ref="L6" r:id="rId4"/>
+    <hyperlink ref="L7" r:id="rId5"/>
+    <hyperlink ref="L8" r:id="rId6"/>
+    <hyperlink ref="L9" r:id="rId7"/>
+    <hyperlink ref="L10" r:id="rId8"/>
+    <hyperlink ref="L11" r:id="rId9"/>
+    <hyperlink ref="L12" r:id="rId10"/>
+    <hyperlink ref="L13" r:id="rId11"/>
+    <hyperlink ref="L14" r:id="rId12"/>
+    <hyperlink ref="L15" r:id="rId13"/>
+    <hyperlink ref="L16" r:id="rId14"/>
+    <hyperlink ref="L17" r:id="rId15"/>
+    <hyperlink ref="L18" r:id="rId16"/>
+    <hyperlink ref="L19" r:id="rId17"/>
+    <hyperlink ref="L20" r:id="rId18"/>
+    <hyperlink ref="L21" r:id="rId19"/>
+    <hyperlink ref="L22" r:id="rId20"/>
+    <hyperlink ref="L23" r:id="rId21"/>
+    <hyperlink ref="L24" r:id="rId22"/>
+    <hyperlink ref="L26" r:id="rId23"/>
+    <hyperlink ref="L27" r:id="rId24"/>
+    <hyperlink ref="L28" r:id="rId25"/>
+    <hyperlink ref="L29" r:id="rId26"/>
+    <hyperlink ref="L30" r:id="rId27"/>
+    <hyperlink ref="L31" r:id="rId28"/>
+    <hyperlink ref="L32" r:id="rId29"/>
+    <hyperlink ref="L33" r:id="rId30"/>
+    <hyperlink ref="L36" r:id="rId31"/>
+    <hyperlink ref="L37" r:id="rId32"/>
+    <hyperlink ref="L38" r:id="rId33"/>
+    <hyperlink ref="L42" r:id="rId34"/>
+    <hyperlink ref="L43" r:id="rId35"/>
+    <hyperlink ref="L45" r:id="rId36"/>
+    <hyperlink ref="L46" r:id="rId37"/>
+    <hyperlink ref="L47" r:id="rId38"/>
+    <hyperlink ref="L50" r:id="rId39"/>
+    <hyperlink ref="L60" r:id="rId40"/>
+    <hyperlink ref="L61" r:id="rId41"/>
+    <hyperlink ref="L67" r:id="rId42"/>
+    <hyperlink ref="L70" r:id="rId43"/>
+    <hyperlink ref="L72" r:id="rId44"/>
+    <hyperlink ref="L73" r:id="rId45"/>
+    <hyperlink ref="L78" r:id="rId46"/>
+    <hyperlink ref="L79" r:id="rId47"/>
+    <hyperlink ref="L80" r:id="rId48"/>
+    <hyperlink ref="L82" r:id="rId49"/>
+    <hyperlink ref="L84" r:id="rId50"/>
+    <hyperlink ref="L86" r:id="rId51"/>
+    <hyperlink ref="L25" r:id="rId52"/>
+    <hyperlink ref="L34" r:id="rId53"/>
+    <hyperlink ref="L35" r:id="rId54"/>
+    <hyperlink ref="L39" r:id="rId55"/>
+    <hyperlink ref="L40" r:id="rId56"/>
+    <hyperlink ref="L41" r:id="rId57"/>
+    <hyperlink ref="L44" r:id="rId58"/>
+    <hyperlink ref="L48" r:id="rId59"/>
+    <hyperlink ref="L49" r:id="rId60"/>
+    <hyperlink ref="L51" r:id="rId61"/>
+    <hyperlink ref="L52" r:id="rId62"/>
+    <hyperlink ref="L53" r:id="rId63"/>
+    <hyperlink ref="L54" r:id="rId64"/>
+    <hyperlink ref="L55" r:id="rId65"/>
+    <hyperlink ref="L57" r:id="rId66"/>
+    <hyperlink ref="L58" r:id="rId67"/>
+    <hyperlink ref="L59" r:id="rId68"/>
+    <hyperlink ref="L62" r:id="rId69"/>
+    <hyperlink ref="L63" r:id="rId70"/>
+    <hyperlink ref="L64" r:id="rId71"/>
+    <hyperlink ref="L65" r:id="rId72"/>
+    <hyperlink ref="L66" r:id="rId73"/>
+    <hyperlink ref="L68" r:id="rId74"/>
+    <hyperlink ref="L69" r:id="rId75"/>
+    <hyperlink ref="L74" r:id="rId76"/>
+    <hyperlink ref="L75" r:id="rId77"/>
+    <hyperlink ref="L76" r:id="rId78"/>
+    <hyperlink ref="L77" r:id="rId79"/>
+    <hyperlink ref="L81" r:id="rId80"/>
+    <hyperlink ref="L83" r:id="rId81"/>
+    <hyperlink ref="L85" r:id="rId82"/>
+    <hyperlink ref="L88" r:id="rId83"/>
+    <hyperlink ref="L87" r:id="rId84"/>
+    <hyperlink ref="L89" r:id="rId85"/>
+    <hyperlink ref="L90" r:id="rId86"/>
+    <hyperlink ref="L91" r:id="rId87"/>
+    <hyperlink ref="L92" r:id="rId88"/>
+    <hyperlink ref="L93" r:id="rId89"/>
+    <hyperlink ref="L95" r:id="rId90"/>
+    <hyperlink ref="L96" r:id="rId91"/>
+    <hyperlink ref="L97" r:id="rId92"/>
+    <hyperlink ref="L98" r:id="rId93"/>
+    <hyperlink ref="L99" r:id="rId94"/>
+    <hyperlink ref="L100" r:id="rId95"/>
+    <hyperlink ref="L101" r:id="rId96"/>
+    <hyperlink ref="L102" r:id="rId97"/>
+    <hyperlink ref="L103" r:id="rId98"/>
+    <hyperlink ref="L104" r:id="rId99"/>
+    <hyperlink ref="L105" r:id="rId100"/>
+    <hyperlink ref="L106" r:id="rId101"/>
+    <hyperlink ref="L108" r:id="rId102"/>
+    <hyperlink ref="L109" r:id="rId103"/>
+    <hyperlink ref="L111" r:id="rId104"/>
+    <hyperlink ref="L112" r:id="rId105"/>
+    <hyperlink ref="L113" r:id="rId106"/>
+    <hyperlink ref="L114" r:id="rId107"/>
+    <hyperlink ref="L115" r:id="rId108"/>
+    <hyperlink ref="L116" r:id="rId109"/>
+    <hyperlink ref="L117" r:id="rId110"/>
+    <hyperlink ref="L118" r:id="rId111"/>
+    <hyperlink ref="L119" r:id="rId112"/>
+    <hyperlink ref="L120" r:id="rId113"/>
+    <hyperlink ref="L122" r:id="rId114"/>
+    <hyperlink ref="L123" r:id="rId115"/>
+    <hyperlink ref="L124" r:id="rId116"/>
+    <hyperlink ref="L125" r:id="rId117"/>
+    <hyperlink ref="L126" r:id="rId118"/>
+    <hyperlink ref="L127" r:id="rId119"/>
+    <hyperlink ref="L128" r:id="rId120"/>
+    <hyperlink ref="L129" r:id="rId121"/>
+    <hyperlink ref="L130" r:id="rId122"/>
+    <hyperlink ref="L131" r:id="rId123"/>
+    <hyperlink ref="L132" r:id="rId124"/>
+    <hyperlink ref="L133" r:id="rId125"/>
+    <hyperlink ref="L135" r:id="rId126"/>
+    <hyperlink ref="L136" r:id="rId127"/>
+    <hyperlink ref="L137" r:id="rId128"/>
+    <hyperlink ref="L138" r:id="rId129"/>
+    <hyperlink ref="L139" r:id="rId130"/>
+    <hyperlink ref="L140" r:id="rId131"/>
+    <hyperlink ref="L141" r:id="rId132"/>
+    <hyperlink ref="L142" r:id="rId133"/>
+    <hyperlink ref="L143" r:id="rId134"/>
+    <hyperlink ref="L144" r:id="rId135"/>
+    <hyperlink ref="L145" r:id="rId136"/>
+    <hyperlink ref="L146" r:id="rId137"/>
+    <hyperlink ref="L147" r:id="rId138"/>
+    <hyperlink ref="L148" r:id="rId139"/>
+    <hyperlink ref="L149" r:id="rId140"/>
+    <hyperlink ref="L150" r:id="rId141"/>
+    <hyperlink ref="L151" r:id="rId142"/>
+    <hyperlink ref="L152" r:id="rId143"/>
+    <hyperlink ref="L153" r:id="rId144"/>
+    <hyperlink ref="L154" r:id="rId145"/>
+    <hyperlink ref="L155" r:id="rId146"/>
+    <hyperlink ref="L156" r:id="rId147"/>
+    <hyperlink ref="L157" r:id="rId148"/>
+    <hyperlink ref="L158" r:id="rId149"/>
+    <hyperlink ref="L159" r:id="rId150"/>
+    <hyperlink ref="L160" r:id="rId151"/>
+    <hyperlink ref="L166" r:id="rId152"/>
+    <hyperlink ref="L165" r:id="rId153"/>
+    <hyperlink ref="L167" r:id="rId154"/>
+    <hyperlink ref="L163" r:id="rId155"/>
+    <hyperlink ref="L162" r:id="rId156"/>
+    <hyperlink ref="L56" r:id="rId157"/>
+    <hyperlink ref="L71" r:id="rId158"/>
+    <hyperlink ref="L134" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="718">
   <si>
     <t>#</t>
   </si>
@@ -2181,6 +2181,12 @@
   </si>
   <si>
     <t>IC RS232 LINE DVR/RCVR 16-SOIC</t>
+  </si>
+  <si>
+    <t>1.8 3dBi Vertical 50W - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BWGSMJWX105-7KJ</t>
   </si>
 </sst>
 </file>
@@ -8983,7 +8989,7 @@
         <v>6</v>
       </c>
       <c r="K132" s="12">
-        <f t="shared" ref="K132:K160" si="11">3*J132</f>
+        <f t="shared" ref="K132:K161" si="11">3*J132</f>
         <v>18</v>
       </c>
       <c r="L132" s="19" t="s">
@@ -10286,7 +10292,7 @@
       </c>
       <c r="O160" s="12"/>
     </row>
-    <row r="161" spans="2:19" ht="15.75" thickBot="1">
+    <row r="161" spans="2:19" ht="24.75" thickBot="1">
       <c r="B161" s="10">
         <f t="shared" ref="B161:B167" si="12">ROW(B161)-ROW($B$2)</f>
         <v>159</v>
@@ -10297,18 +10303,35 @@
       <c r="D161" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="E161" s="13"/>
-      <c r="F161" s="15"/>
-      <c r="G161" s="13"/>
-      <c r="H161" s="12"/>
+      <c r="E161" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="F161" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G161" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>249</v>
+      </c>
       <c r="I161" s="13"/>
-      <c r="J161" s="12"/>
-      <c r="K161" s="12"/>
-      <c r="L161" s="19"/>
-      <c r="M161" s="18"/>
+      <c r="J161" s="12">
+        <v>1</v>
+      </c>
+      <c r="K161" s="12">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="L161" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="M161" s="18">
+        <v>1.0093000000000001</v>
+      </c>
       <c r="N161" s="18">
         <f>M161*K161</f>
-        <v>0</v>
+        <v>3.0279000000000003</v>
       </c>
       <c r="O161" s="12"/>
     </row>
@@ -10546,7 +10569,7 @@
       </c>
       <c r="N168" s="43">
         <f>SUM(N3:N167)</f>
-        <v>767.79249000000004</v>
+        <v>770.82039000000009</v>
       </c>
     </row>
     <row r="169" spans="2:19" ht="15.75" thickBot="1">
@@ -10555,7 +10578,7 @@
       </c>
       <c r="N169" s="45">
         <f>N168/3</f>
-        <v>255.93083000000001</v>
+        <v>256.94013000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10722,6 +10745,7 @@
     <hyperlink ref="L56" r:id="rId157"/>
     <hyperlink ref="L71" r:id="rId158"/>
     <hyperlink ref="L134" r:id="rId159"/>
+    <hyperlink ref="L161" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="715">
   <si>
     <t>#</t>
   </si>
@@ -1420,9 +1420,6 @@
     <t>R56</t>
   </si>
   <si>
-    <t>R58, R66</t>
-  </si>
-  <si>
     <t>RES 12K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -1571,15 +1568,6 @@
   </si>
   <si>
     <t>3K</t>
-  </si>
-  <si>
-    <t>R198</t>
-  </si>
-  <si>
-    <t>RES SMD 12K OHM 1% 1/5W 0402</t>
-  </si>
-  <si>
-    <t>RCS040212K0FKED</t>
   </si>
   <si>
     <t>R201, R202</t>
@@ -2187,6 +2175,9 @@
   </si>
   <si>
     <t>BWGSMJWX105-7KJ</t>
+  </si>
+  <si>
+    <t>R58, R66, R98</t>
   </si>
 </sst>
 </file>
@@ -2923,7 +2914,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S169"/>
+  <dimension ref="A1:S168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.5703125" style="4" customWidth="1"/>
@@ -3047,7 +3038,7 @@
       </c>
       <c r="N3" s="18">
         <f>M3*K3</f>
-        <v>3.1137000000000001</v>
+        <v>3.1136999999999997</v>
       </c>
       <c r="O3" s="12"/>
     </row>
@@ -3093,7 +3084,7 @@
       </c>
       <c r="N4" s="18">
         <f t="shared" ref="N4:N15" si="2">M4*K4</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O4" s="15"/>
     </row>
@@ -3185,7 +3176,7 @@
       </c>
       <c r="N6" s="18">
         <f t="shared" si="2"/>
-        <v>1.74</v>
+        <v>1.7399999999999998</v>
       </c>
       <c r="O6" s="15"/>
     </row>
@@ -3277,7 +3268,7 @@
       </c>
       <c r="N8" s="18">
         <f t="shared" si="2"/>
-        <v>2.52</v>
+        <v>2.5200000000000005</v>
       </c>
       <c r="O8" s="15"/>
     </row>
@@ -3323,7 +3314,7 @@
       </c>
       <c r="N9" s="18">
         <f t="shared" si="2"/>
-        <v>2.0760000000000001</v>
+        <v>2.0759999999999996</v>
       </c>
       <c r="O9" s="12"/>
     </row>
@@ -3553,7 +3544,7 @@
       </c>
       <c r="N14" s="18">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O14" s="15"/>
     </row>
@@ -3599,7 +3590,7 @@
       </c>
       <c r="N15" s="18">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O15" s="12"/>
     </row>
@@ -3645,7 +3636,7 @@
       </c>
       <c r="N16" s="18">
         <f t="shared" ref="N16:N29" si="3">M16*K16</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O16" s="15"/>
     </row>
@@ -3737,7 +3728,7 @@
       </c>
       <c r="N18" s="18">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O18" s="15"/>
     </row>
@@ -3783,7 +3774,7 @@
       </c>
       <c r="N19" s="18">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O19" s="12"/>
     </row>
@@ -3875,7 +3866,7 @@
       </c>
       <c r="N21" s="18">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O21" s="12"/>
     </row>
@@ -4013,7 +4004,7 @@
       </c>
       <c r="N24" s="18">
         <f t="shared" si="3"/>
-        <v>8.1</v>
+        <v>8.1000000000000014</v>
       </c>
       <c r="O24" s="15"/>
     </row>
@@ -4243,7 +4234,7 @@
       </c>
       <c r="N29" s="18">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O29" s="12"/>
     </row>
@@ -4289,7 +4280,7 @@
       </c>
       <c r="N30" s="18">
         <f t="shared" ref="N30:N39" si="4">M30*K30</f>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O30" s="15"/>
     </row>
@@ -4381,7 +4372,7 @@
       </c>
       <c r="N32" s="18">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O32" s="15"/>
     </row>
@@ -4427,7 +4418,7 @@
       </c>
       <c r="N33" s="18">
         <f t="shared" si="4"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O33" s="12"/>
     </row>
@@ -4519,7 +4510,7 @@
       </c>
       <c r="N35" s="18">
         <f t="shared" si="4"/>
-        <v>0.37559999999999999</v>
+        <v>0.37560000000000004</v>
       </c>
       <c r="O35" s="12"/>
     </row>
@@ -4565,7 +4556,7 @@
       </c>
       <c r="N36" s="18">
         <f t="shared" si="4"/>
-        <v>1.1100000000000001</v>
+        <v>1.1099999999999999</v>
       </c>
       <c r="O36" s="15"/>
     </row>
@@ -4887,7 +4878,7 @@
       </c>
       <c r="N43" s="18">
         <f t="shared" si="6"/>
-        <v>4.9800000000000004</v>
+        <v>4.9799999999999995</v>
       </c>
       <c r="O43" s="12"/>
     </row>
@@ -5025,7 +5016,7 @@
       </c>
       <c r="N46" s="18">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O46" s="15"/>
     </row>
@@ -5209,7 +5200,7 @@
       </c>
       <c r="N50" s="18">
         <f t="shared" si="6"/>
-        <v>3.78</v>
+        <v>3.7800000000000002</v>
       </c>
       <c r="O50" s="12"/>
     </row>
@@ -5439,7 +5430,7 @@
       </c>
       <c r="N55" s="18">
         <f t="shared" si="6"/>
-        <v>1.2890999999999999</v>
+        <v>1.2891000000000001</v>
       </c>
       <c r="O55" s="15"/>
     </row>
@@ -5450,22 +5441,22 @@
         <v>54</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>248</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I56" s="16" t="s">
         <v>150</v>
@@ -5531,14 +5522,14 @@
       </c>
       <c r="N57" s="18">
         <f t="shared" si="7"/>
-        <v>3.3</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="O57" s="12"/>
     </row>
     <row r="58" spans="1:15" ht="60.75" thickBot="1">
       <c r="A58" s="5"/>
       <c r="B58" s="10">
-        <f t="shared" ref="B58:B159" si="8">ROW(B58)-ROW($B$2)</f>
+        <f t="shared" ref="B58:B158" si="8">ROW(B58)-ROW($B$2)</f>
         <v>56</v>
       </c>
       <c r="C58" s="14" t="s">
@@ -5715,7 +5706,7 @@
       </c>
       <c r="N61" s="18">
         <f t="shared" si="7"/>
-        <v>1.38</v>
+        <v>1.3800000000000001</v>
       </c>
       <c r="O61" s="12"/>
     </row>
@@ -5807,7 +5798,7 @@
       </c>
       <c r="N63" s="18">
         <f t="shared" si="7"/>
-        <v>15.322800000000001</v>
+        <v>15.322799999999999</v>
       </c>
       <c r="O63" s="12"/>
     </row>
@@ -5945,7 +5936,7 @@
       </c>
       <c r="N66" s="18">
         <f t="shared" si="7"/>
-        <v>1.0169999999999999</v>
+        <v>1.0170000000000001</v>
       </c>
       <c r="O66" s="15"/>
     </row>
@@ -6026,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="K68" s="12">
-        <f t="shared" ref="K68:K131" si="9">3*J68</f>
+        <f t="shared" ref="K68:K130" si="9">3*J68</f>
         <v>6</v>
       </c>
       <c r="L68" s="19" t="s">
@@ -6129,7 +6120,7 @@
       </c>
       <c r="N70" s="18">
         <f t="shared" si="7"/>
-        <v>67.349999999999994</v>
+        <v>67.350000000000009</v>
       </c>
       <c r="O70" s="15"/>
     </row>
@@ -6140,7 +6131,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>307</v>
@@ -6152,7 +6143,7 @@
         <v>111</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="H71" s="15" t="s">
         <v>53</v>
@@ -6267,7 +6258,7 @@
       </c>
       <c r="N73" s="18">
         <f t="shared" si="7"/>
-        <v>1.2</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="O73" s="12"/>
     </row>
@@ -6497,7 +6488,7 @@
       </c>
       <c r="N78" s="18">
         <f t="shared" si="7"/>
-        <v>1.05</v>
+        <v>1.0499999999999998</v>
       </c>
       <c r="O78" s="15"/>
     </row>
@@ -6543,7 +6534,7 @@
       </c>
       <c r="N79" s="18">
         <f t="shared" si="7"/>
-        <v>0.9</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="O79" s="12"/>
     </row>
@@ -6727,7 +6718,7 @@
       </c>
       <c r="N83" s="18">
         <f t="shared" si="7"/>
-        <v>0.54479999999999995</v>
+        <v>0.54480000000000006</v>
       </c>
       <c r="O83" s="12"/>
     </row>
@@ -6773,7 +6764,7 @@
       </c>
       <c r="N84" s="18">
         <f t="shared" si="7"/>
-        <v>1.74</v>
+        <v>1.7399999999999998</v>
       </c>
       <c r="O84" s="15"/>
     </row>
@@ -6819,7 +6810,7 @@
       </c>
       <c r="N85" s="18">
         <f t="shared" si="7"/>
-        <v>6.15</v>
+        <v>6.1499999999999995</v>
       </c>
       <c r="O85" s="12"/>
     </row>
@@ -7283,7 +7274,7 @@
       </c>
       <c r="N95" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O95" s="12"/>
     </row>
@@ -7375,7 +7366,7 @@
       </c>
       <c r="N97" s="18">
         <f t="shared" si="7"/>
-        <v>0.40389000000000003</v>
+        <v>0.40388999999999997</v>
       </c>
       <c r="O97" s="12"/>
     </row>
@@ -7467,7 +7458,7 @@
       </c>
       <c r="N99" s="18">
         <f t="shared" si="7"/>
-        <v>1.4039999999999999</v>
+        <v>1.4040000000000001</v>
       </c>
       <c r="O99" s="12"/>
     </row>
@@ -7605,7 +7596,7 @@
       </c>
       <c r="N102" s="18">
         <f t="shared" si="7"/>
-        <v>5.7000000000000002E-2</v>
+        <v>5.6999999999999995E-2</v>
       </c>
       <c r="O102" s="15"/>
     </row>
@@ -7651,7 +7642,7 @@
       </c>
       <c r="N103" s="18">
         <f t="shared" si="7"/>
-        <v>0.22500000000000001</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="O103" s="12"/>
     </row>
@@ -7697,7 +7688,7 @@
       </c>
       <c r="N104" s="18">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O104" s="15"/>
     </row>
@@ -7743,7 +7734,7 @@
       </c>
       <c r="N105" s="18">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O105" s="12"/>
     </row>
@@ -7789,7 +7780,7 @@
       </c>
       <c r="N106" s="18">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O106" s="15"/>
     </row>
@@ -7853,29 +7844,29 @@
         <v>386</v>
       </c>
       <c r="D108" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="E108" s="16" t="s">
         <v>462</v>
-      </c>
-      <c r="E108" s="16" t="s">
-        <v>463</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>389</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I108" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J108" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K108" s="12">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L108" s="19" t="s">
         <v>21</v>
@@ -7885,7 +7876,7 @@
       </c>
       <c r="N108" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="O108" s="15"/>
     </row>
@@ -7899,22 +7890,22 @@
         <v>386</v>
       </c>
       <c r="D109" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E109" s="13" t="s">
         <v>466</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>467</v>
       </c>
       <c r="F109" s="12" t="s">
         <v>389</v>
       </c>
       <c r="G109" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J109" s="12">
         <v>2</v>
@@ -7931,7 +7922,7 @@
       </c>
       <c r="N109" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O109" s="12"/>
     </row>
@@ -7945,7 +7936,7 @@
         <v>386</v>
       </c>
       <c r="D110" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E110" s="24" t="s">
         <v>426</v>
@@ -7992,19 +7983,19 @@
         <v>386</v>
       </c>
       <c r="D111" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E111" s="13" t="s">
         <v>471</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>472</v>
       </c>
       <c r="F111" s="12" t="s">
         <v>415</v>
       </c>
       <c r="G111" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="H111" s="12" t="s">
         <v>473</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>474</v>
       </c>
       <c r="I111" s="13" t="s">
         <v>407</v>
@@ -8024,7 +8015,7 @@
       </c>
       <c r="N111" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O111" s="12"/>
     </row>
@@ -8038,22 +8029,22 @@
         <v>386</v>
       </c>
       <c r="D112" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="E112" s="16" t="s">
         <v>475</v>
-      </c>
-      <c r="E112" s="16" t="s">
-        <v>476</v>
       </c>
       <c r="F112" s="15" t="s">
         <v>415</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I112" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J112" s="15">
         <v>2</v>
@@ -8070,7 +8061,7 @@
       </c>
       <c r="N112" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O112" s="15"/>
     </row>
@@ -8084,16 +8075,16 @@
         <v>386</v>
       </c>
       <c r="D113" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="E113" s="13" t="s">
         <v>479</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>480</v>
       </c>
       <c r="F113" s="12" t="s">
         <v>415</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>19</v>
@@ -8130,22 +8121,22 @@
         <v>386</v>
       </c>
       <c r="D114" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="E114" s="16" t="s">
         <v>482</v>
-      </c>
-      <c r="E114" s="16" t="s">
-        <v>483</v>
       </c>
       <c r="F114" s="15" t="s">
         <v>389</v>
       </c>
       <c r="G114" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="I114" s="16" t="s">
         <v>484</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="I114" s="16" t="s">
-        <v>485</v>
       </c>
       <c r="J114" s="15">
         <v>2</v>
@@ -8176,22 +8167,22 @@
         <v>386</v>
       </c>
       <c r="D115" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="E115" s="32" t="s">
         <v>486</v>
-      </c>
-      <c r="E115" s="32" t="s">
-        <v>487</v>
       </c>
       <c r="F115" s="31" t="s">
         <v>389</v>
       </c>
       <c r="G115" s="32" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H115" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I115" s="32" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J115" s="31">
         <v>8</v>
@@ -8225,7 +8216,7 @@
         <v>386</v>
       </c>
       <c r="D116" s="33" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E116" s="34" t="s">
         <v>409</v>
@@ -8240,7 +8231,7 @@
         <v>19</v>
       </c>
       <c r="I116" s="34" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J116" s="33">
         <v>8</v>
@@ -8274,22 +8265,22 @@
         <v>386</v>
       </c>
       <c r="D117" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="E117" s="13" t="s">
         <v>492</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>493</v>
       </c>
       <c r="F117" s="12" t="s">
         <v>389</v>
       </c>
       <c r="G117" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J117" s="12">
         <v>2</v>
@@ -8306,7 +8297,7 @@
       </c>
       <c r="N117" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O117" s="12"/>
     </row>
@@ -8320,22 +8311,22 @@
         <v>386</v>
       </c>
       <c r="D118" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="E118" s="16" t="s">
         <v>496</v>
-      </c>
-      <c r="E118" s="16" t="s">
-        <v>497</v>
       </c>
       <c r="F118" s="15" t="s">
         <v>389</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I118" s="16" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J118" s="15">
         <v>2</v>
@@ -8352,7 +8343,7 @@
       </c>
       <c r="N118" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O118" s="15"/>
     </row>
@@ -8363,19 +8354,19 @@
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="D119" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="E119" s="13" t="s">
         <v>501</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>502</v>
       </c>
       <c r="F119" s="12" t="s">
         <v>389</v>
       </c>
       <c r="G119" s="13" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H119" s="12" t="s">
         <v>19</v>
@@ -8398,7 +8389,7 @@
       </c>
       <c r="N119" s="18">
         <f t="shared" si="7"/>
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O119" s="12"/>
     </row>
@@ -8409,25 +8400,25 @@
         <v>118</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D120" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="E120" s="16" t="s">
         <v>504</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>505</v>
       </c>
       <c r="F120" s="15" t="s">
         <v>389</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J120" s="15">
         <v>2</v>
@@ -8443,8 +8434,8 @@
         <v>0.1</v>
       </c>
       <c r="N120" s="18">
-        <f t="shared" ref="N120:N160" si="10">M120*K120</f>
-        <v>0.6</v>
+        <f t="shared" ref="N120:N159" si="10">M120*K120</f>
+        <v>0.60000000000000009</v>
       </c>
       <c r="O120" s="15"/>
     </row>
@@ -8458,7 +8449,7 @@
         <v>386</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E121" s="27" t="s">
         <v>388</v>
@@ -8508,22 +8499,22 @@
         <v>386</v>
       </c>
       <c r="D122" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="E122" s="16" t="s">
         <v>509</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>510</v>
       </c>
       <c r="F122" s="15" t="s">
         <v>389</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J122" s="15">
         <v>1</v>
@@ -8540,89 +8531,89 @@
       </c>
       <c r="N122" s="18">
         <f t="shared" si="10"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="O122" s="15"/>
     </row>
     <row r="123" spans="1:19" ht="15.75" thickBot="1">
       <c r="A123" s="5"/>
       <c r="B123" s="10">
-        <f>ROW(B123)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>121</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E123" s="16" t="s">
         <v>513</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="F123" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="G123" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="F123" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="G123" s="13" t="s">
+      <c r="H123" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="H123" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="I123" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="J123" s="12">
-        <v>1</v>
+      <c r="J123" s="15">
+        <v>2</v>
       </c>
       <c r="K123" s="12">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L123" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M123" s="18">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="N123" s="18">
         <f t="shared" si="10"/>
-        <v>0.33</v>
-      </c>
-      <c r="O123" s="12"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="O123" s="15"/>
     </row>
     <row r="124" spans="1:19" ht="15.75" thickBot="1">
       <c r="A124" s="5"/>
       <c r="B124" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B124)-ROW($B$2)</f>
         <v>122</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="C124" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D124" s="15" t="s">
+      <c r="D124" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="E124" s="16" t="s">
+      <c r="E124" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="F124" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="G124" s="16" t="s">
+      <c r="F124" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="G124" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="H124" s="15" t="s">
+      <c r="H124" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I124" s="16" t="s">
+      <c r="I124" s="13" t="s">
         <v>519</v>
       </c>
-      <c r="J124" s="15">
-        <v>2</v>
+      <c r="J124" s="12">
+        <v>1</v>
       </c>
       <c r="K124" s="12">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L124" s="19" t="s">
         <v>21</v>
@@ -8632,38 +8623,38 @@
       </c>
       <c r="N124" s="18">
         <f t="shared" si="10"/>
-        <v>0.6</v>
-      </c>
-      <c r="O124" s="15"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="O124" s="12"/>
     </row>
     <row r="125" spans="1:19" ht="15.75" thickBot="1">
       <c r="A125" s="5"/>
       <c r="B125" s="10">
-        <f>ROW(B125)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>123</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C125" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="E125" s="13" t="s">
+      <c r="E125" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="F125" s="12" t="s">
+      <c r="F125" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="G125" s="13" t="s">
+      <c r="G125" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="H125" s="12" t="s">
+      <c r="H125" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I125" s="13" t="s">
+      <c r="I125" s="16" t="s">
         <v>523</v>
       </c>
-      <c r="J125" s="12">
+      <c r="J125" s="15">
         <v>1</v>
       </c>
       <c r="K125" s="12">
@@ -8678,38 +8669,38 @@
       </c>
       <c r="N125" s="18">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="O125" s="12"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="O125" s="15"/>
     </row>
     <row r="126" spans="1:19" ht="15.75" thickBot="1">
       <c r="A126" s="5"/>
       <c r="B126" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B126)-ROW($B$2)</f>
         <v>124</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D126" s="15" t="s">
+      <c r="D126" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="E126" s="16" t="s">
+      <c r="E126" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="F126" s="15" t="s">
+      <c r="F126" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="G126" s="16" t="s">
+      <c r="G126" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="H126" s="15" t="s">
+      <c r="H126" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I126" s="16" t="s">
+      <c r="I126" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="J126" s="15">
+      <c r="J126" s="12">
         <v>1</v>
       </c>
       <c r="K126" s="12">
@@ -8724,38 +8715,38 @@
       </c>
       <c r="N126" s="18">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="O126" s="15"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="O126" s="12"/>
     </row>
     <row r="127" spans="1:19" ht="15.75" thickBot="1">
       <c r="A127" s="5"/>
       <c r="B127" s="10">
-        <f>ROW(B127)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>125</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C127" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="15" t="s">
         <v>528</v>
       </c>
-      <c r="E127" s="13" t="s">
+      <c r="E127" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="F127" s="12" t="s">
+      <c r="F127" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="G127" s="13" t="s">
+      <c r="G127" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="H127" s="12" t="s">
+      <c r="H127" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I127" s="13" t="s">
+      <c r="I127" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="J127" s="12">
+      <c r="J127" s="15">
         <v>1</v>
       </c>
       <c r="K127" s="12">
@@ -8770,89 +8761,89 @@
       </c>
       <c r="N127" s="18">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="O127" s="12"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="O127" s="15"/>
     </row>
     <row r="128" spans="1:19" ht="15.75" thickBot="1">
       <c r="A128" s="5"/>
       <c r="B128" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B128)-ROW($B$2)</f>
         <v>126</v>
       </c>
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D128" s="15" t="s">
+      <c r="D128" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E128" s="16" t="s">
+      <c r="E128" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="F128" s="15" t="s">
+      <c r="F128" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="G128" s="16" t="s">
+      <c r="G128" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="H128" s="15" t="s">
+      <c r="H128" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I128" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="J128" s="15">
-        <v>1</v>
+      <c r="I128" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="J128" s="12">
+        <v>2</v>
       </c>
       <c r="K128" s="12">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L128" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M128" s="18">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="N128" s="18">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="O128" s="15"/>
+        <v>0.96</v>
+      </c>
+      <c r="O128" s="12"/>
     </row>
     <row r="129" spans="1:15" ht="15.75" thickBot="1">
       <c r="A129" s="5"/>
       <c r="B129" s="10">
-        <f>ROW(B129)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>127</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C129" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="E129" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="E129" s="13" t="s">
+      <c r="F129" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="G129" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="F129" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>538</v>
-      </c>
-      <c r="H129" s="12" t="s">
+      <c r="H129" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I129" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="J129" s="12">
-        <v>2</v>
+      <c r="I129" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="J129" s="15">
+        <v>1</v>
       </c>
       <c r="K129" s="12">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L129" s="19" t="s">
         <v>21</v>
@@ -8862,176 +8853,176 @@
       </c>
       <c r="N129" s="18">
         <f t="shared" si="10"/>
-        <v>0.96</v>
-      </c>
-      <c r="O129" s="12"/>
+        <v>0.48</v>
+      </c>
+      <c r="O129" s="15"/>
     </row>
     <row r="130" spans="1:15" ht="15.75" thickBot="1">
       <c r="A130" s="5"/>
       <c r="B130" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B130)-ROW($B$2)</f>
         <v>128</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D130" s="15" t="s">
+      <c r="D130" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="E130" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="E130" s="16" t="s">
+      <c r="F130" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="F130" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="G130" s="16" t="s">
+      <c r="G130" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="H130" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I130" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="J130" s="15">
-        <v>1</v>
+      <c r="H130" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="I130" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="J130" s="12">
+        <v>2</v>
       </c>
       <c r="K130" s="12">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L130" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M130" s="18">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="N130" s="18">
         <f t="shared" si="10"/>
-        <v>0.48</v>
-      </c>
-      <c r="O130" s="15"/>
-    </row>
-    <row r="131" spans="1:15" ht="15.75" thickBot="1">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="O130" s="12"/>
+    </row>
+    <row r="131" spans="1:15" ht="36.75" thickBot="1">
       <c r="A131" s="5"/>
       <c r="B131" s="10">
-        <f>ROW(B131)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>129</v>
       </c>
-      <c r="C131" s="11" t="s">
-        <v>386</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>542</v>
-      </c>
-      <c r="E131" s="13" t="s">
+      <c r="C131" s="14" t="s">
         <v>543</v>
       </c>
-      <c r="F131" s="12" t="s">
+      <c r="D131" s="15" t="s">
         <v>544</v>
       </c>
-      <c r="G131" s="13" t="s">
+      <c r="E131" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="H131" s="12" t="s">
+      <c r="F131" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G131" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="I131" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="J131" s="12">
-        <v>2</v>
+      <c r="H131" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="I131" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="J131" s="15">
+        <v>6</v>
       </c>
       <c r="K131" s="12">
-        <f t="shared" si="9"/>
-        <v>6</v>
+        <f t="shared" ref="K131:K160" si="11">3*J131</f>
+        <v>18</v>
       </c>
       <c r="L131" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M131" s="18">
-        <v>0.15</v>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="N131" s="18">
         <f t="shared" si="10"/>
-        <v>0.9</v>
-      </c>
-      <c r="O131" s="12"/>
-    </row>
-    <row r="132" spans="1:15" ht="36.75" thickBot="1">
+        <v>1.2492000000000001</v>
+      </c>
+      <c r="O131" s="15"/>
+    </row>
+    <row r="132" spans="1:15" ht="24.75" thickBot="1">
       <c r="A132" s="5"/>
       <c r="B132" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B132)-ROW($B$2)</f>
         <v>130</v>
       </c>
-      <c r="C132" s="14" t="s">
-        <v>547</v>
-      </c>
-      <c r="D132" s="15" t="s">
+      <c r="C132" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="E132" s="16" t="s">
+      <c r="D132" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="F132" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G132" s="16" t="s">
+      <c r="E132" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="H132" s="15" t="s">
+      <c r="F132" s="12" t="s">
         <v>551</v>
+      </c>
+      <c r="G132" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="H132" s="12" t="s">
+        <v>553</v>
       </c>
       <c r="I132" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J132" s="15">
-        <v>6</v>
+      <c r="J132" s="12">
+        <v>1</v>
       </c>
       <c r="K132" s="12">
-        <f t="shared" ref="K132:K161" si="11">3*J132</f>
-        <v>18</v>
+        <f t="shared" si="11"/>
+        <v>3</v>
       </c>
       <c r="L132" s="19" t="s">
         <v>114</v>
       </c>
       <c r="M132" s="18">
-        <v>6.9400000000000003E-2</v>
+        <v>0.25340000000000001</v>
       </c>
       <c r="N132" s="18">
         <f t="shared" si="10"/>
-        <v>1.2492000000000001</v>
-      </c>
-      <c r="O132" s="15"/>
+        <v>0.76019999999999999</v>
+      </c>
+      <c r="O132" s="12"/>
     </row>
     <row r="133" spans="1:15" ht="24.75" thickBot="1">
       <c r="A133" s="5"/>
       <c r="B133" s="10">
-        <f>ROW(B133)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="E133" s="13" t="s">
         <v>554</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>711</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="G133" s="13" t="s">
+      <c r="G133" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="H133" s="12" t="s">
         <v>556</v>
-      </c>
-      <c r="H133" s="12" t="s">
-        <v>557</v>
       </c>
       <c r="I133" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J133" s="12">
+      <c r="J133" s="15">
         <v>1</v>
       </c>
       <c r="K133" s="12">
@@ -9039,229 +9030,229 @@
         <v>3</v>
       </c>
       <c r="L133" s="19" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="M133" s="18">
-        <v>0.25340000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="N133" s="18">
         <f t="shared" si="10"/>
-        <v>0.76019999999999999</v>
-      </c>
-      <c r="O133" s="12"/>
-    </row>
-    <row r="134" spans="1:15" ht="24.75" thickBot="1">
+        <v>4.5</v>
+      </c>
+      <c r="O133" s="40"/>
+    </row>
+    <row r="134" spans="1:15" ht="15.75" thickBot="1">
       <c r="A134" s="5"/>
       <c r="B134" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B134)-ROW($B$2)</f>
         <v>132</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D134" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="E134" s="13" t="s">
         <v>558</v>
-      </c>
-      <c r="E134" s="12" t="s">
-        <v>715</v>
       </c>
       <c r="F134" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="G134" s="12" t="s">
-        <v>710</v>
+      <c r="G134" s="13" t="s">
+        <v>560</v>
       </c>
       <c r="H134" s="12" t="s">
-        <v>560</v>
+        <v>160</v>
       </c>
       <c r="I134" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J134" s="15">
-        <v>1</v>
+      <c r="J134" s="12">
+        <v>2</v>
       </c>
       <c r="K134" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L134" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M134" s="18">
-        <v>1.5</v>
+        <v>0.46</v>
       </c>
       <c r="N134" s="18">
         <f t="shared" si="10"/>
-        <v>4.5</v>
-      </c>
-      <c r="O134" s="40"/>
-    </row>
-    <row r="135" spans="1:15" ht="15.75" thickBot="1">
+        <v>2.7600000000000002</v>
+      </c>
+      <c r="O134" s="12"/>
+    </row>
+    <row r="135" spans="1:15" ht="24.75" thickBot="1">
       <c r="A135" s="5"/>
       <c r="B135" s="10">
-        <f>ROW(B135)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>133</v>
       </c>
-      <c r="C135" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D135" s="12" t="s">
+      <c r="C135" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D135" s="15" t="s">
         <v>561</v>
       </c>
-      <c r="E135" s="13" t="s">
+      <c r="E135" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="F135" s="12" t="s">
+      <c r="F135" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="G135" s="13" t="s">
+      <c r="G135" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="H135" s="12" t="s">
-        <v>160</v>
+      <c r="H135" s="15" t="s">
+        <v>556</v>
       </c>
       <c r="I135" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J135" s="12">
-        <v>2</v>
+      <c r="J135" s="15">
+        <v>1</v>
       </c>
       <c r="K135" s="12">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L135" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M135" s="18">
-        <v>0.46</v>
+        <v>1.18</v>
       </c>
       <c r="N135" s="18">
         <f t="shared" si="10"/>
-        <v>2.76</v>
-      </c>
-      <c r="O135" s="12"/>
+        <v>3.54</v>
+      </c>
+      <c r="O135" s="15"/>
     </row>
     <row r="136" spans="1:15" ht="24.75" thickBot="1">
       <c r="A136" s="5"/>
       <c r="B136" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B136)-ROW($B$2)</f>
         <v>134</v>
       </c>
-      <c r="C136" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D136" s="15" t="s">
+      <c r="C136" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D136" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="E136" s="16" t="s">
+      <c r="E136" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="F136" s="15" t="s">
+      <c r="F136" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="G136" s="16" t="s">
+      <c r="G136" s="13" t="s">
         <v>568</v>
       </c>
-      <c r="H136" s="15" t="s">
-        <v>560</v>
+      <c r="H136" s="12" t="s">
+        <v>569</v>
       </c>
       <c r="I136" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J136" s="15">
-        <v>1</v>
+      <c r="J136" s="12">
+        <v>4</v>
       </c>
       <c r="K136" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L136" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M136" s="18">
-        <v>1.18</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="N136" s="18">
         <f t="shared" si="10"/>
-        <v>3.54</v>
-      </c>
-      <c r="O136" s="15"/>
-    </row>
-    <row r="137" spans="1:15" ht="24.75" thickBot="1">
+        <v>1.1255999999999999</v>
+      </c>
+      <c r="O136" s="12"/>
+    </row>
+    <row r="137" spans="1:15" ht="15.75" thickBot="1">
       <c r="A137" s="5"/>
       <c r="B137" s="10">
-        <f>ROW(B137)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="C137" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D137" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="E137" s="13" t="s">
+      <c r="C137" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D137" s="15" t="s">
         <v>570</v>
       </c>
-      <c r="F137" s="12" t="s">
+      <c r="E137" s="16" t="s">
         <v>571</v>
       </c>
-      <c r="G137" s="13" t="s">
+      <c r="F137" s="15" t="s">
         <v>572</v>
       </c>
-      <c r="H137" s="12" t="s">
+      <c r="G137" s="16" t="s">
         <v>573</v>
+      </c>
+      <c r="H137" s="15" t="s">
+        <v>574</v>
       </c>
       <c r="I137" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J137" s="12">
-        <v>4</v>
+      <c r="J137" s="15">
+        <v>1</v>
       </c>
       <c r="K137" s="12">
         <f t="shared" si="11"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L137" s="19" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="M137" s="18">
-        <v>9.3799999999999994E-2</v>
+        <v>1.51</v>
       </c>
       <c r="N137" s="18">
         <f t="shared" si="10"/>
-        <v>1.1255999999999999</v>
-      </c>
-      <c r="O137" s="12"/>
-    </row>
-    <row r="138" spans="1:15" ht="15.75" thickBot="1">
+        <v>4.53</v>
+      </c>
+      <c r="O137" s="15"/>
+    </row>
+    <row r="138" spans="1:15" ht="24.75" thickBot="1">
       <c r="A138" s="5"/>
       <c r="B138" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B138)-ROW($B$2)</f>
         <v>136</v>
       </c>
-      <c r="C138" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D138" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="E138" s="16" t="s">
+      <c r="C138" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D138" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="F138" s="15" t="s">
+      <c r="E138" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="G138" s="16" t="s">
+      <c r="F138" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="H138" s="15" t="s">
+      <c r="G138" s="13" t="s">
         <v>578</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>556</v>
       </c>
       <c r="I138" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J138" s="15">
+      <c r="J138" s="12">
         <v>1</v>
       </c>
       <c r="K138" s="12">
@@ -9272,42 +9263,42 @@
         <v>21</v>
       </c>
       <c r="M138" s="18">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="N138" s="18">
         <f t="shared" si="10"/>
-        <v>4.53</v>
-      </c>
-      <c r="O138" s="15"/>
-    </row>
-    <row r="139" spans="1:15" ht="24.75" thickBot="1">
+        <v>5.37</v>
+      </c>
+      <c r="O138" s="12"/>
+    </row>
+    <row r="139" spans="1:15" ht="15.75" thickBot="1">
       <c r="A139" s="5"/>
       <c r="B139" s="10">
-        <f>ROW(B139)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>137</v>
       </c>
-      <c r="C139" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D139" s="12" t="s">
+      <c r="C139" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D139" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="E139" s="13" t="s">
+      <c r="E139" s="16" t="s">
         <v>580</v>
       </c>
-      <c r="F139" s="12" t="s">
+      <c r="F139" s="15" t="s">
         <v>581</v>
       </c>
-      <c r="G139" s="13" t="s">
+      <c r="G139" s="16" t="s">
         <v>582</v>
       </c>
-      <c r="H139" s="12" t="s">
-        <v>560</v>
+      <c r="H139" s="15" t="s">
+        <v>583</v>
       </c>
       <c r="I139" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J139" s="12">
+      <c r="J139" s="15">
         <v>1</v>
       </c>
       <c r="K139" s="12">
@@ -9318,42 +9309,42 @@
         <v>21</v>
       </c>
       <c r="M139" s="18">
-        <v>1.79</v>
+        <v>2.5253999999999999</v>
       </c>
       <c r="N139" s="18">
         <f t="shared" si="10"/>
-        <v>5.37</v>
-      </c>
-      <c r="O139" s="12"/>
+        <v>7.5762</v>
+      </c>
+      <c r="O139" s="15"/>
     </row>
     <row r="140" spans="1:15" ht="15.75" thickBot="1">
       <c r="A140" s="5"/>
       <c r="B140" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B140)-ROW($B$2)</f>
         <v>138</v>
       </c>
-      <c r="C140" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="E140" s="16" t="s">
+      <c r="C140" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D140" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="F140" s="15" t="s">
+      <c r="E140" s="13" t="s">
         <v>585</v>
       </c>
-      <c r="G140" s="16" t="s">
+      <c r="F140" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="G140" s="13" t="s">
         <v>586</v>
       </c>
-      <c r="H140" s="15" t="s">
+      <c r="H140" s="12" t="s">
         <v>587</v>
       </c>
       <c r="I140" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J140" s="15">
+      <c r="J140" s="12">
         <v>1</v>
       </c>
       <c r="K140" s="12">
@@ -9364,42 +9355,42 @@
         <v>21</v>
       </c>
       <c r="M140" s="18">
-        <v>2.5253999999999999</v>
+        <v>5.57</v>
       </c>
       <c r="N140" s="18">
         <f t="shared" si="10"/>
-        <v>7.5762</v>
-      </c>
-      <c r="O140" s="15"/>
-    </row>
-    <row r="141" spans="1:15" ht="15.75" thickBot="1">
+        <v>16.71</v>
+      </c>
+      <c r="O140" s="12"/>
+    </row>
+    <row r="141" spans="1:15" ht="24.75" thickBot="1">
       <c r="A141" s="5"/>
       <c r="B141" s="10">
-        <f>ROW(B141)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>139</v>
       </c>
-      <c r="C141" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D141" s="12" t="s">
+      <c r="C141" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="E141" s="13" t="s">
+      <c r="D141" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="F141" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="G141" s="13" t="s">
+      <c r="E141" s="16" t="s">
         <v>590</v>
       </c>
-      <c r="H141" s="12" t="s">
+      <c r="F141" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G141" s="16" t="s">
         <v>591</v>
+      </c>
+      <c r="H141" s="15" t="s">
+        <v>592</v>
       </c>
       <c r="I141" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J141" s="12">
+      <c r="J141" s="15">
         <v>1</v>
       </c>
       <c r="K141" s="12">
@@ -9410,42 +9401,42 @@
         <v>21</v>
       </c>
       <c r="M141" s="18">
-        <v>5.57</v>
+        <v>18.03</v>
       </c>
       <c r="N141" s="18">
         <f t="shared" si="10"/>
-        <v>16.71</v>
-      </c>
-      <c r="O141" s="12"/>
+        <v>54.09</v>
+      </c>
+      <c r="O141" s="15"/>
     </row>
     <row r="142" spans="1:15" ht="24.75" thickBot="1">
       <c r="A142" s="5"/>
       <c r="B142" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B142)-ROW($B$2)</f>
         <v>140</v>
       </c>
-      <c r="C142" s="14" t="s">
-        <v>592</v>
-      </c>
-      <c r="D142" s="15" t="s">
+      <c r="C142" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D142" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="E142" s="16" t="s">
+      <c r="E142" s="13" t="s">
         <v>594</v>
       </c>
       <c r="F142" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G142" s="16" t="s">
+      <c r="G142" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="H142" s="15" t="s">
-        <v>596</v>
+      <c r="H142" s="12" t="s">
+        <v>556</v>
       </c>
       <c r="I142" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J142" s="15">
+      <c r="J142" s="12">
         <v>1</v>
       </c>
       <c r="K142" s="12">
@@ -9456,134 +9447,134 @@
         <v>21</v>
       </c>
       <c r="M142" s="18">
-        <v>18.03</v>
+        <v>1.06</v>
       </c>
       <c r="N142" s="18">
         <f t="shared" si="10"/>
-        <v>54.09</v>
-      </c>
-      <c r="O142" s="15"/>
+        <v>3.18</v>
+      </c>
+      <c r="O142" s="12"/>
     </row>
     <row r="143" spans="1:15" ht="24.75" thickBot="1">
       <c r="A143" s="5"/>
       <c r="B143" s="10">
-        <f>ROW(B143)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>141</v>
       </c>
-      <c r="C143" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D143" s="12" t="s">
+      <c r="C143" s="14" t="s">
+        <v>596</v>
+      </c>
+      <c r="D143" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="E143" s="13" t="s">
+      <c r="E143" s="16" t="s">
         <v>598</v>
       </c>
       <c r="F143" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G143" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G143" s="16" t="s">
         <v>599</v>
       </c>
-      <c r="H143" s="12" t="s">
-        <v>560</v>
+      <c r="H143" s="15" t="s">
+        <v>600</v>
       </c>
       <c r="I143" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J143" s="12">
-        <v>1</v>
+      <c r="J143" s="15">
+        <v>2</v>
       </c>
       <c r="K143" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L143" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M143" s="18">
-        <v>1.06</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="N143" s="18">
         <f t="shared" si="10"/>
-        <v>3.18</v>
-      </c>
-      <c r="O143" s="12"/>
+        <v>0.13919999999999999</v>
+      </c>
+      <c r="O143" s="15"/>
     </row>
     <row r="144" spans="1:15" ht="24.75" thickBot="1">
       <c r="A144" s="5"/>
       <c r="B144" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
-      <c r="C144" s="14" t="s">
-        <v>600</v>
-      </c>
-      <c r="D144" s="15" t="s">
+      <c r="C144" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D144" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E144" s="13" t="s">
         <v>602</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="G144" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G144" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="H144" s="15" t="s">
+      <c r="H144" s="12" t="s">
         <v>604</v>
       </c>
       <c r="I144" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J144" s="15">
-        <v>2</v>
+      <c r="J144" s="12">
+        <v>1</v>
       </c>
       <c r="K144" s="12">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L144" s="19" t="s">
         <v>114</v>
       </c>
       <c r="M144" s="18">
-        <v>2.3199999999999998E-2</v>
+        <v>8.3531999999999993</v>
       </c>
       <c r="N144" s="18">
         <f t="shared" si="10"/>
-        <v>0.13919999999999999</v>
-      </c>
-      <c r="O144" s="15"/>
-    </row>
-    <row r="145" spans="1:15" ht="24.75" thickBot="1">
+        <v>25.059599999999996</v>
+      </c>
+      <c r="O144" s="12"/>
+    </row>
+    <row r="145" spans="1:15" ht="26.25" thickBot="1">
       <c r="A145" s="5"/>
       <c r="B145" s="10">
-        <f>ROW(B145)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>143</v>
       </c>
-      <c r="C145" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D145" s="12" t="s">
+      <c r="C145" s="14" t="s">
         <v>605</v>
       </c>
-      <c r="E145" s="13" t="s">
+      <c r="D145" s="15" t="s">
         <v>606</v>
       </c>
+      <c r="E145" s="16" t="s">
+        <v>607</v>
+      </c>
       <c r="F145" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G145" s="13" t="s">
-        <v>607</v>
-      </c>
-      <c r="H145" s="12" t="s">
         <v>608</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>609</v>
+      </c>
+      <c r="H145" s="15" t="s">
+        <v>610</v>
       </c>
       <c r="I145" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J145" s="12">
+      <c r="J145" s="15">
         <v>1</v>
       </c>
       <c r="K145" s="12">
@@ -9594,42 +9585,42 @@
         <v>114</v>
       </c>
       <c r="M145" s="18">
-        <v>8.3531999999999993</v>
+        <v>0.63719999999999999</v>
       </c>
       <c r="N145" s="18">
         <f t="shared" si="10"/>
-        <v>25.0596</v>
-      </c>
-      <c r="O145" s="12"/>
-    </row>
-    <row r="146" spans="1:15" ht="26.25" thickBot="1">
+        <v>1.9116</v>
+      </c>
+      <c r="O145" s="15"/>
+    </row>
+    <row r="146" spans="1:15" ht="60.75" thickBot="1">
       <c r="A146" s="5"/>
       <c r="B146" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B146)-ROW($B$2)</f>
         <v>144</v>
       </c>
-      <c r="C146" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>610</v>
-      </c>
-      <c r="E146" s="16" t="s">
+      <c r="C146" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D146" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="F146" s="15" t="s">
+      <c r="E146" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="G146" s="16" t="s">
+      <c r="F146" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="H146" s="15" t="s">
+      <c r="G146" s="13" t="s">
         <v>614</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>615</v>
       </c>
       <c r="I146" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J146" s="15">
+      <c r="J146" s="12">
         <v>1</v>
       </c>
       <c r="K146" s="12">
@@ -9640,42 +9631,42 @@
         <v>114</v>
       </c>
       <c r="M146" s="18">
-        <v>0.63719999999999999</v>
+        <v>7.8799999999999995E-2</v>
       </c>
       <c r="N146" s="18">
         <f t="shared" si="10"/>
-        <v>1.9116</v>
-      </c>
-      <c r="O146" s="15"/>
-    </row>
-    <row r="147" spans="1:15" ht="60.75" thickBot="1">
+        <v>0.2364</v>
+      </c>
+      <c r="O146" s="12"/>
+    </row>
+    <row r="147" spans="1:15" ht="15.75" thickBot="1">
       <c r="A147" s="5"/>
       <c r="B147" s="10">
-        <f>ROW(B147)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>145</v>
       </c>
-      <c r="C147" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>615</v>
-      </c>
-      <c r="E147" s="13" t="s">
+      <c r="C147" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D147" s="15" t="s">
         <v>616</v>
       </c>
-      <c r="F147" s="12" t="s">
+      <c r="E147" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="G147" s="13" t="s">
+      <c r="F147" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="H147" s="12" t="s">
+      <c r="G147" s="16" t="s">
         <v>619</v>
+      </c>
+      <c r="H147" s="15" t="s">
+        <v>620</v>
       </c>
       <c r="I147" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J147" s="12">
+      <c r="J147" s="15">
         <v>1</v>
       </c>
       <c r="K147" s="12">
@@ -9683,45 +9674,45 @@
         <v>3</v>
       </c>
       <c r="L147" s="19" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="M147" s="18">
-        <v>7.8799999999999995E-2</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="N147" s="18">
         <f t="shared" si="10"/>
-        <v>0.2364</v>
-      </c>
-      <c r="O147" s="12"/>
-    </row>
-    <row r="148" spans="1:15" ht="15.75" thickBot="1">
+        <v>13.32</v>
+      </c>
+      <c r="O147" s="15"/>
+    </row>
+    <row r="148" spans="1:15" ht="24.75" thickBot="1">
       <c r="A148" s="5"/>
       <c r="B148" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B148)-ROW($B$2)</f>
         <v>146</v>
       </c>
-      <c r="C148" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D148" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="E148" s="16" t="s">
+      <c r="C148" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D148" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="F148" s="15" t="s">
+      <c r="E148" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="G148" s="16" t="s">
+      <c r="F148" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="H148" s="15" t="s">
+      <c r="G148" s="13" t="s">
         <v>624</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>556</v>
       </c>
       <c r="I148" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J148" s="15">
+      <c r="J148" s="12">
         <v>1</v>
       </c>
       <c r="K148" s="12">
@@ -9732,77 +9723,77 @@
         <v>21</v>
       </c>
       <c r="M148" s="18">
-        <v>4.4400000000000004</v>
+        <v>0.78</v>
       </c>
       <c r="N148" s="18">
         <f t="shared" si="10"/>
-        <v>13.32</v>
-      </c>
-      <c r="O148" s="15"/>
-    </row>
-    <row r="149" spans="1:15" ht="24.75" thickBot="1">
+        <v>2.34</v>
+      </c>
+      <c r="O148" s="12"/>
+    </row>
+    <row r="149" spans="1:15" ht="15.75" thickBot="1">
       <c r="A149" s="5"/>
       <c r="B149" s="10">
-        <f>ROW(B149)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>147</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D149" s="12" t="s">
+      <c r="C149" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D149" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="E149" s="13" t="s">
+      <c r="E149" s="16" t="s">
         <v>626</v>
       </c>
-      <c r="F149" s="12" t="s">
+      <c r="F149" s="15" t="s">
         <v>627</v>
       </c>
-      <c r="G149" s="13" t="s">
+      <c r="G149" s="16" t="s">
         <v>628</v>
       </c>
-      <c r="H149" s="12" t="s">
-        <v>560</v>
+      <c r="H149" s="15" t="s">
+        <v>629</v>
       </c>
       <c r="I149" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J149" s="12">
-        <v>1</v>
+      <c r="J149" s="15">
+        <v>2</v>
       </c>
       <c r="K149" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L149" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M149" s="18">
-        <v>0.78</v>
+        <v>0.99080000000000001</v>
       </c>
       <c r="N149" s="18">
         <f t="shared" si="10"/>
-        <v>2.34</v>
-      </c>
-      <c r="O149" s="12"/>
-    </row>
-    <row r="150" spans="1:15" ht="15.75" thickBot="1">
+        <v>5.9447999999999999</v>
+      </c>
+      <c r="O149" s="15"/>
+    </row>
+    <row r="150" spans="1:15" ht="24.75" thickBot="1">
       <c r="A150" s="5"/>
       <c r="B150" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B150)-ROW($B$2)</f>
         <v>148</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E150" s="16" t="s">
-        <v>630</v>
-      </c>
-      <c r="F150" s="15" t="s">
         <v>631</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="G150" s="16" t="s">
         <v>632</v>
@@ -9814,47 +9805,47 @@
         <v>150</v>
       </c>
       <c r="J150" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150" s="12">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L150" s="19" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="M150" s="18">
-        <v>0.99080000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="N150" s="18">
         <f t="shared" si="10"/>
-        <v>5.9447999999999999</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="O150" s="15"/>
     </row>
-    <row r="151" spans="1:15" ht="24.75" thickBot="1">
+    <row r="151" spans="1:15" ht="15.75" thickBot="1">
       <c r="A151" s="5"/>
       <c r="B151" s="10">
         <f>ROW(B151)-ROW($B$2)</f>
         <v>149</v>
       </c>
-      <c r="C151" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D151" s="15" t="s">
+      <c r="C151" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D151" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="E151" s="16" t="s">
+      <c r="E151" s="12" t="s">
         <v>635</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G151" s="16" t="s">
         <v>636</v>
       </c>
-      <c r="H151" s="15" t="s">
+      <c r="G151" s="12" t="s">
         <v>637</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>638</v>
       </c>
       <c r="I151" s="16" t="s">
         <v>150</v>
@@ -9870,37 +9861,37 @@
         <v>21</v>
       </c>
       <c r="M151" s="18">
-        <v>0.56000000000000005</v>
+        <v>2.89</v>
       </c>
       <c r="N151" s="18">
         <f t="shared" si="10"/>
-        <v>1.68</v>
+        <v>8.67</v>
       </c>
       <c r="O151" s="15"/>
     </row>
-    <row r="152" spans="1:15" ht="15.75" thickBot="1">
+    <row r="152" spans="1:15" ht="24.75" thickBot="1">
       <c r="A152" s="5"/>
       <c r="B152" s="10">
-        <f>ROW(B152)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="C152" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D152" s="12" t="s">
-        <v>638</v>
-      </c>
-      <c r="E152" s="12" t="s">
+      <c r="C152" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D152" s="15" t="s">
         <v>639</v>
       </c>
-      <c r="F152" s="12" t="s">
+      <c r="E152" s="16" t="s">
         <v>640</v>
       </c>
-      <c r="G152" s="12" t="s">
+      <c r="F152" s="15" t="s">
         <v>641</v>
       </c>
-      <c r="H152" s="12" t="s">
+      <c r="G152" s="16" t="s">
         <v>642</v>
+      </c>
+      <c r="H152" s="15" t="s">
+        <v>643</v>
       </c>
       <c r="I152" s="16" t="s">
         <v>150</v>
@@ -9916,42 +9907,42 @@
         <v>21</v>
       </c>
       <c r="M152" s="18">
-        <v>2.89</v>
+        <v>1.35</v>
       </c>
       <c r="N152" s="18">
         <f t="shared" si="10"/>
-        <v>8.67</v>
+        <v>4.0500000000000007</v>
       </c>
       <c r="O152" s="15"/>
     </row>
     <row r="153" spans="1:15" ht="24.75" thickBot="1">
       <c r="A153" s="5"/>
       <c r="B153" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B153)-ROW($B$2)</f>
         <v>151</v>
       </c>
-      <c r="C153" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="E153" s="16" t="s">
+      <c r="C153" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D153" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="F153" s="15" t="s">
+      <c r="E153" s="13" t="s">
         <v>645</v>
       </c>
-      <c r="G153" s="16" t="s">
+      <c r="F153" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="H153" s="15" t="s">
+      <c r="G153" s="13" t="s">
         <v>647</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>556</v>
       </c>
       <c r="I153" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J153" s="15">
+      <c r="J153" s="12">
         <v>1</v>
       </c>
       <c r="K153" s="12">
@@ -9962,42 +9953,42 @@
         <v>21</v>
       </c>
       <c r="M153" s="18">
-        <v>1.35</v>
+        <v>2.13</v>
       </c>
       <c r="N153" s="18">
         <f t="shared" si="10"/>
-        <v>4.05</v>
-      </c>
-      <c r="O153" s="15"/>
-    </row>
-    <row r="154" spans="1:15" ht="24.75" thickBot="1">
+        <v>6.39</v>
+      </c>
+      <c r="O153" s="12"/>
+    </row>
+    <row r="154" spans="1:15" ht="15.75" thickBot="1">
       <c r="A154" s="5"/>
       <c r="B154" s="10">
-        <f>ROW(B154)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>152</v>
       </c>
-      <c r="C154" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D154" s="12" t="s">
+      <c r="C154" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D154" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="E154" s="13" t="s">
+      <c r="E154" s="16" t="s">
         <v>649</v>
       </c>
-      <c r="F154" s="12" t="s">
+      <c r="F154" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G154" s="16" t="s">
         <v>650</v>
       </c>
-      <c r="G154" s="13" t="s">
+      <c r="H154" s="15" t="s">
         <v>651</v>
-      </c>
-      <c r="H154" s="12" t="s">
-        <v>560</v>
       </c>
       <c r="I154" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J154" s="12">
+      <c r="J154" s="15">
         <v>1</v>
       </c>
       <c r="K154" s="12">
@@ -10008,42 +9999,42 @@
         <v>21</v>
       </c>
       <c r="M154" s="18">
-        <v>2.13</v>
+        <v>0.15684999999999999</v>
       </c>
       <c r="N154" s="18">
         <f t="shared" si="10"/>
-        <v>6.39</v>
-      </c>
-      <c r="O154" s="12"/>
+        <v>0.47054999999999997</v>
+      </c>
+      <c r="O154" s="15"/>
     </row>
     <row r="155" spans="1:15" ht="15.75" thickBot="1">
       <c r="A155" s="5"/>
       <c r="B155" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B155)-ROW($B$2)</f>
         <v>153</v>
       </c>
-      <c r="C155" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D155" s="15" t="s">
+      <c r="C155" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D155" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="E155" s="16" t="s">
+      <c r="E155" s="13" t="s">
         <v>653</v>
       </c>
-      <c r="F155" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G155" s="16" t="s">
+      <c r="F155" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="H155" s="15" t="s">
+      <c r="G155" s="13" t="s">
         <v>655</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>656</v>
       </c>
       <c r="I155" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J155" s="15">
+      <c r="J155" s="12">
         <v>1</v>
       </c>
       <c r="K155" s="12">
@@ -10054,42 +10045,42 @@
         <v>21</v>
       </c>
       <c r="M155" s="18">
-        <v>0.15684999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="N155" s="18">
         <f t="shared" si="10"/>
-        <v>0.47055000000000002</v>
-      </c>
-      <c r="O155" s="15"/>
-    </row>
-    <row r="156" spans="1:15" ht="15.75" thickBot="1">
+        <v>1.08</v>
+      </c>
+      <c r="O155" s="12"/>
+    </row>
+    <row r="156" spans="1:15" ht="24.75" thickBot="1">
       <c r="A156" s="5"/>
       <c r="B156" s="10">
-        <f>ROW(B156)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>154</v>
       </c>
-      <c r="C156" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D156" s="12" t="s">
-        <v>656</v>
-      </c>
-      <c r="E156" s="13" t="s">
+      <c r="C156" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D156" s="15" t="s">
         <v>657</v>
       </c>
-      <c r="F156" s="12" t="s">
+      <c r="E156" s="16" t="s">
         <v>658</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="F156" s="15" t="s">
         <v>659</v>
       </c>
-      <c r="H156" s="12" t="s">
+      <c r="G156" s="16" t="s">
         <v>660</v>
+      </c>
+      <c r="H156" s="15" t="s">
+        <v>661</v>
       </c>
       <c r="I156" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J156" s="12">
+      <c r="J156" s="15">
         <v>1</v>
       </c>
       <c r="K156" s="12">
@@ -10097,45 +10088,45 @@
         <v>3</v>
       </c>
       <c r="L156" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M156" s="18">
-        <v>0.36</v>
+        <v>0.34460000000000002</v>
       </c>
       <c r="N156" s="18">
         <f t="shared" si="10"/>
-        <v>1.08</v>
-      </c>
-      <c r="O156" s="12"/>
-    </row>
-    <row r="157" spans="1:15" ht="24.75" thickBot="1">
+        <v>1.0338000000000001</v>
+      </c>
+      <c r="O156" s="15"/>
+    </row>
+    <row r="157" spans="1:15" ht="36.75" thickBot="1">
       <c r="A157" s="5"/>
       <c r="B157" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B157)-ROW($B$2)</f>
         <v>155</v>
       </c>
-      <c r="C157" s="14" t="s">
-        <v>552</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>661</v>
-      </c>
-      <c r="E157" s="16" t="s">
+      <c r="C157" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D157" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="F157" s="15" t="s">
+      <c r="E157" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="G157" s="16" t="s">
+      <c r="F157" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="H157" s="15" t="s">
+      <c r="G157" s="13" t="s">
         <v>665</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>666</v>
       </c>
       <c r="I157" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="J157" s="15">
+      <c r="J157" s="12">
         <v>1</v>
       </c>
       <c r="K157" s="12">
@@ -10143,45 +10134,45 @@
         <v>3</v>
       </c>
       <c r="L157" s="19" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="M157" s="18">
-        <v>0.34460000000000002</v>
+        <v>0.94</v>
       </c>
       <c r="N157" s="18">
         <f t="shared" si="10"/>
-        <v>1.0338000000000001</v>
-      </c>
-      <c r="O157" s="15"/>
+        <v>2.82</v>
+      </c>
+      <c r="O157" s="12"/>
     </row>
     <row r="158" spans="1:15" ht="36.75" thickBot="1">
       <c r="A158" s="5"/>
       <c r="B158" s="10">
-        <f>ROW(B158)-ROW($B$2)</f>
+        <f t="shared" si="8"/>
         <v>156</v>
       </c>
-      <c r="C158" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="D158" s="12" t="s">
-        <v>666</v>
-      </c>
-      <c r="E158" s="13" t="s">
+      <c r="C158" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="F158" s="12" t="s">
+      <c r="D158" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="G158" s="13" t="s">
+      <c r="E158" s="16" t="s">
         <v>669</v>
       </c>
-      <c r="H158" s="12" t="s">
+      <c r="F158" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G158" s="16" t="s">
         <v>670</v>
       </c>
+      <c r="H158" s="15" t="s">
+        <v>671</v>
+      </c>
       <c r="I158" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="J158" s="12">
+        <v>672</v>
+      </c>
+      <c r="J158" s="15">
         <v>1</v>
       </c>
       <c r="K158" s="12">
@@ -10192,171 +10183,169 @@
         <v>21</v>
       </c>
       <c r="M158" s="18">
-        <v>0.94</v>
+        <v>0.28784999999999999</v>
       </c>
       <c r="N158" s="18">
         <f t="shared" si="10"/>
-        <v>2.82</v>
-      </c>
-      <c r="O158" s="12"/>
-    </row>
-    <row r="159" spans="1:15" ht="36.75" thickBot="1">
+        <v>0.86355000000000004</v>
+      </c>
+      <c r="O158" s="15"/>
+    </row>
+    <row r="159" spans="1:15" ht="15.75" thickBot="1">
       <c r="A159" s="5"/>
       <c r="B159" s="10">
-        <f t="shared" si="8"/>
+        <f>ROW(B159)-ROW($B$2)</f>
         <v>157</v>
       </c>
-      <c r="C159" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>672</v>
-      </c>
-      <c r="E159" s="16" t="s">
+      <c r="C159" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="D159" s="12" t="s">
         <v>673</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>674</v>
       </c>
       <c r="F159" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G159" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="H159" s="15" t="s">
+      <c r="G159" s="13" t="s">
         <v>675</v>
       </c>
-      <c r="I159" s="16" t="s">
+      <c r="H159" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="J159" s="15">
-        <v>1</v>
+      <c r="I159" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="J159" s="12">
+        <v>2</v>
       </c>
       <c r="K159" s="12">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L159" s="19" t="s">
         <v>21</v>
       </c>
       <c r="M159" s="18">
-        <v>0.28784999999999999</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="N159" s="18">
         <f t="shared" si="10"/>
-        <v>0.86355000000000004</v>
-      </c>
-      <c r="O159" s="15"/>
-    </row>
-    <row r="160" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A160" s="5"/>
+        <v>4.8360000000000003</v>
+      </c>
+      <c r="O159" s="12"/>
+    </row>
+    <row r="160" spans="1:15" ht="24.75" thickBot="1">
       <c r="B160" s="10">
-        <f>ROW(B160)-ROW($B$2)</f>
+        <f t="shared" ref="B160:B166" si="12">ROW(B160)-ROW($B$2)</f>
         <v>158</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>678</v>
+        <v>712</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>679</v>
+        <v>713</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>680</v>
-      </c>
-      <c r="I160" s="13" t="s">
-        <v>681</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="I160" s="13"/>
       <c r="J160" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K160" s="12">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L160" s="19" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="M160" s="18">
-        <v>0.80600000000000005</v>
+        <v>1.0093000000000001</v>
       </c>
       <c r="N160" s="18">
-        <f t="shared" si="10"/>
-        <v>4.8360000000000003</v>
+        <f>M160*K160</f>
+        <v>3.0279000000000003</v>
       </c>
       <c r="O160" s="12"/>
     </row>
-    <row r="161" spans="2:19" ht="24.75" thickBot="1">
+    <row r="161" spans="2:19" ht="36.75" thickBot="1">
       <c r="B161" s="10">
-        <f t="shared" ref="B161:B167" si="12">ROW(B161)-ROW($B$2)</f>
+        <f t="shared" si="12"/>
         <v>159</v>
       </c>
       <c r="C161" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>681</v>
+      </c>
+      <c r="F161" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G161" s="13" t="s">
         <v>682</v>
-      </c>
-      <c r="D161" s="12" t="s">
-        <v>683</v>
-      </c>
-      <c r="E161" s="13" t="s">
-        <v>716</v>
-      </c>
-      <c r="F161" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G161" s="13" t="s">
-        <v>717</v>
       </c>
       <c r="H161" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="I161" s="13"/>
+      <c r="I161" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="J161" s="12">
         <v>1</v>
       </c>
       <c r="K161" s="12">
-        <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="L161" s="19" t="s">
+      <c r="L161" s="17" t="s">
         <v>114</v>
       </c>
       <c r="M161" s="18">
-        <v>1.0093000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="N161" s="18">
         <f>M161*K161</f>
-        <v>3.0279000000000003</v>
+        <v>1.29</v>
       </c>
       <c r="O161" s="12"/>
     </row>
-    <row r="162" spans="2:19" ht="36.75" thickBot="1">
+    <row r="162" spans="2:19" ht="30.75" thickBot="1">
       <c r="B162" s="10">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D162" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="E162" s="13" t="s">
         <v>684</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>685</v>
       </c>
       <c r="F162" s="15" t="s">
         <v>150</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>686</v>
+        <v>150</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>249</v>
+        <v>685</v>
       </c>
       <c r="I162" s="13" t="s">
         <v>150</v>
@@ -10367,25 +10356,25 @@
       <c r="K162" s="12">
         <v>3</v>
       </c>
-      <c r="L162" s="17" t="s">
-        <v>114</v>
+      <c r="L162" s="19" t="s">
+        <v>686</v>
       </c>
       <c r="M162" s="18">
-        <v>0.43</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="N162" s="18">
         <f>M162*K162</f>
-        <v>1.29</v>
+        <v>29.61</v>
       </c>
       <c r="O162" s="12"/>
     </row>
-    <row r="163" spans="2:19" ht="30.75" thickBot="1">
+    <row r="163" spans="2:19" ht="15.75" thickBot="1">
       <c r="B163" s="10">
         <f t="shared" si="12"/>
         <v>161</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D163" s="12" t="s">
         <v>687</v>
@@ -10397,10 +10386,10 @@
         <v>150</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>150</v>
+        <v>689</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>150</v>
@@ -10412,59 +10401,46 @@
         <v>3</v>
       </c>
       <c r="L163" s="19" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M163" s="18">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="N163" s="18">
         <f>M163*K163</f>
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="O163" s="12"/>
     </row>
-    <row r="164" spans="2:19" ht="15.75" thickBot="1">
+    <row r="164" spans="2:19" ht="24.75" thickBot="1">
       <c r="B164" s="10">
         <f t="shared" si="12"/>
         <v>162</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>691</v>
+        <v>150</v>
       </c>
       <c r="E164" s="13" t="s">
         <v>692</v>
       </c>
-      <c r="F164" s="15" t="s">
-        <v>150</v>
-      </c>
+      <c r="F164" s="15"/>
       <c r="G164" s="13" t="s">
         <v>693</v>
       </c>
       <c r="H164" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="I164" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="J164" s="12">
-        <v>1</v>
-      </c>
-      <c r="K164" s="12">
-        <v>3</v>
-      </c>
-      <c r="L164" s="19" t="s">
-        <v>695</v>
-      </c>
-      <c r="M164" s="18">
-        <v>99</v>
-      </c>
-      <c r="N164" s="18">
-        <f>M164*K164</f>
-        <v>297</v>
-      </c>
+      <c r="I164" s="13"/>
+      <c r="J164" s="12"/>
+      <c r="K164" s="12"/>
+      <c r="L164" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="M164" s="18"/>
+      <c r="N164" s="18"/>
       <c r="O164" s="12"/>
     </row>
     <row r="165" spans="2:19" ht="24.75" thickBot="1">
@@ -10473,51 +10449,51 @@
         <v>163</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D165" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F165" s="15"/>
       <c r="G165" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="H165" s="12" t="s">
         <v>697</v>
-      </c>
-      <c r="H165" s="12" t="s">
-        <v>698</v>
       </c>
       <c r="I165" s="13"/>
       <c r="J165" s="12"/>
       <c r="K165" s="12"/>
       <c r="L165" s="17" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M165" s="18"/>
       <c r="N165" s="18"/>
       <c r="O165" s="12"/>
     </row>
-    <row r="166" spans="2:19" ht="24.75" thickBot="1">
+    <row r="166" spans="2:19" s="3" customFormat="1" ht="24.75" thickBot="1">
       <c r="B166" s="10">
         <f t="shared" si="12"/>
         <v>164</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D166" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F166" s="15"/>
       <c r="G166" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="H166" s="12" t="s">
         <v>700</v>
-      </c>
-      <c r="H166" s="12" t="s">
-        <v>701</v>
       </c>
       <c r="I166" s="13"/>
       <c r="J166" s="12"/>
@@ -10525,60 +10501,29 @@
       <c r="L166" s="17" t="s">
         <v>701</v>
       </c>
-      <c r="M166" s="18"/>
-      <c r="N166" s="18"/>
+      <c r="M166" s="41"/>
+      <c r="N166" s="41"/>
       <c r="O166" s="12"/>
-    </row>
-    <row r="167" spans="2:19" s="3" customFormat="1" ht="24.75" thickBot="1">
-      <c r="B167" s="10">
-        <f t="shared" si="12"/>
-        <v>165</v>
-      </c>
-      <c r="C167" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="D167" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E167" s="13" t="s">
+      <c r="Q166"/>
+      <c r="R166"/>
+      <c r="S166"/>
+    </row>
+    <row r="167" spans="2:19">
+      <c r="M167" s="42" t="s">
         <v>702</v>
       </c>
-      <c r="F167" s="15"/>
-      <c r="G167" s="13" t="s">
+      <c r="N167" s="43">
+        <f>SUM(N3:N166)</f>
+        <v>779.40039000000013</v>
+      </c>
+    </row>
+    <row r="168" spans="2:19" ht="15.75" thickBot="1">
+      <c r="M168" s="44" t="s">
         <v>703</v>
       </c>
-      <c r="H167" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="I167" s="13"/>
-      <c r="J167" s="12"/>
-      <c r="K167" s="12"/>
-      <c r="L167" s="17" t="s">
-        <v>705</v>
-      </c>
-      <c r="M167" s="41"/>
-      <c r="N167" s="41"/>
-      <c r="O167" s="12"/>
-      <c r="Q167"/>
-      <c r="R167"/>
-      <c r="S167"/>
-    </row>
-    <row r="168" spans="2:19">
-      <c r="M168" s="42" t="s">
-        <v>706</v>
-      </c>
-      <c r="N168" s="43">
-        <f>SUM(N3:N167)</f>
-        <v>770.82039000000009</v>
-      </c>
-    </row>
-    <row r="169" spans="2:19" ht="15.75" thickBot="1">
-      <c r="M169" s="44" t="s">
-        <v>707</v>
-      </c>
-      <c r="N169" s="45">
-        <f>N168/3</f>
-        <v>256.94013000000001</v>
+      <c r="N168" s="45">
+        <f>N167/3</f>
+        <v>259.80013000000002</v>
       </c>
     </row>
   </sheetData>
@@ -10710,7 +10655,7 @@
     <hyperlink ref="L130" r:id="rId122"/>
     <hyperlink ref="L131" r:id="rId123"/>
     <hyperlink ref="L132" r:id="rId124"/>
-    <hyperlink ref="L133" r:id="rId125"/>
+    <hyperlink ref="L134" r:id="rId125"/>
     <hyperlink ref="L135" r:id="rId126"/>
     <hyperlink ref="L136" r:id="rId127"/>
     <hyperlink ref="L137" r:id="rId128"/>
@@ -10736,16 +10681,15 @@
     <hyperlink ref="L157" r:id="rId148"/>
     <hyperlink ref="L158" r:id="rId149"/>
     <hyperlink ref="L159" r:id="rId150"/>
-    <hyperlink ref="L160" r:id="rId151"/>
-    <hyperlink ref="L166" r:id="rId152"/>
-    <hyperlink ref="L165" r:id="rId153"/>
-    <hyperlink ref="L167" r:id="rId154"/>
-    <hyperlink ref="L163" r:id="rId155"/>
-    <hyperlink ref="L162" r:id="rId156"/>
-    <hyperlink ref="L56" r:id="rId157"/>
-    <hyperlink ref="L71" r:id="rId158"/>
-    <hyperlink ref="L134" r:id="rId159"/>
-    <hyperlink ref="L161" r:id="rId160"/>
+    <hyperlink ref="L165" r:id="rId151"/>
+    <hyperlink ref="L164" r:id="rId152"/>
+    <hyperlink ref="L166" r:id="rId153"/>
+    <hyperlink ref="L162" r:id="rId154"/>
+    <hyperlink ref="L161" r:id="rId155"/>
+    <hyperlink ref="L56" r:id="rId156"/>
+    <hyperlink ref="L71" r:id="rId157"/>
+    <hyperlink ref="L133" r:id="rId158"/>
+    <hyperlink ref="L160" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -2150,9 +2150,6 @@
     <t>HJ-SMA175</t>
   </si>
   <si>
-    <t>MCZ1210CH900CPTA0G</t>
-  </si>
-  <si>
     <t>MAX3232EIDR</t>
   </si>
   <si>
@@ -2178,6 +2175,9 @@
   </si>
   <si>
     <t>R58, R66, R98</t>
+  </si>
+  <si>
+    <t>MCZ1210CH900L2TA0G</t>
   </si>
 </sst>
 </file>
@@ -5441,13 +5441,13 @@
         <v>54</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>248</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>111</v>
@@ -5456,7 +5456,7 @@
         <v>704</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I56" s="16" t="s">
         <v>150</v>
@@ -6131,7 +6131,7 @@
         <v>69</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>307</v>
@@ -6143,7 +6143,7 @@
         <v>111</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
       <c r="H71" s="15" t="s">
         <v>53</v>
@@ -7844,7 +7844,7 @@
         <v>386</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E108" s="16" t="s">
         <v>462</v>
@@ -9008,13 +9008,13 @@
         <v>554</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F133" s="12" t="s">
         <v>555</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H133" s="12" t="s">
         <v>556</v>
@@ -10249,13 +10249,13 @@
         <v>679</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>111</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H160" s="12" t="s">
         <v>249</v>

--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -1,38 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20409"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eSpark Cons Group\Documents\GitHub\Melih-SoundSensor\anis-carrierboard\Design-Files\Carrier-Board-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7B6B56-2D88-44EF-B20E-815CDE545A32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="712">
   <si>
     <t>#</t>
   </si>
@@ -341,15 +329,6 @@
   </si>
   <si>
     <t>C82, C83</t>
-  </si>
-  <si>
-    <t>CAP CER 9PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>CQ0402CRNPO9BN9R0</t>
-  </si>
-  <si>
-    <t>9pF</t>
   </si>
   <si>
     <t>C86, C87, C90, C99, C102, C105, C108, C112, C156, C157</t>
@@ -2183,7 +2162,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
@@ -2503,7 +2482,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -2629,6 +2608,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2912,7 +2894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -3929,19 +3911,19 @@
         <v>102</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="J23" s="12">
         <v>2</v>
@@ -3950,15 +3932,15 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="47" t="s">
         <v>21</v>
       </c>
       <c r="M23" s="18">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="N23" s="18">
-        <f t="shared" si="3"/>
-        <v>0.66</v>
+        <f>M23*K23</f>
+        <v>1.1400000000000001</v>
       </c>
       <c r="O23" s="12"/>
     </row>
@@ -3972,16 +3954,16 @@
         <v>14</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="15" t="s">
         <v>37</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>53</v>
@@ -4018,19 +4000,19 @@
         <v>14</v>
       </c>
       <c r="D25" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>94</v>
@@ -4043,7 +4025,7 @@
         <v>3</v>
       </c>
       <c r="L25" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M25" s="18">
         <v>5.6800000000000003E-2</v>
@@ -4064,22 +4046,22 @@
         <v>14</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F26" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J26" s="15">
         <v>7</v>
@@ -4110,22 +4092,22 @@
         <v>14</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J27" s="12">
         <v>4</v>
@@ -4156,7 +4138,7 @@
         <v>14</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>66</v>
@@ -4202,22 +4184,22 @@
         <v>14</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J29" s="12">
         <v>2</v>
@@ -4248,22 +4230,22 @@
         <v>14</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J30" s="15">
         <v>2</v>
@@ -4294,22 +4276,22 @@
         <v>14</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J31" s="12">
         <v>1</v>
@@ -4340,16 +4322,16 @@
         <v>14</v>
       </c>
       <c r="D32" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G32" s="16" t="s">
         <v>137</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>140</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>19</v>
@@ -4386,16 +4368,16 @@
         <v>14</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F33" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>19</v>
@@ -4429,25 +4411,25 @@
         <v>32</v>
       </c>
       <c r="C34" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="G34" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="H34" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="I34" s="16" t="s">
         <v>147</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>150</v>
       </c>
       <c r="J34" s="15">
         <v>30</v>
@@ -4457,7 +4439,7 @@
         <v>90</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M34" s="18">
         <v>8.3000000000000001E-3</v>
@@ -4475,25 +4457,25 @@
         <v>33</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="H35" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>155</v>
-      </c>
       <c r="I35" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J35" s="12">
         <v>2</v>
@@ -4503,7 +4485,7 @@
         <v>6</v>
       </c>
       <c r="L35" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M35" s="18">
         <v>6.2600000000000003E-2</v>
@@ -4521,25 +4503,25 @@
         <v>34</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D36" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="H36" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>160</v>
-      </c>
       <c r="I36" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J36" s="15">
         <v>1</v>
@@ -4567,25 +4549,25 @@
         <v>35</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D37" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>165</v>
-      </c>
       <c r="I37" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J37" s="12">
         <v>6</v>
@@ -4613,25 +4595,25 @@
         <v>36</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D38" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="G38" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="H38" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="I38" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J38" s="15">
         <v>1</v>
@@ -4659,25 +4641,25 @@
         <v>37</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D39" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>174</v>
-      </c>
       <c r="H39" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J39" s="12">
         <v>21</v>
@@ -4687,7 +4669,7 @@
         <v>63</v>
       </c>
       <c r="L39" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M39" s="18">
         <v>1.9099999999999999E-2</v>
@@ -4705,25 +4687,25 @@
         <v>38</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D40" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="E40" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>178</v>
-      </c>
       <c r="H40" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J40" s="15">
         <v>1</v>
@@ -4733,7 +4715,7 @@
         <v>3</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M40" s="18">
         <v>7.9399999999999998E-2</v>
@@ -4751,25 +4733,25 @@
         <v>39</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="H41" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="E41" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>182</v>
-      </c>
       <c r="I41" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J41" s="12">
         <v>2</v>
@@ -4779,7 +4761,7 @@
         <v>6</v>
       </c>
       <c r="L41" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M41" s="18">
         <v>2.9100000000000001E-2</v>
@@ -4797,25 +4779,25 @@
         <v>40</v>
       </c>
       <c r="C42" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="G42" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="H42" s="15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J42" s="15">
         <v>2</v>
@@ -4843,25 +4825,25 @@
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F43" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="G43" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="H43" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="F43" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>193</v>
-      </c>
       <c r="I43" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J43" s="12">
         <v>1</v>
@@ -4889,25 +4871,25 @@
         <v>42</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D44" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="G44" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="H44" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="F44" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="H44" s="15" t="s">
-        <v>198</v>
-      </c>
       <c r="I44" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J44" s="15">
         <v>1</v>
@@ -4917,7 +4899,7 @@
         <v>3</v>
       </c>
       <c r="L44" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M44" s="18">
         <v>3.9399999999999998E-2</v>
@@ -4935,25 +4917,25 @@
         <v>43</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F45" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="G45" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>203</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>44</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J45" s="12">
         <v>1</v>
@@ -4981,25 +4963,25 @@
         <v>44</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D46" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" s="16" t="s">
         <v>204</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>207</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>44</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J46" s="15">
         <v>1</v>
@@ -5027,25 +5009,25 @@
         <v>45</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G47" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>44</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J47" s="12">
         <v>2</v>
@@ -5073,25 +5055,25 @@
         <v>46</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G48" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="H48" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="E48" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G48" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>216</v>
-      </c>
       <c r="I48" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J48" s="12">
         <v>1</v>
@@ -5101,7 +5083,7 @@
         <v>3</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M48" s="18">
         <v>7.4099999999999999E-2</v>
@@ -5119,25 +5101,25 @@
         <v>47</v>
       </c>
       <c r="C49" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G49" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="H49" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="E49" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>221</v>
-      </c>
       <c r="I49" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J49" s="15">
         <v>1</v>
@@ -5147,7 +5129,7 @@
         <v>3</v>
       </c>
       <c r="L49" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M49" s="18">
         <v>4.2946</v>
@@ -5165,25 +5147,25 @@
         <v>48</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G50" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="H50" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="E50" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>226</v>
-      </c>
       <c r="I50" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J50" s="12">
         <v>1</v>
@@ -5211,25 +5193,25 @@
         <v>49</v>
       </c>
       <c r="C51" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G51" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="H51" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="E51" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>231</v>
-      </c>
       <c r="I51" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J51" s="15">
         <v>1</v>
@@ -5239,7 +5221,7 @@
         <v>3</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M51" s="18">
         <v>1.52E-2</v>
@@ -5257,25 +5239,25 @@
         <v>50</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J52" s="12">
         <v>1</v>
@@ -5285,7 +5267,7 @@
         <v>3</v>
       </c>
       <c r="L52" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M52" s="18">
         <v>1.9199999999999998E-2</v>
@@ -5303,25 +5285,25 @@
         <v>51</v>
       </c>
       <c r="C53" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G53" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="H53" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="E53" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>238</v>
-      </c>
       <c r="I53" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J53" s="15">
         <v>1</v>
@@ -5331,7 +5313,7 @@
         <v>3</v>
       </c>
       <c r="L53" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M53" s="18">
         <v>0.1726</v>
@@ -5349,25 +5331,25 @@
         <v>52</v>
       </c>
       <c r="C54" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G54" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>242</v>
-      </c>
       <c r="H54" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I54" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J54" s="12">
         <v>1</v>
@@ -5377,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="L54" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M54" s="18">
         <v>0.70579999999999998</v>
@@ -5395,25 +5377,25 @@
         <v>53</v>
       </c>
       <c r="C55" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="F55" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G55" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="H55" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G55" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>247</v>
-      </c>
       <c r="I55" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J55" s="15">
         <v>1</v>
@@ -5423,7 +5405,7 @@
         <v>3</v>
       </c>
       <c r="L55" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M55" s="18">
         <v>0.42970000000000003</v>
@@ -5441,25 +5423,25 @@
         <v>54</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J56" s="12">
         <v>1</v>
@@ -5469,7 +5451,7 @@
         <v>3</v>
       </c>
       <c r="L56" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M56" s="18">
         <v>0.80400000000000005</v>
@@ -5487,25 +5469,25 @@
         <v>55</v>
       </c>
       <c r="C57" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="H57" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="E57" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="H57" s="12" t="s">
-        <v>254</v>
-      </c>
       <c r="I57" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J57" s="12">
         <v>2</v>
@@ -5515,7 +5497,7 @@
         <v>6</v>
       </c>
       <c r="L57" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M57" s="18">
         <v>0.55000000000000004</v>
@@ -5533,25 +5515,25 @@
         <v>56</v>
       </c>
       <c r="C58" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G58" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="H58" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="E58" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>259</v>
-      </c>
       <c r="I58" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J58" s="15">
         <v>5</v>
@@ -5561,7 +5543,7 @@
         <v>15</v>
       </c>
       <c r="L58" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M58" s="18">
         <v>9.8699999999999996E-2</v>
@@ -5579,25 +5561,25 @@
         <v>57</v>
       </c>
       <c r="C59" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F59" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G59" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>263</v>
-      </c>
       <c r="H59" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J59" s="12">
         <v>1</v>
@@ -5607,7 +5589,7 @@
         <v>3</v>
       </c>
       <c r="L59" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M59" s="18">
         <v>0.18920000000000001</v>
@@ -5625,25 +5607,25 @@
         <v>58</v>
       </c>
       <c r="C60" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G60" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="H60" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="E60" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>268</v>
-      </c>
       <c r="I60" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J60" s="15">
         <v>1</v>
@@ -5671,25 +5653,25 @@
         <v>59</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="H61" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="E61" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>273</v>
-      </c>
       <c r="I61" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J61" s="12">
         <v>1</v>
@@ -5717,25 +5699,25 @@
         <v>60</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G62" s="16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H62" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I62" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J62" s="15">
         <v>1</v>
@@ -5745,7 +5727,7 @@
         <v>3</v>
       </c>
       <c r="L62" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M62" s="18">
         <v>1.2999999999999999E-2</v>
@@ -5763,25 +5745,25 @@
         <v>61</v>
       </c>
       <c r="C63" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G63" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="H63" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="H63" s="12" t="s">
-        <v>281</v>
-      </c>
       <c r="I63" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J63" s="12">
         <v>2</v>
@@ -5791,7 +5773,7 @@
         <v>6</v>
       </c>
       <c r="L63" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M63" s="18">
         <v>2.5537999999999998</v>
@@ -5809,25 +5791,25 @@
         <v>62</v>
       </c>
       <c r="C64" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G64" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>285</v>
-      </c>
       <c r="H64" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I64" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J64" s="15">
         <v>1</v>
@@ -5837,7 +5819,7 @@
         <v>3</v>
       </c>
       <c r="L64" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M64" s="18">
         <v>1.52E-2</v>
@@ -5855,25 +5837,25 @@
         <v>63</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I65" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J65" s="12">
         <v>1</v>
@@ -5883,7 +5865,7 @@
         <v>3</v>
       </c>
       <c r="L65" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M65" s="18">
         <v>1.67E-2</v>
@@ -5901,25 +5883,25 @@
         <v>64</v>
       </c>
       <c r="C66" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G66" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="D66" s="15" t="s">
-        <v>289</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>291</v>
-      </c>
       <c r="H66" s="15" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I66" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J66" s="15">
         <v>1</v>
@@ -5929,7 +5911,7 @@
         <v>3</v>
       </c>
       <c r="L66" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M66" s="18">
         <v>0.33900000000000002</v>
@@ -5947,25 +5929,25 @@
         <v>65</v>
       </c>
       <c r="C67" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G67" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="E67" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G67" s="13" t="s">
-        <v>295</v>
-      </c>
       <c r="H67" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="I67" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J67" s="12">
         <v>1</v>
@@ -5993,25 +5975,25 @@
         <v>66</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J68" s="15">
         <v>2</v>
@@ -6021,7 +6003,7 @@
         <v>6</v>
       </c>
       <c r="L68" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M68" s="18">
         <v>6.8999999999999999E-3</v>
@@ -6039,25 +6021,25 @@
         <v>67</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I69" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J69" s="12">
         <v>1</v>
@@ -6067,7 +6049,7 @@
         <v>3</v>
       </c>
       <c r="L69" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M69" s="18">
         <v>0.49419999999999997</v>
@@ -6085,25 +6067,25 @@
         <v>68</v>
       </c>
       <c r="C70" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G70" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D70" s="15" t="s">
+      <c r="H70" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="E70" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>306</v>
-      </c>
       <c r="I70" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J70" s="15">
         <v>5</v>
@@ -6131,25 +6113,25 @@
         <v>69</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H71" s="15" t="s">
         <v>53</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J71" s="12">
         <v>4</v>
@@ -6177,25 +6159,25 @@
         <v>70</v>
       </c>
       <c r="C72" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G72" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="H72" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="I72" s="16" t="s">
         <v>311</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="H72" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="I72" s="16" t="s">
-        <v>314</v>
       </c>
       <c r="J72" s="15">
         <v>1</v>
@@ -6223,25 +6205,25 @@
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D73" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="E73" s="13" t="s">
+      <c r="I73" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="I73" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="J73" s="12">
         <v>2</v>
@@ -6269,25 +6251,25 @@
         <v>72</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D74" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="H74" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="I74" s="16" t="s">
         <v>321</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="H74" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="I74" s="16" t="s">
-        <v>324</v>
       </c>
       <c r="J74" s="15">
         <v>2</v>
@@ -6297,7 +6279,7 @@
         <v>6</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M74" s="18">
         <v>0.79559999999999997</v>
@@ -6315,25 +6297,25 @@
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>324</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="G75" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="E75" s="13" t="s">
+      <c r="H75" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F75" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="H75" s="12" t="s">
-        <v>330</v>
-      </c>
       <c r="I75" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J75" s="12">
         <v>1</v>
@@ -6343,7 +6325,7 @@
         <v>3</v>
       </c>
       <c r="L75" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M75" s="18">
         <v>2.18E-2</v>
@@ -6361,25 +6343,25 @@
         <v>74</v>
       </c>
       <c r="C76" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="F76" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="D76" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>328</v>
-      </c>
       <c r="G76" s="16" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H76" s="15" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I76" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J76" s="15">
         <v>2</v>
@@ -6389,7 +6371,7 @@
         <v>6</v>
       </c>
       <c r="L76" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M76" s="18">
         <v>2.18E-2</v>
@@ -6407,25 +6389,25 @@
         <v>75</v>
       </c>
       <c r="C77" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F77" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="D77" s="12" t="s">
-        <v>334</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>328</v>
-      </c>
       <c r="G77" s="13" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J77" s="12">
         <v>1</v>
@@ -6435,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="L77" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M77" s="18">
         <v>1.9599999999999999E-2</v>
@@ -6453,25 +6435,25 @@
         <v>76</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D78" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="G78" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="E78" s="16" t="s">
+      <c r="H78" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="F78" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="H78" s="15" t="s">
-        <v>341</v>
-      </c>
       <c r="I78" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J78" s="15">
         <v>1</v>
@@ -6499,25 +6481,25 @@
         <v>77</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J79" s="12">
         <v>1</v>
@@ -6545,25 +6527,25 @@
         <v>78</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G80" s="16" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H80" s="15" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J80" s="15">
         <v>1</v>
@@ -6591,25 +6573,25 @@
         <v>79</v>
       </c>
       <c r="C81" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="G81" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="E81" s="13" t="s">
+      <c r="H81" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="F81" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="H81" s="12" t="s">
-        <v>353</v>
-      </c>
       <c r="I81" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J81" s="12">
         <v>6</v>
@@ -6619,7 +6601,7 @@
         <v>18</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M81" s="18">
         <v>8.6800000000000002E-2</v>
@@ -6637,25 +6619,25 @@
         <v>80</v>
       </c>
       <c r="C82" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="F82" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="G82" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="E82" s="16" t="s">
+      <c r="H82" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="F82" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="G82" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>359</v>
-      </c>
       <c r="I82" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J82" s="15">
         <v>1</v>
@@ -6683,25 +6665,25 @@
         <v>81</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H83" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J83" s="12">
         <v>4</v>
@@ -6711,7 +6693,7 @@
         <v>12</v>
       </c>
       <c r="L83" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M83" s="18">
         <v>4.5400000000000003E-2</v>
@@ -6729,25 +6711,25 @@
         <v>82</v>
       </c>
       <c r="C84" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G84" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="D84" s="15" t="s">
+      <c r="H84" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="E84" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="F84" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="H84" s="15" t="s">
-        <v>367</v>
-      </c>
       <c r="I84" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J84" s="15">
         <v>2</v>
@@ -6775,25 +6757,25 @@
         <v>83</v>
       </c>
       <c r="C85" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="G85" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="H85" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="E85" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="G85" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="H85" s="12" t="s">
-        <v>372</v>
-      </c>
       <c r="I85" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J85" s="12">
         <v>5</v>
@@ -6821,25 +6803,25 @@
         <v>84</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D86" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="H86" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="E86" s="16" t="s">
-        <v>374</v>
-      </c>
-      <c r="F86" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="H86" s="15" t="s">
-        <v>376</v>
-      </c>
       <c r="I86" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J86" s="15">
         <v>1</v>
@@ -6867,25 +6849,25 @@
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D87" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="F87" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="G87" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E87" s="13" t="s">
+      <c r="H87" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="F87" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="G87" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>381</v>
-      </c>
       <c r="I87" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J87" s="12">
         <v>1</v>
@@ -6913,25 +6895,25 @@
         <v>86</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D88" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="E88" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="F88" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>385</v>
-      </c>
       <c r="H88" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J88" s="15">
         <v>1</v>
@@ -6941,7 +6923,7 @@
         <v>3</v>
       </c>
       <c r="L88" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M88" s="18">
         <v>2.8000000000000001E-2</v>
@@ -6959,25 +6941,25 @@
         <v>87</v>
       </c>
       <c r="C89" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="F89" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="G89" s="13" t="s">
         <v>387</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="G89" s="13" t="s">
-        <v>390</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J89" s="12">
         <v>40</v>
@@ -7005,25 +6987,25 @@
         <v>88</v>
       </c>
       <c r="C90" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="F90" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D90" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="F90" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G90" s="16" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J90" s="15">
         <v>6</v>
@@ -7051,25 +7033,25 @@
         <v>89</v>
       </c>
       <c r="C91" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="F91" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D91" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G91" s="13" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H91" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J91" s="12">
         <v>7</v>
@@ -7097,25 +7079,25 @@
         <v>90</v>
       </c>
       <c r="C92" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="F92" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D92" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="E92" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="F92" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G92" s="16" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H92" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I92" s="16" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J92" s="15">
         <v>49</v>
@@ -7143,25 +7125,25 @@
         <v>91</v>
       </c>
       <c r="C93" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="F93" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D93" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G93" s="13" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H93" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J93" s="12">
         <v>7</v>
@@ -7189,25 +7171,25 @@
         <v>92</v>
       </c>
       <c r="C94" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="D94" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="F94" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="D94" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="F94" s="23" t="s">
-        <v>389</v>
-      </c>
       <c r="G94" s="24" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H94" s="23" t="s">
         <v>19</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J94" s="23">
         <v>2</v>
@@ -7220,13 +7202,13 @@
         <v>21</v>
       </c>
       <c r="M94" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N94" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O94" s="37" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Q94"/>
       <c r="R94"/>
@@ -7239,25 +7221,25 @@
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D95" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="G95" s="13" t="s">
         <v>413</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="G95" s="13" t="s">
-        <v>416</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J95" s="12">
         <v>2</v>
@@ -7285,25 +7267,25 @@
         <v>94</v>
       </c>
       <c r="C96" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="F96" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D96" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="E96" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G96" s="16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="H96" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I96" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J96" s="15">
         <v>26</v>
@@ -7331,25 +7313,25 @@
         <v>95</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J97" s="12">
         <v>1</v>
@@ -7377,25 +7359,25 @@
         <v>96</v>
       </c>
       <c r="C98" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="F98" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D98" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="F98" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G98" s="16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H98" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I98" s="16" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J98" s="15">
         <v>27</v>
@@ -7423,25 +7405,25 @@
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G99" s="13" t="s">
         <v>429</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G99" s="13" t="s">
-        <v>432</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J99" s="12">
         <v>4</v>
@@ -7469,25 +7451,25 @@
         <v>98</v>
       </c>
       <c r="C100" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="F100" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D100" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="F100" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G100" s="16" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H100" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I100" s="16" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J100" s="15">
         <v>4</v>
@@ -7515,25 +7497,25 @@
         <v>99</v>
       </c>
       <c r="C101" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="F101" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D101" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G101" s="13" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J101" s="12">
         <v>4</v>
@@ -7561,25 +7543,25 @@
         <v>100</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I102" s="16" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J102" s="15">
         <v>1</v>
@@ -7607,25 +7589,25 @@
         <v>101</v>
       </c>
       <c r="C103" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="F103" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D103" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G103" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J103" s="12">
         <v>5</v>
@@ -7653,25 +7635,25 @@
         <v>102</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="H104" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I104" s="16" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J104" s="15">
         <v>1</v>
@@ -7699,25 +7681,25 @@
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J105" s="12">
         <v>1</v>
@@ -7745,25 +7727,25 @@
         <v>104</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I106" s="16" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J106" s="15">
         <v>1</v>
@@ -7791,25 +7773,25 @@
         <v>105</v>
       </c>
       <c r="C107" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>458</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="F107" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="D107" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>389</v>
-      </c>
       <c r="G107" s="27" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H107" s="26" t="s">
         <v>19</v>
       </c>
       <c r="I107" s="27" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J107" s="26">
         <v>1</v>
@@ -7822,13 +7804,13 @@
         <v>21</v>
       </c>
       <c r="M107" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N107" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O107" s="37" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Q107"/>
       <c r="R107"/>
@@ -7841,25 +7823,25 @@
         <v>106</v>
       </c>
       <c r="C108" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="F108" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D108" s="15" t="s">
-        <v>713</v>
-      </c>
-      <c r="E108" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="F108" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G108" s="16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I108" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J108" s="15">
         <v>3</v>
@@ -7887,25 +7869,25 @@
         <v>107</v>
       </c>
       <c r="C109" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="F109" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D109" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G109" s="13" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J109" s="12">
         <v>2</v>
@@ -7933,25 +7915,25 @@
         <v>108</v>
       </c>
       <c r="C110" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="D110" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="E110" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="F110" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="D110" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="E110" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="F110" s="23" t="s">
-        <v>389</v>
-      </c>
       <c r="G110" s="24" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H110" s="23" t="s">
         <v>19</v>
       </c>
       <c r="I110" s="24" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J110" s="23">
         <v>2</v>
@@ -7964,13 +7946,13 @@
         <v>21</v>
       </c>
       <c r="M110" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N110" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O110" s="37" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="15.75" thickBot="1">
@@ -7980,25 +7962,25 @@
         <v>109</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D111" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="G111" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="H111" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="E111" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="G111" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>473</v>
-      </c>
       <c r="I111" s="13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J111" s="12">
         <v>2</v>
@@ -8026,25 +8008,25 @@
         <v>110</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I112" s="16" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="J112" s="15">
         <v>2</v>
@@ -8072,25 +8054,25 @@
         <v>111</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G113" s="13" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J113" s="12">
         <v>4</v>
@@ -8118,25 +8100,25 @@
         <v>112</v>
       </c>
       <c r="C114" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="F114" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D114" s="15" t="s">
+      <c r="G114" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="I114" s="16" t="s">
         <v>481</v>
-      </c>
-      <c r="E114" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="F114" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="G114" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="I114" s="16" t="s">
-        <v>484</v>
       </c>
       <c r="J114" s="15">
         <v>2</v>
@@ -8164,25 +8146,25 @@
         <v>113</v>
       </c>
       <c r="C115" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="D115" s="31" t="s">
+        <v>482</v>
+      </c>
+      <c r="E115" s="32" t="s">
+        <v>483</v>
+      </c>
+      <c r="F115" s="31" t="s">
         <v>386</v>
       </c>
-      <c r="D115" s="31" t="s">
-        <v>485</v>
-      </c>
-      <c r="E115" s="32" t="s">
-        <v>486</v>
-      </c>
-      <c r="F115" s="31" t="s">
-        <v>389</v>
-      </c>
       <c r="G115" s="32" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H115" s="31" t="s">
         <v>19</v>
       </c>
       <c r="I115" s="32" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J115" s="31">
         <v>8</v>
@@ -8213,25 +8195,25 @@
         <v>114</v>
       </c>
       <c r="C116" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="D116" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="E116" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="F116" s="33" t="s">
         <v>386</v>
       </c>
-      <c r="D116" s="33" t="s">
-        <v>489</v>
-      </c>
-      <c r="E116" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="F116" s="33" t="s">
-        <v>389</v>
-      </c>
       <c r="G116" s="34" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="H116" s="33" t="s">
         <v>19</v>
       </c>
       <c r="I116" s="34" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J116" s="33">
         <v>8</v>
@@ -8262,25 +8244,25 @@
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="F117" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D117" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="F117" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G117" s="13" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J117" s="12">
         <v>2</v>
@@ -8308,25 +8290,25 @@
         <v>116</v>
       </c>
       <c r="C118" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="E118" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="F118" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D118" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="E118" s="16" t="s">
-        <v>496</v>
-      </c>
-      <c r="F118" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G118" s="16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I118" s="16" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J118" s="15">
         <v>2</v>
@@ -8354,25 +8336,25 @@
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="G119" s="13" t="s">
         <v>499</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>500</v>
-      </c>
-      <c r="E119" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="F119" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>502</v>
       </c>
       <c r="H119" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I119" s="13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J119" s="12">
         <v>2</v>
@@ -8400,25 +8382,25 @@
         <v>118</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="16" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J120" s="15">
         <v>2</v>
@@ -8446,25 +8428,25 @@
         <v>119</v>
       </c>
       <c r="C121" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="D121" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="F121" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="D121" s="26" t="s">
-        <v>507</v>
-      </c>
-      <c r="E121" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>389</v>
-      </c>
       <c r="G121" s="27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H121" s="26" t="s">
         <v>19</v>
       </c>
       <c r="I121" s="27" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J121" s="26">
         <v>2</v>
@@ -8477,13 +8459,13 @@
         <v>21</v>
       </c>
       <c r="M121" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N121" s="36" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O121" s="37" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Q121"/>
       <c r="R121"/>
@@ -8496,25 +8478,25 @@
         <v>120</v>
       </c>
       <c r="C122" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="E122" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="F122" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D122" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="F122" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G122" s="16" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="16" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J122" s="15">
         <v>1</v>
@@ -8542,25 +8524,25 @@
         <v>121</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H123" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I123" s="16" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J123" s="15">
         <v>2</v>
@@ -8588,25 +8570,25 @@
         <v>122</v>
       </c>
       <c r="C124" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="F124" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D124" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="F124" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G124" s="13" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H124" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I124" s="13" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J124" s="12">
         <v>1</v>
@@ -8634,25 +8616,25 @@
         <v>123</v>
       </c>
       <c r="C125" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="F125" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D125" s="15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="F125" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G125" s="16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="H125" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I125" s="16" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J125" s="15">
         <v>1</v>
@@ -8680,25 +8662,25 @@
         <v>124</v>
       </c>
       <c r="C126" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E126" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="F126" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D126" s="12" t="s">
-        <v>524</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>525</v>
-      </c>
-      <c r="F126" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G126" s="13" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H126" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I126" s="13" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J126" s="12">
         <v>1</v>
@@ -8726,25 +8708,25 @@
         <v>125</v>
       </c>
       <c r="C127" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="F127" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D127" s="15" t="s">
-        <v>528</v>
-      </c>
-      <c r="E127" s="16" t="s">
-        <v>529</v>
-      </c>
-      <c r="F127" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G127" s="16" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H127" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I127" s="16" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J127" s="15">
         <v>1</v>
@@ -8772,25 +8754,25 @@
         <v>126</v>
       </c>
       <c r="C128" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="E128" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="F128" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="D128" s="12" t="s">
-        <v>532</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="F128" s="12" t="s">
-        <v>389</v>
-      </c>
       <c r="G128" s="13" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H128" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I128" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J128" s="12">
         <v>2</v>
@@ -8818,25 +8800,25 @@
         <v>127</v>
       </c>
       <c r="C129" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="F129" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="D129" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="E129" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="F129" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="G129" s="16" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H129" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I129" s="16" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J129" s="15">
         <v>1</v>
@@ -8864,25 +8846,25 @@
         <v>128</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D130" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="E130" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="G130" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="E130" s="13" t="s">
+      <c r="H130" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="F130" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="G130" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="H130" s="12" t="s">
-        <v>542</v>
-      </c>
       <c r="I130" s="13" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J130" s="12">
         <v>2</v>
@@ -8910,25 +8892,25 @@
         <v>129</v>
       </c>
       <c r="C131" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="D131" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="F131" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G131" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="H131" s="15" t="s">
         <v>544</v>
       </c>
-      <c r="E131" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="F131" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G131" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="H131" s="15" t="s">
-        <v>547</v>
-      </c>
       <c r="I131" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J131" s="15">
         <v>6</v>
@@ -8938,7 +8920,7 @@
         <v>18</v>
       </c>
       <c r="L131" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M131" s="18">
         <v>6.9400000000000003E-2</v>
@@ -8956,25 +8938,25 @@
         <v>130</v>
       </c>
       <c r="C132" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="E132" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="F132" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="G132" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="E132" s="13" t="s">
+      <c r="H132" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="F132" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="G132" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="H132" s="12" t="s">
-        <v>553</v>
-      </c>
       <c r="I132" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J132" s="12">
         <v>1</v>
@@ -8984,7 +8966,7 @@
         <v>3</v>
       </c>
       <c r="L132" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M132" s="18">
         <v>0.25340000000000001</v>
@@ -9002,25 +8984,25 @@
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E133" s="12" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G133" s="12" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="H133" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I133" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J133" s="15">
         <v>1</v>
@@ -9048,25 +9030,25 @@
         <v>132</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D134" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="G134" s="13" t="s">
         <v>557</v>
       </c>
-      <c r="E134" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="F134" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="G134" s="13" t="s">
-        <v>560</v>
-      </c>
       <c r="H134" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I134" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J134" s="12">
         <v>2</v>
@@ -9094,25 +9076,25 @@
         <v>133</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D135" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="E135" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F135" s="15" t="s">
+        <v>560</v>
+      </c>
+      <c r="G135" s="16" t="s">
         <v>561</v>
       </c>
-      <c r="E135" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="F135" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="G135" s="16" t="s">
-        <v>564</v>
-      </c>
       <c r="H135" s="15" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I135" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J135" s="15">
         <v>1</v>
@@ -9140,25 +9122,25 @@
         <v>134</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D136" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>563</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="G136" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="E136" s="13" t="s">
+      <c r="H136" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="F136" s="12" t="s">
-        <v>567</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="H136" s="12" t="s">
-        <v>569</v>
-      </c>
       <c r="I136" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J136" s="12">
         <v>4</v>
@@ -9168,7 +9150,7 @@
         <v>12</v>
       </c>
       <c r="L136" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M136" s="18">
         <v>9.3799999999999994E-2</v>
@@ -9186,25 +9168,25 @@
         <v>135</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D137" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="E137" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="F137" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="G137" s="16" t="s">
         <v>570</v>
       </c>
-      <c r="E137" s="16" t="s">
+      <c r="H137" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="F137" s="15" t="s">
-        <v>572</v>
-      </c>
-      <c r="G137" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="H137" s="15" t="s">
-        <v>574</v>
-      </c>
       <c r="I137" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J137" s="15">
         <v>1</v>
@@ -9232,25 +9214,25 @@
         <v>136</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D138" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>573</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="G138" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="E138" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="F138" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="G138" s="13" t="s">
-        <v>578</v>
-      </c>
       <c r="H138" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I138" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J138" s="12">
         <v>1</v>
@@ -9278,25 +9260,25 @@
         <v>137</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D139" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="E139" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="F139" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="G139" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="E139" s="16" t="s">
+      <c r="H139" s="15" t="s">
         <v>580</v>
       </c>
-      <c r="F139" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="G139" s="16" t="s">
-        <v>582</v>
-      </c>
-      <c r="H139" s="15" t="s">
-        <v>583</v>
-      </c>
       <c r="I139" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J139" s="15">
         <v>1</v>
@@ -9324,25 +9306,25 @@
         <v>138</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D140" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>582</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="G140" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="H140" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="E140" s="13" t="s">
-        <v>585</v>
-      </c>
-      <c r="F140" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="G140" s="13" t="s">
-        <v>586</v>
-      </c>
-      <c r="H140" s="12" t="s">
-        <v>587</v>
-      </c>
       <c r="I140" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J140" s="12">
         <v>1</v>
@@ -9370,25 +9352,25 @@
         <v>139</v>
       </c>
       <c r="C141" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="E141" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="F141" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G141" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="D141" s="15" t="s">
+      <c r="H141" s="15" t="s">
         <v>589</v>
       </c>
-      <c r="E141" s="16" t="s">
-        <v>590</v>
-      </c>
-      <c r="F141" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G141" s="16" t="s">
-        <v>591</v>
-      </c>
-      <c r="H141" s="15" t="s">
-        <v>592</v>
-      </c>
       <c r="I141" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J141" s="15">
         <v>1</v>
@@ -9416,25 +9398,25 @@
         <v>140</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I142" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J142" s="12">
         <v>1</v>
@@ -9462,25 +9444,25 @@
         <v>141</v>
       </c>
       <c r="C143" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="E143" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="F143" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G143" s="16" t="s">
         <v>596</v>
       </c>
-      <c r="D143" s="15" t="s">
+      <c r="H143" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="E143" s="16" t="s">
-        <v>598</v>
-      </c>
-      <c r="F143" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="G143" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="H143" s="15" t="s">
-        <v>600</v>
-      </c>
       <c r="I143" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J143" s="15">
         <v>2</v>
@@ -9490,7 +9472,7 @@
         <v>6</v>
       </c>
       <c r="L143" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M143" s="18">
         <v>2.3199999999999998E-2</v>
@@ -9508,25 +9490,25 @@
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D144" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="F144" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G144" s="13" t="s">
+        <v>600</v>
+      </c>
+      <c r="H144" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="E144" s="13" t="s">
-        <v>602</v>
-      </c>
-      <c r="F144" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G144" s="13" t="s">
-        <v>603</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>604</v>
-      </c>
       <c r="I144" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J144" s="12">
         <v>1</v>
@@ -9536,7 +9518,7 @@
         <v>3</v>
       </c>
       <c r="L144" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M144" s="18">
         <v>8.3531999999999993</v>
@@ -9554,25 +9536,25 @@
         <v>143</v>
       </c>
       <c r="C145" s="14" t="s">
+        <v>602</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="E145" s="16" t="s">
+        <v>604</v>
+      </c>
+      <c r="F145" s="15" t="s">
         <v>605</v>
       </c>
-      <c r="D145" s="15" t="s">
+      <c r="G145" s="16" t="s">
         <v>606</v>
       </c>
-      <c r="E145" s="16" t="s">
+      <c r="H145" s="15" t="s">
         <v>607</v>
       </c>
-      <c r="F145" s="15" t="s">
-        <v>608</v>
-      </c>
-      <c r="G145" s="16" t="s">
-        <v>609</v>
-      </c>
-      <c r="H145" s="15" t="s">
-        <v>610</v>
-      </c>
       <c r="I145" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J145" s="15">
         <v>1</v>
@@ -9582,7 +9564,7 @@
         <v>3</v>
       </c>
       <c r="L145" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M145" s="18">
         <v>0.63719999999999999</v>
@@ -9600,25 +9582,25 @@
         <v>144</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D146" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="G146" s="13" t="s">
         <v>611</v>
       </c>
-      <c r="E146" s="13" t="s">
+      <c r="H146" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="F146" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>615</v>
-      </c>
       <c r="I146" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J146" s="12">
         <v>1</v>
@@ -9628,7 +9610,7 @@
         <v>3</v>
       </c>
       <c r="L146" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M146" s="18">
         <v>7.8799999999999995E-2</v>
@@ -9646,25 +9628,25 @@
         <v>145</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D147" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="E147" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="F147" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="G147" s="16" t="s">
         <v>616</v>
       </c>
-      <c r="E147" s="16" t="s">
+      <c r="H147" s="15" t="s">
         <v>617</v>
       </c>
-      <c r="F147" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="G147" s="16" t="s">
-        <v>619</v>
-      </c>
-      <c r="H147" s="15" t="s">
-        <v>620</v>
-      </c>
       <c r="I147" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J147" s="15">
         <v>1</v>
@@ -9692,25 +9674,25 @@
         <v>146</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D148" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="G148" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="E148" s="13" t="s">
-        <v>622</v>
-      </c>
-      <c r="F148" s="12" t="s">
-        <v>623</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>624</v>
-      </c>
       <c r="H148" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I148" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J148" s="12">
         <v>1</v>
@@ -9738,25 +9720,25 @@
         <v>147</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D149" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="E149" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="G149" s="16" t="s">
         <v>625</v>
       </c>
-      <c r="E149" s="16" t="s">
+      <c r="H149" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="F149" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="G149" s="16" t="s">
-        <v>628</v>
-      </c>
-      <c r="H149" s="15" t="s">
-        <v>629</v>
-      </c>
       <c r="I149" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J149" s="15">
         <v>2</v>
@@ -9766,7 +9748,7 @@
         <v>6</v>
       </c>
       <c r="L149" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M149" s="18">
         <v>0.99080000000000001</v>
@@ -9784,25 +9766,25 @@
         <v>148</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D150" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="E150" s="16" t="s">
+        <v>628</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G150" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="H150" s="15" t="s">
         <v>630</v>
       </c>
-      <c r="E150" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="F150" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G150" s="16" t="s">
-        <v>632</v>
-      </c>
-      <c r="H150" s="15" t="s">
-        <v>633</v>
-      </c>
       <c r="I150" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J150" s="15">
         <v>1</v>
@@ -9830,25 +9812,25 @@
         <v>149</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D151" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="G151" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="E151" s="12" t="s">
+      <c r="H151" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="F151" s="12" t="s">
-        <v>636</v>
-      </c>
-      <c r="G151" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="H151" s="12" t="s">
-        <v>638</v>
-      </c>
       <c r="I151" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J151" s="15">
         <v>1</v>
@@ -9876,25 +9858,25 @@
         <v>150</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D152" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="E152" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="G152" s="16" t="s">
         <v>639</v>
       </c>
-      <c r="E152" s="16" t="s">
+      <c r="H152" s="15" t="s">
         <v>640</v>
       </c>
-      <c r="F152" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="G152" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="H152" s="15" t="s">
-        <v>643</v>
-      </c>
       <c r="I152" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J152" s="15">
         <v>1</v>
@@ -9922,25 +9904,25 @@
         <v>151</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D153" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="E153" s="13" t="s">
+        <v>642</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="G153" s="13" t="s">
         <v>644</v>
       </c>
-      <c r="E153" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="F153" s="12" t="s">
-        <v>646</v>
-      </c>
-      <c r="G153" s="13" t="s">
-        <v>647</v>
-      </c>
       <c r="H153" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="I153" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J153" s="12">
         <v>1</v>
@@ -9968,25 +9950,25 @@
         <v>152</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D154" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="E154" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="H154" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="E154" s="16" t="s">
-        <v>649</v>
-      </c>
-      <c r="F154" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G154" s="16" t="s">
-        <v>650</v>
-      </c>
-      <c r="H154" s="15" t="s">
-        <v>651</v>
-      </c>
       <c r="I154" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J154" s="15">
         <v>1</v>
@@ -10014,25 +9996,25 @@
         <v>153</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D155" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="E155" s="13" t="s">
+        <v>650</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="G155" s="13" t="s">
         <v>652</v>
       </c>
-      <c r="E155" s="13" t="s">
+      <c r="H155" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="F155" s="12" t="s">
-        <v>654</v>
-      </c>
-      <c r="G155" s="13" t="s">
-        <v>655</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>656</v>
-      </c>
       <c r="I155" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J155" s="12">
         <v>1</v>
@@ -10060,25 +10042,25 @@
         <v>154</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D156" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="E156" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="F156" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="G156" s="16" t="s">
         <v>657</v>
       </c>
-      <c r="E156" s="16" t="s">
+      <c r="H156" s="15" t="s">
         <v>658</v>
       </c>
-      <c r="F156" s="15" t="s">
-        <v>659</v>
-      </c>
-      <c r="G156" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="H156" s="15" t="s">
-        <v>661</v>
-      </c>
       <c r="I156" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J156" s="15">
         <v>1</v>
@@ -10088,7 +10070,7 @@
         <v>3</v>
       </c>
       <c r="L156" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M156" s="18">
         <v>0.34460000000000002</v>
@@ -10106,25 +10088,25 @@
         <v>155</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D157" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="E157" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="G157" s="13" t="s">
         <v>662</v>
       </c>
-      <c r="E157" s="13" t="s">
+      <c r="H157" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="F157" s="12" t="s">
-        <v>664</v>
-      </c>
-      <c r="G157" s="13" t="s">
-        <v>665</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>666</v>
-      </c>
       <c r="I157" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J157" s="12">
         <v>1</v>
@@ -10152,25 +10134,25 @@
         <v>156</v>
       </c>
       <c r="C158" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="E158" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G158" s="16" t="s">
         <v>667</v>
       </c>
-      <c r="D158" s="15" t="s">
+      <c r="H158" s="15" t="s">
         <v>668</v>
       </c>
-      <c r="E158" s="16" t="s">
+      <c r="I158" s="16" t="s">
         <v>669</v>
-      </c>
-      <c r="F158" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G158" s="16" t="s">
-        <v>670</v>
-      </c>
-      <c r="H158" s="15" t="s">
-        <v>671</v>
-      </c>
-      <c r="I158" s="16" t="s">
-        <v>672</v>
       </c>
       <c r="J158" s="15">
         <v>1</v>
@@ -10198,25 +10180,25 @@
         <v>157</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D159" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="F159" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G159" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="H159" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="E159" s="13" t="s">
+      <c r="I159" s="13" t="s">
         <v>674</v>
-      </c>
-      <c r="F159" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G159" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>676</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>677</v>
       </c>
       <c r="J159" s="12">
         <v>2</v>
@@ -10243,22 +10225,22 @@
         <v>158</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I160" s="13"/>
       <c r="J160" s="12">
@@ -10269,7 +10251,7 @@
         <v>3</v>
       </c>
       <c r="L160" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M160" s="18">
         <v>1.0093000000000001</v>
@@ -10286,25 +10268,25 @@
         <v>159</v>
       </c>
       <c r="C161" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="E161" s="13" t="s">
         <v>678</v>
       </c>
-      <c r="D161" s="12" t="s">
-        <v>680</v>
-      </c>
-      <c r="E161" s="13" t="s">
-        <v>681</v>
-      </c>
       <c r="F161" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I161" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J161" s="12">
         <v>1</v>
@@ -10313,7 +10295,7 @@
         <v>3</v>
       </c>
       <c r="L161" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M161" s="18">
         <v>0.43</v>
@@ -10330,25 +10312,25 @@
         <v>160</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="I162" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J162" s="12">
         <v>1</v>
@@ -10357,7 +10339,7 @@
         <v>3</v>
       </c>
       <c r="L162" s="19" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="M162" s="18">
         <v>9.8699999999999992</v>
@@ -10374,25 +10356,25 @@
         <v>161</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D163" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="E163" s="13" t="s">
+        <v>685</v>
+      </c>
+      <c r="F163" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G163" s="13" t="s">
+        <v>686</v>
+      </c>
+      <c r="H163" s="12" t="s">
         <v>687</v>
       </c>
-      <c r="E163" s="13" t="s">
-        <v>688</v>
-      </c>
-      <c r="F163" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="G163" s="13" t="s">
-        <v>689</v>
-      </c>
-      <c r="H163" s="12" t="s">
-        <v>690</v>
-      </c>
       <c r="I163" s="13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J163" s="12">
         <v>1</v>
@@ -10401,7 +10383,7 @@
         <v>3</v>
       </c>
       <c r="L163" s="19" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="M163" s="18">
         <v>99</v>
@@ -10418,26 +10400,26 @@
         <v>162</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F164" s="15"/>
       <c r="G164" s="13" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="12"/>
       <c r="K164" s="12"/>
       <c r="L164" s="17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="M164" s="18"/>
       <c r="N164" s="18"/>
@@ -10449,26 +10431,26 @@
         <v>163</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="F165" s="15"/>
       <c r="G165" s="13" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I165" s="13"/>
       <c r="J165" s="12"/>
       <c r="K165" s="12"/>
       <c r="L165" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="M165" s="18"/>
       <c r="N165" s="18"/>
@@ -10480,26 +10462,26 @@
         <v>164</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F166" s="15"/>
       <c r="G166" s="13" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="I166" s="13"/>
       <c r="J166" s="12"/>
       <c r="K166" s="12"/>
       <c r="L166" s="17" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="M166" s="41"/>
       <c r="N166" s="41"/>
@@ -10510,20 +10492,20 @@
     </row>
     <row r="167" spans="2:19">
       <c r="M167" s="42" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="N167" s="43">
         <f>SUM(N3:N166)</f>
-        <v>779.40039000000013</v>
+        <v>779.88039000000015</v>
       </c>
     </row>
     <row r="168" spans="2:19" ht="15.75" thickBot="1">
       <c r="M168" s="44" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="N168" s="45">
         <f>N167/3</f>
-        <v>259.80013000000002</v>
+        <v>259.96013000000005</v>
       </c>
     </row>
   </sheetData>
@@ -10531,167 +10513,167 @@
     <mergeCell ref="I1:O1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1"/>
-    <hyperlink ref="L4" r:id="rId2"/>
-    <hyperlink ref="L5" r:id="rId3"/>
-    <hyperlink ref="L6" r:id="rId4"/>
-    <hyperlink ref="L7" r:id="rId5"/>
-    <hyperlink ref="L8" r:id="rId6"/>
-    <hyperlink ref="L9" r:id="rId7"/>
-    <hyperlink ref="L10" r:id="rId8"/>
-    <hyperlink ref="L11" r:id="rId9"/>
-    <hyperlink ref="L12" r:id="rId10"/>
-    <hyperlink ref="L13" r:id="rId11"/>
-    <hyperlink ref="L14" r:id="rId12"/>
-    <hyperlink ref="L15" r:id="rId13"/>
-    <hyperlink ref="L16" r:id="rId14"/>
-    <hyperlink ref="L17" r:id="rId15"/>
-    <hyperlink ref="L18" r:id="rId16"/>
-    <hyperlink ref="L19" r:id="rId17"/>
-    <hyperlink ref="L20" r:id="rId18"/>
-    <hyperlink ref="L21" r:id="rId19"/>
-    <hyperlink ref="L22" r:id="rId20"/>
-    <hyperlink ref="L23" r:id="rId21"/>
-    <hyperlink ref="L24" r:id="rId22"/>
-    <hyperlink ref="L26" r:id="rId23"/>
-    <hyperlink ref="L27" r:id="rId24"/>
-    <hyperlink ref="L28" r:id="rId25"/>
-    <hyperlink ref="L29" r:id="rId26"/>
-    <hyperlink ref="L30" r:id="rId27"/>
-    <hyperlink ref="L31" r:id="rId28"/>
-    <hyperlink ref="L32" r:id="rId29"/>
-    <hyperlink ref="L33" r:id="rId30"/>
-    <hyperlink ref="L36" r:id="rId31"/>
-    <hyperlink ref="L37" r:id="rId32"/>
-    <hyperlink ref="L38" r:id="rId33"/>
-    <hyperlink ref="L42" r:id="rId34"/>
-    <hyperlink ref="L43" r:id="rId35"/>
-    <hyperlink ref="L45" r:id="rId36"/>
-    <hyperlink ref="L46" r:id="rId37"/>
-    <hyperlink ref="L47" r:id="rId38"/>
-    <hyperlink ref="L50" r:id="rId39"/>
-    <hyperlink ref="L60" r:id="rId40"/>
-    <hyperlink ref="L61" r:id="rId41"/>
-    <hyperlink ref="L67" r:id="rId42"/>
-    <hyperlink ref="L70" r:id="rId43"/>
-    <hyperlink ref="L72" r:id="rId44"/>
-    <hyperlink ref="L73" r:id="rId45"/>
-    <hyperlink ref="L78" r:id="rId46"/>
-    <hyperlink ref="L79" r:id="rId47"/>
-    <hyperlink ref="L80" r:id="rId48"/>
-    <hyperlink ref="L82" r:id="rId49"/>
-    <hyperlink ref="L84" r:id="rId50"/>
-    <hyperlink ref="L86" r:id="rId51"/>
-    <hyperlink ref="L25" r:id="rId52"/>
-    <hyperlink ref="L34" r:id="rId53"/>
-    <hyperlink ref="L35" r:id="rId54"/>
-    <hyperlink ref="L39" r:id="rId55"/>
-    <hyperlink ref="L40" r:id="rId56"/>
-    <hyperlink ref="L41" r:id="rId57"/>
-    <hyperlink ref="L44" r:id="rId58"/>
-    <hyperlink ref="L48" r:id="rId59"/>
-    <hyperlink ref="L49" r:id="rId60"/>
-    <hyperlink ref="L51" r:id="rId61"/>
-    <hyperlink ref="L52" r:id="rId62"/>
-    <hyperlink ref="L53" r:id="rId63"/>
-    <hyperlink ref="L54" r:id="rId64"/>
-    <hyperlink ref="L55" r:id="rId65"/>
-    <hyperlink ref="L57" r:id="rId66"/>
-    <hyperlink ref="L58" r:id="rId67"/>
-    <hyperlink ref="L59" r:id="rId68"/>
-    <hyperlink ref="L62" r:id="rId69"/>
-    <hyperlink ref="L63" r:id="rId70"/>
-    <hyperlink ref="L64" r:id="rId71"/>
-    <hyperlink ref="L65" r:id="rId72"/>
-    <hyperlink ref="L66" r:id="rId73"/>
-    <hyperlink ref="L68" r:id="rId74"/>
-    <hyperlink ref="L69" r:id="rId75"/>
-    <hyperlink ref="L74" r:id="rId76"/>
-    <hyperlink ref="L75" r:id="rId77"/>
-    <hyperlink ref="L76" r:id="rId78"/>
-    <hyperlink ref="L77" r:id="rId79"/>
-    <hyperlink ref="L81" r:id="rId80"/>
-    <hyperlink ref="L83" r:id="rId81"/>
-    <hyperlink ref="L85" r:id="rId82"/>
-    <hyperlink ref="L88" r:id="rId83"/>
-    <hyperlink ref="L87" r:id="rId84"/>
-    <hyperlink ref="L89" r:id="rId85"/>
-    <hyperlink ref="L90" r:id="rId86"/>
-    <hyperlink ref="L91" r:id="rId87"/>
-    <hyperlink ref="L92" r:id="rId88"/>
-    <hyperlink ref="L93" r:id="rId89"/>
-    <hyperlink ref="L95" r:id="rId90"/>
-    <hyperlink ref="L96" r:id="rId91"/>
-    <hyperlink ref="L97" r:id="rId92"/>
-    <hyperlink ref="L98" r:id="rId93"/>
-    <hyperlink ref="L99" r:id="rId94"/>
-    <hyperlink ref="L100" r:id="rId95"/>
-    <hyperlink ref="L101" r:id="rId96"/>
-    <hyperlink ref="L102" r:id="rId97"/>
-    <hyperlink ref="L103" r:id="rId98"/>
-    <hyperlink ref="L104" r:id="rId99"/>
-    <hyperlink ref="L105" r:id="rId100"/>
-    <hyperlink ref="L106" r:id="rId101"/>
-    <hyperlink ref="L108" r:id="rId102"/>
-    <hyperlink ref="L109" r:id="rId103"/>
-    <hyperlink ref="L111" r:id="rId104"/>
-    <hyperlink ref="L112" r:id="rId105"/>
-    <hyperlink ref="L113" r:id="rId106"/>
-    <hyperlink ref="L114" r:id="rId107"/>
-    <hyperlink ref="L115" r:id="rId108"/>
-    <hyperlink ref="L116" r:id="rId109"/>
-    <hyperlink ref="L117" r:id="rId110"/>
-    <hyperlink ref="L118" r:id="rId111"/>
-    <hyperlink ref="L119" r:id="rId112"/>
-    <hyperlink ref="L120" r:id="rId113"/>
-    <hyperlink ref="L122" r:id="rId114"/>
-    <hyperlink ref="L123" r:id="rId115"/>
-    <hyperlink ref="L124" r:id="rId116"/>
-    <hyperlink ref="L125" r:id="rId117"/>
-    <hyperlink ref="L126" r:id="rId118"/>
-    <hyperlink ref="L127" r:id="rId119"/>
-    <hyperlink ref="L128" r:id="rId120"/>
-    <hyperlink ref="L129" r:id="rId121"/>
-    <hyperlink ref="L130" r:id="rId122"/>
-    <hyperlink ref="L131" r:id="rId123"/>
-    <hyperlink ref="L132" r:id="rId124"/>
-    <hyperlink ref="L134" r:id="rId125"/>
-    <hyperlink ref="L135" r:id="rId126"/>
-    <hyperlink ref="L136" r:id="rId127"/>
-    <hyperlink ref="L137" r:id="rId128"/>
-    <hyperlink ref="L138" r:id="rId129"/>
-    <hyperlink ref="L139" r:id="rId130"/>
-    <hyperlink ref="L140" r:id="rId131"/>
-    <hyperlink ref="L141" r:id="rId132"/>
-    <hyperlink ref="L142" r:id="rId133"/>
-    <hyperlink ref="L143" r:id="rId134"/>
-    <hyperlink ref="L144" r:id="rId135"/>
-    <hyperlink ref="L145" r:id="rId136"/>
-    <hyperlink ref="L146" r:id="rId137"/>
-    <hyperlink ref="L147" r:id="rId138"/>
-    <hyperlink ref="L148" r:id="rId139"/>
-    <hyperlink ref="L149" r:id="rId140"/>
-    <hyperlink ref="L150" r:id="rId141"/>
-    <hyperlink ref="L151" r:id="rId142"/>
-    <hyperlink ref="L152" r:id="rId143"/>
-    <hyperlink ref="L153" r:id="rId144"/>
-    <hyperlink ref="L154" r:id="rId145"/>
-    <hyperlink ref="L155" r:id="rId146"/>
-    <hyperlink ref="L156" r:id="rId147"/>
-    <hyperlink ref="L157" r:id="rId148"/>
-    <hyperlink ref="L158" r:id="rId149"/>
-    <hyperlink ref="L159" r:id="rId150"/>
-    <hyperlink ref="L165" r:id="rId151"/>
-    <hyperlink ref="L164" r:id="rId152"/>
-    <hyperlink ref="L166" r:id="rId153"/>
-    <hyperlink ref="L162" r:id="rId154"/>
-    <hyperlink ref="L161" r:id="rId155"/>
-    <hyperlink ref="L56" r:id="rId156"/>
-    <hyperlink ref="L71" r:id="rId157"/>
-    <hyperlink ref="L133" r:id="rId158"/>
-    <hyperlink ref="L160" r:id="rId159"/>
+    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="L7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="L8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="L9" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="L10" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="L11" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="L12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="L13" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="L14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="L15" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="L16" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="L17" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="L18" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="L19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="L20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="L21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="L22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="L24" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="L26" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="L27" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="L28" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="L29" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="L30" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="L31" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="L32" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="L33" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="L36" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="L37" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="L38" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="L42" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="L43" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="L45" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="L46" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="L47" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="L50" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="L60" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="L61" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="L67" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="L70" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="L72" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="L73" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="L78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="L79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="L80" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="L82" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="L84" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="L86" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="L25" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="L34" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="L35" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="L39" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="L40" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="L41" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="L44" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="L48" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="L49" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="L51" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="L52" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="L53" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="L54" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="L55" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="L57" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="L58" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="L59" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="L62" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="L63" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="L64" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="L65" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="L66" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="L68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="L69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="L74" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="L75" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="L76" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="L77" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="L81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="L83" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="L85" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="L88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="L87" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="L89" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="L90" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="L91" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="L92" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="L93" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="L95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="L96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="L97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="L98" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="L99" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="L100" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="L101" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="L102" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="L103" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="L104" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="L105" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="L106" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="L108" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="L109" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="L111" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="L112" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="L113" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="L114" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="L115" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="L116" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="L117" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="L118" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="L119" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="L120" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="L122" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="L123" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="L124" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="L125" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="L126" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="L127" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="L128" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="L129" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="L130" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="L131" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="L132" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="L134" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="L135" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="L136" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="L137" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="L138" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="L139" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="L140" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="L141" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="L142" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="L143" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="L144" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="L145" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="L146" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="L147" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="L148" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="L149" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="L150" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="L151" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="L152" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="L153" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="L154" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="L155" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="L156" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="L157" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="L158" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="L159" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="L165" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="L164" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="L166" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="L162" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="L161" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="L56" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="L71" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="L133" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="L160" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="L23" r:id="rId159" xr:uid="{FE6A792A-CBF2-4519-AA9F-3440E70CCF81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId160"/>
 </worksheet>
 </file>
--- a/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
+++ b/Design-Files/Carrier-Board-v1.0/BOM/Client BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="725">
   <si>
     <t>#</t>
   </si>
@@ -2171,6 +2171,30 @@
   </si>
   <si>
     <t>Surge Protection (TVS/ESD)</t>
+  </si>
+  <si>
+    <t>250V 10A 3 -40℃~+105℃ 1.5 1 16~28 3.5mm 1x3P Green Plug P=3.5mm Pluggable System Terminal Block ROHS</t>
+  </si>
+  <si>
+    <t>DB2EK-3.5-3P-GN-S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORABO </t>
+  </si>
+  <si>
+    <t>Network cables ROHS</t>
+  </si>
+  <si>
+    <t>S108510003</t>
+  </si>
+  <si>
+    <t>Ckmtw</t>
+  </si>
+  <si>
+    <t>S108510001</t>
+  </si>
+  <si>
+    <t>S108510002</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2520,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -2623,6 +2647,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2907,7 +2934,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V170"/>
+  <dimension ref="A1:V174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.5703125" style="4" customWidth="1"/>
@@ -8444,7 +8471,7 @@
         <v>0.1</v>
       </c>
       <c r="N120" s="18">
-        <f t="shared" ref="N120:N159" si="11">M120*K120</f>
+        <f t="shared" ref="N120:N163" si="11">M120*K120</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="O120" s="15"/>
@@ -8947,7 +8974,7 @@
         <v>6</v>
       </c>
       <c r="K131" s="12">
-        <f t="shared" ref="K131:K160" si="12">3*J131</f>
+        <f t="shared" ref="K131:K164" si="12">3*J131</f>
         <v>18</v>
       </c>
       <c r="L131" s="19" t="s">
@@ -10250,118 +10277,121 @@
       </c>
       <c r="O159" s="12"/>
     </row>
-    <row r="160" spans="1:15" ht="24.75" thickBot="1">
+    <row r="160" spans="1:15" ht="15.75" thickBot="1">
       <c r="A160" s="5"/>
       <c r="B160" s="10">
-        <f t="shared" ref="B160:B167" si="13">ROW(B160)-ROW($B$2)</f>
+        <f t="shared" ref="B160:B162" si="13">ROW(B160)-ROW($B$2)</f>
         <v>158</v>
       </c>
-      <c r="C160" s="11" t="s">
+      <c r="C160" s="47" t="s">
         <v>661</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>662</v>
+        <v>144</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>694</v>
+        <v>720</v>
       </c>
       <c r="F160" s="15" t="s">
         <v>107</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>695</v>
+        <v>721</v>
       </c>
       <c r="H160" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="I160" s="13"/>
+        <v>722</v>
+      </c>
+      <c r="I160" s="13" t="s">
+        <v>144</v>
+      </c>
       <c r="J160" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K160" s="12">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L160" s="19" t="s">
         <v>110</v>
       </c>
       <c r="M160" s="18">
-        <v>1.0093000000000001</v>
+        <v>0.1767</v>
       </c>
       <c r="N160" s="18">
-        <f>M160*K160</f>
-        <v>3.0279000000000003</v>
+        <f t="shared" si="11"/>
+        <v>1.0602</v>
       </c>
       <c r="O160" s="12"/>
     </row>
-    <row r="161" spans="1:22" ht="36.75" thickBot="1">
+    <row r="161" spans="1:22" ht="15.75" thickBot="1">
       <c r="A161" s="5"/>
       <c r="B161" s="10">
         <f t="shared" si="13"/>
         <v>159</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="47" t="s">
         <v>661</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>663</v>
+        <v>144</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>664</v>
+        <v>720</v>
       </c>
       <c r="F161" s="15" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>665</v>
+        <v>723</v>
       </c>
       <c r="H161" s="12" t="s">
-        <v>242</v>
+        <v>722</v>
       </c>
       <c r="I161" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J161" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K161" s="12">
-        <v>3</v>
-      </c>
-      <c r="L161" s="17" t="s">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="L161" s="19" t="s">
         <v>110</v>
       </c>
       <c r="M161" s="18">
-        <v>0.43</v>
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="N161" s="18">
-        <f>M161*K161</f>
-        <v>1.29</v>
+        <f t="shared" si="11"/>
+        <v>0.82350000000000001</v>
       </c>
       <c r="O161" s="12"/>
     </row>
-    <row r="162" spans="1:22" ht="30.75" thickBot="1">
+    <row r="162" spans="1:22" ht="15.75" thickBot="1">
       <c r="A162" s="5"/>
       <c r="B162" s="10">
         <f t="shared" si="13"/>
         <v>160</v>
       </c>
-      <c r="C162" s="11" t="s">
+      <c r="C162" s="47" t="s">
         <v>661</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>666</v>
+        <v>144</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>667</v>
+        <v>720</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>144</v>
+        <v>724</v>
       </c>
       <c r="H162" s="12" t="s">
-        <v>668</v>
+        <v>722</v>
       </c>
       <c r="I162" s="13" t="s">
         <v>144</v>
@@ -10370,252 +10400,433 @@
         <v>1</v>
       </c>
       <c r="K162" s="12">
+        <f t="shared" si="12"/>
         <v>3</v>
       </c>
       <c r="L162" s="19" t="s">
-        <v>669</v>
+        <v>110</v>
       </c>
       <c r="M162" s="18">
-        <v>9.8699999999999992</v>
+        <v>0.1381</v>
       </c>
       <c r="N162" s="18">
-        <f>M162*K162</f>
-        <v>29.61</v>
+        <f t="shared" si="11"/>
+        <v>0.4143</v>
       </c>
       <c r="O162" s="12"/>
     </row>
-    <row r="163" spans="1:22" ht="15.75" thickBot="1">
+    <row r="163" spans="1:22" ht="48.75" thickBot="1">
+      <c r="A163" s="5"/>
       <c r="B163" s="10">
-        <f t="shared" si="13"/>
+        <f>ROW(B163)-ROW($B$2)</f>
         <v>161</v>
       </c>
-      <c r="C163" s="11" t="s">
+      <c r="C163" s="47" t="s">
         <v>661</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>670</v>
+        <v>144</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="F163" s="15" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
       <c r="H163" s="12" t="s">
-        <v>673</v>
+        <v>719</v>
       </c>
       <c r="I163" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J163" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K163" s="12">
-        <v>3</v>
+        <f t="shared" si="12"/>
+        <v>15</v>
       </c>
       <c r="L163" s="19" t="s">
-        <v>674</v>
+        <v>110</v>
       </c>
       <c r="M163" s="18">
-        <v>99</v>
+        <v>0.28139999999999998</v>
       </c>
       <c r="N163" s="18">
-        <f>M163*K163</f>
-        <v>297</v>
+        <f t="shared" si="11"/>
+        <v>4.2210000000000001</v>
       </c>
       <c r="O163" s="12"/>
     </row>
     <row r="164" spans="1:22" ht="24.75" thickBot="1">
+      <c r="A164" s="5"/>
       <c r="B164" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="B164:B171" si="14">ROW(B164)-ROW($B$2)</f>
         <v>162</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>661</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>144</v>
+        <v>662</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="F164" s="15"/>
+        <v>694</v>
+      </c>
+      <c r="F164" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="G164" s="13" t="s">
-        <v>676</v>
+        <v>695</v>
       </c>
       <c r="H164" s="12" t="s">
-        <v>677</v>
+        <v>242</v>
       </c>
       <c r="I164" s="13"/>
-      <c r="J164" s="12"/>
-      <c r="K164" s="12"/>
-      <c r="L164" s="17" t="s">
-        <v>677</v>
-      </c>
-      <c r="M164" s="18"/>
+      <c r="J164" s="12">
+        <v>1</v>
+      </c>
+      <c r="K164" s="12">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="L164" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="M164" s="18">
+        <v>1.0093000000000001</v>
+      </c>
       <c r="N164" s="18">
-        <f t="shared" ref="N164:N167" si="14">M164*K164</f>
-        <v>0</v>
+        <f>M164*K164</f>
+        <v>3.0279000000000003</v>
       </c>
       <c r="O164" s="12"/>
     </row>
-    <row r="165" spans="1:22" ht="24.75" thickBot="1">
+    <row r="165" spans="1:22" ht="36.75" thickBot="1">
+      <c r="A165" s="5"/>
       <c r="B165" s="10">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>163</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>661</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>144</v>
+        <v>663</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="F165" s="15"/>
+        <v>664</v>
+      </c>
+      <c r="F165" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="G165" s="13" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="H165" s="12" t="s">
-        <v>680</v>
-      </c>
-      <c r="I165" s="13"/>
-      <c r="J165" s="12"/>
-      <c r="K165" s="12"/>
+        <v>242</v>
+      </c>
+      <c r="I165" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J165" s="12">
+        <v>1</v>
+      </c>
+      <c r="K165" s="12">
+        <v>3</v>
+      </c>
       <c r="L165" s="17" t="s">
-        <v>680</v>
-      </c>
-      <c r="M165" s="18"/>
+        <v>110</v>
+      </c>
+      <c r="M165" s="18">
+        <v>0.43</v>
+      </c>
       <c r="N165" s="18">
+        <f>M165*K165</f>
+        <v>1.29</v>
+      </c>
+      <c r="O165" s="12"/>
+    </row>
+    <row r="166" spans="1:22" ht="30.75" thickBot="1">
+      <c r="A166" s="5"/>
+      <c r="B166" s="10">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="O165" s="12"/>
-    </row>
-    <row r="166" spans="1:22" ht="48.75" thickBot="1">
-      <c r="B166" s="10">
-        <f t="shared" si="13"/>
         <v>164</v>
       </c>
       <c r="C166" s="11" t="s">
         <v>661</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>144</v>
+        <v>666</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>698</v>
+        <v>667</v>
       </c>
       <c r="F166" s="15" t="s">
         <v>144</v>
       </c>
       <c r="G166" s="13" t="s">
-        <v>699</v>
+        <v>144</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>144</v>
+        <v>668</v>
       </c>
       <c r="I166" s="13" t="s">
         <v>144</v>
       </c>
       <c r="J166" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K166" s="12">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="L166" s="19" t="s">
         <v>669</v>
       </c>
-      <c r="M166" s="40">
-        <v>2.3199999999999998</v>
+      <c r="M166" s="18">
+        <v>9.8699999999999992</v>
       </c>
       <c r="N166" s="18">
+        <f>M166*K166</f>
+        <v>29.61</v>
+      </c>
+      <c r="O166" s="12"/>
+    </row>
+    <row r="167" spans="1:22" ht="15.75" thickBot="1">
+      <c r="B167" s="10">
         <f t="shared" si="14"/>
-        <v>231.99999999999997</v>
-      </c>
-      <c r="O166" s="12"/>
-      <c r="T166" s="3"/>
-      <c r="U166" s="3"/>
-      <c r="V166" s="3"/>
-    </row>
-    <row r="167" spans="1:22" ht="24.75" thickBot="1">
-      <c r="B167" s="10">
-        <f t="shared" si="13"/>
         <v>165</v>
       </c>
       <c r="C167" s="11" t="s">
         <v>661</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>144</v>
+        <v>670</v>
       </c>
       <c r="E167" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="F167" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G167" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="I167" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J167" s="12">
+        <v>1</v>
+      </c>
+      <c r="K167" s="12">
+        <v>3</v>
+      </c>
+      <c r="L167" s="19" t="s">
+        <v>674</v>
+      </c>
+      <c r="M167" s="18">
+        <v>99</v>
+      </c>
+      <c r="N167" s="18">
+        <f>M167*K167</f>
+        <v>297</v>
+      </c>
+      <c r="O167" s="12"/>
+    </row>
+    <row r="168" spans="1:22" ht="24.75" thickBot="1">
+      <c r="B168" s="10">
+        <f t="shared" si="14"/>
+        <v>166</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E168" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="F168" s="15"/>
+      <c r="G168" s="13" t="s">
+        <v>676</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="I168" s="13"/>
+      <c r="J168" s="12"/>
+      <c r="K168" s="12"/>
+      <c r="L168" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="M168" s="18"/>
+      <c r="N168" s="18">
+        <f t="shared" ref="N168:N171" si="15">M168*K168</f>
+        <v>0</v>
+      </c>
+      <c r="O168" s="12"/>
+    </row>
+    <row r="169" spans="1:22" ht="24.75" thickBot="1">
+      <c r="B169" s="10">
+        <f t="shared" si="14"/>
+        <v>167</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E169" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="F169" s="15"/>
+      <c r="G169" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="I169" s="13"/>
+      <c r="J169" s="12"/>
+      <c r="K169" s="12"/>
+      <c r="L169" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="M169" s="18"/>
+      <c r="N169" s="18">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O169" s="12"/>
+    </row>
+    <row r="170" spans="1:22" ht="48.75" thickBot="1">
+      <c r="B170" s="10">
+        <f t="shared" si="14"/>
+        <v>168</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E170" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="F170" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G170" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="I170" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J170" s="12">
+        <v>4</v>
+      </c>
+      <c r="K170" s="12">
+        <v>100</v>
+      </c>
+      <c r="L170" s="19" t="s">
+        <v>669</v>
+      </c>
+      <c r="M170" s="40">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="N170" s="18">
+        <f t="shared" si="15"/>
+        <v>231.99999999999997</v>
+      </c>
+      <c r="O170" s="12"/>
+      <c r="T170" s="3"/>
+      <c r="U170" s="3"/>
+      <c r="V170" s="3"/>
+    </row>
+    <row r="171" spans="1:22" ht="24.75" thickBot="1">
+      <c r="B171" s="10">
+        <f t="shared" si="14"/>
+        <v>169</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E171" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="F167" s="15"/>
-      <c r="G167" s="13" t="s">
+      <c r="F171" s="15"/>
+      <c r="G171" s="13" t="s">
         <v>682</v>
       </c>
-      <c r="H167" s="12" t="s">
+      <c r="H171" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="I167" s="13"/>
-      <c r="J167" s="12"/>
-      <c r="K167" s="12"/>
-      <c r="L167" s="17" t="s">
+      <c r="I171" s="13"/>
+      <c r="J171" s="12"/>
+      <c r="K171" s="12"/>
+      <c r="L171" s="17" t="s">
         <v>684</v>
       </c>
-      <c r="M167" s="40"/>
-      <c r="N167" s="18">
-        <f t="shared" si="14"/>
+      <c r="M171" s="40"/>
+      <c r="N171" s="18">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="O167" s="12"/>
-    </row>
-    <row r="168" spans="1:22">
-      <c r="M168" s="41" t="s">
+      <c r="O171" s="12"/>
+    </row>
+    <row r="172" spans="1:22">
+      <c r="M172" s="41" t="s">
         <v>685</v>
       </c>
-      <c r="N168" s="42">
-        <f>SUM(N3:N167)</f>
-        <v>1037.1835900000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:22" ht="15.75" thickBot="1">
-      <c r="M169" s="43" t="s">
+      <c r="N172" s="42">
+        <f>SUM(N3:N171)</f>
+        <v>1043.7025900000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:22" ht="15.75" thickBot="1">
+      <c r="M173" s="43" t="s">
         <v>686</v>
       </c>
-      <c r="N169" s="44">
-        <f>N168/3</f>
-        <v>345.72786333333335</v>
-      </c>
-    </row>
-    <row r="170" spans="1:22" s="3" customFormat="1">
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170"/>
-      <c r="E170"/>
-      <c r="F170"/>
-      <c r="G170"/>
-      <c r="H170"/>
-      <c r="I170"/>
-      <c r="J170"/>
-      <c r="K170"/>
-      <c r="L170"/>
-      <c r="M170"/>
-      <c r="N170"/>
-      <c r="O170"/>
-      <c r="Q170"/>
-      <c r="R170"/>
-      <c r="S170"/>
-      <c r="T170"/>
-      <c r="U170"/>
-      <c r="V170"/>
+      <c r="N173" s="44">
+        <f>N172/3</f>
+        <v>347.90086333333335</v>
+      </c>
+    </row>
+    <row r="174" spans="1:22" s="3" customFormat="1">
+      <c r="B174" s="4"/>
+      <c r="C174" s="4"/>
+      <c r="D174"/>
+      <c r="E174"/>
+      <c r="F174"/>
+      <c r="G174"/>
+      <c r="H174"/>
+      <c r="I174"/>
+      <c r="J174"/>
+      <c r="K174"/>
+      <c r="L174"/>
+      <c r="M174"/>
+      <c r="N174"/>
+      <c r="O174"/>
+      <c r="Q174"/>
+      <c r="R174"/>
+      <c r="S174"/>
+      <c r="T174"/>
+      <c r="U174"/>
+      <c r="V174"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10766,23 +10977,27 @@
     <hyperlink ref="L157" r:id="rId142"/>
     <hyperlink ref="L158" r:id="rId143"/>
     <hyperlink ref="L159" r:id="rId144"/>
-    <hyperlink ref="L165" r:id="rId145"/>
-    <hyperlink ref="L164" r:id="rId146"/>
-    <hyperlink ref="L167" r:id="rId147"/>
-    <hyperlink ref="L162" r:id="rId148"/>
-    <hyperlink ref="L161" r:id="rId149"/>
+    <hyperlink ref="L169" r:id="rId145"/>
+    <hyperlink ref="L168" r:id="rId146"/>
+    <hyperlink ref="L171" r:id="rId147"/>
+    <hyperlink ref="L166" r:id="rId148"/>
+    <hyperlink ref="L165" r:id="rId149"/>
     <hyperlink ref="L56" r:id="rId150"/>
     <hyperlink ref="L71" r:id="rId151"/>
     <hyperlink ref="L133" r:id="rId152"/>
-    <hyperlink ref="L160" r:id="rId153"/>
+    <hyperlink ref="L164" r:id="rId153"/>
     <hyperlink ref="L23" r:id="rId154"/>
-    <hyperlink ref="L166" r:id="rId155"/>
+    <hyperlink ref="L170" r:id="rId155"/>
     <hyperlink ref="L33" r:id="rId156"/>
     <hyperlink ref="L51" r:id="rId157"/>
     <hyperlink ref="L85" r:id="rId158"/>
     <hyperlink ref="L132" r:id="rId159"/>
+    <hyperlink ref="L163" r:id="rId160"/>
+    <hyperlink ref="L160" r:id="rId161"/>
+    <hyperlink ref="L161" r:id="rId162"/>
+    <hyperlink ref="L162" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId160"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId164"/>
 </worksheet>
 </file>